--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>226185</v>
+        <v>285434</v>
       </c>
       <c r="E2" t="n">
-        <v>48873</v>
+        <v>1653</v>
       </c>
       <c r="F2" t="n">
-        <v>177311</v>
+        <v>283781</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>76972</v>
+        <v>134123</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+193.9%</t>
+          <t>+112.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>33265</v>
+        <v>-1947</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+433.0%</t>
+          <t>-14671.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2374</v>
+        <v>1981</v>
       </c>
       <c r="E3" t="n">
-        <v>17617</v>
+        <v>1357</v>
       </c>
       <c r="F3" t="n">
-        <v>-15243</v>
+        <v>624</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14372</v>
+        <v>15606</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-83.5%</t>
+          <t>-87.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-10409</v>
+        <v>-9417</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+46.4%</t>
+          <t>-106.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>283989</v>
+        <v>299447</v>
       </c>
       <c r="E4" t="n">
-        <v>85383</v>
+        <v>8006</v>
       </c>
       <c r="F4" t="n">
-        <v>198606</v>
+        <v>291441</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>193192</v>
+        <v>246432</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+47.0%</t>
+          <t>+21.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>111956</v>
+        <v>135996</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+77.4%</t>
+          <t>+114.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>88050</v>
+        <v>132197</v>
       </c>
       <c r="E5" t="n">
-        <v>123069</v>
+        <v>162</v>
       </c>
       <c r="F5" t="n">
-        <v>-35019</v>
+        <v>132035</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23329</v>
+        <v>236399</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>+277.4%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>-45829</v>
+        <v>167164</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-21.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>282837</v>
+        <v>359335</v>
       </c>
       <c r="E6" t="n">
-        <v>31751</v>
+        <v>6442</v>
       </c>
       <c r="F6" t="n">
-        <v>251085</v>
+        <v>352892</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>135037</v>
+        <v>180311</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+109.5%</t>
+          <t>+99.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>94039</v>
+        <v>133617</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+167.0%</t>
+          <t>+164.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>204887</v>
+        <v>231947</v>
       </c>
       <c r="E7" t="n">
-        <v>31890</v>
+        <v>31441</v>
       </c>
       <c r="F7" t="n">
-        <v>172997</v>
+        <v>200506</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>141875</v>
+        <v>187591</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+44.4%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>104515</v>
+        <v>149146</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+65.5%</t>
+          <t>+34.4%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>194751</v>
+        <v>206042</v>
       </c>
       <c r="E8" t="n">
-        <v>71584</v>
+        <v>2687</v>
       </c>
       <c r="F8" t="n">
-        <v>123167</v>
+        <v>203355</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>169379</v>
+        <v>189162</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>+8.9%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>154372</v>
+        <v>163218</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>+24.6%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>467449</v>
+        <v>534687</v>
       </c>
       <c r="E9" t="n">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>328449</v>
+        <v>534687</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>315641</v>
+        <v>411931</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+48.1%</t>
+          <t>+29.8%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>262067</v>
+        <v>328557</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+25.3%</t>
+          <t>+62.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>559150</v>
+        <v>906375</v>
       </c>
       <c r="E10" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F10" t="n">
-        <v>558851</v>
+        <v>906067</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>571948</v>
+        <v>753225</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>+20.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>571948</v>
+        <v>753225</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>+20.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>220995</v>
+        <v>340223</v>
       </c>
       <c r="P10" t="n">
-        <v>337856</v>
+        <v>565844</v>
       </c>
       <c r="Q10" t="n">
-        <v>508453</v>
+        <v>844475</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>143231</v>
+        <v>143638</v>
       </c>
       <c r="E11" t="n">
-        <v>26399</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>116831</v>
+        <v>143638</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>40294</v>
+        <v>128403</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+255.5%</t>
+          <t>+11.9%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40285</v>
+        <v>103594</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+190.0%</t>
+          <t>+38.7%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>18445</v>
+        <v>28854</v>
       </c>
       <c r="P11" t="n">
-        <v>98176</v>
+        <v>114574</v>
       </c>
       <c r="Q11" t="n">
-        <v>75651</v>
+        <v>75660</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>201094</v>
+        <v>281083</v>
       </c>
       <c r="E12" t="n">
-        <v>10028</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>191066</v>
+        <v>281026</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>126918</v>
+        <v>149314</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+58.4%</t>
+          <t>+88.2%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>126619</v>
+        <v>147335</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+50.9%</t>
+          <t>+90.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>52699</v>
+        <v>53163</v>
       </c>
       <c r="P12" t="n">
-        <v>138367</v>
+        <v>227863</v>
       </c>
       <c r="Q12" t="n">
-        <v>4868</v>
+        <v>19814</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>211257</v>
+        <v>309747</v>
       </c>
       <c r="E13" t="n">
-        <v>25908</v>
+        <v>394</v>
       </c>
       <c r="F13" t="n">
-        <v>185348</v>
+        <v>309353</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>184643</v>
+        <v>250625</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+14.4%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>158862</v>
+        <v>191064</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+16.7%</t>
+          <t>+61.9%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>6816</v>
       </c>
       <c r="O13" t="n">
-        <v>17307</v>
+        <v>13947</v>
       </c>
       <c r="P13" t="n">
-        <v>161225</v>
+        <v>288590</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3429</v>
+        <v>33879</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>123464</v>
+        <v>147271</v>
       </c>
       <c r="E14" t="n">
-        <v>14866</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>108598</v>
+        <v>147204</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>97656</v>
+        <v>119413</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+26.4%</t>
+          <t>+23.3%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>80490</v>
+        <v>101835</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+34.9%</t>
+          <t>+44.6%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>7276</v>
+        <v>9842</v>
       </c>
       <c r="O14" t="n">
-        <v>49420</v>
+        <v>54766</v>
       </c>
       <c r="P14" t="n">
-        <v>51902</v>
+        <v>82596</v>
       </c>
       <c r="Q14" t="n">
-        <v>17020</v>
+        <v>19932</v>
       </c>
     </row>
     <row r="15">
@@ -1291,50 +1291,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>77070</v>
+        <v>98100</v>
       </c>
       <c r="E15" t="n">
-        <v>15857</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>61213</v>
+        <v>98062</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>110788</v>
+        <v>128497</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>95511</v>
+        <v>113191</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>442</v>
+        <v>6735</v>
       </c>
       <c r="P15" t="n">
-        <v>60771</v>
+        <v>91327</v>
       </c>
       <c r="Q15" t="n">
-        <v>27421</v>
+        <v>36480</v>
       </c>
     </row>
     <row r="16">
@@ -1352,50 +1352,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>107075</v>
+        <v>197885</v>
       </c>
       <c r="E16" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>106677</v>
+        <v>197885</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>52693</v>
+        <v>76687</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+103.2%</t>
+          <t>+158.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>52693</v>
+        <v>66487</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+102.5%</t>
+          <t>+197.6%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12495</v>
+        <v>16715</v>
       </c>
       <c r="P16" t="n">
-        <v>94182</v>
+        <v>181170</v>
       </c>
       <c r="Q16" t="n">
-        <v>39693</v>
+        <v>41011</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>192525</v>
+        <v>229924</v>
       </c>
       <c r="E17" t="n">
-        <v>46658</v>
+        <v>229</v>
       </c>
       <c r="F17" t="n">
-        <v>145867</v>
+        <v>229695</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>166248</v>
+        <v>206992</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+15.8%</t>
+          <t>+11.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>159549</v>
+        <v>181126</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>18732</v>
+        <v>19928</v>
       </c>
       <c r="O17" t="n">
-        <v>2053</v>
+        <v>3295</v>
       </c>
       <c r="P17" t="n">
-        <v>125082</v>
+        <v>206472</v>
       </c>
       <c r="Q17" t="n">
-        <v>-16808</v>
+        <v>20835</v>
       </c>
     </row>
     <row r="18">
@@ -1476,50 +1476,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>285737</v>
+        <v>632424</v>
       </c>
       <c r="E18" t="n">
-        <v>19666</v>
+        <v>47</v>
       </c>
       <c r="F18" t="n">
-        <v>266071</v>
+        <v>632377</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>222982</v>
+        <v>333091</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+28.1%</t>
+          <t>+89.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>208926</v>
+        <v>297535</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+27.4%</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>+112.5%</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>850</v>
+      </c>
       <c r="O18" t="n">
-        <v>99340</v>
+        <v>188736</v>
       </c>
       <c r="P18" t="n">
-        <v>166731</v>
+        <v>442791</v>
       </c>
       <c r="Q18" t="n">
-        <v>148479</v>
+        <v>393977</v>
       </c>
     </row>
     <row r="19">
@@ -1537,52 +1539,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>113893</v>
+        <v>161943</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>113884</v>
+        <v>161928</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>123537</v>
+        <v>131454</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>+23.2%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-22460</v>
+        <v>-14543</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-607.0%</t>
+          <t>-1213.4%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3616</v>
+        <v>7220</v>
       </c>
       <c r="O19" t="n">
-        <v>10376</v>
+        <v>28516</v>
       </c>
       <c r="P19" t="n">
-        <v>100092</v>
+        <v>126392</v>
       </c>
       <c r="Q19" t="n">
-        <v>20298</v>
+        <v>24252</v>
       </c>
     </row>
     <row r="20">
@@ -1600,50 +1602,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>228790</v>
+        <v>250143</v>
       </c>
       <c r="E20" t="n">
-        <v>40737</v>
+        <v>351</v>
       </c>
       <c r="F20" t="n">
-        <v>188053</v>
+        <v>249792</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>204364</v>
+        <v>254036</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+12.0%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>195564</v>
+        <v>240236</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>+4.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>82993</v>
+        <v>91262</v>
       </c>
       <c r="P20" t="n">
-        <v>105060</v>
+        <v>158530</v>
       </c>
       <c r="Q20" t="n">
-        <v>31967</v>
+        <v>46016</v>
       </c>
     </row>
     <row r="21">
@@ -1661,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>4008733</v>
+        <v>5424529</v>
       </c>
       <c r="E21" t="n">
-        <v>763106</v>
+        <v>53254</v>
       </c>
       <c r="F21" t="n">
-        <v>3245626</v>
+        <v>5371274</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2971872</v>
+        <v>4133298</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+34.9%</t>
+          <t>+31.2%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2371966</v>
+        <v>3247422</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+36.8%</t>
+          <t>+65.4%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>36651</v>
+        <v>44867</v>
       </c>
       <c r="O21" t="n">
-        <v>1649374</v>
+        <v>2656762</v>
       </c>
       <c r="P21" t="n">
-        <v>1559800</v>
+        <v>2669843</v>
       </c>
       <c r="Q21" t="n">
-        <v>1761725</v>
+        <v>3085452</v>
       </c>
     </row>
   </sheetData>
@@ -1759,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>240</v>
+        <v>404</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>931.1</v>
+        <v>402.5</v>
       </c>
       <c r="E2" t="n">
-        <v>128358</v>
+        <v>60710</v>
       </c>
     </row>
     <row r="3">
@@ -1778,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>327.6</v>
+        <v>30.1</v>
       </c>
       <c r="E3" t="n">
-        <v>520</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -1797,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="C4" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="D4" t="n">
-        <v>1589.5</v>
+        <v>1162.6</v>
       </c>
       <c r="E4" t="n">
-        <v>7598</v>
+        <v>3500</v>
       </c>
     </row>
   </sheetData>
@@ -1862,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>872029</v>
+        <v>1404622</v>
       </c>
       <c r="D2" t="n">
-        <v>875</v>
+        <v>60013</v>
       </c>
       <c r="E2" t="n">
-        <v>724909</v>
+        <v>1196426</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>222169</v>
+        <v>424207</v>
       </c>
       <c r="D3" t="n">
-        <v>106280</v>
+        <v>110480</v>
       </c>
       <c r="E3" t="n">
-        <v>183971</v>
+        <v>330971</v>
       </c>
     </row>
     <row r="4">
@@ -1904,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>566566</v>
+        <v>826213</v>
       </c>
       <c r="D4" t="n">
-        <v>1439445</v>
+        <v>2486150</v>
       </c>
       <c r="E4" t="n">
-        <v>853614</v>
+        <v>1556334</v>
       </c>
     </row>
     <row r="5">
@@ -1925,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>176293</v>
+        <v>282744</v>
       </c>
       <c r="D5" t="n">
-        <v>1018</v>
+        <v>1037</v>
       </c>
       <c r="E5" t="n">
-        <v>167311</v>
+        <v>273781</v>
       </c>
     </row>
     <row r="6">
@@ -1946,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15378</v>
+        <v>489</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-5243</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7">
@@ -1967,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>204946</v>
+        <v>285430</v>
       </c>
       <c r="D7" t="n">
-        <v>-6340</v>
+        <v>6010</v>
       </c>
       <c r="E7" t="n">
-        <v>207718</v>
+        <v>266655</v>
       </c>
     </row>
     <row r="8">
@@ -1988,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-36407</v>
+        <v>88647</v>
       </c>
       <c r="D8" t="n">
-        <v>1388</v>
+        <v>43388</v>
       </c>
       <c r="E8" t="n">
-        <v>-35019</v>
+        <v>93215</v>
       </c>
     </row>
     <row r="9">
@@ -2009,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>247266</v>
+        <v>345985</v>
       </c>
       <c r="D9" t="n">
-        <v>3819</v>
+        <v>6907</v>
       </c>
       <c r="E9" t="n">
-        <v>196289</v>
+        <v>285100</v>
       </c>
     </row>
     <row r="10">
@@ -2030,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>143178</v>
+        <v>198807</v>
       </c>
       <c r="D10" t="n">
-        <v>29819</v>
+        <v>1699</v>
       </c>
       <c r="E10" t="n">
-        <v>81083</v>
+        <v>94092</v>
       </c>
     </row>
     <row r="11">
@@ -2051,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>152130</v>
+        <v>202518</v>
       </c>
       <c r="D11" t="n">
-        <v>-28963</v>
+        <v>837</v>
       </c>
       <c r="E11" t="n">
-        <v>112769</v>
+        <v>182957</v>
       </c>
     </row>
     <row r="12">
@@ -2072,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>222169</v>
+        <v>424207</v>
       </c>
       <c r="D12" t="n">
-        <v>106280</v>
+        <v>110480</v>
       </c>
       <c r="E12" t="n">
-        <v>183971</v>
+        <v>330971</v>
       </c>
     </row>
     <row r="13">
@@ -2093,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>220995</v>
+        <v>340223</v>
       </c>
       <c r="D13" t="n">
-        <v>337856</v>
+        <v>565844</v>
       </c>
       <c r="E13" t="n">
-        <v>508453</v>
+        <v>844475</v>
       </c>
     </row>
     <row r="14">
@@ -2114,13 +2116,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18445</v>
+        <v>28854</v>
       </c>
       <c r="D14" t="n">
-        <v>98176</v>
+        <v>114574</v>
       </c>
       <c r="E14" t="n">
-        <v>75651</v>
+        <v>75660</v>
       </c>
     </row>
     <row r="15">
@@ -2135,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>52699</v>
+        <v>53163</v>
       </c>
       <c r="D15" t="n">
-        <v>138367</v>
+        <v>227863</v>
       </c>
       <c r="E15" t="n">
-        <v>4868</v>
+        <v>19814</v>
       </c>
     </row>
     <row r="16">
@@ -2156,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17307</v>
+        <v>13947</v>
       </c>
       <c r="D16" t="n">
-        <v>161225</v>
+        <v>288590</v>
       </c>
       <c r="E16" t="n">
-        <v>-3429</v>
+        <v>33879</v>
       </c>
     </row>
     <row r="17">
@@ -2177,13 +2179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49420</v>
+        <v>54766</v>
       </c>
       <c r="D17" t="n">
-        <v>51902</v>
+        <v>82596</v>
       </c>
       <c r="E17" t="n">
-        <v>17020</v>
+        <v>19932</v>
       </c>
     </row>
     <row r="18">
@@ -2198,13 +2200,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>442</v>
+        <v>6735</v>
       </c>
       <c r="D18" t="n">
-        <v>60771</v>
+        <v>91327</v>
       </c>
       <c r="E18" t="n">
-        <v>27421</v>
+        <v>36480</v>
       </c>
     </row>
     <row r="19">
@@ -2219,13 +2221,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12495</v>
+        <v>16715</v>
       </c>
       <c r="D19" t="n">
-        <v>94182</v>
+        <v>181170</v>
       </c>
       <c r="E19" t="n">
-        <v>39693</v>
+        <v>41011</v>
       </c>
     </row>
     <row r="20">
@@ -2240,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2053</v>
+        <v>3295</v>
       </c>
       <c r="D20" t="n">
-        <v>125082</v>
+        <v>206472</v>
       </c>
       <c r="E20" t="n">
-        <v>-16808</v>
+        <v>20835</v>
       </c>
     </row>
     <row r="21">
@@ -2261,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>99340</v>
+        <v>188736</v>
       </c>
       <c r="D21" t="n">
-        <v>166731</v>
+        <v>442791</v>
       </c>
       <c r="E21" t="n">
-        <v>148479</v>
+        <v>393977</v>
       </c>
     </row>
     <row r="22">
@@ -2282,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>10376</v>
+        <v>28516</v>
       </c>
       <c r="D22" t="n">
-        <v>100092</v>
+        <v>126392</v>
       </c>
       <c r="E22" t="n">
-        <v>20298</v>
+        <v>24252</v>
       </c>
     </row>
     <row r="23">
@@ -2303,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82993</v>
+        <v>91262</v>
       </c>
       <c r="D23" t="n">
-        <v>105060</v>
+        <v>158530</v>
       </c>
       <c r="E23" t="n">
-        <v>31967</v>
+        <v>46016</v>
       </c>
     </row>
     <row r="24">
@@ -2324,13 +2326,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-11391</v>
+        <v>1720</v>
       </c>
       <c r="D24" t="n">
         <v>13200</v>
       </c>
       <c r="E24" t="n">
-        <v>-770</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="25">
@@ -2345,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1649374</v>
+        <v>2656762</v>
       </c>
       <c r="D25" t="n">
-        <v>1559800</v>
+        <v>2669843</v>
       </c>
       <c r="E25" t="n">
-        <v>1761725</v>
+        <v>3085452</v>
       </c>
     </row>
   </sheetData>
@@ -2435,31 +2437,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>91940</v>
+        <v>116840</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8366.66</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>83573.34</v>
+        <v>116840</v>
       </c>
     </row>
     <row r="3">
@@ -2477,23 +2479,23 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4980</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19389</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -2501,7 +2503,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-19389</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="4">
@@ -2519,31 +2521,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>21420</v>
+        <v>26400</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11580</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9840</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="5">
@@ -2561,31 +2563,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>54820</v>
+        <v>64780</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6397.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>48422.5</v>
+        <v>64780</v>
       </c>
     </row>
     <row r="6">
@@ -2603,31 +2605,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>36440</v>
+        <v>41420</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>34760</v>
+        <v>41420</v>
       </c>
     </row>
     <row r="7">
@@ -2657,19 +2659,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49800</v>
+        <v>59800</v>
       </c>
     </row>
     <row r="8">
@@ -2699,19 +2701,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47150</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>407.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-35570</v>
+        <v>11580</v>
       </c>
     </row>
     <row r="9">
@@ -2741,19 +2743,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>10960</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="10">
@@ -2783,19 +2785,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47878</v>
+        <v>51858</v>
       </c>
     </row>
     <row r="11">
@@ -2813,31 +2815,31 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>31560</v>
+        <v>38160</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>27580</v>
+        <v>38160</v>
       </c>
     </row>
     <row r="12">
@@ -2855,31 +2857,31 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>12490</v>
+        <v>32290</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>5890</v>
+        <v>32290</v>
       </c>
     </row>
     <row r="13">
@@ -2897,19 +2899,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>129020</v>
+        <v>130418</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>161.3%</t>
+          <t>163.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>161.3%</t>
+          <t>163.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2921,7 +2923,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>129020</v>
+        <v>130418</v>
       </c>
     </row>
     <row r="14">
@@ -2951,19 +2953,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>60600</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="15">
@@ -3023,31 +3025,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>52738</v>
+        <v>47758</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>46138</v>
+        <v>47758</v>
       </c>
     </row>
     <row r="17">
@@ -3065,23 +3067,23 @@
         <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>27820</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -3089,7 +3091,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-45600</v>
+        <v>27820</v>
       </c>
     </row>
     <row r="18">
@@ -3119,19 +3121,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-3020</v>
+        <v>13980</v>
       </c>
     </row>
     <row r="19">
@@ -3149,31 +3151,31 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>60920</v>
+        <v>67520</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>26920</v>
+        <v>67520</v>
       </c>
     </row>
     <row r="20">
@@ -3233,19 +3235,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>10000</v>
+        <v>26600</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3257,7 +3259,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10000</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="22">
@@ -3287,19 +3289,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="23">
@@ -3413,19 +3415,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13070</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8084</v>
+        <v>21154</v>
       </c>
     </row>
     <row r="26">
@@ -3455,19 +3457,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9786</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>60590</v>
+        <v>70376</v>
       </c>
     </row>
     <row r="27">
@@ -3539,19 +3541,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>18600</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-3660</v>
+        <v>14940</v>
       </c>
     </row>
     <row r="29">
@@ -3569,31 +3571,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>29880</v>
+        <v>34860</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>25900</v>
+        <v>34860</v>
       </c>
     </row>
     <row r="30">
@@ -3623,19 +3625,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>35800</v>
+        <v>47800</v>
       </c>
     </row>
     <row r="31">
@@ -3665,19 +3667,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>82.0%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>17080</v>
+        <v>29800</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>131124</v>
+        <v>118404</v>
       </c>
     </row>
     <row r="32">
@@ -3695,31 +3697,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>68700</v>
+        <v>73680</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>64720</v>
+        <v>73680</v>
       </c>
     </row>
     <row r="33">
@@ -3737,31 +3739,31 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>27761</v>
+        <v>47422</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>17801</v>
+        <v>47422</v>
       </c>
     </row>
     <row r="34">
@@ -3821,19 +3823,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>33680</v>
+        <v>51110</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3845,7 +3847,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>33680</v>
+        <v>51110</v>
       </c>
     </row>
     <row r="36">
@@ -3863,31 +3865,31 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>45698</v>
+        <v>60638</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>41718</v>
+        <v>60638</v>
       </c>
     </row>
     <row r="37">
@@ -3905,31 +3907,31 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>29880</v>
+        <v>58116</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3980</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25900</v>
+        <v>58116</v>
       </c>
     </row>
     <row r="38">
@@ -3947,31 +3949,31 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>5700</v>
+        <v>44520</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>85708</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1503.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-80008</v>
+        <v>44520</v>
       </c>
     </row>
     <row r="39">
@@ -3989,19 +3991,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>71748</v>
+        <v>75548</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4013,7 +4015,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71748</v>
+        <v>75548</v>
       </c>
     </row>
     <row r="40">
@@ -4085,19 +4087,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1680</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>17240</v>
+        <v>18920</v>
       </c>
     </row>
   </sheetData>
@@ -4171,23 +4173,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>83568.2</v>
+        <v>130768.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22866.67</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60701.53</v>
+        <v>130768.2</v>
       </c>
     </row>
     <row r="3">
@@ -4205,11 +4207,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>29303.2</v>
+        <v>53603.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4221,7 +4223,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>29303.2</v>
+        <v>53603.2</v>
       </c>
     </row>
     <row r="4">
@@ -4239,11 +4241,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>40296</v>
+        <v>48596</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4255,7 +4257,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>40296</v>
+        <v>48596</v>
       </c>
     </row>
     <row r="5">
@@ -4273,23 +4275,23 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>7086.3</v>
+        <v>14586.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4486.3</v>
+        <v>14586.3</v>
       </c>
     </row>
     <row r="6">
@@ -4307,11 +4309,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>38529.36</v>
+        <v>48927.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4323,7 +4325,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38529.36</v>
+        <v>48927.36</v>
       </c>
     </row>
     <row r="7">
@@ -4341,11 +4343,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4357,7 +4359,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
     </row>
     <row r="8">
@@ -4375,11 +4377,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>15029.91</v>
+        <v>26035.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4391,7 +4393,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15029.91</v>
+        <v>26035.41</v>
       </c>
     </row>
     <row r="9">
@@ -4409,11 +4411,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>21695.11</v>
+        <v>22476.03</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4425,7 +4427,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>21495.11</v>
+        <v>22276.03</v>
       </c>
     </row>
     <row r="10">
@@ -4443,11 +4445,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>35796</v>
+        <v>46266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4459,7 +4461,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35796</v>
+        <v>46266.7</v>
       </c>
     </row>
     <row r="11">
@@ -4477,11 +4479,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>7800</v>
+        <v>8600</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4493,7 +4495,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7800</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="12">
@@ -4511,11 +4513,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>33400</v>
+        <v>57307.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4527,7 +4529,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>33400</v>
+        <v>57307.7</v>
       </c>
     </row>
     <row r="13">
@@ -4579,11 +4581,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>72784</v>
+        <v>85576</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4595,7 +4597,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>72784</v>
+        <v>85576</v>
       </c>
     </row>
     <row r="15">
@@ -4613,23 +4615,23 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>9996</v>
+        <v>24188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>9598</v>
+        <v>24188</v>
       </c>
     </row>
     <row r="16">
@@ -4647,11 +4649,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>12996</v>
+        <v>74190</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4663,7 +4665,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>12996</v>
+        <v>74190</v>
       </c>
     </row>
     <row r="17">
@@ -4681,11 +4683,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>11194</v>
+        <v>13788</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4697,7 +4699,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11194</v>
+        <v>13788</v>
       </c>
     </row>
     <row r="18">
@@ -4715,11 +4717,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>2530.6</v>
+        <v>2914.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4731,7 +4733,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2530.6</v>
+        <v>2914.6</v>
       </c>
     </row>
     <row r="19">
@@ -4749,23 +4751,23 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>47955.8</v>
+        <v>50733.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>42955.8</v>
+        <v>50733.9</v>
       </c>
     </row>
     <row r="20">
@@ -4783,23 +4785,23 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>54149.8</v>
+        <v>74747.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>50149.8</v>
+        <v>74747.8</v>
       </c>
     </row>
     <row r="21">
@@ -4885,11 +4887,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>74584</v>
+        <v>84982</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4901,7 +4903,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>74584</v>
+        <v>84982</v>
       </c>
     </row>
     <row r="24">
@@ -4919,11 +4921,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>1200</v>
+        <v>2196</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4935,7 +4937,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1200</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="25">
@@ -4957,19 +4959,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68166</v>
+        <v>77966</v>
       </c>
     </row>
     <row r="26">
@@ -4987,11 +4989,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>20358</v>
+        <v>21154</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5003,7 +5005,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>20358</v>
+        <v>21154</v>
       </c>
     </row>
     <row r="27">
@@ -5021,11 +5023,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>20398</v>
+        <v>24058</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5037,7 +5039,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>20398</v>
+        <v>24058</v>
       </c>
     </row>
     <row r="28">
@@ -5055,23 +5057,23 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>12996</v>
+        <v>13394</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19399.98</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>149.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-6403.98</v>
+        <v>13394</v>
       </c>
     </row>
     <row r="29">
@@ -5093,19 +5095,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>73382</v>
+        <v>80382</v>
       </c>
     </row>
     <row r="30">
@@ -5225,23 +5227,23 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>70181.64</v>
+        <v>94375.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>36381.64</v>
+        <v>94375.64</v>
       </c>
     </row>
     <row r="34">
@@ -5259,23 +5261,23 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>67279.75999999999</v>
+        <v>77529.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>61279.75999999999</v>
+        <v>77529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5293,23 +5295,23 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>43549</v>
+        <v>45488.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>36949</v>
+        <v>45488.92</v>
       </c>
     </row>
     <row r="36">
@@ -5327,11 +5329,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10398</v>
+        <v>10996</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5343,7 +5345,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10398</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="37">
@@ -5395,11 +5397,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>499</v>
+        <v>897</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5411,7 +5413,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>499</v>
+        <v>897</v>
       </c>
     </row>
     <row r="39">
@@ -5429,11 +5431,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>28074</v>
+        <v>48472</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5445,7 +5447,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>28074</v>
+        <v>48472</v>
       </c>
     </row>
     <row r="40">
@@ -5463,23 +5465,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>174694</v>
+        <v>380238</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>162694</v>
+        <v>380238</v>
       </c>
     </row>
     <row r="41">
@@ -5497,11 +5499,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>28395</v>
+        <v>49191</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5513,7 +5515,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>28395</v>
+        <v>49191</v>
       </c>
     </row>
     <row r="42">
@@ -5531,23 +5533,23 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>16596</v>
+        <v>116372</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8996</v>
+        <v>116372</v>
       </c>
     </row>
     <row r="43">
@@ -5633,11 +5635,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>23481.5</v>
+        <v>42355.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5649,7 +5651,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>23481.5</v>
+        <v>42355.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5701,11 +5703,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>66477</v>
+        <v>139540</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5717,7 +5719,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>66477</v>
+        <v>139540</v>
       </c>
     </row>
     <row r="48">
@@ -5735,11 +5737,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>27983</v>
+        <v>64521</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5751,7 +5753,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>27983</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="49">
@@ -5769,11 +5771,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>95807</v>
+        <v>134512.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5785,7 +5787,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>95807</v>
+        <v>134512.5</v>
       </c>
     </row>
     <row r="50">
@@ -5871,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>91504</v>
+        <v>196419</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5887,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>91504</v>
+        <v>196419</v>
       </c>
     </row>
     <row r="53">
@@ -5905,11 +5907,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>35106.1</v>
+        <v>57792.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5921,7 +5923,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>35106.1</v>
+        <v>57792.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -5939,11 +5941,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>130278</v>
+        <v>167022</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5955,7 +5957,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>130278</v>
+        <v>167022</v>
       </c>
     </row>
     <row r="55">
@@ -5973,23 +5975,23 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>26295</v>
+        <v>90393</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>16295</v>
+        <v>90393</v>
       </c>
     </row>
     <row r="56">
@@ -6041,11 +6043,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>44058</v>
+        <v>54456</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6057,7 +6059,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>44058</v>
+        <v>54456</v>
       </c>
     </row>
     <row r="58">
@@ -6143,11 +6145,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>20000</v>
+        <v>25398</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>127.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6159,7 +6161,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>20000</v>
+        <v>25398</v>
       </c>
     </row>
     <row r="61">
@@ -6177,11 +6179,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>24194</v>
+        <v>26970</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6193,7 +6195,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>24194</v>
+        <v>26970</v>
       </c>
     </row>
     <row r="62">
@@ -6211,23 +6213,23 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>44497</v>
+        <v>60675</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>28697</v>
+        <v>60675</v>
       </c>
     </row>
     <row r="63">
@@ -6245,11 +6247,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>8278</v>
+        <v>9074</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>138.0%</t>
+          <t>151.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6261,7 +6263,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>8278</v>
+        <v>9074</v>
       </c>
     </row>
   </sheetData>
@@ -6322,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>991544.5600000001</v>
+        <v>1215526.8</v>
       </c>
       <c r="D2" t="n">
-        <v>5324</v>
+        <v>6721</v>
       </c>
       <c r="E2" t="n">
-        <v>882370.5600000001</v>
+        <v>1076088.8</v>
       </c>
       <c r="F2" t="n">
-        <v>109174</v>
+        <v>139438</v>
       </c>
     </row>
     <row r="3">
@@ -6346,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>852428</v>
+        <v>1031938</v>
       </c>
       <c r="D3" t="n">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="E3" t="n">
-        <v>751703</v>
+        <v>906354</v>
       </c>
       <c r="F3" t="n">
-        <v>100725</v>
+        <v>125584</v>
       </c>
     </row>
     <row r="4">
@@ -6370,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>139116.56</v>
+        <v>183588.8</v>
       </c>
       <c r="D4" t="n">
-        <v>5054</v>
+        <v>6418</v>
       </c>
       <c r="E4" t="n">
-        <v>130667.56</v>
+        <v>169734.8</v>
       </c>
       <c r="F4" t="n">
-        <v>8449</v>
+        <v>13854</v>
       </c>
     </row>
     <row r="5">
@@ -6394,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1722320</v>
+        <v>2285822</v>
       </c>
       <c r="D5" t="n">
-        <v>311</v>
+        <v>421</v>
       </c>
       <c r="E5" t="n">
-        <v>377474</v>
+        <v>471926</v>
       </c>
       <c r="F5" t="n">
-        <v>1344846</v>
+        <v>1813896</v>
       </c>
     </row>
     <row r="6">
@@ -6418,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1099440</v>
+        <v>1507918</v>
       </c>
       <c r="D6" t="n">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="E6" t="n">
         <v>14820</v>
       </c>
       <c r="F6" t="n">
-        <v>1084620</v>
+        <v>1493098</v>
       </c>
     </row>
     <row r="7">
@@ -6442,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>612880</v>
+        <v>777904</v>
       </c>
       <c r="D7" t="n">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E7" t="n">
-        <v>362654</v>
+        <v>457106</v>
       </c>
       <c r="F7" t="n">
-        <v>250226</v>
+        <v>320798</v>
       </c>
     </row>
     <row r="8">
@@ -6466,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>560585.09</v>
+        <v>889900.38</v>
       </c>
       <c r="D8" t="n">
-        <v>828</v>
+        <v>1023</v>
       </c>
       <c r="E8" t="n">
-        <v>11206.74</v>
+        <v>14807.22</v>
       </c>
       <c r="F8" t="n">
-        <v>549378.35</v>
+        <v>875093.16</v>
       </c>
     </row>
     <row r="9">
@@ -6490,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>325152.72</v>
+        <v>547015.98</v>
       </c>
       <c r="D9" t="n">
-        <v>394</v>
+        <v>453</v>
       </c>
       <c r="E9" t="n">
-        <v>2661.37</v>
+        <v>2993.86</v>
       </c>
       <c r="F9" t="n">
-        <v>322491.35</v>
+        <v>544022.12</v>
       </c>
     </row>
     <row r="10">
@@ -6514,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>235432.37</v>
+        <v>342884.4</v>
       </c>
       <c r="D10" t="n">
-        <v>434</v>
+        <v>570</v>
       </c>
       <c r="E10" t="n">
-        <v>8545.370000000001</v>
+        <v>11813.36</v>
       </c>
       <c r="F10" t="n">
-        <v>226887</v>
+        <v>331071.04</v>
       </c>
     </row>
     <row r="11">
@@ -6538,16 +6540,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>167600</v>
+        <v>305400</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>122000</v>
+        <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>45600</v>
+        <v>182400</v>
       </c>
     </row>
     <row r="12">
@@ -6562,16 +6564,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>182391.9</v>
+        <v>291765.9</v>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>101495.9</v>
+        <v>107293.9</v>
       </c>
       <c r="F12" t="n">
-        <v>80896</v>
+        <v>184472</v>
       </c>
     </row>
     <row r="13">
@@ -6586,16 +6588,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>263380</v>
+        <v>267340</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>235580</v>
+        <v>237560</v>
       </c>
       <c r="F13" t="n">
-        <v>27800</v>
+        <v>29780</v>
       </c>
     </row>
     <row r="14">
@@ -6610,16 +6612,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>95040</v>
+        <v>99000</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
         <v>13860</v>
       </c>
       <c r="F14" t="n">
-        <v>81180</v>
+        <v>85140</v>
       </c>
     </row>
     <row r="15">
@@ -6634,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25871.6</v>
+        <v>69774</v>
       </c>
       <c r="D15" t="n">
-        <v>55</v>
+        <v>170</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
       </c>
       <c r="F15" t="n">
-        <v>19335.24</v>
+        <v>63237.64</v>
       </c>
     </row>
   </sheetData>
@@ -6704,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>991544.5600000001</v>
+        <v>1215526.8</v>
       </c>
       <c r="C2" t="n">
-        <v>241446.06</v>
+        <v>21388</v>
       </c>
       <c r="D2" t="n">
-        <v>16871</v>
+        <v>21388</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>224575.06</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>22.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6729,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1722320</v>
+        <v>2285822</v>
       </c>
       <c r="C3" t="n">
-        <v>228418.98</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6741,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>228418.98</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>13.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6754,10 +6756,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>560585.09</v>
+        <v>889900.38</v>
       </c>
       <c r="C4" t="n">
-        <v>2849</v>
+        <v>49</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -6766,10 +6768,10 @@
         <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6779,10 +6781,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>167600</v>
+        <v>305400</v>
       </c>
       <c r="C5" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6791,10 +6793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>45600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>27.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6804,22 +6806,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>182391.9</v>
+        <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>95125.89999999999</v>
+        <v>2017.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>93108</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>51.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6829,22 +6831,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>263380</v>
+        <v>267340</v>
       </c>
       <c r="C7" t="n">
-        <v>149666.67</v>
+        <v>29800</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>29800</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>11.15</v>
       </c>
       <c r="F7" t="n">
-        <v>149666.67</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>56.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6854,7 +6856,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95040</v>
+        <v>99000</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6879,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25871.6</v>
+        <v>69774</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -6908,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6940,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C2" t="n">
-        <v>426898.65</v>
+        <v>33238</v>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -6956,140 +6958,124 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C3" t="n">
-        <v>203842.4</v>
+        <v>10973.9</v>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
-        <v>61364</v>
+        <v>6699</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>28000</v>
+        <v>1184</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>15595.66</v>
+        <v>1046</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>14149</v>
+        <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>9474</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>3070.9</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>617</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>95</v>
-      </c>
-      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7104,7 +7090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D83"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7132,7 +7118,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7141,16 +7127,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>116400</v>
+        <v>30179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7159,70 +7145,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>8400</v>
+        <v>850</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>6600</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>6600</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7231,70 +7217,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D7" t="n">
-        <v>71886</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>51108</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7303,10 +7289,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12">
@@ -7317,14 +7303,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>42950</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7339,70 +7325,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21766</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>11803</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>3706</v>
+        <v>2018.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>2490</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7414,13 +7400,13 @@
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>2059</v>
+        <v>191</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7429,46 +7415,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>571</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>60406</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -7479,14 +7465,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>10522</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="22">
@@ -7497,14 +7483,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="D22" t="n">
-        <v>343</v>
+        <v>658</v>
       </c>
     </row>
     <row r="23">
@@ -7519,10 +7505,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24">
@@ -7537,28 +7523,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>19865.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -7569,14 +7555,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D26" t="n">
-        <v>16800</v>
+        <v>893</v>
       </c>
     </row>
     <row r="27">
@@ -7587,14 +7573,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" t="n">
-        <v>7446.66</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28">
@@ -7605,14 +7591,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>4609</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29">
@@ -7623,7 +7609,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7641,14 +7627,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31">
@@ -7690,61 +7676,61 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>36400</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>10000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>200</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7753,28 +7739,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -7785,14 +7771,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D38" t="n">
-        <v>31309</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39">
@@ -7803,14 +7789,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>9000</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
@@ -7821,14 +7807,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>228</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -7839,14 +7825,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
@@ -7857,38 +7843,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>57</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7897,93 +7883,93 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>27837</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>3071</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>598</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>337</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -7996,61 +7982,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>19164.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>8424</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>3464</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8059,57 +8045,57 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>490</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>133</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -8122,12 +8108,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -8140,7 +8126,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8149,34 +8135,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>18399.98</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>8000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8185,424 +8171,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>20994.67</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" t="n">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>3</v>
-      </c>
-      <c r="D64" t="n">
-        <v>19609</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" t="n">
-        <v>6289</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="n">
-        <v>6800</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>4</v>
-      </c>
-      <c r="D73" t="n">
-        <v>9318</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
-        <v>10621</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2</v>
-      </c>
-      <c r="D79" t="n">
-        <v>10009</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -8639,131 +8211,131 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>分享咨询</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>182897.98</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>630</v>
       </c>
       <c r="C3" t="n">
-        <v>145466.67</v>
+        <v>10906</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>299元青春期家庭21天陪跑</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>104715.16</v>
+        <v>4784</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>完形心理基训课</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>95760</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>【前端】少年说</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>93108</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>1280智慧父母成长营年卡</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>45600</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>裴盈299青少年及儿童焦虑基础营月卡</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>41900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>韩冰成人专线（体验）</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>13200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>29睡眠基础营</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>10621</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>59元青少年体验课（韩小冰版）</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>573</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>9985</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -8800,40 +8372,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>134514.33</v>
+        <v>30599</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>90015.5</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="C4" t="n">
-        <v>73066</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="5">
@@ -8843,153 +8415,153 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>65552.98</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="C6" t="n">
-        <v>51879</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>51537</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>37938</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>37200</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>37108</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>35827</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
-        <v>29848</v>
+        <v>715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>18648</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>14903</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>13934.9</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>12953</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -531,10 +531,10 @@
         <v>285434</v>
       </c>
       <c r="E2" t="n">
-        <v>1653</v>
+        <v>66158</v>
       </c>
       <c r="F2" t="n">
-        <v>283781</v>
+        <v>219275</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -546,7 +546,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-14671.6%</t>
+          <t>-11359.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -588,10 +588,10 @@
         <v>1981</v>
       </c>
       <c r="E3" t="n">
-        <v>1357</v>
+        <v>17617</v>
       </c>
       <c r="F3" t="n">
-        <v>624</v>
+        <v>-15636</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-106.6%</t>
+          <t>+66.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -641,10 +641,10 @@
         <v>299447</v>
       </c>
       <c r="E4" t="n">
-        <v>8006</v>
+        <v>96968</v>
       </c>
       <c r="F4" t="n">
-        <v>291441</v>
+        <v>202479</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -656,7 +656,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+114.3%</t>
+          <t>+48.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -698,10 +698,10 @@
         <v>132197</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>136695</v>
       </c>
       <c r="F5" t="n">
-        <v>132035</v>
+        <v>-4498</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-21.0%</t>
+          <t>-102.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -755,10 +755,10 @@
         <v>359335</v>
       </c>
       <c r="E6" t="n">
-        <v>6442</v>
+        <v>36387</v>
       </c>
       <c r="F6" t="n">
-        <v>352892</v>
+        <v>322947</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+164.1%</t>
+          <t>+141.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -812,10 +812,10 @@
         <v>231947</v>
       </c>
       <c r="E7" t="n">
-        <v>31441</v>
+        <v>62463</v>
       </c>
       <c r="F7" t="n">
-        <v>200506</v>
+        <v>169484</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+34.4%</t>
+          <t>+13.6%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -869,10 +869,10 @@
         <v>206042</v>
       </c>
       <c r="E8" t="n">
-        <v>2687</v>
+        <v>73425</v>
       </c>
       <c r="F8" t="n">
-        <v>203355</v>
+        <v>132617</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+24.6%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -926,10 +926,10 @@
         <v>534687</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>170300</v>
       </c>
       <c r="F9" t="n">
-        <v>534687</v>
+        <v>364387</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+62.7%</t>
+          <t>+10.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1044,20 +1044,20 @@
         <v>143638</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>26399</v>
       </c>
       <c r="F11" t="n">
-        <v>143638</v>
+        <v>117238</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+38.7%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>28854</v>
+        <v>18454</v>
       </c>
       <c r="P11" t="n">
-        <v>114574</v>
+        <v>98574</v>
       </c>
       <c r="Q11" t="n">
         <v>75660</v>
@@ -1107,20 +1107,20 @@
         <v>281083</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>23057</v>
       </c>
       <c r="F12" t="n">
-        <v>281026</v>
+        <v>258026</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+90.7%</t>
+          <t>+75.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1144,7 +1144,7 @@
         <v>53163</v>
       </c>
       <c r="P12" t="n">
-        <v>227863</v>
+        <v>204863</v>
       </c>
       <c r="Q12" t="n">
         <v>19814</v>
@@ -1168,20 +1168,20 @@
         <v>309747</v>
       </c>
       <c r="E13" t="n">
-        <v>394</v>
+        <v>25927</v>
       </c>
       <c r="F13" t="n">
-        <v>309353</v>
+        <v>283819</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+61.9%</t>
+          <t>+48.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>6816</v>
       </c>
       <c r="O13" t="n">
-        <v>13947</v>
+        <v>13899</v>
       </c>
       <c r="P13" t="n">
-        <v>288590</v>
+        <v>263104</v>
       </c>
       <c r="Q13" t="n">
-        <v>33879</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="14">
@@ -1231,20 +1231,20 @@
         <v>147271</v>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>147204</v>
+        <v>132405</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1260,20 +1260,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+44.6%</t>
+          <t>+30.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>9842</v>
       </c>
       <c r="O14" t="n">
-        <v>54766</v>
+        <v>49467</v>
       </c>
       <c r="P14" t="n">
-        <v>82596</v>
+        <v>73096</v>
       </c>
       <c r="Q14" t="n">
-        <v>19932</v>
+        <v>19633</v>
       </c>
     </row>
     <row r="15">
@@ -1294,20 +1294,20 @@
         <v>98100</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>98062</v>
+        <v>82224</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1323,18 +1323,18 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>6735</v>
+        <v>6697</v>
       </c>
       <c r="P15" t="n">
-        <v>91327</v>
+        <v>75527</v>
       </c>
       <c r="Q15" t="n">
-        <v>36480</v>
+        <v>36442</v>
       </c>
     </row>
     <row r="16">
@@ -1355,20 +1355,20 @@
         <v>197885</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="F16" t="n">
-        <v>197885</v>
+        <v>197487</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+197.6%</t>
+          <t>+197.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>16715</v>
+        <v>16317</v>
       </c>
       <c r="P16" t="n">
         <v>181170</v>
@@ -1416,20 +1416,20 @@
         <v>229924</v>
       </c>
       <c r="E17" t="n">
-        <v>229</v>
+        <v>46658</v>
       </c>
       <c r="F17" t="n">
-        <v>229695</v>
+        <v>183266</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1445,20 +1445,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>19928</v>
       </c>
       <c r="O17" t="n">
-        <v>3295</v>
+        <v>3266</v>
       </c>
       <c r="P17" t="n">
-        <v>206472</v>
+        <v>160072</v>
       </c>
       <c r="Q17" t="n">
-        <v>20835</v>
+        <v>-15593</v>
       </c>
     </row>
     <row r="18">
@@ -1479,20 +1479,20 @@
         <v>632424</v>
       </c>
       <c r="E18" t="n">
-        <v>47</v>
+        <v>19675</v>
       </c>
       <c r="F18" t="n">
-        <v>632377</v>
+        <v>612749</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1508,20 +1508,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+112.5%</t>
+          <t>+105.9%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>188736</v>
+        <v>188708</v>
       </c>
       <c r="P18" t="n">
-        <v>442791</v>
+        <v>423191</v>
       </c>
       <c r="Q18" t="n">
-        <v>393977</v>
+        <v>393949</v>
       </c>
     </row>
     <row r="19">
@@ -1542,10 +1542,10 @@
         <v>161943</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>161928</v>
+        <v>161919</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -1571,20 +1571,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-1213.4%</t>
+          <t>-1213.3%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>7220</v>
       </c>
       <c r="O19" t="n">
-        <v>28516</v>
+        <v>28507</v>
       </c>
       <c r="P19" t="n">
         <v>126392</v>
       </c>
       <c r="Q19" t="n">
-        <v>24252</v>
+        <v>24243</v>
       </c>
     </row>
     <row r="20">
@@ -1605,20 +1605,20 @@
         <v>250143</v>
       </c>
       <c r="E20" t="n">
-        <v>351</v>
+        <v>40832</v>
       </c>
       <c r="F20" t="n">
-        <v>249792</v>
+        <v>209311</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1634,18 +1634,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>91262</v>
+        <v>85081</v>
       </c>
       <c r="P20" t="n">
-        <v>158530</v>
+        <v>124230</v>
       </c>
       <c r="Q20" t="n">
-        <v>46016</v>
+        <v>36035</v>
       </c>
     </row>
     <row r="21">
@@ -1666,22 +1666,22 @@
         <v>5424529</v>
       </c>
       <c r="E21" t="n">
-        <v>53254</v>
+        <v>887147</v>
       </c>
       <c r="F21" t="n">
-        <v>5371274</v>
+        <v>4537381</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+65.4%</t>
+          <t>+39.7%</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>44867</v>
       </c>
       <c r="O21" t="n">
-        <v>2656762</v>
+        <v>2100955</v>
       </c>
       <c r="P21" t="n">
-        <v>2669843</v>
+        <v>2391758</v>
       </c>
       <c r="Q21" t="n">
-        <v>3085452</v>
+        <v>2499478</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1404622</v>
+        <v>1050456</v>
       </c>
       <c r="D2" t="n">
-        <v>60013</v>
+        <v>-23786</v>
       </c>
       <c r="E2" t="n">
-        <v>1196426</v>
+        <v>816459</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>424207</v>
+        <v>258107</v>
       </c>
       <c r="D3" t="n">
-        <v>110480</v>
+        <v>106280</v>
       </c>
       <c r="E3" t="n">
-        <v>330971</v>
+        <v>194171</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>826213</v>
+        <v>803783</v>
       </c>
       <c r="D4" t="n">
-        <v>2486150</v>
+        <v>2296064</v>
       </c>
       <c r="E4" t="n">
-        <v>1556334</v>
+        <v>1489617</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>282744</v>
+        <v>218238</v>
       </c>
       <c r="D5" t="n">
         <v>1037</v>
       </c>
       <c r="E5" t="n">
-        <v>273781</v>
+        <v>209275</v>
       </c>
     </row>
     <row r="6">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>489</v>
+        <v>-15771</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>624</v>
+        <v>-5636</v>
       </c>
     </row>
     <row r="7">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>285430</v>
+        <v>208468</v>
       </c>
       <c r="D7" t="n">
-        <v>6010</v>
+        <v>-5989</v>
       </c>
       <c r="E7" t="n">
-        <v>266655</v>
+        <v>211193</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>88647</v>
+        <v>-5886</v>
       </c>
       <c r="D8" t="n">
-        <v>43388</v>
+        <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>93215</v>
+        <v>-43318</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>345985</v>
+        <v>316040</v>
       </c>
       <c r="D9" t="n">
         <v>6907</v>
       </c>
       <c r="E9" t="n">
-        <v>285100</v>
+        <v>255155</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>198807</v>
+        <v>167785</v>
       </c>
       <c r="D10" t="n">
         <v>1699</v>
       </c>
       <c r="E10" t="n">
-        <v>94092</v>
+        <v>67570</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>202518</v>
+        <v>161580</v>
       </c>
       <c r="D11" t="n">
-        <v>837</v>
+        <v>-28963</v>
       </c>
       <c r="E11" t="n">
-        <v>182957</v>
+        <v>122219</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>424207</v>
+        <v>258107</v>
       </c>
       <c r="D12" t="n">
-        <v>110480</v>
+        <v>106280</v>
       </c>
       <c r="E12" t="n">
-        <v>330971</v>
+        <v>194171</v>
       </c>
     </row>
     <row r="13">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28854</v>
+        <v>18454</v>
       </c>
       <c r="D14" t="n">
-        <v>114574</v>
+        <v>98574</v>
       </c>
       <c r="E14" t="n">
         <v>75660</v>
@@ -2140,7 +2140,7 @@
         <v>53163</v>
       </c>
       <c r="D15" t="n">
-        <v>227863</v>
+        <v>204863</v>
       </c>
       <c r="E15" t="n">
         <v>19814</v>
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13947</v>
+        <v>13899</v>
       </c>
       <c r="D16" t="n">
-        <v>288590</v>
+        <v>263104</v>
       </c>
       <c r="E16" t="n">
-        <v>33879</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="17">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>54766</v>
+        <v>49467</v>
       </c>
       <c r="D17" t="n">
-        <v>82596</v>
+        <v>73096</v>
       </c>
       <c r="E17" t="n">
-        <v>19932</v>
+        <v>19633</v>
       </c>
     </row>
     <row r="18">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6735</v>
+        <v>6697</v>
       </c>
       <c r="D18" t="n">
-        <v>91327</v>
+        <v>75527</v>
       </c>
       <c r="E18" t="n">
-        <v>36480</v>
+        <v>36442</v>
       </c>
     </row>
     <row r="19">
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16715</v>
+        <v>16317</v>
       </c>
       <c r="D19" t="n">
         <v>181170</v>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3295</v>
+        <v>3266</v>
       </c>
       <c r="D20" t="n">
-        <v>206472</v>
+        <v>160072</v>
       </c>
       <c r="E20" t="n">
-        <v>20835</v>
+        <v>-15593</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>188736</v>
+        <v>188708</v>
       </c>
       <c r="D21" t="n">
-        <v>442791</v>
+        <v>423191</v>
       </c>
       <c r="E21" t="n">
-        <v>393977</v>
+        <v>393949</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28516</v>
+        <v>28507</v>
       </c>
       <c r="D22" t="n">
         <v>126392</v>
       </c>
       <c r="E22" t="n">
-        <v>24252</v>
+        <v>24243</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>91262</v>
+        <v>85081</v>
       </c>
       <c r="D23" t="n">
-        <v>158530</v>
+        <v>124230</v>
       </c>
       <c r="E23" t="n">
-        <v>46016</v>
+        <v>36035</v>
       </c>
     </row>
     <row r="24">
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1720</v>
+        <v>-11391</v>
       </c>
       <c r="D24" t="n">
         <v>13200</v>
       </c>
       <c r="E24" t="n">
-        <v>1720</v>
+        <v>-770</v>
       </c>
     </row>
     <row r="25">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2656762</v>
+        <v>2100955</v>
       </c>
       <c r="D25" t="n">
-        <v>2669843</v>
+        <v>2391758</v>
       </c>
       <c r="E25" t="n">
-        <v>3085452</v>
+        <v>2499478</v>
       </c>
     </row>
   </sheetData>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>8366.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>116840</v>
+        <v>108473.34</v>
       </c>
     </row>
     <row r="3">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>19389</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>389.3%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4980</v>
+        <v>-14409</v>
       </c>
     </row>
     <row r="4">
@@ -2533,19 +2533,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>28380</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>26400</v>
+        <v>-1980</v>
       </c>
     </row>
     <row r="5">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>6397.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>64780</v>
+        <v>58382.5</v>
       </c>
     </row>
     <row r="6">
@@ -2617,19 +2617,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41420</v>
+        <v>39740</v>
       </c>
     </row>
     <row r="7">
@@ -2659,19 +2659,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59800</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="8">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>47150</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>407.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11580</v>
+        <v>-35570</v>
       </c>
     </row>
     <row r="9">
@@ -2743,19 +2743,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4979</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>9961</v>
       </c>
     </row>
     <row r="10">
@@ -2785,19 +2785,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>51858</v>
+        <v>47878</v>
       </c>
     </row>
     <row r="11">
@@ -2827,19 +2827,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>38160</v>
+        <v>34180</v>
       </c>
     </row>
     <row r="12">
@@ -2869,19 +2869,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32290</v>
+        <v>25690</v>
       </c>
     </row>
     <row r="13">
@@ -2953,19 +2953,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>39800</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>75600</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="15">
@@ -3037,19 +3037,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>47758</v>
+        <v>41158</v>
       </c>
     </row>
     <row r="17">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>52100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>187.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>27820</v>
+        <v>-24280</v>
       </c>
     </row>
     <row r="18">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>13980</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="19">
@@ -3163,19 +3163,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>67520</v>
+        <v>33520</v>
       </c>
     </row>
     <row r="20">
@@ -3289,19 +3289,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6600</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="23">
@@ -3415,19 +3415,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>13070</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>21154</v>
+        <v>8084</v>
       </c>
     </row>
     <row r="26">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>9786</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>70376</v>
+        <v>60590</v>
       </c>
     </row>
     <row r="27">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>14940</v>
+        <v>-3660</v>
       </c>
     </row>
     <row r="29">
@@ -3583,19 +3583,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>8960</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>34860</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="30">
@@ -3625,19 +3625,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47800</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="31">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29800</v>
+        <v>46880</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>118404</v>
+        <v>101324</v>
       </c>
     </row>
     <row r="32">
@@ -3709,19 +3709,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>73680</v>
+        <v>69700</v>
       </c>
     </row>
     <row r="33">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>9960</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47422</v>
+        <v>37462</v>
       </c>
     </row>
     <row r="34">
@@ -3793,19 +3793,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>57619</v>
+        <v>54019</v>
       </c>
     </row>
     <row r="35">
@@ -3877,19 +3877,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>60638</v>
+        <v>56658</v>
       </c>
     </row>
     <row r="37">
@@ -3919,19 +3919,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>3980</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>58116</v>
+        <v>54136</v>
       </c>
     </row>
     <row r="38">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>95508</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>214.5%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>44520</v>
+        <v>-50988</v>
       </c>
     </row>
     <row r="39">
@@ -4003,19 +4003,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3788</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>75548</v>
+        <v>71760</v>
       </c>
     </row>
     <row r="40">
@@ -4087,19 +4087,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1680</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>18920</v>
+        <v>17240</v>
       </c>
     </row>
   </sheetData>
@@ -4177,19 +4177,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>22866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>130768.2</v>
+        <v>107901.53</v>
       </c>
     </row>
     <row r="3">
@@ -4279,19 +4279,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>14586.3</v>
+        <v>11986.3</v>
       </c>
     </row>
     <row r="6">
@@ -4619,19 +4619,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24188</v>
+        <v>23790</v>
       </c>
     </row>
     <row r="16">
@@ -4755,19 +4755,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>50733.9</v>
+        <v>45733.9</v>
       </c>
     </row>
     <row r="20">
@@ -4789,19 +4789,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74747.8</v>
+        <v>70747.8</v>
       </c>
     </row>
     <row r="21">
@@ -4959,19 +4959,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>77966</v>
+        <v>68166</v>
       </c>
     </row>
     <row r="26">
@@ -5061,19 +5061,19 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>19399.98</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>144.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>13394</v>
+        <v>-6005.98</v>
       </c>
     </row>
     <row r="29">
@@ -5095,19 +5095,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>80382</v>
+        <v>73382</v>
       </c>
     </row>
     <row r="30">
@@ -5231,19 +5231,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>33800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>94375.64</v>
+        <v>60575.64</v>
       </c>
     </row>
     <row r="34">
@@ -5265,19 +5265,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>77529.84999999999</v>
+        <v>71529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5299,19 +5299,19 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>45488.92</v>
+        <v>38888.92</v>
       </c>
     </row>
     <row r="36">
@@ -5469,19 +5469,19 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>380238</v>
+        <v>368238</v>
       </c>
     </row>
     <row r="41">
@@ -5537,19 +5537,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>116372</v>
+        <v>108772</v>
       </c>
     </row>
     <row r="43">
@@ -5979,19 +5979,19 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>90393</v>
+        <v>80393</v>
       </c>
     </row>
     <row r="56">
@@ -6013,19 +6013,19 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>30796</v>
+        <v>25796</v>
       </c>
     </row>
     <row r="57">
@@ -6115,19 +6115,19 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>69208</v>
+        <v>61208</v>
       </c>
     </row>
     <row r="60">
@@ -6217,19 +6217,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>15800</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>60675</v>
+        <v>44875</v>
       </c>
     </row>
     <row r="63">
@@ -6709,7 +6709,7 @@
         <v>1215526.8</v>
       </c>
       <c r="C2" t="n">
-        <v>21388</v>
+        <v>260999.06</v>
       </c>
       <c r="D2" t="n">
         <v>21388</v>
@@ -6718,10 +6718,10 @@
         <v>1.76</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>239611.06</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="3">
@@ -6734,7 +6734,7 @@
         <v>2285822</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>247918.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>247918.98</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="4">
@@ -6759,7 +6759,7 @@
         <v>889900.38</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>2849</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -6768,10 +6768,10 @@
         <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="5">
@@ -6784,7 +6784,7 @@
         <v>305400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6793,10 +6793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>70400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
     </row>
     <row r="6">
@@ -6809,7 +6809,7 @@
         <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>2017.9</v>
+        <v>98913.89999999999</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6818,10 +6818,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>96896</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>33.21</v>
       </c>
     </row>
     <row r="7">
@@ -6834,7 +6834,7 @@
         <v>267340</v>
       </c>
       <c r="C7" t="n">
-        <v>29800</v>
+        <v>206066.67</v>
       </c>
       <c r="D7" t="n">
         <v>29800</v>
@@ -6843,10 +6843,10 @@
         <v>11.15</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>176266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -6910,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231</v>
+        <v>318</v>
       </c>
       <c r="C2" t="n">
-        <v>33238</v>
+        <v>512809.65</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -6958,124 +6958,140 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>326</v>
+        <v>428</v>
       </c>
       <c r="C3" t="n">
-        <v>10973.9</v>
+        <v>232636.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>6699</v>
+        <v>61383</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>1184</v>
+        <v>28000</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>1046</v>
+        <v>16608.66</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14149</v>
+      </c>
+      <c r="D7" t="n">
         <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>57</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>11241.9</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>9607</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>617</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>教材问题</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>95</v>
+      </c>
+      <c r="D11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7090,7 +7106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7118,7 +7134,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7127,16 +7143,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>30179</v>
+        <v>141200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -7145,70 +7161,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>850</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>318</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -7217,70 +7233,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>93</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>3735</v>
+        <v>85493</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>1801</v>
+        <v>51127</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>102</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1524</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>508</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -7289,10 +7305,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>400</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="12">
@@ -7303,14 +7319,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>48249</v>
       </c>
     </row>
     <row r="13">
@@ -7325,70 +7341,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>21785</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="D14" t="n">
-        <v>3648</v>
+        <v>17543</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>2018.9</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>414</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7397,16 +7413,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>191</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7415,46 +7431,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D18" t="n">
-        <v>133</v>
+        <v>609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>61932</v>
       </c>
     </row>
     <row r="21">
@@ -7465,14 +7481,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>1653</v>
+        <v>10742</v>
       </c>
     </row>
     <row r="22">
@@ -7483,14 +7499,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>658</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23">
@@ -7505,10 +7521,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23" t="n">
-        <v>209</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24">
@@ -7523,28 +7539,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>21479</v>
       </c>
     </row>
     <row r="26">
@@ -7559,10 +7575,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D26" t="n">
-        <v>893</v>
+        <v>20188.5</v>
       </c>
     </row>
     <row r="27">
@@ -7573,14 +7589,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>346</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="28">
@@ -7595,10 +7611,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>281</v>
+        <v>7519.66</v>
       </c>
     </row>
     <row r="29">
@@ -7613,10 +7629,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30">
@@ -7631,10 +7647,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
@@ -7676,151 +7692,151 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>1309</v>
+        <v>57836</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>299</v>
+        <v>598</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>67</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>209</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>76</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7832,49 +7848,49 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>19</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>299</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7883,34 +7899,34 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>31309</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>200</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7919,124 +7935,124 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D46" t="n">
-        <v>29</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>19630.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D51" t="n">
-        <v>29</v>
+        <v>12095</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8045,57 +8061,57 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>595</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -8108,12 +8124,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -8126,7 +8142,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8135,46 +8151,496 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>9</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>38</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>20994.67</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15009</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="n">
+        <v>19618</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6289</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>课程2组</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>服务未交付/联系不上</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>9318</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>效果不满意</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>10621</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C60" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" t="n">
-        <v>15</v>
+      <c r="C85" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -8215,127 +8681,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>29800</v>
+        <v>201866.67</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>分享咨询</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>630</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>10906</v>
+        <v>194397.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>299元青春期家庭21天陪跑</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
-        <v>4784</v>
+        <v>113675.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>完形心理基训课</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>1998</v>
+        <v>95760</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【前端】少年说</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>1680</v>
+        <v>93108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1280智慧父母成长营年卡</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>1280</v>
+        <v>70400</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>裴盈299青少年及儿童焦虑基础营月卡</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>897</v>
+        <v>49900</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>韩冰成人专线（体验）</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29睡眠基础营</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>750</v>
       </c>
       <c r="C10" t="n">
-        <v>551</v>
+        <v>13031</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>59元青少年体验课（韩小冰版）</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>342</v>
+        <v>10621</v>
       </c>
     </row>
   </sheetData>
@@ -8372,196 +8838,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>205</v>
       </c>
       <c r="C2" t="n">
-        <v>30599</v>
+        <v>152210.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>4440</v>
+        <v>96315.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>3979</v>
+        <v>77452.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="C5" t="n">
-        <v>2892</v>
+        <v>77096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>1982</v>
+        <v>68184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1691</v>
+        <v>55686</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1422</v>
+        <v>51836</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C9" t="n">
-        <v>1155</v>
+        <v>51354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1092</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C11" t="n">
-        <v>746</v>
+        <v>36174</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C12" t="n">
-        <v>715</v>
+        <v>35197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>617</v>
+        <v>29867</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>388</v>
+        <v>18648</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n">
-        <v>362</v>
+        <v>15249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C16" t="n">
-        <v>299</v>
+        <v>14048.9</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>285434</v>
+        <v>299635</v>
       </c>
       <c r="E2" t="n">
-        <v>66158</v>
+        <v>76730</v>
       </c>
       <c r="F2" t="n">
-        <v>219275</v>
+        <v>222904</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>134123</v>
+        <v>159638</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+112.8%</t>
+          <t>+87.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1947</v>
+        <v>18549</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-11359.4%</t>
+          <t>+1101.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1981</v>
+        <v>2000</v>
       </c>
       <c r="E3" t="n">
         <v>17617</v>
       </c>
       <c r="F3" t="n">
-        <v>-15636</v>
+        <v>-15617</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.3%</t>
+          <t>-87.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+66.0%</t>
+          <t>+65.8%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>299447</v>
+        <v>382919</v>
       </c>
       <c r="E4" t="n">
-        <v>96968</v>
+        <v>102367</v>
       </c>
       <c r="F4" t="n">
-        <v>202479</v>
+        <v>280552</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>246432</v>
+        <v>248888</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+21.5%</t>
+          <t>+53.9%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>135996</v>
+        <v>138367</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+48.9%</t>
+          <t>+102.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>132197</v>
+        <v>176035</v>
       </c>
       <c r="E5" t="n">
-        <v>136695</v>
+        <v>176695</v>
       </c>
       <c r="F5" t="n">
-        <v>-4498</v>
+        <v>-660</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>236399</v>
+        <v>241463</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>167164</v>
+        <v>135411</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-102.7%</t>
+          <t>-100.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>359335</v>
+        <v>370755</v>
       </c>
       <c r="E6" t="n">
-        <v>36387</v>
+        <v>37549</v>
       </c>
       <c r="F6" t="n">
-        <v>322947</v>
+        <v>333205</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>180311</v>
+        <v>196886</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+99.3%</t>
+          <t>+88.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>133617</v>
+        <v>148288</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+141.7%</t>
+          <t>+124.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>231947</v>
+        <v>253168</v>
       </c>
       <c r="E7" t="n">
-        <v>62463</v>
+        <v>62719</v>
       </c>
       <c r="F7" t="n">
-        <v>169484</v>
+        <v>190449</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>187591</v>
+        <v>192995</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>+31.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>149146</v>
+        <v>154494</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+23.3%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>206042</v>
+        <v>278809</v>
       </c>
       <c r="E8" t="n">
-        <v>73425</v>
+        <v>73780</v>
       </c>
       <c r="F8" t="n">
-        <v>132617</v>
+        <v>205029</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>189162</v>
+        <v>213450</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+8.9%</t>
+          <t>+30.6%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>163218</v>
+        <v>185747</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>+10.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>534687</v>
+        <v>551647</v>
       </c>
       <c r="E9" t="n">
-        <v>170300</v>
+        <v>176900</v>
       </c>
       <c r="F9" t="n">
-        <v>364387</v>
+        <v>374747</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>411931</v>
+        <v>555848</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+29.8%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>328557</v>
+        <v>418924</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+10.9%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>906375</v>
+        <v>920186</v>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>1308</v>
       </c>
       <c r="F10" t="n">
-        <v>906067</v>
+        <v>918878</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>753225</v>
+        <v>812095</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+20.3%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>753225</v>
+        <v>812095</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+20.3%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>340223</v>
+        <v>364346</v>
       </c>
       <c r="P10" t="n">
-        <v>565844</v>
+        <v>554532</v>
       </c>
       <c r="Q10" t="n">
-        <v>844475</v>
+        <v>857490</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>143638</v>
+        <v>157851</v>
       </c>
       <c r="E11" t="n">
         <v>26399</v>
       </c>
       <c r="F11" t="n">
-        <v>117238</v>
+        <v>131451</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>128403</v>
+        <v>139100</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+11.9%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>103594</v>
+        <v>113992</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+15.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>18454</v>
+        <v>18852</v>
       </c>
       <c r="P11" t="n">
-        <v>98574</v>
+        <v>112389</v>
       </c>
       <c r="Q11" t="n">
-        <v>75660</v>
+        <v>78479</v>
       </c>
     </row>
     <row r="12">
@@ -1104,23 +1104,23 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>281083</v>
+        <v>288179</v>
       </c>
       <c r="E12" t="n">
-        <v>23057</v>
+        <v>23076</v>
       </c>
       <c r="F12" t="n">
-        <v>258026</v>
+        <v>265103</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+88.2%</t>
+          <t>+93.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1136,18 +1136,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+75.1%</t>
+          <t>+79.9%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>53163</v>
+        <v>54862</v>
       </c>
       <c r="P12" t="n">
-        <v>204863</v>
+        <v>210241</v>
       </c>
       <c r="Q12" t="n">
-        <v>19814</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>309747</v>
+        <v>326952</v>
       </c>
       <c r="E13" t="n">
-        <v>25927</v>
+        <v>44927</v>
       </c>
       <c r="F13" t="n">
-        <v>283819</v>
+        <v>282025</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>250625</v>
+        <v>252023</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>+29.7%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>191064</v>
+        <v>192462</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+48.5%</t>
+          <t>+46.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6816</v>
+        <v>7322</v>
       </c>
       <c r="O13" t="n">
-        <v>13899</v>
+        <v>12718</v>
       </c>
       <c r="P13" t="n">
-        <v>263104</v>
+        <v>261984</v>
       </c>
       <c r="Q13" t="n">
-        <v>13945</v>
+        <v>16351</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>147271</v>
+        <v>137761</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>132405</v>
+        <v>122895</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>119413</v>
+        <v>130509</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+23.3%</t>
+          <t>+5.6%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>101835</v>
+        <v>112931</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+30.0%</t>
+          <t>+8.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>9842</v>
+        <v>9934</v>
       </c>
       <c r="O14" t="n">
         <v>49467</v>
       </c>
       <c r="P14" t="n">
-        <v>73096</v>
+        <v>63494</v>
       </c>
       <c r="Q14" t="n">
-        <v>19633</v>
+        <v>19725</v>
       </c>
     </row>
     <row r="15">
@@ -1291,39 +1291,39 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98100</v>
+        <v>98498</v>
       </c>
       <c r="E15" t="n">
         <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>82224</v>
+        <v>82622</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>128497</v>
+        <v>130575</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>113191</v>
+        <v>115269</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1331,7 +1331,7 @@
         <v>6697</v>
       </c>
       <c r="P15" t="n">
-        <v>75527</v>
+        <v>75925</v>
       </c>
       <c r="Q15" t="n">
         <v>36442</v>
@@ -1352,23 +1352,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>197885</v>
+        <v>215302</v>
       </c>
       <c r="E16" t="n">
-        <v>398</v>
+        <v>9198</v>
       </c>
       <c r="F16" t="n">
-        <v>197487</v>
+        <v>206104</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+158.0%</t>
+          <t>+180.8%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1384,18 +1384,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+197.0%</t>
+          <t>+210.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>16317</v>
+        <v>7536</v>
       </c>
       <c r="P16" t="n">
-        <v>181170</v>
+        <v>198568</v>
       </c>
       <c r="Q16" t="n">
-        <v>41011</v>
+        <v>41030</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>229924</v>
+        <v>288920</v>
       </c>
       <c r="E17" t="n">
-        <v>46658</v>
+        <v>48658</v>
       </c>
       <c r="F17" t="n">
-        <v>183266</v>
+        <v>240262</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>206992</v>
+        <v>235988</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+11.1%</t>
+          <t>+22.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>181126</v>
+        <v>200122</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+20.1%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>19928</v>
+        <v>43128</v>
       </c>
       <c r="O17" t="n">
-        <v>3266</v>
+        <v>3664</v>
       </c>
       <c r="P17" t="n">
-        <v>160072</v>
+        <v>193670</v>
       </c>
       <c r="Q17" t="n">
-        <v>-15593</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="18">
@@ -1476,52 +1476,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>632424</v>
+        <v>677602</v>
       </c>
       <c r="E18" t="n">
-        <v>19675</v>
+        <v>26275</v>
       </c>
       <c r="F18" t="n">
-        <v>612749</v>
+        <v>651327</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>333091</v>
+        <v>345010</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+89.9%</t>
+          <t>+96.4%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>297535</v>
+        <v>293454</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+105.9%</t>
+          <t>+122.0%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>188708</v>
+        <v>210706</v>
       </c>
       <c r="P18" t="n">
-        <v>423191</v>
+        <v>439771</v>
       </c>
       <c r="Q18" t="n">
-        <v>393949</v>
+        <v>395929</v>
       </c>
     </row>
     <row r="19">
@@ -1539,52 +1539,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>161943</v>
+        <v>193126</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>161919</v>
+        <v>193102</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>131454</v>
+        <v>172852</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+23.2%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-14543</v>
+        <v>26854</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-1213.3%</t>
+          <t>+619.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7220</v>
+        <v>7583</v>
       </c>
       <c r="O19" t="n">
-        <v>28507</v>
+        <v>28227</v>
       </c>
       <c r="P19" t="n">
-        <v>126392</v>
+        <v>157492</v>
       </c>
       <c r="Q19" t="n">
-        <v>24243</v>
+        <v>24326</v>
       </c>
     </row>
     <row r="20">
@@ -1602,50 +1602,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>250143</v>
+        <v>260702</v>
       </c>
       <c r="E20" t="n">
-        <v>40832</v>
+        <v>40870</v>
       </c>
       <c r="F20" t="n">
-        <v>209311</v>
+        <v>219832</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>254036</v>
+        <v>299636</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>240236</v>
+        <v>243636</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>85081</v>
+        <v>85204</v>
       </c>
       <c r="P20" t="n">
-        <v>124230</v>
+        <v>134628</v>
       </c>
       <c r="Q20" t="n">
-        <v>36035</v>
+        <v>36158</v>
       </c>
     </row>
     <row r="21">
@@ -1663,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>5424529</v>
+        <v>5894973</v>
       </c>
       <c r="E21" t="n">
-        <v>887147</v>
+        <v>988948</v>
       </c>
       <c r="F21" t="n">
-        <v>4537381</v>
+        <v>4906024</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4133298</v>
+        <v>4568569</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+31.2%</t>
+          <t>+29.0%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3247422</v>
+        <v>3515006</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+39.7%</t>
+          <t>+39.6%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>44867</v>
+        <v>69028</v>
       </c>
       <c r="O21" t="n">
-        <v>2100955</v>
+        <v>2331580</v>
       </c>
       <c r="P21" t="n">
-        <v>2391758</v>
+        <v>2505815</v>
       </c>
       <c r="Q21" t="n">
-        <v>2499478</v>
+        <v>2666233</v>
       </c>
     </row>
   </sheetData>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D2" t="n">
-        <v>402.5</v>
+        <v>1208.2</v>
       </c>
       <c r="E2" t="n">
-        <v>60710</v>
+        <v>112162</v>
       </c>
     </row>
     <row r="3">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>30.1</v>
+        <v>533.3</v>
       </c>
       <c r="E3" t="n">
-        <v>139</v>
+        <v>883</v>
       </c>
     </row>
     <row r="4">
@@ -1799,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>607</v>
+        <v>534</v>
       </c>
       <c r="C4" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D4" t="n">
-        <v>1162.6</v>
+        <v>1484.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3500</v>
+        <v>2622</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1050456</v>
+        <v>1239184</v>
       </c>
       <c r="D2" t="n">
-        <v>-23786</v>
+        <v>-23320</v>
       </c>
       <c r="E2" t="n">
-        <v>816459</v>
+        <v>931639</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>258107</v>
+        <v>261507</v>
       </c>
       <c r="D3" t="n">
-        <v>106280</v>
+        <v>113240</v>
       </c>
       <c r="E3" t="n">
-        <v>194171</v>
+        <v>194531</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>803783</v>
+        <v>842280</v>
       </c>
       <c r="D4" t="n">
-        <v>2296064</v>
+        <v>2402695</v>
       </c>
       <c r="E4" t="n">
-        <v>1489617</v>
+        <v>1540832</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>218238</v>
+        <v>221818</v>
       </c>
       <c r="D5" t="n">
-        <v>1037</v>
+        <v>1086</v>
       </c>
       <c r="E5" t="n">
-        <v>209275</v>
+        <v>212506</v>
       </c>
     </row>
     <row r="6">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15771</v>
+        <v>-15752</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-5636</v>
+        <v>-5617</v>
       </c>
     </row>
     <row r="7">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>208468</v>
+        <v>286522</v>
       </c>
       <c r="D7" t="n">
-        <v>-5989</v>
+        <v>-5970</v>
       </c>
       <c r="E7" t="n">
-        <v>211193</v>
+        <v>277266</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-5886</v>
+        <v>-2048</v>
       </c>
       <c r="D8" t="n">
         <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-43318</v>
+        <v>-78300</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>316040</v>
+        <v>326298</v>
       </c>
       <c r="D9" t="n">
         <v>6907</v>
       </c>
       <c r="E9" t="n">
-        <v>255155</v>
+        <v>265413</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>167785</v>
+        <v>188750</v>
       </c>
       <c r="D10" t="n">
         <v>1699</v>
       </c>
       <c r="E10" t="n">
-        <v>67570</v>
+        <v>88535</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>161580</v>
+        <v>233594</v>
       </c>
       <c r="D11" t="n">
-        <v>-28963</v>
+        <v>-28565</v>
       </c>
       <c r="E11" t="n">
-        <v>122219</v>
+        <v>171835</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>258107</v>
+        <v>261507</v>
       </c>
       <c r="D12" t="n">
-        <v>106280</v>
+        <v>113240</v>
       </c>
       <c r="E12" t="n">
-        <v>194171</v>
+        <v>194531</v>
       </c>
     </row>
     <row r="13">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>340223</v>
+        <v>364346</v>
       </c>
       <c r="D13" t="n">
-        <v>565844</v>
+        <v>554532</v>
       </c>
       <c r="E13" t="n">
-        <v>844475</v>
+        <v>857490</v>
       </c>
     </row>
     <row r="14">
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18454</v>
+        <v>18852</v>
       </c>
       <c r="D14" t="n">
-        <v>98574</v>
+        <v>112389</v>
       </c>
       <c r="E14" t="n">
-        <v>75660</v>
+        <v>78479</v>
       </c>
     </row>
     <row r="15">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53163</v>
+        <v>54862</v>
       </c>
       <c r="D15" t="n">
-        <v>204863</v>
+        <v>210241</v>
       </c>
       <c r="E15" t="n">
-        <v>19814</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="16">
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13899</v>
+        <v>12718</v>
       </c>
       <c r="D16" t="n">
-        <v>263104</v>
+        <v>261984</v>
       </c>
       <c r="E16" t="n">
-        <v>13945</v>
+        <v>16351</v>
       </c>
     </row>
     <row r="17">
@@ -2182,10 +2182,10 @@
         <v>49467</v>
       </c>
       <c r="D17" t="n">
-        <v>73096</v>
+        <v>63494</v>
       </c>
       <c r="E17" t="n">
-        <v>19633</v>
+        <v>19725</v>
       </c>
     </row>
     <row r="18">
@@ -2203,7 +2203,7 @@
         <v>6697</v>
       </c>
       <c r="D18" t="n">
-        <v>75527</v>
+        <v>75925</v>
       </c>
       <c r="E18" t="n">
         <v>36442</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16317</v>
+        <v>7536</v>
       </c>
       <c r="D19" t="n">
-        <v>181170</v>
+        <v>198568</v>
       </c>
       <c r="E19" t="n">
-        <v>41011</v>
+        <v>41030</v>
       </c>
     </row>
     <row r="20">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3266</v>
+        <v>3664</v>
       </c>
       <c r="D20" t="n">
-        <v>160072</v>
+        <v>193670</v>
       </c>
       <c r="E20" t="n">
-        <v>-15593</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>188708</v>
+        <v>210706</v>
       </c>
       <c r="D21" t="n">
-        <v>423191</v>
+        <v>439771</v>
       </c>
       <c r="E21" t="n">
-        <v>393949</v>
+        <v>395929</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28507</v>
+        <v>28227</v>
       </c>
       <c r="D22" t="n">
-        <v>126392</v>
+        <v>157492</v>
       </c>
       <c r="E22" t="n">
-        <v>24243</v>
+        <v>24326</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85081</v>
+        <v>85204</v>
       </c>
       <c r="D23" t="n">
-        <v>124230</v>
+        <v>134628</v>
       </c>
       <c r="E23" t="n">
-        <v>36035</v>
+        <v>36158</v>
       </c>
     </row>
     <row r="24">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2100955</v>
+        <v>2331580</v>
       </c>
       <c r="D25" t="n">
-        <v>2391758</v>
+        <v>2505815</v>
       </c>
       <c r="E25" t="n">
-        <v>2499478</v>
+        <v>2666233</v>
       </c>
     </row>
   </sheetData>
@@ -2437,31 +2437,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>116840</v>
+        <v>119400</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>8366.66</v>
+        <v>13346.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>108473.34</v>
+        <v>106053.34</v>
       </c>
     </row>
     <row r="3">
@@ -2521,31 +2521,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>26400</v>
+        <v>31778</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>28380</v>
+        <v>33360</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1980</v>
+        <v>-1582</v>
       </c>
     </row>
     <row r="5">
@@ -2647,19 +2647,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>59800</v>
+        <v>69760</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>58.1%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>49.8%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>41.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2667,11 +2667,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>49800</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="8">
@@ -2731,19 +2731,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>14940</v>
+        <v>29880</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9961</v>
+        <v>24901</v>
       </c>
     </row>
     <row r="10">
@@ -2773,19 +2773,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>51858</v>
+        <v>77196</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>47878</v>
+        <v>73216</v>
       </c>
     </row>
     <row r="11">
@@ -2815,19 +2815,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>38160</v>
+        <v>60518</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2835,11 +2835,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>34180</v>
+        <v>56538</v>
       </c>
     </row>
     <row r="12">
@@ -2899,19 +2899,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>130418</v>
+        <v>135398</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>163.0%</t>
+          <t>169.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>163.0%</t>
+          <t>169.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>130418</v>
+        <v>135398</v>
       </c>
     </row>
     <row r="14">
@@ -3025,19 +3025,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>47758</v>
+        <v>49738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3045,11 +3045,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>41158</v>
+        <v>43138</v>
       </c>
     </row>
     <row r="17">
@@ -3193,19 +3193,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>41220</v>
+        <v>51220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>41220</v>
+        <v>51220</v>
       </c>
     </row>
     <row r="21">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>57580</v>
+        <v>50980</v>
       </c>
     </row>
     <row r="24">
@@ -3445,31 +3445,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>70376</v>
+        <v>107276</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9786</v>
+        <v>13766</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>60590</v>
+        <v>93510</v>
       </c>
     </row>
     <row r="27">
@@ -3487,19 +3487,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>24900</v>
+        <v>29880</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>24900</v>
+        <v>29880</v>
       </c>
     </row>
     <row r="28">
@@ -3529,19 +3529,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>14940</v>
+        <v>24900</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3549,11 +3549,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>-3660</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="29">
@@ -3571,19 +3571,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>34860</v>
+        <v>49800</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3591,11 +3591,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>25900</v>
+        <v>40840</v>
       </c>
     </row>
     <row r="30">
@@ -3613,19 +3613,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>47800</v>
+        <v>62740</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>35800</v>
+        <v>50740</v>
       </c>
     </row>
     <row r="31">
@@ -3655,19 +3655,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>148204</v>
+        <v>150694</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>101324</v>
+        <v>103814</v>
       </c>
     </row>
     <row r="32">
@@ -3739,19 +3739,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>47422</v>
+        <v>52402</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37462</v>
+        <v>42442</v>
       </c>
     </row>
     <row r="34">
@@ -3781,19 +3781,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>57619</v>
+        <v>62599</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54019</v>
+        <v>58999</v>
       </c>
     </row>
     <row r="35">
@@ -3865,19 +3865,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>60638</v>
+        <v>62318</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>56658</v>
+        <v>58338</v>
       </c>
     </row>
     <row r="37">
@@ -3949,19 +3949,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>44520</v>
+        <v>83340</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3969,11 +3969,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>214.5%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-50988</v>
+        <v>-12168</v>
       </c>
     </row>
     <row r="39">
@@ -3991,19 +3991,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>75548</v>
+        <v>80528</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4011,11 +4011,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71760</v>
+        <v>76740</v>
       </c>
     </row>
     <row r="40">
@@ -4075,19 +4075,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>18920</v>
+        <v>28880</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>17240</v>
+        <v>27200</v>
       </c>
     </row>
   </sheetData>
@@ -4173,23 +4173,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>130768.2</v>
+        <v>146448.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22866.67</v>
+        <v>39866.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>107901.53</v>
+        <v>106581.53</v>
       </c>
     </row>
     <row r="3">
@@ -4241,11 +4241,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48596</v>
+        <v>49902.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>48596</v>
+        <v>49902.6</v>
       </c>
     </row>
     <row r="5">
@@ -4377,11 +4377,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26035.41</v>
+        <v>36035.41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26035.41</v>
+        <v>36035.41</v>
       </c>
     </row>
     <row r="9">
@@ -4411,11 +4411,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>22476.03</v>
+        <v>32838.64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22276.03</v>
+        <v>32638.64</v>
       </c>
     </row>
     <row r="10">
@@ -4445,11 +4445,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>46266.7</v>
+        <v>54266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>46266.7</v>
+        <v>54266.7</v>
       </c>
     </row>
     <row r="11">
@@ -4479,11 +4479,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>8600</v>
+        <v>11700</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8600</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="12">
@@ -4615,23 +4615,23 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>24188</v>
+        <v>36188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>398</v>
+        <v>9198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>23790</v>
+        <v>26990</v>
       </c>
     </row>
     <row r="16">
@@ -4649,11 +4649,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>74190</v>
+        <v>74588</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>74190</v>
+        <v>74588</v>
       </c>
     </row>
     <row r="17">
@@ -4683,11 +4683,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>13788</v>
+        <v>18788</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>13788</v>
+        <v>18788</v>
       </c>
     </row>
     <row r="18">
@@ -4785,7 +4785,7 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>74747.8</v>
+        <v>74839.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4797,11 +4797,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70747.8</v>
+        <v>70839.8</v>
       </c>
     </row>
     <row r="21">
@@ -4819,11 +4819,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>18318</v>
+        <v>8716</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>18318</v>
+        <v>8716</v>
       </c>
     </row>
     <row r="22">
@@ -4989,11 +4989,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>21154</v>
+        <v>31154</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>21154</v>
+        <v>31154</v>
       </c>
     </row>
     <row r="27">
@@ -5023,11 +5023,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24058</v>
+        <v>24456</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24058</v>
+        <v>24456</v>
       </c>
     </row>
     <row r="28">
@@ -5057,11 +5057,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>13394</v>
+        <v>14390</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5069,11 +5069,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>144.8%</t>
+          <t>134.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-6005.98</v>
+        <v>-5009.98</v>
       </c>
     </row>
     <row r="29">
@@ -5091,11 +5091,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>80382</v>
+        <v>83580</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>73382</v>
+        <v>76580</v>
       </c>
     </row>
     <row r="30">
@@ -5125,11 +5125,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>16176</v>
+        <v>26176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16176</v>
+        <v>26176</v>
       </c>
     </row>
     <row r="31">
@@ -5261,11 +5261,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>77529.84999999999</v>
+        <v>85529.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5273,11 +5273,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>71529.84999999999</v>
+        <v>79529.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5295,11 +5295,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>45488.92</v>
+        <v>55488.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5307,11 +5307,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>38888.92</v>
+        <v>48888.92</v>
       </c>
     </row>
     <row r="36">
@@ -5329,23 +5329,23 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>10996</v>
+        <v>42192</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10996</v>
+        <v>41992</v>
       </c>
     </row>
     <row r="37">
@@ -5397,11 +5397,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>897</v>
+        <v>10897</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>897</v>
+        <v>10897</v>
       </c>
     </row>
     <row r="39">
@@ -5465,23 +5465,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>380238</v>
+        <v>425416</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>12000</v>
+        <v>18600</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>368238</v>
+        <v>406816</v>
       </c>
     </row>
     <row r="41">
@@ -5669,11 +5669,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>1980</v>
+        <v>5078</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1980</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="47">
@@ -5703,11 +5703,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>139540</v>
+        <v>126544</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>139540</v>
+        <v>126544</v>
       </c>
     </row>
     <row r="48">
@@ -5873,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>196419</v>
+        <v>198311</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>196419</v>
+        <v>198311</v>
       </c>
     </row>
     <row r="53">
@@ -5941,11 +5941,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>167022</v>
+        <v>167420</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>167022</v>
+        <v>167420</v>
       </c>
     </row>
     <row r="55">
@@ -6009,11 +6009,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>30796</v>
+        <v>31194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6021,11 +6021,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>25796</v>
+        <v>26194</v>
       </c>
     </row>
     <row r="57">
@@ -6077,11 +6077,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>10000</v>
+        <v>16660</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>10000</v>
+        <v>16660</v>
       </c>
     </row>
     <row r="59">
@@ -6179,11 +6179,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>26970</v>
+        <v>27368</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>26970</v>
+        <v>27368</v>
       </c>
     </row>
     <row r="62">
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1215526.8</v>
+        <v>1407282.8</v>
       </c>
       <c r="D2" t="n">
-        <v>6721</v>
+        <v>7245</v>
       </c>
       <c r="E2" t="n">
-        <v>1076088.8</v>
+        <v>1252909.8</v>
       </c>
       <c r="F2" t="n">
-        <v>139438</v>
+        <v>154373</v>
       </c>
     </row>
     <row r="3">
@@ -6348,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1031938</v>
+        <v>1208750</v>
       </c>
       <c r="D3" t="n">
-        <v>303</v>
+        <v>342</v>
       </c>
       <c r="E3" t="n">
-        <v>906354</v>
+        <v>1068207</v>
       </c>
       <c r="F3" t="n">
-        <v>125584</v>
+        <v>140543</v>
       </c>
     </row>
     <row r="4">
@@ -6372,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>183588.8</v>
+        <v>198532.8</v>
       </c>
       <c r="D4" t="n">
-        <v>6418</v>
+        <v>6903</v>
       </c>
       <c r="E4" t="n">
-        <v>169734.8</v>
+        <v>184702.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13854</v>
+        <v>13830</v>
       </c>
     </row>
     <row r="5">
@@ -6396,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2285822</v>
+        <v>2528510</v>
       </c>
       <c r="D5" t="n">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="E5" t="n">
-        <v>471926</v>
+        <v>555940</v>
       </c>
       <c r="F5" t="n">
-        <v>1813896</v>
+        <v>1972570</v>
       </c>
     </row>
     <row r="6">
@@ -6420,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1507918</v>
+        <v>1639996</v>
       </c>
       <c r="D6" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="E6" t="n">
-        <v>14820</v>
+        <v>15218</v>
       </c>
       <c r="F6" t="n">
-        <v>1493098</v>
+        <v>1624778</v>
       </c>
     </row>
     <row r="7">
@@ -6444,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>777904</v>
+        <v>878514</v>
       </c>
       <c r="D7" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="E7" t="n">
-        <v>457106</v>
+        <v>540722</v>
       </c>
       <c r="F7" t="n">
-        <v>320798</v>
+        <v>337792</v>
       </c>
     </row>
     <row r="8">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>889900.38</v>
+        <v>963712.97</v>
       </c>
       <c r="D8" t="n">
-        <v>1023</v>
+        <v>1288</v>
       </c>
       <c r="E8" t="n">
-        <v>14807.22</v>
+        <v>15890.21</v>
       </c>
       <c r="F8" t="n">
-        <v>875093.16</v>
+        <v>947822.76</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>547015.98</v>
+        <v>578574.4</v>
       </c>
       <c r="D9" t="n">
-        <v>453</v>
+        <v>571</v>
       </c>
       <c r="E9" t="n">
-        <v>2993.86</v>
+        <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>544022.12</v>
+        <v>575531.54</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>342884.4</v>
+        <v>385138.57</v>
       </c>
       <c r="D10" t="n">
-        <v>570</v>
+        <v>717</v>
       </c>
       <c r="E10" t="n">
-        <v>11813.36</v>
+        <v>12847.35</v>
       </c>
       <c r="F10" t="n">
-        <v>331071.04</v>
+        <v>372291.22</v>
       </c>
     </row>
     <row r="11">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>305400</v>
+        <v>306400</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>182400</v>
+        <v>183400</v>
       </c>
     </row>
     <row r="12">
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99000</v>
+        <v>102960</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>13860</v>
+        <v>15840</v>
       </c>
       <c r="F14" t="n">
-        <v>85140</v>
+        <v>87120</v>
       </c>
     </row>
     <row r="15">
@@ -6636,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69774</v>
+        <v>27001.61</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
       </c>
       <c r="F15" t="n">
-        <v>63237.64</v>
+        <v>20465.25</v>
       </c>
     </row>
   </sheetData>
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1215526.8</v>
+        <v>1407282.8</v>
       </c>
       <c r="C2" t="n">
-        <v>260999.06</v>
+        <v>292000.06</v>
       </c>
       <c r="D2" t="n">
-        <v>21388</v>
+        <v>28577</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="F2" t="n">
-        <v>239611.06</v>
+        <v>263423.06</v>
       </c>
       <c r="G2" t="n">
-        <v>19.71</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="3">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2285822</v>
+        <v>2528510</v>
       </c>
       <c r="C3" t="n">
-        <v>247918.98</v>
+        <v>278718.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>247918.98</v>
+        <v>278718.98</v>
       </c>
       <c r="G3" t="n">
-        <v>10.85</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="4">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>889900.38</v>
+        <v>963712.97</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6771,7 +6771,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="5">
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>305400</v>
+        <v>306400</v>
       </c>
       <c r="C5" t="n">
         <v>70400</v>
@@ -6796,7 +6796,7 @@
         <v>70400</v>
       </c>
       <c r="G5" t="n">
-        <v>23.05</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="6">
@@ -6809,7 +6809,7 @@
         <v>291765.9</v>
       </c>
       <c r="C6" t="n">
-        <v>98913.89999999999</v>
+        <v>138913.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6818,10 +6818,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>96896</v>
+        <v>136896</v>
       </c>
       <c r="G6" t="n">
-        <v>33.21</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="7">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>99000</v>
+        <v>102960</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69774</v>
+        <v>27001.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -6910,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>318</v>
+        <v>360</v>
       </c>
       <c r="C2" t="n">
-        <v>512809.65</v>
+        <v>596802.65</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>428</v>
+        <v>461</v>
       </c>
       <c r="C3" t="n">
-        <v>232636.4</v>
+        <v>238584.4</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>61383</v>
+        <v>66363</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>28000</v>
+        <v>33000</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C6" t="n">
-        <v>16608.66</v>
+        <v>16719.66</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -7038,13 +7038,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>11241.9</v>
+        <v>12953.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>9607</v>
+        <v>9645</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -7092,6 +7092,22 @@
         <v>95</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>商家操作失误</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7106,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7143,10 +7159,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>141200</v>
+        <v>147800</v>
       </c>
     </row>
     <row r="3">
@@ -7229,14 +7245,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>85493</v>
+        <v>91127</v>
       </c>
     </row>
     <row r="8">
@@ -7247,14 +7263,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>51127</v>
+        <v>85493</v>
       </c>
     </row>
     <row r="9">
@@ -7323,10 +7339,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>48249</v>
+        <v>52273</v>
       </c>
     </row>
     <row r="13">
@@ -7359,10 +7375,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D14" t="n">
-        <v>17543</v>
+        <v>17581</v>
       </c>
     </row>
     <row r="15">
@@ -7377,10 +7393,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>4157</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="16">
@@ -7391,14 +7407,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>2490</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="17">
@@ -7409,14 +7425,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2097</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="18">
@@ -7431,10 +7447,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>609</v>
+        <v>628</v>
       </c>
     </row>
     <row r="19">
@@ -7458,61 +7474,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>61932</v>
+        <v>26563</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>10742</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="D22" t="n">
-        <v>362</v>
+        <v>20620.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7521,28 +7537,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D23" t="n">
-        <v>247</v>
+        <v>7576.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>142</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
@@ -7553,14 +7569,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>21479</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -7571,14 +7587,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20188.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27">
@@ -7589,14 +7605,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>16800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -7607,104 +7623,104 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>7519.66</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>62231</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="D30" t="n">
-        <v>57</v>
+        <v>10798</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>362</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>57836</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34">
@@ -7715,14 +7731,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D34" t="n">
-        <v>3579</v>
+        <v>57940</v>
       </c>
     </row>
     <row r="35">
@@ -7733,14 +7749,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>598</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="36">
@@ -7751,14 +7767,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>356</v>
+        <v>598</v>
       </c>
     </row>
     <row r="37">
@@ -7769,14 +7785,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>56</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38">
@@ -7787,32 +7803,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>36400</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -7823,14 +7839,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>10000</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="41">
@@ -7841,14 +7857,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="42">
@@ -7859,14 +7875,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43">
@@ -7877,7 +7893,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -7890,91 +7906,91 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>31309</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D45" t="n">
-        <v>9000</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>285</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>124</v>
+        <v>4634</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>57</v>
+        <v>299</v>
       </c>
     </row>
     <row r="49">
@@ -7985,56 +8001,56 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>57</v>
+        <v>31309</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>19630.9</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>12095</v>
+        <v>304</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8043,16 +8059,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>3820</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8061,16 +8077,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>595</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8079,10 +8095,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>171</v>
+        <v>57</v>
       </c>
     </row>
     <row r="55">
@@ -8093,14 +8109,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="D55" t="n">
-        <v>38</v>
+        <v>20157.9</v>
       </c>
     </row>
     <row r="56">
@@ -8111,14 +8127,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>12320</v>
       </c>
     </row>
     <row r="57">
@@ -8129,176 +8145,176 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D58" t="n">
-        <v>18399.98</v>
+        <v>951</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>8000</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>20994.67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>4500</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>299</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>134</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D64" t="n">
-        <v>15009</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>8000</v>
+        <v>26218</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67">
@@ -8309,68 +8325,68 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>19618</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>38</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>10000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
@@ -8381,14 +8397,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>6289</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="72">
@@ -8399,32 +8415,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>1328</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>9000</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="74">
@@ -8435,14 +8451,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>6800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="75">
@@ -8453,32 +8469,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>76</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>9318</v>
+        <v>76</v>
       </c>
     </row>
     <row r="77">
@@ -8489,14 +8505,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>5500</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="78">
@@ -8507,14 +8523,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>29</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="79">
@@ -8525,32 +8541,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>10621</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
@@ -8561,85 +8577,139 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>2490</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>398</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>299</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>9</v>
+        <v>398</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="C88" t="n">
         <v>3</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D88" t="n">
         <v>24</v>
       </c>
     </row>
@@ -8677,66 +8747,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>分享咨询</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>201866.67</v>
+        <v>225197.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>分享咨询</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>194397.98</v>
+        <v>201866.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>113675.16</v>
+        <v>133108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>95760</v>
+        <v>127615.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>93108</v>
+        <v>102360</v>
       </c>
     </row>
     <row r="7">
@@ -8772,10 +8842,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>13200</v>
+        <v>19800</v>
       </c>
     </row>
     <row r="10">
@@ -8785,10 +8855,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>750</v>
+        <v>829</v>
       </c>
       <c r="C10" t="n">
-        <v>13031</v>
+        <v>14416</v>
       </c>
     </row>
     <row r="11">
@@ -8842,10 +8912,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="C2" t="n">
-        <v>152210.33</v>
+        <v>176437.33</v>
       </c>
     </row>
     <row r="3">
@@ -8855,10 +8925,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>96315.5</v>
+        <v>138315.5</v>
       </c>
     </row>
     <row r="4">
@@ -8868,10 +8938,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C4" t="n">
-        <v>77452.98</v>
+        <v>88184.98</v>
       </c>
     </row>
     <row r="5">
@@ -8881,10 +8951,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>77096</v>
+        <v>79229</v>
       </c>
     </row>
     <row r="6">
@@ -8894,10 +8964,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
-        <v>68184</v>
+        <v>69540</v>
       </c>
     </row>
     <row r="7">
@@ -8907,10 +8977,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>55686</v>
+        <v>55705</v>
       </c>
     </row>
     <row r="8">
@@ -8933,49 +9003,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C9" t="n">
-        <v>51354</v>
+        <v>51804</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>37200</v>
+        <v>49088</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>36174</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C12" t="n">
-        <v>35197</v>
+        <v>36297</v>
       </c>
     </row>
     <row r="13">
@@ -9011,10 +9081,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
-        <v>15249</v>
+        <v>15277</v>
       </c>
     </row>
     <row r="16">
@@ -9024,10 +9094,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n">
-        <v>14048.9</v>
+        <v>14073.9</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>299635</v>
+        <v>311994</v>
       </c>
       <c r="E2" t="n">
-        <v>76730</v>
+        <v>81919</v>
       </c>
       <c r="F2" t="n">
-        <v>222904</v>
+        <v>230074</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>159638</v>
+        <v>164960</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+87.7%</t>
+          <t>+89.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>18549</v>
+        <v>23824</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+1101.7%</t>
+          <t>+865.7%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15606</v>
+        <v>15875</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.2%</t>
+          <t>-87.4%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-9417</v>
+        <v>-9148</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+65.8%</t>
+          <t>+70.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>382919</v>
+        <v>447037</v>
       </c>
       <c r="E4" t="n">
-        <v>102367</v>
+        <v>109639</v>
       </c>
       <c r="F4" t="n">
-        <v>280552</v>
+        <v>337398</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>248888</v>
+        <v>281079</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+53.9%</t>
+          <t>+59.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>138367</v>
+        <v>170388</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+102.8%</t>
+          <t>+98.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,13 +695,13 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176035</v>
+        <v>176054</v>
       </c>
       <c r="E5" t="n">
         <v>176695</v>
       </c>
       <c r="F5" t="n">
-        <v>-660</v>
+        <v>-641</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>241463</v>
+        <v>241492</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>135411</v>
+        <v>135440</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>370755</v>
+        <v>377840</v>
       </c>
       <c r="E6" t="n">
-        <v>37549</v>
+        <v>38414</v>
       </c>
       <c r="F6" t="n">
-        <v>333205</v>
+        <v>339425</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>196886</v>
+        <v>198707</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+88.3%</t>
+          <t>+90.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>148288</v>
+        <v>149310</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+124.7%</t>
+          <t>+127.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>253168</v>
+        <v>276079</v>
       </c>
       <c r="E7" t="n">
-        <v>62719</v>
+        <v>62823</v>
       </c>
       <c r="F7" t="n">
-        <v>190449</v>
+        <v>213256</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>192995</v>
+        <v>193460</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+31.2%</t>
+          <t>+42.7%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>154494</v>
+        <v>154893</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+23.3%</t>
+          <t>+37.7%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>278809</v>
+        <v>302771</v>
       </c>
       <c r="E8" t="n">
-        <v>73780</v>
+        <v>78005</v>
       </c>
       <c r="F8" t="n">
-        <v>205029</v>
+        <v>224766</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213450</v>
+        <v>213497</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+30.6%</t>
+          <t>+41.8%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>185747</v>
+        <v>185700</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+10.4%</t>
+          <t>+21.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>551647</v>
+        <v>598562</v>
       </c>
       <c r="E9" t="n">
-        <v>176900</v>
+        <v>215700</v>
       </c>
       <c r="F9" t="n">
-        <v>374747</v>
+        <v>382862</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>555848</v>
+        <v>575848</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>418924</v>
+        <v>438924</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>920186</v>
+        <v>931293</v>
       </c>
       <c r="E10" t="n">
-        <v>1308</v>
+        <v>11308</v>
       </c>
       <c r="F10" t="n">
-        <v>918878</v>
+        <v>919985</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>812095</v>
+        <v>896759</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>812095</v>
+        <v>896759</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+2.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>364346</v>
+        <v>364744</v>
       </c>
       <c r="P10" t="n">
-        <v>554532</v>
+        <v>555241</v>
       </c>
       <c r="Q10" t="n">
-        <v>857490</v>
+        <v>868597</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>157851</v>
+        <v>170748</v>
       </c>
       <c r="E11" t="n">
         <v>26399</v>
       </c>
       <c r="F11" t="n">
-        <v>131451</v>
+        <v>144348</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>139100</v>
+        <v>151364</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>113992</v>
+        <v>126256</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+15.3%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>18852</v>
+        <v>19749</v>
       </c>
       <c r="P11" t="n">
-        <v>112389</v>
+        <v>124389</v>
       </c>
       <c r="Q11" t="n">
-        <v>78479</v>
+        <v>78778</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>288179</v>
+        <v>323995</v>
       </c>
       <c r="E12" t="n">
         <v>23076</v>
       </c>
       <c r="F12" t="n">
-        <v>265103</v>
+        <v>300919</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>149314</v>
+        <v>180906</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+93.0%</t>
+          <t>+79.1%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>147335</v>
+        <v>178927</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+79.9%</t>
+          <t>+68.2%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>54862</v>
+        <v>55260</v>
       </c>
       <c r="P12" t="n">
-        <v>210241</v>
+        <v>245659</v>
       </c>
       <c r="Q12" t="n">
-        <v>26493</v>
+        <v>21513</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>326952</v>
+        <v>331040</v>
       </c>
       <c r="E13" t="n">
-        <v>44927</v>
+        <v>44984</v>
       </c>
       <c r="F13" t="n">
-        <v>282025</v>
+        <v>286055</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>252023</v>
+        <v>260338</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+29.7%</t>
+          <t>+27.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>192462</v>
+        <v>200777</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+46.5%</t>
+          <t>+42.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>7322</v>
+        <v>8188</v>
       </c>
       <c r="O13" t="n">
-        <v>12718</v>
+        <v>11909</v>
       </c>
       <c r="P13" t="n">
-        <v>261984</v>
+        <v>265958</v>
       </c>
       <c r="Q13" t="n">
-        <v>16351</v>
+        <v>19187</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>137761</v>
+        <v>139203</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>122895</v>
+        <v>124337</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>130509</v>
+        <v>164305</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>112931</v>
+        <v>146727</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+8.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>9934</v>
       </c>
       <c r="O14" t="n">
-        <v>49467</v>
+        <v>39913</v>
       </c>
       <c r="P14" t="n">
-        <v>63494</v>
+        <v>74490</v>
       </c>
       <c r="Q14" t="n">
-        <v>19725</v>
+        <v>19773</v>
       </c>
     </row>
     <row r="15">
@@ -1291,50 +1291,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98498</v>
+        <v>98915</v>
       </c>
       <c r="E15" t="n">
         <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>82622</v>
+        <v>83039</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>130575</v>
+        <v>132963</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>115269</v>
+        <v>117657</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>6697</v>
+        <v>6716</v>
       </c>
       <c r="P15" t="n">
-        <v>75925</v>
+        <v>76323</v>
       </c>
       <c r="Q15" t="n">
-        <v>36442</v>
+        <v>36461</v>
       </c>
     </row>
     <row r="16">
@@ -1352,50 +1352,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>215302</v>
+        <v>227151</v>
       </c>
       <c r="E16" t="n">
         <v>9198</v>
       </c>
       <c r="F16" t="n">
-        <v>206104</v>
+        <v>217953</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>76687</v>
+        <v>176061</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+180.8%</t>
+          <t>+29.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>66487</v>
+        <v>165861</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+210.0%</t>
+          <t>+31.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>7536</v>
+        <v>8968</v>
       </c>
       <c r="P16" t="n">
-        <v>198568</v>
+        <v>208985</v>
       </c>
       <c r="Q16" t="n">
-        <v>41030</v>
+        <v>41087</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>288920</v>
+        <v>290874</v>
       </c>
       <c r="E17" t="n">
         <v>48658</v>
       </c>
       <c r="F17" t="n">
-        <v>240262</v>
+        <v>242216</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>235988</v>
+        <v>249780</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+22.4%</t>
+          <t>+16.5%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>200122</v>
+        <v>213914</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+20.1%</t>
+          <t>+13.2%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>43128</v>
+        <v>43488</v>
       </c>
       <c r="O17" t="n">
         <v>3664</v>
       </c>
       <c r="P17" t="n">
-        <v>193670</v>
+        <v>195264</v>
       </c>
       <c r="Q17" t="n">
-        <v>8406</v>
+        <v>8766</v>
       </c>
     </row>
     <row r="18">
@@ -1476,52 +1476,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>677602</v>
+        <v>693057</v>
       </c>
       <c r="E18" t="n">
-        <v>26275</v>
+        <v>77975</v>
       </c>
       <c r="F18" t="n">
-        <v>651327</v>
+        <v>615082</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>345010</v>
+        <v>361173</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+96.4%</t>
+          <t>+91.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>293454</v>
+        <v>309617</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+122.0%</t>
+          <t>+98.7%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>210706</v>
+        <v>215263</v>
       </c>
       <c r="P18" t="n">
-        <v>439771</v>
+        <v>398969</v>
       </c>
       <c r="Q18" t="n">
-        <v>395929</v>
+        <v>364786</v>
       </c>
     </row>
     <row r="19">
@@ -1539,52 +1539,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>193126</v>
+        <v>183516</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="F19" t="n">
-        <v>193102</v>
+        <v>183454</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>172852</v>
+        <v>182415</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26854</v>
+        <v>36417</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+619.1%</t>
+          <t>+403.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7583</v>
+        <v>7655</v>
       </c>
       <c r="O19" t="n">
-        <v>28227</v>
+        <v>28507</v>
       </c>
       <c r="P19" t="n">
-        <v>157492</v>
+        <v>147492</v>
       </c>
       <c r="Q19" t="n">
-        <v>24326</v>
+        <v>24678</v>
       </c>
     </row>
     <row r="20">
@@ -1602,50 +1602,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>260702</v>
+        <v>263428</v>
       </c>
       <c r="E20" t="n">
-        <v>40870</v>
+        <v>47926</v>
       </c>
       <c r="F20" t="n">
-        <v>219832</v>
+        <v>215502</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>299636</v>
+        <v>314630</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>243636</v>
+        <v>258630</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>85204</v>
+        <v>85780</v>
       </c>
       <c r="P20" t="n">
-        <v>134628</v>
+        <v>129722</v>
       </c>
       <c r="Q20" t="n">
-        <v>36158</v>
+        <v>36336</v>
       </c>
     </row>
     <row r="21">
@@ -1663,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>5894973</v>
+        <v>6160484</v>
       </c>
       <c r="E21" t="n">
-        <v>988948</v>
+        <v>1114254</v>
       </c>
       <c r="F21" t="n">
-        <v>4906024</v>
+        <v>5046229</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4568569</v>
+        <v>4955620</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+29.0%</t>
+          <t>+24.3%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3515006</v>
+        <v>3900880</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+39.6%</t>
+          <t>+29.4%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>69028</v>
+        <v>70326</v>
       </c>
       <c r="O21" t="n">
-        <v>2331580</v>
+        <v>2425989</v>
       </c>
       <c r="P21" t="n">
-        <v>2505815</v>
+        <v>2550313</v>
       </c>
       <c r="Q21" t="n">
-        <v>2666233</v>
+        <v>2729084</v>
       </c>
     </row>
   </sheetData>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>441</v>
+        <v>321</v>
       </c>
       <c r="C2" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D2" t="n">
-        <v>1208.2</v>
+        <v>1203.6</v>
       </c>
       <c r="E2" t="n">
-        <v>112162</v>
+        <v>102202</v>
       </c>
     </row>
     <row r="3">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>533.3</v>
+        <v>849</v>
       </c>
       <c r="E3" t="n">
-        <v>883</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="4">
@@ -1799,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>534</v>
+        <v>640</v>
       </c>
       <c r="C4" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="D4" t="n">
-        <v>1484.2</v>
+        <v>1278.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2622</v>
+        <v>3130</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1239184</v>
+        <v>1327284</v>
       </c>
       <c r="D2" t="n">
-        <v>-23320</v>
+        <v>1379</v>
       </c>
       <c r="E2" t="n">
-        <v>931639</v>
+        <v>1016639</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>261507</v>
+        <v>269622</v>
       </c>
       <c r="D3" t="n">
         <v>113240</v>
       </c>
       <c r="E3" t="n">
-        <v>194531</v>
+        <v>193248</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>842280</v>
+        <v>840474</v>
       </c>
       <c r="D4" t="n">
-        <v>2402695</v>
+        <v>2422493</v>
       </c>
       <c r="E4" t="n">
-        <v>1540832</v>
+        <v>1519966</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>221818</v>
+        <v>233968</v>
       </c>
       <c r="D5" t="n">
-        <v>1086</v>
+        <v>-3894</v>
       </c>
       <c r="E5" t="n">
-        <v>212506</v>
+        <v>219676</v>
       </c>
     </row>
     <row r="6">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>286522</v>
+        <v>323667</v>
       </c>
       <c r="D7" t="n">
-        <v>-5970</v>
+        <v>13730</v>
       </c>
       <c r="E7" t="n">
-        <v>277266</v>
+        <v>314112</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2048</v>
+        <v>-2029</v>
       </c>
       <c r="D8" t="n">
         <v>1388</v>
       </c>
       <c r="E8" t="n">
-        <v>-78300</v>
+        <v>-78281</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>326298</v>
+        <v>332499</v>
       </c>
       <c r="D9" t="n">
-        <v>6907</v>
+        <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>265413</v>
+        <v>271633</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>188750</v>
+        <v>211557</v>
       </c>
       <c r="D10" t="n">
         <v>1699</v>
       </c>
       <c r="E10" t="n">
-        <v>88535</v>
+        <v>103542</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>233594</v>
+        <v>243371</v>
       </c>
       <c r="D11" t="n">
-        <v>-28565</v>
+        <v>-18605</v>
       </c>
       <c r="E11" t="n">
-        <v>171835</v>
+        <v>191572</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>261507</v>
+        <v>269622</v>
       </c>
       <c r="D12" t="n">
         <v>113240</v>
       </c>
       <c r="E12" t="n">
-        <v>194531</v>
+        <v>193248</v>
       </c>
     </row>
     <row r="13">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>364346</v>
+        <v>364744</v>
       </c>
       <c r="D13" t="n">
-        <v>554532</v>
+        <v>555241</v>
       </c>
       <c r="E13" t="n">
-        <v>857490</v>
+        <v>868597</v>
       </c>
     </row>
     <row r="14">
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18852</v>
+        <v>19749</v>
       </c>
       <c r="D14" t="n">
-        <v>112389</v>
+        <v>124389</v>
       </c>
       <c r="E14" t="n">
-        <v>78479</v>
+        <v>78778</v>
       </c>
     </row>
     <row r="15">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54862</v>
+        <v>55260</v>
       </c>
       <c r="D15" t="n">
-        <v>210241</v>
+        <v>245659</v>
       </c>
       <c r="E15" t="n">
-        <v>26493</v>
+        <v>21513</v>
       </c>
     </row>
     <row r="16">
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12718</v>
+        <v>11909</v>
       </c>
       <c r="D16" t="n">
-        <v>261984</v>
+        <v>265958</v>
       </c>
       <c r="E16" t="n">
-        <v>16351</v>
+        <v>19187</v>
       </c>
     </row>
     <row r="17">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>49467</v>
+        <v>39913</v>
       </c>
       <c r="D17" t="n">
-        <v>63494</v>
+        <v>74490</v>
       </c>
       <c r="E17" t="n">
-        <v>19725</v>
+        <v>19773</v>
       </c>
     </row>
     <row r="18">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6697</v>
+        <v>6716</v>
       </c>
       <c r="D18" t="n">
-        <v>75925</v>
+        <v>76323</v>
       </c>
       <c r="E18" t="n">
-        <v>36442</v>
+        <v>36461</v>
       </c>
     </row>
     <row r="19">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7536</v>
+        <v>8968</v>
       </c>
       <c r="D19" t="n">
-        <v>198568</v>
+        <v>208985</v>
       </c>
       <c r="E19" t="n">
-        <v>41030</v>
+        <v>41087</v>
       </c>
     </row>
     <row r="20">
@@ -2245,10 +2245,10 @@
         <v>3664</v>
       </c>
       <c r="D20" t="n">
-        <v>193670</v>
+        <v>195264</v>
       </c>
       <c r="E20" t="n">
-        <v>8406</v>
+        <v>8766</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>210706</v>
+        <v>215263</v>
       </c>
       <c r="D21" t="n">
-        <v>439771</v>
+        <v>398969</v>
       </c>
       <c r="E21" t="n">
-        <v>395929</v>
+        <v>364786</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28227</v>
+        <v>28507</v>
       </c>
       <c r="D22" t="n">
-        <v>157492</v>
+        <v>147492</v>
       </c>
       <c r="E22" t="n">
-        <v>24326</v>
+        <v>24678</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85204</v>
+        <v>85780</v>
       </c>
       <c r="D23" t="n">
-        <v>134628</v>
+        <v>129722</v>
       </c>
       <c r="E23" t="n">
-        <v>36158</v>
+        <v>36336</v>
       </c>
     </row>
     <row r="24">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2331580</v>
+        <v>2425989</v>
       </c>
       <c r="D25" t="n">
-        <v>2505815</v>
+        <v>2550313</v>
       </c>
       <c r="E25" t="n">
-        <v>2666233</v>
+        <v>2729084</v>
       </c>
     </row>
   </sheetData>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>13346.66</v>
+        <v>18326.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>106053.34</v>
+        <v>101073.34</v>
       </c>
     </row>
     <row r="3">
@@ -2479,19 +2479,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>4980</v>
+        <v>6960</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2499,11 +2499,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>389.3%</t>
+          <t>278.6%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-14409</v>
+        <v>-12429</v>
       </c>
     </row>
     <row r="4">
@@ -2521,19 +2521,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>31778</v>
+        <v>41678</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-1582</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="5">
@@ -2647,19 +2647,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>69760</v>
+        <v>74740</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2667,11 +2667,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59760</v>
+        <v>64740</v>
       </c>
     </row>
     <row r="8">
@@ -2689,19 +2689,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>11580</v>
+        <v>21540</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2709,11 +2709,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>407.2%</t>
+          <t>218.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-35570</v>
+        <v>-25610</v>
       </c>
     </row>
     <row r="9">
@@ -2731,19 +2731,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>29880</v>
+        <v>36480</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24901</v>
+        <v>31501</v>
       </c>
     </row>
     <row r="10">
@@ -2785,19 +2785,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3980</v>
+        <v>7959</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>73216</v>
+        <v>69237</v>
       </c>
     </row>
     <row r="11">
@@ -2899,31 +2899,31 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>135398</v>
+        <v>141338</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>169.2%</t>
+          <t>176.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>169.2%</t>
+          <t>165.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>135398</v>
+        <v>132338</v>
       </c>
     </row>
     <row r="14">
@@ -2953,19 +2953,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>39800</v>
+        <v>69600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>35800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15">
@@ -2983,31 +2983,31 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16">
@@ -3025,19 +3025,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>49738</v>
+        <v>59738</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3045,11 +3045,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>43138</v>
+        <v>53138</v>
       </c>
     </row>
     <row r="17">
@@ -3193,19 +3193,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>51220</v>
+        <v>59220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>51220</v>
+        <v>59220</v>
       </c>
     </row>
     <row r="21">
@@ -3277,19 +3277,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>6600</v>
+        <v>26400</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>-1000</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="23">
@@ -3319,19 +3319,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>57580</v>
+        <v>59560</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3339,11 +3339,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>50980</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="24">
@@ -3403,19 +3403,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>21154</v>
+        <v>26134</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3423,11 +3423,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8084</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="26">
@@ -3445,19 +3445,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>107276</v>
+        <v>137236</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3465,11 +3465,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>93510</v>
+        <v>123470</v>
       </c>
     </row>
     <row r="27">
@@ -3529,19 +3529,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>24900</v>
+        <v>39840</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3549,11 +3549,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6300</v>
+        <v>21240</v>
       </c>
     </row>
     <row r="29">
@@ -3571,19 +3571,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>49800</v>
+        <v>54780</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3591,11 +3591,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>40840</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="30">
@@ -3613,14 +3613,14 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>62740</v>
+        <v>67720</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3629,11 +3629,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12000</v>
+        <v>16980</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3655,19 +3655,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>150694</v>
+        <v>163474</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>103814</v>
+        <v>116594</v>
       </c>
     </row>
     <row r="32">
@@ -3739,19 +3739,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>52402</v>
+        <v>57382</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>42442</v>
+        <v>47422</v>
       </c>
     </row>
     <row r="34">
@@ -3781,19 +3781,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>62599</v>
+        <v>57819</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>58999</v>
+        <v>54219</v>
       </c>
     </row>
     <row r="35">
@@ -3823,19 +3823,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>51110</v>
+        <v>57710</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>51110</v>
+        <v>57710</v>
       </c>
     </row>
     <row r="36">
@@ -3907,19 +3907,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>58116</v>
+        <v>63096</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3927,11 +3927,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>54136</v>
+        <v>59116</v>
       </c>
     </row>
     <row r="38">
@@ -4075,19 +4075,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>28880</v>
+        <v>33860</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>27200</v>
+        <v>32180</v>
       </c>
     </row>
   </sheetData>
@@ -4173,11 +4173,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>146448.2</v>
+        <v>150258.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>106581.53</v>
+        <v>110392.13</v>
       </c>
     </row>
     <row r="3">
@@ -4275,11 +4275,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>14586.3</v>
+        <v>14815.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4287,11 +4287,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11986.3</v>
+        <v>12215.1</v>
       </c>
     </row>
     <row r="6">
@@ -4377,11 +4377,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>36035.41</v>
+        <v>26108.11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>36035.41</v>
+        <v>26108.11</v>
       </c>
     </row>
     <row r="9">
@@ -4581,11 +4581,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>85576</v>
+        <v>95974</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>85576</v>
+        <v>95974</v>
       </c>
     </row>
     <row r="15">
@@ -4649,11 +4649,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>74588</v>
+        <v>75982</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>74588</v>
+        <v>75982</v>
       </c>
     </row>
     <row r="17">
@@ -4717,11 +4717,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>2914.6</v>
+        <v>3710.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2914.6</v>
+        <v>3710.6</v>
       </c>
     </row>
     <row r="19">
@@ -4819,11 +4819,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>8716</v>
+        <v>9314</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>8716</v>
+        <v>9314</v>
       </c>
     </row>
     <row r="22">
@@ -4887,11 +4887,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>84982</v>
+        <v>85380</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>84982</v>
+        <v>85380</v>
       </c>
     </row>
     <row r="24">
@@ -4921,11 +4921,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>2196</v>
+        <v>2794</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2196</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="25">
@@ -4955,11 +4955,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77966</v>
+        <v>78564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4967,11 +4967,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68166</v>
+        <v>68764</v>
       </c>
     </row>
     <row r="26">
@@ -4989,11 +4989,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>31154</v>
+        <v>31552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>31154</v>
+        <v>31552</v>
       </c>
     </row>
     <row r="27">
@@ -5023,11 +5023,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24456</v>
+        <v>24956</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24456</v>
+        <v>24956</v>
       </c>
     </row>
     <row r="28">
@@ -5091,11 +5091,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>83580</v>
+        <v>84178</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>76580</v>
+        <v>77178</v>
       </c>
     </row>
     <row r="30">
@@ -5125,11 +5125,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>26176</v>
+        <v>38176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>26176</v>
+        <v>38176</v>
       </c>
     </row>
     <row r="31">
@@ -5227,11 +5227,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>94375.64</v>
+        <v>94773.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5239,11 +5239,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>60575.64</v>
+        <v>60973.64</v>
       </c>
     </row>
     <row r="34">
@@ -5261,11 +5261,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>85529.84999999999</v>
+        <v>86127.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>79529.84999999999</v>
+        <v>80127.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5295,11 +5295,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>55488.92</v>
+        <v>56446.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5307,11 +5307,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>48888.92</v>
+        <v>49846.92</v>
       </c>
     </row>
     <row r="36">
@@ -5465,23 +5465,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>425416</v>
+        <v>440814</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>101.7%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18600</v>
+        <v>59800</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>406816</v>
+        <v>381014</v>
       </c>
     </row>
     <row r="41">
@@ -5669,11 +5669,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>5078</v>
+        <v>15078</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5078</v>
+        <v>15078</v>
       </c>
     </row>
     <row r="47">
@@ -5873,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>198311</v>
+        <v>198850</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>198311</v>
+        <v>198850</v>
       </c>
     </row>
     <row r="53">
@@ -5907,7 +5907,7 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>57792.10000000001</v>
+        <v>57962.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>57792.10000000001</v>
+        <v>57962.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -6077,11 +6077,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>16660</v>
+        <v>22078</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -6093,7 +6093,7 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>16660</v>
+        <v>22078</v>
       </c>
     </row>
     <row r="59">
@@ -6111,11 +6111,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>69208</v>
+        <v>99606</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>152.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>61208</v>
+        <v>91606</v>
       </c>
     </row>
     <row r="60">
@@ -6247,11 +6247,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9074</v>
+        <v>9472</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>151.2%</t>
+          <t>157.9%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9074</v>
+        <v>9472</v>
       </c>
     </row>
   </sheetData>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1407282.8</v>
+        <v>1513756.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7245</v>
+        <v>7674</v>
       </c>
       <c r="E2" t="n">
-        <v>1252909.8</v>
+        <v>1363283.8</v>
       </c>
       <c r="F2" t="n">
-        <v>154373</v>
+        <v>150473</v>
       </c>
     </row>
     <row r="3">
@@ -6348,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1208750</v>
+        <v>1306490</v>
       </c>
       <c r="D3" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="E3" t="n">
-        <v>1068207</v>
+        <v>1170927</v>
       </c>
       <c r="F3" t="n">
-        <v>140543</v>
+        <v>135563</v>
       </c>
     </row>
     <row r="4">
@@ -6372,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>198532.8</v>
+        <v>207266.8</v>
       </c>
       <c r="D4" t="n">
-        <v>6903</v>
+        <v>7313</v>
       </c>
       <c r="E4" t="n">
-        <v>184702.8</v>
+        <v>192356.8</v>
       </c>
       <c r="F4" t="n">
-        <v>13830</v>
+        <v>14910</v>
       </c>
     </row>
     <row r="5">
@@ -6396,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2528510</v>
+        <v>2652364</v>
       </c>
       <c r="D5" t="n">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="E5" t="n">
-        <v>555940</v>
+        <v>602138</v>
       </c>
       <c r="F5" t="n">
-        <v>1972570</v>
+        <v>2050226</v>
       </c>
     </row>
     <row r="6">
@@ -6420,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1639996</v>
+        <v>1730266</v>
       </c>
       <c r="D6" t="n">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="E6" t="n">
-        <v>15218</v>
+        <v>35218</v>
       </c>
       <c r="F6" t="n">
-        <v>1624778</v>
+        <v>1695048</v>
       </c>
     </row>
     <row r="7">
@@ -6444,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>878514</v>
+        <v>912098</v>
       </c>
       <c r="D7" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E7" t="n">
-        <v>540722</v>
+        <v>566920</v>
       </c>
       <c r="F7" t="n">
-        <v>337792</v>
+        <v>345178</v>
       </c>
     </row>
     <row r="8">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>963712.97</v>
+        <v>977116.0600000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1288</v>
+        <v>1313</v>
       </c>
       <c r="E8" t="n">
-        <v>15890.21</v>
+        <v>16888.2</v>
       </c>
       <c r="F8" t="n">
-        <v>947822.76</v>
+        <v>960227.86</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>578574.4</v>
+        <v>580508.8</v>
       </c>
       <c r="D9" t="n">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>575531.54</v>
+        <v>577465.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>385138.57</v>
+        <v>396607.26</v>
       </c>
       <c r="D10" t="n">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E10" t="n">
-        <v>12847.35</v>
+        <v>13845.34</v>
       </c>
       <c r="F10" t="n">
-        <v>372291.22</v>
+        <v>382761.92</v>
       </c>
     </row>
     <row r="11">
@@ -6543,7 +6543,7 @@
         <v>306400</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>267340</v>
+        <v>285160</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>237560</v>
+        <v>255380</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>102960</v>
+        <v>106920</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>15840</v>
+        <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>87120</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="15">
@@ -6639,7 +6639,7 @@
         <v>27001.61</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E15" t="n">
         <v>6536.36</v>
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1407282.8</v>
+        <v>1513756.8</v>
       </c>
       <c r="C2" t="n">
-        <v>292000.06</v>
+        <v>316406.06</v>
       </c>
       <c r="D2" t="n">
-        <v>28577</v>
+        <v>32444</v>
       </c>
       <c r="E2" t="n">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="F2" t="n">
-        <v>263423.06</v>
+        <v>283962.06</v>
       </c>
       <c r="G2" t="n">
-        <v>18.72</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="3">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2528510</v>
+        <v>2652364</v>
       </c>
       <c r="C3" t="n">
-        <v>278718.98</v>
+        <v>325218.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>278718.98</v>
+        <v>325218.98</v>
       </c>
       <c r="G3" t="n">
-        <v>11.02</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="4">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>963712.97</v>
+        <v>977116.0600000001</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6831,22 +6831,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267340</v>
+        <v>285160</v>
       </c>
       <c r="C7" t="n">
-        <v>206066.67</v>
+        <v>260466.67</v>
       </c>
       <c r="D7" t="n">
-        <v>29800</v>
+        <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15</v>
+        <v>18.59</v>
       </c>
       <c r="F7" t="n">
-        <v>176266.67</v>
+        <v>207466.67</v>
       </c>
       <c r="G7" t="n">
-        <v>65.93000000000001</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="8">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>102960</v>
+        <v>106920</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="C2" t="n">
-        <v>596802.65</v>
+        <v>718636.65</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>238584.4</v>
+        <v>239288.4</v>
       </c>
       <c r="D3" t="n">
         <v>31</v>
@@ -7006,13 +7006,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C6" t="n">
-        <v>16719.66</v>
+        <v>18476.66</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7022,10 +7022,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>14149</v>
+        <v>14187</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>12953.9</v>
+        <v>13888.9</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>9645</v>
+        <v>9683</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -7122,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>147800</v>
+        <v>186600</v>
       </c>
     </row>
     <row r="3">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>52273</v>
+        <v>57356</v>
       </c>
     </row>
     <row r="13">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>17581</v>
+        <v>17790</v>
       </c>
     </row>
     <row r="15">
@@ -7393,10 +7393,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>4138</v>
+        <v>5520</v>
       </c>
     </row>
     <row r="16">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" t="n">
-        <v>3434</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="17">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D20" t="n">
-        <v>26563</v>
+        <v>31619</v>
       </c>
     </row>
     <row r="21">
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>20620.5</v>
+        <v>20696.5</v>
       </c>
     </row>
     <row r="23">
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>7576.66</v>
+        <v>7614.66</v>
       </c>
     </row>
     <row r="24">
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25">
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D29" t="n">
-        <v>62231</v>
+        <v>62383</v>
       </c>
     </row>
     <row r="30">
@@ -7663,10 +7663,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>10798</v>
+        <v>14852</v>
       </c>
     </row>
     <row r="31">
@@ -7717,16 +7717,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7735,46 +7735,46 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>57940</v>
+        <v>77918</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>3712</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>598</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
@@ -7785,14 +7785,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D37" t="n">
-        <v>375</v>
+        <v>57968</v>
       </c>
     </row>
     <row r="38">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>56</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="39">
@@ -7821,86 +7821,86 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>36400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>12000</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44">
@@ -7911,56 +7911,56 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>33494.67</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>6500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7969,16 +7969,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>4634</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7990,7 +7990,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>299</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>31309</v>
+        <v>38327</v>
       </c>
     </row>
     <row r="50">
@@ -8041,10 +8041,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D51" t="n">
-        <v>304</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52">
@@ -8104,73 +8104,73 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>20157.9</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>12320</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D57" t="n">
-        <v>3855</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>951</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59">
@@ -8181,14 +8181,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="D59" t="n">
-        <v>190</v>
+        <v>20272.9</v>
       </c>
     </row>
     <row r="60">
@@ -8199,14 +8199,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="D60" t="n">
-        <v>38</v>
+        <v>12396</v>
       </c>
     </row>
     <row r="61">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="62">
@@ -8235,122 +8235,122 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D63" t="n">
-        <v>18399.98</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>8000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>26218</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>19</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D68" t="n">
-        <v>15009</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="69">
@@ -8361,14 +8361,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>8019</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="70">
@@ -8379,32 +8379,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>48</v>
+        <v>8019</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>10000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>6289</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="73">
@@ -8433,32 +8433,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>1328</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>9000</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="75">
@@ -8469,14 +8469,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>6800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="76">
@@ -8487,32 +8487,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>76</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>9318</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78">
@@ -8523,14 +8523,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>5500</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="79">
@@ -8541,14 +8541,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>29</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="80">
@@ -8559,32 +8559,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>10621</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82">
@@ -8595,50 +8595,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>2490</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>8800</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D84" t="n">
-        <v>398</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="85">
@@ -8680,7 +8680,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8692,25 +8692,61 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>9</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C88" t="n">
-        <v>3</v>
-      </c>
-      <c r="D88" t="n">
-        <v>24</v>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -8751,10 +8787,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>225197.98</v>
+        <v>271697.98</v>
       </c>
     </row>
     <row r="3">
@@ -8764,36 +8800,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>201866.67</v>
+        <v>225066.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>133108</v>
+        <v>141554.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>127615.16</v>
+        <v>133108</v>
       </c>
     </row>
     <row r="6">
@@ -8829,7 +8865,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>49900</v>
@@ -8838,40 +8874,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>19800</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>829</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>14416</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>902</v>
       </c>
       <c r="C11" t="n">
-        <v>10621</v>
+        <v>15723</v>
       </c>
     </row>
   </sheetData>
@@ -8912,10 +8948,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C2" t="n">
-        <v>176437.33</v>
+        <v>177002.33</v>
       </c>
     </row>
     <row r="3">
@@ -8925,36 +8961,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>138315.5</v>
+        <v>138334.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C4" t="n">
-        <v>88184.98</v>
+        <v>115542</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C5" t="n">
-        <v>79229</v>
+        <v>110481.98</v>
       </c>
     </row>
     <row r="6">
@@ -8964,10 +9000,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>69540</v>
+        <v>108797</v>
       </c>
     </row>
     <row r="7">
@@ -8980,33 +9016,33 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>55705</v>
+        <v>59385</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>51836</v>
+        <v>53243</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>51804</v>
+        <v>51836</v>
       </c>
     </row>
     <row r="10">
@@ -9016,36 +9052,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>49088</v>
+        <v>49164</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C11" t="n">
-        <v>37200</v>
+        <v>41747</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>36297</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="13">
@@ -9055,49 +9091,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>29867</v>
+        <v>30185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="C14" t="n">
-        <v>18648</v>
+        <v>19856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>15277</v>
+        <v>18648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C16" t="n">
-        <v>14073.9</v>
+        <v>15371</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>311994</v>
+        <v>317655</v>
       </c>
       <c r="E2" t="n">
-        <v>81919</v>
+        <v>134066</v>
       </c>
       <c r="F2" t="n">
-        <v>230074</v>
+        <v>183589</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>164960</v>
+        <v>190460</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+89.1%</t>
+          <t>+66.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>23824</v>
+        <v>49201</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+865.7%</t>
+          <t>+273.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="E3" t="n">
         <v>17617</v>
       </c>
       <c r="F3" t="n">
-        <v>-15617</v>
+        <v>-15598</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.4%</t>
+          <t>-87.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+70.7%</t>
+          <t>+70.5%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,41 +638,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>447037</v>
+        <v>474893</v>
       </c>
       <c r="E4" t="n">
-        <v>109639</v>
+        <v>124529</v>
       </c>
       <c r="F4" t="n">
-        <v>337398</v>
+        <v>350364</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>281079</v>
+        <v>304915</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+59.0%</t>
+          <t>+55.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>170388</v>
+        <v>194167</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+98.0%</t>
+          <t>+80.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,41 +695,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176054</v>
+        <v>224419</v>
       </c>
       <c r="E5" t="n">
-        <v>176695</v>
+        <v>189822</v>
       </c>
       <c r="F5" t="n">
-        <v>-641</v>
+        <v>34596</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>241492</v>
+        <v>324974</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>135440</v>
+        <v>218922</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-100.5%</t>
+          <t>-84.2%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>377840</v>
+        <v>381749</v>
       </c>
       <c r="E6" t="n">
-        <v>38414</v>
+        <v>44245</v>
       </c>
       <c r="F6" t="n">
-        <v>339425</v>
+        <v>337503</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>198707</v>
+        <v>200192</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+90.1%</t>
+          <t>+90.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>149310</v>
+        <v>150580</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+127.3%</t>
+          <t>+124.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>276079</v>
+        <v>277672</v>
       </c>
       <c r="E7" t="n">
-        <v>62823</v>
+        <v>77690</v>
       </c>
       <c r="F7" t="n">
-        <v>213256</v>
+        <v>199982</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>193460</v>
+        <v>200489</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+42.7%</t>
+          <t>+38.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>154893</v>
+        <v>161903</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+37.7%</t>
+          <t>+23.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>302771</v>
+        <v>306180</v>
       </c>
       <c r="E8" t="n">
-        <v>78005</v>
+        <v>78238</v>
       </c>
       <c r="F8" t="n">
-        <v>224766</v>
+        <v>227942</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>213497</v>
+        <v>217591</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+41.8%</t>
+          <t>+40.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>185700</v>
+        <v>184477</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+21.0%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>598562</v>
+        <v>698349</v>
       </c>
       <c r="E9" t="n">
-        <v>215700</v>
+        <v>258700</v>
       </c>
       <c r="F9" t="n">
-        <v>382862</v>
+        <v>439649</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>575848</v>
+        <v>587348</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>+18.9%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>438924</v>
+        <v>450424</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>931293</v>
+        <v>1008367</v>
       </c>
       <c r="E10" t="n">
         <v>11308</v>
       </c>
       <c r="F10" t="n">
-        <v>919985</v>
+        <v>997059</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>896759</v>
+        <v>1029341</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+3.9%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>896759</v>
+        <v>1029341</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+2.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>364744</v>
+        <v>372293</v>
       </c>
       <c r="P10" t="n">
-        <v>555241</v>
+        <v>624766</v>
       </c>
       <c r="Q10" t="n">
-        <v>868597</v>
+        <v>935671</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>170748</v>
+        <v>171155</v>
       </c>
       <c r="E11" t="n">
         <v>26399</v>
       </c>
       <c r="F11" t="n">
-        <v>144348</v>
+        <v>144755</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>151364</v>
+        <v>174764</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>126256</v>
+        <v>149656</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>19749</v>
+        <v>19758</v>
       </c>
       <c r="P11" t="n">
-        <v>124389</v>
+        <v>124787</v>
       </c>
       <c r="Q11" t="n">
-        <v>78778</v>
+        <v>78787</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>323995</v>
+        <v>330614</v>
       </c>
       <c r="E12" t="n">
-        <v>23076</v>
+        <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>300919</v>
+        <v>300538</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>180906</v>
+        <v>181702</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+79.1%</t>
+          <t>+82.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>178927</v>
+        <v>179723</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+68.2%</t>
+          <t>+67.2%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>55260</v>
+        <v>61879</v>
       </c>
       <c r="P12" t="n">
-        <v>245659</v>
+        <v>238659</v>
       </c>
       <c r="Q12" t="n">
-        <v>21513</v>
+        <v>28132</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>331040</v>
+        <v>390798</v>
       </c>
       <c r="E13" t="n">
         <v>44984</v>
       </c>
       <c r="F13" t="n">
-        <v>286055</v>
+        <v>345813</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>260338</v>
+        <v>267635</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+27.2%</t>
+          <t>+46.0%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>200777</v>
+        <v>208074</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+42.5%</t>
+          <t>+66.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8188</v>
+        <v>8748</v>
       </c>
       <c r="O13" t="n">
         <v>11909</v>
       </c>
       <c r="P13" t="n">
-        <v>265958</v>
+        <v>325156</v>
       </c>
       <c r="Q13" t="n">
-        <v>19187</v>
+        <v>66547</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>139203</v>
+        <v>166999</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>124337</v>
+        <v>152133</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>164305</v>
+        <v>202801</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>146727</v>
+        <v>184423</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>9934</v>
       </c>
       <c r="O14" t="n">
-        <v>39913</v>
+        <v>40511</v>
       </c>
       <c r="P14" t="n">
-        <v>74490</v>
+        <v>101688</v>
       </c>
       <c r="Q14" t="n">
-        <v>19773</v>
+        <v>26373</v>
       </c>
     </row>
     <row r="15">
@@ -1291,23 +1291,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98915</v>
+        <v>99313</v>
       </c>
       <c r="E15" t="n">
         <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>83039</v>
+        <v>83437</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>6716</v>
+        <v>7114</v>
       </c>
       <c r="P15" t="n">
         <v>76323</v>
@@ -1352,39 +1352,39 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>227151</v>
+        <v>227549</v>
       </c>
       <c r="E16" t="n">
-        <v>9198</v>
+        <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>217953</v>
+        <v>209151</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>176061</v>
+        <v>216446</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+29.0%</t>
+          <t>+5.1%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>165861</v>
+        <v>206246</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+31.4%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1392,7 +1392,7 @@
         <v>8968</v>
       </c>
       <c r="P16" t="n">
-        <v>208985</v>
+        <v>200183</v>
       </c>
       <c r="Q16" t="n">
         <v>41087</v>
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>290874</v>
+        <v>296969</v>
       </c>
       <c r="E17" t="n">
-        <v>48658</v>
+        <v>59158</v>
       </c>
       <c r="F17" t="n">
-        <v>242216</v>
+        <v>237811</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>249780</v>
+        <v>256910</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+15.6%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>213914</v>
+        <v>211044</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+13.2%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>43488</v>
       </c>
       <c r="O17" t="n">
-        <v>3664</v>
+        <v>4361</v>
       </c>
       <c r="P17" t="n">
-        <v>195264</v>
+        <v>190162</v>
       </c>
       <c r="Q17" t="n">
-        <v>8766</v>
+        <v>9463</v>
       </c>
     </row>
     <row r="18">
@@ -1476,52 +1476,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>693057</v>
+        <v>735249</v>
       </c>
       <c r="E18" t="n">
-        <v>77975</v>
+        <v>77994</v>
       </c>
       <c r="F18" t="n">
-        <v>615082</v>
+        <v>657255</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>361173</v>
+        <v>399865</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+91.9%</t>
+          <t>+83.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>309617</v>
+        <v>348309</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+98.7%</t>
+          <t>+88.7%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>215263</v>
+        <v>215642</v>
       </c>
       <c r="P18" t="n">
-        <v>398969</v>
+        <v>440763</v>
       </c>
       <c r="Q18" t="n">
-        <v>364786</v>
+        <v>404367</v>
       </c>
     </row>
     <row r="19">
@@ -1539,52 +1539,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>183516</v>
+        <v>231996</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>361</v>
       </c>
       <c r="F19" t="n">
-        <v>183454</v>
+        <v>231635</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>182415</v>
+        <v>186561</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+24.4%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36417</v>
+        <v>40563</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+403.8%</t>
+          <t>+471.0%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>7655</v>
       </c>
       <c r="O19" t="n">
-        <v>28507</v>
+        <v>29888</v>
       </c>
       <c r="P19" t="n">
-        <v>147492</v>
+        <v>194292</v>
       </c>
       <c r="Q19" t="n">
-        <v>24678</v>
+        <v>71659</v>
       </c>
     </row>
     <row r="20">
@@ -1602,50 +1602,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>263428</v>
+        <v>283526</v>
       </c>
       <c r="E20" t="n">
         <v>47926</v>
       </c>
       <c r="F20" t="n">
-        <v>215502</v>
+        <v>235600</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>314630</v>
+        <v>336730</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>258630</v>
+        <v>280730</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>85780</v>
+        <v>87082</v>
       </c>
       <c r="P20" t="n">
-        <v>129722</v>
+        <v>148518</v>
       </c>
       <c r="Q20" t="n">
-        <v>36336</v>
+        <v>36444</v>
       </c>
     </row>
     <row r="21">
@@ -1663,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>6160484</v>
+        <v>6640398</v>
       </c>
       <c r="E21" t="n">
-        <v>1114254</v>
+        <v>1285367</v>
       </c>
       <c r="F21" t="n">
-        <v>5046229</v>
+        <v>5355030</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4955620</v>
+        <v>5427570</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+24.3%</t>
+          <t>+22.3%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3900880</v>
+        <v>4356300</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+29.4%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>70326</v>
+        <v>70886</v>
       </c>
       <c r="O21" t="n">
-        <v>2425989</v>
+        <v>2470807</v>
       </c>
       <c r="P21" t="n">
-        <v>2550313</v>
+        <v>2813736</v>
       </c>
       <c r="Q21" t="n">
-        <v>2729084</v>
+        <v>2881608</v>
       </c>
     </row>
   </sheetData>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>321</v>
+        <v>196</v>
       </c>
       <c r="C2" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>1203.6</v>
+        <v>559.8</v>
       </c>
       <c r="E2" t="n">
-        <v>102202</v>
+        <v>120264</v>
       </c>
     </row>
     <row r="3">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
-        <v>849</v>
+        <v>1506</v>
       </c>
       <c r="E3" t="n">
-        <v>1337</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="4">
@@ -1799,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>640</v>
+        <v>455</v>
       </c>
       <c r="C4" t="n">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="D4" t="n">
-        <v>1278.6</v>
+        <v>1236.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3130</v>
+        <v>4418</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1327284</v>
+        <v>1318383</v>
       </c>
       <c r="D2" t="n">
-        <v>1379</v>
+        <v>-2</v>
       </c>
       <c r="E2" t="n">
-        <v>1016639</v>
+        <v>995386</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>269622</v>
+        <v>304409</v>
       </c>
       <c r="D3" t="n">
-        <v>113240</v>
+        <v>135240</v>
       </c>
       <c r="E3" t="n">
-        <v>193248</v>
+        <v>151997</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>840474</v>
+        <v>859406</v>
       </c>
       <c r="D4" t="n">
-        <v>2422493</v>
+        <v>2665298</v>
       </c>
       <c r="E4" t="n">
-        <v>1519966</v>
+        <v>1734995</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>233968</v>
+        <v>187184</v>
       </c>
       <c r="D5" t="n">
-        <v>-3894</v>
+        <v>-3595</v>
       </c>
       <c r="E5" t="n">
-        <v>219676</v>
+        <v>184391</v>
       </c>
     </row>
     <row r="6">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15752</v>
+        <v>-15733</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-5617</v>
+        <v>-5598</v>
       </c>
     </row>
     <row r="7">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>323667</v>
+        <v>342133</v>
       </c>
       <c r="D7" t="n">
-        <v>13730</v>
+        <v>8230</v>
       </c>
       <c r="E7" t="n">
-        <v>314112</v>
+        <v>332578</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2029</v>
+        <v>29408</v>
       </c>
       <c r="D8" t="n">
-        <v>1388</v>
+        <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-78281</v>
+        <v>-85563</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>332499</v>
+        <v>330577</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>271633</v>
+        <v>269740</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>211557</v>
+        <v>198264</v>
       </c>
       <c r="D10" t="n">
-        <v>1699</v>
+        <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>103542</v>
+        <v>105088</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>243371</v>
+        <v>246547</v>
       </c>
       <c r="D11" t="n">
         <v>-18605</v>
       </c>
       <c r="E11" t="n">
-        <v>191572</v>
+        <v>194748</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>269622</v>
+        <v>304409</v>
       </c>
       <c r="D12" t="n">
-        <v>113240</v>
+        <v>135240</v>
       </c>
       <c r="E12" t="n">
-        <v>193248</v>
+        <v>151997</v>
       </c>
     </row>
     <row r="13">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>364744</v>
+        <v>372293</v>
       </c>
       <c r="D13" t="n">
-        <v>555241</v>
+        <v>624766</v>
       </c>
       <c r="E13" t="n">
-        <v>868597</v>
+        <v>935671</v>
       </c>
     </row>
     <row r="14">
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19749</v>
+        <v>19758</v>
       </c>
       <c r="D14" t="n">
-        <v>124389</v>
+        <v>124787</v>
       </c>
       <c r="E14" t="n">
-        <v>78778</v>
+        <v>78787</v>
       </c>
     </row>
     <row r="15">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55260</v>
+        <v>61879</v>
       </c>
       <c r="D15" t="n">
-        <v>245659</v>
+        <v>238659</v>
       </c>
       <c r="E15" t="n">
-        <v>21513</v>
+        <v>28132</v>
       </c>
     </row>
     <row r="16">
@@ -2161,10 +2161,10 @@
         <v>11909</v>
       </c>
       <c r="D16" t="n">
-        <v>265958</v>
+        <v>325156</v>
       </c>
       <c r="E16" t="n">
-        <v>19187</v>
+        <v>66547</v>
       </c>
     </row>
     <row r="17">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>39913</v>
+        <v>40511</v>
       </c>
       <c r="D17" t="n">
-        <v>74490</v>
+        <v>101688</v>
       </c>
       <c r="E17" t="n">
-        <v>19773</v>
+        <v>26373</v>
       </c>
     </row>
     <row r="18">
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6716</v>
+        <v>7114</v>
       </c>
       <c r="D18" t="n">
         <v>76323</v>
@@ -2224,7 +2224,7 @@
         <v>8968</v>
       </c>
       <c r="D19" t="n">
-        <v>208985</v>
+        <v>200183</v>
       </c>
       <c r="E19" t="n">
         <v>41087</v>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3664</v>
+        <v>4361</v>
       </c>
       <c r="D20" t="n">
-        <v>195264</v>
+        <v>190162</v>
       </c>
       <c r="E20" t="n">
-        <v>8766</v>
+        <v>9463</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>215263</v>
+        <v>215642</v>
       </c>
       <c r="D21" t="n">
-        <v>398969</v>
+        <v>440763</v>
       </c>
       <c r="E21" t="n">
-        <v>364786</v>
+        <v>404367</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>28507</v>
+        <v>29888</v>
       </c>
       <c r="D22" t="n">
-        <v>147492</v>
+        <v>194292</v>
       </c>
       <c r="E22" t="n">
-        <v>24678</v>
+        <v>71659</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>85780</v>
+        <v>87082</v>
       </c>
       <c r="D23" t="n">
-        <v>129722</v>
+        <v>148518</v>
       </c>
       <c r="E23" t="n">
-        <v>36336</v>
+        <v>36444</v>
       </c>
     </row>
     <row r="24">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2425989</v>
+        <v>2470807</v>
       </c>
       <c r="D25" t="n">
-        <v>2550313</v>
+        <v>2813736</v>
       </c>
       <c r="E25" t="n">
-        <v>2729084</v>
+        <v>2881608</v>
       </c>
     </row>
   </sheetData>
@@ -2449,19 +2449,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18326.66</v>
+        <v>38126.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>101073.34</v>
+        <v>81273.34</v>
       </c>
     </row>
     <row r="3">
@@ -2521,31 +2521,31 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>41678</v>
+        <v>43658</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>33360</v>
+        <v>44560</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8318</v>
+        <v>-902</v>
       </c>
     </row>
     <row r="5">
@@ -2605,19 +2605,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>41420</v>
+        <v>43400</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>39740</v>
+        <v>41720</v>
       </c>
     </row>
     <row r="7">
@@ -2857,19 +2857,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>32290</v>
+        <v>59110</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>25690</v>
+        <v>52510</v>
       </c>
     </row>
     <row r="13">
@@ -2941,19 +2941,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>75600</v>
+        <v>114420</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2961,11 +2961,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>6000</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="15">
@@ -2983,31 +2983,31 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>398</v>
+        <v>-2802</v>
       </c>
     </row>
     <row r="16">
@@ -3025,31 +3025,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>59738</v>
+        <v>60136</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6600</v>
+        <v>36400</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>53138</v>
+        <v>23736</v>
       </c>
     </row>
     <row r="17">
@@ -3109,19 +3109,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>13980</v>
+        <v>14980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3129,11 +3129,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-3020</v>
+        <v>-2020</v>
       </c>
     </row>
     <row r="19">
@@ -3193,19 +3193,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>59220</v>
+        <v>69220</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>59220</v>
+        <v>69220</v>
       </c>
     </row>
     <row r="21">
@@ -3235,19 +3235,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>26600</v>
+        <v>38600</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26600</v>
+        <v>38600</v>
       </c>
     </row>
     <row r="22">
@@ -3403,14 +3403,14 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>26134</v>
+        <v>31114</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3419,11 +3419,11 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13070</v>
+        <v>18050</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3445,19 +3445,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>137236</v>
+        <v>142216</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3465,11 +3465,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>123470</v>
+        <v>128450</v>
       </c>
     </row>
     <row r="27">
@@ -3487,19 +3487,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>29880</v>
+        <v>33580</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>29880</v>
+        <v>33580</v>
       </c>
     </row>
     <row r="28">
@@ -3571,31 +3571,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>54780</v>
+        <v>61380</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>8960</v>
+        <v>12940</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>45820</v>
+        <v>48440</v>
       </c>
     </row>
     <row r="30">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>9960</v>
+        <v>24780</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>47422</v>
+        <v>32602</v>
       </c>
     </row>
     <row r="34">
@@ -3781,19 +3781,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>57819</v>
+        <v>58019</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54219</v>
+        <v>54419</v>
       </c>
     </row>
     <row r="35">
@@ -3919,19 +3919,19 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>59116</v>
+        <v>55136</v>
       </c>
     </row>
     <row r="38">
@@ -3949,19 +3949,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>83340</v>
+        <v>125860</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3969,11 +3969,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>-12168</v>
+        <v>30352</v>
       </c>
     </row>
     <row r="39">
@@ -3991,31 +3991,31 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>80528</v>
+        <v>86228</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3788</v>
+        <v>16896</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>76740</v>
+        <v>69332</v>
       </c>
     </row>
     <row r="40">
@@ -4173,11 +4173,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>150258.8</v>
+        <v>209058.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>110392.13</v>
+        <v>169192.13</v>
       </c>
     </row>
     <row r="3">
@@ -4275,11 +4275,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>14815.1</v>
+        <v>15015.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4287,11 +4287,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12215.1</v>
+        <v>12415.1</v>
       </c>
     </row>
     <row r="6">
@@ -4309,11 +4309,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>48927.36</v>
+        <v>49685.36</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48927.36</v>
+        <v>49685.36</v>
       </c>
     </row>
     <row r="7">
@@ -4411,11 +4411,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>32838.64</v>
+        <v>34038.64</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>32638.64</v>
+        <v>33838.64</v>
       </c>
     </row>
     <row r="10">
@@ -4513,11 +4513,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>57307.7</v>
+        <v>102907.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>57307.7</v>
+        <v>102907.7</v>
       </c>
     </row>
     <row r="13">
@@ -4581,11 +4581,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>95974</v>
+        <v>96372</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>95974</v>
+        <v>96372</v>
       </c>
     </row>
     <row r="15">
@@ -4653,19 +4653,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75982</v>
+        <v>66782</v>
       </c>
     </row>
     <row r="17">
@@ -4717,11 +4717,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>3710.6</v>
+        <v>10310.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3710.6</v>
+        <v>10310.6</v>
       </c>
     </row>
     <row r="19">
@@ -4751,11 +4751,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>50733.9</v>
+        <v>70733.89999999999</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4763,11 +4763,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>45733.9</v>
+        <v>65733.89999999999</v>
       </c>
     </row>
     <row r="20">
@@ -4785,11 +4785,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>74839.8</v>
+        <v>76035.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70839.8</v>
+        <v>72035.8</v>
       </c>
     </row>
     <row r="21">
@@ -4887,11 +4887,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>85380</v>
+        <v>90778</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>85380</v>
+        <v>90778</v>
       </c>
     </row>
     <row r="24">
@@ -4921,11 +4921,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>2794</v>
+        <v>3590</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2794</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="25">
@@ -4955,11 +4955,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>78564</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4967,11 +4967,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>68764</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -5023,11 +5023,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>24956</v>
+        <v>35752</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>24956</v>
+        <v>35752</v>
       </c>
     </row>
     <row r="28">
@@ -5057,11 +5057,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>14390</v>
+        <v>14788</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5069,11 +5069,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-5009.98</v>
+        <v>-4611.98</v>
       </c>
     </row>
     <row r="29">
@@ -5261,23 +5261,23 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>86127.84999999999</v>
+        <v>91127.84999999999</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6000</v>
+        <v>14500</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>80127.84999999999</v>
+        <v>76627.84999999999</v>
       </c>
     </row>
     <row r="35">
@@ -5329,11 +5329,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>42192</v>
+        <v>42988</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5345,7 +5345,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>41992</v>
+        <v>42788</v>
       </c>
     </row>
     <row r="37">
@@ -5465,11 +5465,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>440814</v>
+        <v>461410</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5477,11 +5477,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>381014</v>
+        <v>401610</v>
       </c>
     </row>
     <row r="41">
@@ -5499,11 +5499,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>49191</v>
+        <v>69389</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>49191</v>
+        <v>69389</v>
       </c>
     </row>
     <row r="42">
@@ -5533,11 +5533,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>116372</v>
+        <v>117770</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>103.6%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>108772</v>
+        <v>110170</v>
       </c>
     </row>
     <row r="43">
@@ -5635,11 +5635,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>42355.64000000001</v>
+        <v>43411.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42355.64000000001</v>
+        <v>43411.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5669,11 +5669,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>15078</v>
+        <v>25476</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>15078</v>
+        <v>25476</v>
       </c>
     </row>
     <row r="47">
@@ -5703,11 +5703,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>126544</v>
+        <v>130600</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>126544</v>
+        <v>130600</v>
       </c>
     </row>
     <row r="48">
@@ -5737,11 +5737,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>64521</v>
+        <v>66421</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>64521</v>
+        <v>66421</v>
       </c>
     </row>
     <row r="49">
@@ -5771,11 +5771,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>134512.5</v>
+        <v>142401.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>134512.5</v>
+        <v>142401.5</v>
       </c>
     </row>
     <row r="50">
@@ -5873,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>198850</v>
+        <v>216049</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>198850</v>
+        <v>216049</v>
       </c>
     </row>
     <row r="53">
@@ -5907,11 +5907,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>57962.10000000001</v>
+        <v>61756.10000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>57962.10000000001</v>
+        <v>61756.10000000001</v>
       </c>
     </row>
     <row r="54">
@@ -5941,11 +5941,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>167420</v>
+        <v>200551</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>167420</v>
+        <v>200551</v>
       </c>
     </row>
     <row r="55">
@@ -6081,19 +6081,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>22078</v>
+        <v>15078</v>
       </c>
     </row>
     <row r="59">
@@ -6111,11 +6111,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>99606</v>
+        <v>106206</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>152.7%</t>
+          <t>163.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>91606</v>
+        <v>98206</v>
       </c>
     </row>
     <row r="60">
@@ -6213,11 +6213,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>60675</v>
+        <v>61073</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6225,11 +6225,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>44875</v>
+        <v>45273</v>
       </c>
     </row>
     <row r="63">
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1513756.8</v>
+        <v>1603908.8</v>
       </c>
       <c r="D2" t="n">
-        <v>7674</v>
+        <v>8132</v>
       </c>
       <c r="E2" t="n">
-        <v>1363283.8</v>
+        <v>1398507.8</v>
       </c>
       <c r="F2" t="n">
-        <v>150473</v>
+        <v>205401</v>
       </c>
     </row>
     <row r="3">
@@ -6348,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1306490</v>
+        <v>1382230</v>
       </c>
       <c r="D3" t="n">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E3" t="n">
-        <v>1170927</v>
+        <v>1192187</v>
       </c>
       <c r="F3" t="n">
-        <v>135563</v>
+        <v>190043</v>
       </c>
     </row>
     <row r="4">
@@ -6372,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>207266.8</v>
+        <v>221678.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7313</v>
+        <v>7761</v>
       </c>
       <c r="E4" t="n">
-        <v>192356.8</v>
+        <v>206320.8</v>
       </c>
       <c r="F4" t="n">
-        <v>14910</v>
+        <v>15358</v>
       </c>
     </row>
     <row r="5">
@@ -6396,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2652364</v>
+        <v>2866890</v>
       </c>
       <c r="D5" t="n">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="E5" t="n">
-        <v>602138</v>
+        <v>742696</v>
       </c>
       <c r="F5" t="n">
-        <v>2050226</v>
+        <v>2124194</v>
       </c>
     </row>
     <row r="6">
@@ -6420,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1730266</v>
+        <v>1823248</v>
       </c>
       <c r="D6" t="n">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="E6" t="n">
-        <v>35218</v>
+        <v>57218</v>
       </c>
       <c r="F6" t="n">
-        <v>1695048</v>
+        <v>1766030</v>
       </c>
     </row>
     <row r="7">
@@ -6444,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>912098</v>
+        <v>1033642</v>
       </c>
       <c r="D7" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E7" t="n">
-        <v>566920</v>
+        <v>685478</v>
       </c>
       <c r="F7" t="n">
-        <v>345178</v>
+        <v>348164</v>
       </c>
     </row>
     <row r="8">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>977116.0600000001</v>
+        <v>1047216.27</v>
       </c>
       <c r="D8" t="n">
-        <v>1313</v>
+        <v>1412</v>
       </c>
       <c r="E8" t="n">
-        <v>16888.2</v>
+        <v>18167.41</v>
       </c>
       <c r="F8" t="n">
-        <v>960227.86</v>
+        <v>1029048.86</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>580508.8</v>
+        <v>641433.8</v>
       </c>
       <c r="D9" t="n">
-        <v>589</v>
+        <v>656</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>577465.9399999999</v>
+        <v>638390.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>396607.26</v>
+        <v>405782.47</v>
       </c>
       <c r="D10" t="n">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="E10" t="n">
-        <v>13845.34</v>
+        <v>15124.55</v>
       </c>
       <c r="F10" t="n">
-        <v>382761.92</v>
+        <v>390657.92</v>
       </c>
     </row>
     <row r="11">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>306400</v>
+        <v>397600</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E11" t="n">
         <v>123000</v>
       </c>
       <c r="F11" t="n">
-        <v>183400</v>
+        <v>274600</v>
       </c>
     </row>
     <row r="12">
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>291765.9</v>
+        <v>297465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>107293.9</v>
+        <v>112993.9</v>
       </c>
       <c r="F12" t="n">
         <v>184472</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>285160</v>
+        <v>291100</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>255380</v>
+        <v>261320</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -6636,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27001.61</v>
+        <v>29297.61</v>
       </c>
       <c r="D15" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>6536.36</v>
+        <v>8434.360000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>20465.25</v>
+        <v>20863.25</v>
       </c>
     </row>
   </sheetData>
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1513756.8</v>
+        <v>1603908.8</v>
       </c>
       <c r="C2" t="n">
-        <v>316406.06</v>
+        <v>365562.06</v>
       </c>
       <c r="D2" t="n">
-        <v>32444</v>
+        <v>35641</v>
       </c>
       <c r="E2" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="F2" t="n">
-        <v>283962.06</v>
+        <v>329921.06</v>
       </c>
       <c r="G2" t="n">
-        <v>18.76</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="3">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2652364</v>
+        <v>2866890</v>
       </c>
       <c r="C3" t="n">
-        <v>325218.98</v>
+        <v>383467.98</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>325218.98</v>
+        <v>383467.98</v>
       </c>
       <c r="G3" t="n">
-        <v>12.26</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="4">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>977116.0600000001</v>
+        <v>1047216.27</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6765,13 +6765,13 @@
         <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="5">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>306400</v>
+        <v>397600</v>
       </c>
       <c r="C5" t="n">
-        <v>70400</v>
+        <v>91200</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6793,10 +6793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>70400</v>
+        <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>22.98</v>
+        <v>22.94</v>
       </c>
     </row>
     <row r="6">
@@ -6806,22 +6806,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>291765.9</v>
+        <v>297465.9</v>
       </c>
       <c r="C6" t="n">
-        <v>138913.9</v>
+        <v>152021.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="F6" t="n">
-        <v>136896</v>
+        <v>150004</v>
       </c>
       <c r="G6" t="n">
-        <v>46.92</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="7">
@@ -6831,22 +6831,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>285160</v>
+        <v>291100</v>
       </c>
       <c r="C7" t="n">
-        <v>260466.67</v>
+        <v>290266.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>18.59</v>
+        <v>18.21</v>
       </c>
       <c r="F7" t="n">
-        <v>207466.67</v>
+        <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>72.75</v>
+        <v>81.51000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27001.61</v>
+        <v>29297.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="C2" t="n">
-        <v>718636.65</v>
+        <v>793881.65</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>498</v>
+        <v>532</v>
       </c>
       <c r="C3" t="n">
-        <v>239288.4</v>
+        <v>253105.4</v>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>66363</v>
+        <v>96163</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>33000</v>
+        <v>54700</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>18476.66</v>
+        <v>29007</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>14187</v>
+        <v>20926.9</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>13888.9</v>
+        <v>20251.66</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>9683</v>
+        <v>16601</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7122,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>186600</v>
+        <v>193200</v>
       </c>
     </row>
     <row r="3">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>14900</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="4">
@@ -7191,14 +7191,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>6600</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="5">
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="6">
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>91127</v>
+        <v>104254</v>
       </c>
     </row>
     <row r="8">
@@ -7330,7 +7330,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7339,16 +7339,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="D12" t="n">
-        <v>57356</v>
+        <v>72238</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7357,16 +7357,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>21785</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7375,100 +7375,100 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>17790</v>
+        <v>20725.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5520</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>4032</v>
+        <v>7614.66</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>2490</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>628</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -7479,14 +7479,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>31619</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -7497,158 +7497,158 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>21780</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="D22" t="n">
-        <v>20696.5</v>
+        <v>62956</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D23" t="n">
-        <v>7614.66</v>
+        <v>26947</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>21785</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>5596</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>647</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>84</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>62383</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -7659,14 +7659,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="D30" t="n">
-        <v>14852</v>
+        <v>62592</v>
       </c>
     </row>
     <row r="31">
@@ -7677,14 +7677,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>362</v>
+        <v>14876</v>
       </c>
     </row>
     <row r="32">
@@ -7695,14 +7695,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>247</v>
+        <v>362</v>
       </c>
     </row>
     <row r="33">
@@ -7713,32 +7713,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D33" t="n">
-        <v>161</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>77918</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>38</v>
+        <v>77918</v>
       </c>
     </row>
     <row r="36">
@@ -7771,28 +7771,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>57968</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D38" t="n">
-        <v>3750</v>
+        <v>57996</v>
       </c>
     </row>
     <row r="39">
@@ -7821,14 +7821,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>598</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="40">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D40" t="n">
-        <v>394</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="41">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>598</v>
       </c>
     </row>
     <row r="42">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>38</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43">
@@ -7893,32 +7893,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>36400</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>12000</v>
+        <v>36400</v>
       </c>
     </row>
     <row r="46">
@@ -7947,14 +7947,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>200</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="47">
@@ -7965,14 +7965,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -7996,19 +7996,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>38327</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D50" t="n">
-        <v>9000</v>
+        <v>38327</v>
       </c>
     </row>
     <row r="51">
@@ -8037,14 +8037,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>342</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="52">
@@ -8055,14 +8055,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D52" t="n">
-        <v>143</v>
+        <v>342</v>
       </c>
     </row>
     <row r="53">
@@ -8073,14 +8073,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>57</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -8104,19 +8104,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>33494.67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56">
@@ -8127,14 +8127,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>6500</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="57">
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>4691</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="58">
@@ -8163,32 +8163,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D58" t="n">
-        <v>299</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>20272.9</v>
+        <v>299</v>
       </c>
     </row>
     <row r="60">
@@ -8199,14 +8199,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="D60" t="n">
-        <v>12396</v>
+        <v>24357.9</v>
       </c>
     </row>
     <row r="61">
@@ -8217,14 +8217,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D61" t="n">
-        <v>4173</v>
+        <v>12443</v>
       </c>
     </row>
     <row r="62">
@@ -8235,14 +8235,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D62" t="n">
-        <v>1269</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="63">
@@ -8253,14 +8253,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D63" t="n">
-        <v>209</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="64">
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
-        <v>38</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -8307,50 +8307,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>18399.98</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>8000</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="69">
@@ -8379,92 +8379,92 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>8019</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>48</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>6289</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1328</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8476,49 +8476,49 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>6800</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>76</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8527,46 +8527,46 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>9318</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>5500</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -8577,110 +8577,110 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>10621</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>2490</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>10009</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1000</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>299</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8689,46 +8689,46 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>8800</v>
+        <v>10009</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>398</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>43</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90">
@@ -8743,10 +8743,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -8787,10 +8805,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>271697.98</v>
+        <v>315097.98</v>
       </c>
     </row>
     <row r="3">
@@ -8800,10 +8818,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>225066.67</v>
+        <v>254866.67</v>
       </c>
     </row>
     <row r="4">
@@ -8813,10 +8831,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>141554.16</v>
+        <v>154494.16</v>
       </c>
     </row>
     <row r="5">
@@ -8826,10 +8844,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>133108</v>
+        <v>146216</v>
       </c>
     </row>
     <row r="6">
@@ -8839,10 +8857,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>102360</v>
+        <v>135360</v>
       </c>
     </row>
     <row r="7">
@@ -8852,10 +8870,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>70400</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="8">
@@ -8900,14 +8918,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19元青少年（体验课）</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>902</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>15723</v>
+        <v>25441</v>
       </c>
     </row>
   </sheetData>
@@ -8948,10 +8966,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C2" t="n">
-        <v>177002.33</v>
+        <v>181124.33</v>
       </c>
     </row>
     <row r="3">
@@ -8961,10 +8979,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>138334.5</v>
+        <v>142553.5</v>
       </c>
     </row>
     <row r="4">
@@ -8974,10 +8992,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C4" t="n">
-        <v>115542</v>
+        <v>135645</v>
       </c>
     </row>
     <row r="5">
@@ -8987,10 +9005,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>110481.98</v>
+        <v>110610.98</v>
       </c>
     </row>
     <row r="6">
@@ -9000,140 +9018,140 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" t="n">
-        <v>108797</v>
+        <v>108867</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>59385</v>
+        <v>66656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>53243</v>
+        <v>65985</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="C9" t="n">
-        <v>51836</v>
+        <v>62903</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>49164</v>
+        <v>62018</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>41747</v>
+        <v>54163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
-        <v>37200</v>
+        <v>49985</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>30185</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>19856</v>
+        <v>31756</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>18648</v>
+        <v>29838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C16" t="n">
-        <v>15371</v>
+        <v>26903</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>190460</v>
+        <v>235559</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+66.8%</t>
+          <t>+34.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>49201</v>
+        <v>89887</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+273.1%</t>
+          <t>+104.2%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15875</v>
+        <v>15909</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -611,11 +611,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-9148</v>
+        <v>-9120</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+70.5%</t>
+          <t>+71.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>304915</v>
+        <v>361124</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+55.7%</t>
+          <t>+31.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>194167</v>
+        <v>245078</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+80.4%</t>
+          <t>+43.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>324974</v>
+        <v>391449</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>218922</v>
+        <v>285397</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-84.2%</t>
+          <t>-87.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>200192</v>
+        <v>203014</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+90.7%</t>
+          <t>+88.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>150580</v>
+        <v>145339</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+124.1%</t>
+          <t>+132.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -831,19 +831,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>200489</v>
+        <v>230370</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+38.5%</t>
+          <t>+20.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>161903</v>
+        <v>171689</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+23.5%</t>
+          <t>+16.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -888,19 +888,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>217591</v>
+        <v>280445</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+40.7%</t>
+          <t>+9.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>184477</v>
+        <v>247322</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>587348</v>
+        <v>612148</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+18.9%</t>
+          <t>+14.1%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>450424</v>
+        <v>471224</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1008367</v>
+        <v>1073626</v>
       </c>
       <c r="E10" t="n">
         <v>11308</v>
       </c>
       <c r="F10" t="n">
-        <v>997059</v>
+        <v>1062318</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1029341</v>
+        <v>1014789</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1029341</v>
+        <v>1014789</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+4.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>372293</v>
+        <v>426472</v>
       </c>
       <c r="P10" t="n">
-        <v>624766</v>
+        <v>635845</v>
       </c>
       <c r="Q10" t="n">
-        <v>935671</v>
+        <v>1000930</v>
       </c>
     </row>
     <row r="11">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>174764</v>
+        <v>192897</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>149656</v>
+        <v>167789</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>181702</v>
+        <v>192100</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+82.0%</t>
+          <t>+72.1%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>179723</v>
+        <v>190121</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+67.2%</t>
+          <t>+58.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1165,43 +1165,43 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>390798</v>
+        <v>408275</v>
       </c>
       <c r="E13" t="n">
         <v>44984</v>
       </c>
       <c r="F13" t="n">
-        <v>345813</v>
+        <v>363290</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>267635</v>
+        <v>298276</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+46.0%</t>
+          <t>+36.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>208074</v>
+        <v>238715</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+66.2%</t>
+          <t>+52.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8748</v>
+        <v>26225</v>
       </c>
       <c r="O13" t="n">
         <v>11909</v>
@@ -1210,7 +1210,7 @@
         <v>325156</v>
       </c>
       <c r="Q13" t="n">
-        <v>66547</v>
+        <v>84024</v>
       </c>
     </row>
     <row r="14">
@@ -1248,19 +1248,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>202801</v>
+        <v>212952</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-17.7%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>184423</v>
+        <v>194574</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1311,19 +1311,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>132963</v>
+        <v>134157</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>117657</v>
+        <v>118851</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1413,13 +1413,13 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>296969</v>
+        <v>297284</v>
       </c>
       <c r="E17" t="n">
         <v>59158</v>
       </c>
       <c r="F17" t="n">
-        <v>237811</v>
+        <v>238126</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1433,23 +1433,23 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>256910</v>
+        <v>257611</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+15.6%</t>
+          <t>+15.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>211044</v>
+        <v>211745</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+12.5%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>43488</v>
+        <v>43803</v>
       </c>
       <c r="O17" t="n">
         <v>4361</v>
@@ -1458,7 +1458,7 @@
         <v>190162</v>
       </c>
       <c r="Q17" t="n">
-        <v>9463</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="18">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>399865</v>
+        <v>407163</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+83.9%</t>
+          <t>+80.6%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>348309</v>
+        <v>355607</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+88.7%</t>
+          <t>+84.8%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1539,43 +1539,43 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>231996</v>
+        <v>233196</v>
       </c>
       <c r="E19" t="n">
         <v>361</v>
       </c>
       <c r="F19" t="n">
-        <v>231635</v>
+        <v>232835</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>186561</v>
+        <v>201959</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+24.4%</t>
+          <t>+15.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>40563</v>
+        <v>55961</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+471.0%</t>
+          <t>+316.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>7655</v>
+        <v>8855</v>
       </c>
       <c r="O19" t="n">
         <v>29888</v>
@@ -1584,7 +1584,7 @@
         <v>194292</v>
       </c>
       <c r="Q19" t="n">
-        <v>71659</v>
+        <v>72859</v>
       </c>
     </row>
     <row r="20">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>336730</v>
+        <v>339326</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>280730</v>
+        <v>278326</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1663,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>6640398</v>
+        <v>6724650</v>
       </c>
       <c r="E21" t="n">
         <v>1285367</v>
       </c>
       <c r="F21" t="n">
-        <v>5355030</v>
+        <v>5439282</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5427570</v>
+        <v>5797703</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+22.3%</t>
+          <t>+16.0%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4356300</v>
+        <v>4679549</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+22.9%</t>
+          <t>+16.2%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>70886</v>
+        <v>89879</v>
       </c>
       <c r="O21" t="n">
-        <v>2470807</v>
+        <v>2524987</v>
       </c>
       <c r="P21" t="n">
-        <v>2813736</v>
+        <v>2824815</v>
       </c>
       <c r="Q21" t="n">
-        <v>2881608</v>
+        <v>2965860</v>
       </c>
     </row>
   </sheetData>
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D3" t="n">
-        <v>1506</v>
+        <v>1602.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1411</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>859406</v>
+        <v>913585</v>
       </c>
       <c r="D4" t="n">
-        <v>2665298</v>
+        <v>2676377</v>
       </c>
       <c r="E4" t="n">
-        <v>1734995</v>
+        <v>1819247</v>
       </c>
     </row>
     <row r="5">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>372293</v>
+        <v>426472</v>
       </c>
       <c r="D13" t="n">
-        <v>624766</v>
+        <v>635845</v>
       </c>
       <c r="E13" t="n">
-        <v>935671</v>
+        <v>1000930</v>
       </c>
     </row>
     <row r="14">
@@ -2164,7 +2164,7 @@
         <v>325156</v>
       </c>
       <c r="E16" t="n">
-        <v>66547</v>
+        <v>84024</v>
       </c>
     </row>
     <row r="17">
@@ -2248,7 +2248,7 @@
         <v>190162</v>
       </c>
       <c r="E20" t="n">
-        <v>9463</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="21">
@@ -2290,7 +2290,7 @@
         <v>194292</v>
       </c>
       <c r="E22" t="n">
-        <v>71659</v>
+        <v>72859</v>
       </c>
     </row>
     <row r="23">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2470807</v>
+        <v>2524987</v>
       </c>
       <c r="D25" t="n">
-        <v>2813736</v>
+        <v>2824815</v>
       </c>
       <c r="E25" t="n">
-        <v>2881608</v>
+        <v>2965860</v>
       </c>
     </row>
   </sheetData>
@@ -4173,11 +4173,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>209058.8</v>
+        <v>214823.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>169192.13</v>
+        <v>174956.63</v>
       </c>
     </row>
     <row r="3">
@@ -4207,11 +4207,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>53603.2</v>
+        <v>53844.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53603.2</v>
+        <v>53844.1</v>
       </c>
     </row>
     <row r="4">
@@ -4241,11 +4241,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>49902.6</v>
+        <v>60169.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>49902.6</v>
+        <v>60169.8</v>
       </c>
     </row>
     <row r="5">
@@ -4309,11 +4309,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>49685.36</v>
+        <v>50890.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49685.36</v>
+        <v>50890.16</v>
       </c>
     </row>
     <row r="7">
@@ -5261,11 +5261,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>91127.84999999999</v>
+        <v>91443.25</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76627.84999999999</v>
+        <v>76943.25</v>
       </c>
     </row>
     <row r="35">
@@ -5635,11 +5635,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>43411.64000000001</v>
+        <v>75876.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>43411.64000000001</v>
+        <v>75876.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5737,11 +5737,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>66421</v>
+        <v>77268</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>66421</v>
+        <v>77268</v>
       </c>
     </row>
     <row r="49">
@@ -5771,11 +5771,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>142401.5</v>
+        <v>148555.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>142401.5</v>
+        <v>148555.04</v>
       </c>
     </row>
     <row r="50">
@@ -5873,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>216049</v>
+        <v>229564.64</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>216049</v>
+        <v>229564.64</v>
       </c>
     </row>
     <row r="53">
@@ -5941,11 +5941,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>200551</v>
+        <v>201951</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>200551</v>
+        <v>201951</v>
       </c>
     </row>
     <row r="55">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1047216.27</v>
+        <v>1119548.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1412</v>
+        <v>1575</v>
       </c>
       <c r="E8" t="n">
         <v>18167.41</v>
       </c>
       <c r="F8" t="n">
-        <v>1029048.86</v>
+        <v>1101380.84</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>641433.8</v>
+        <v>658712.39</v>
       </c>
       <c r="D9" t="n">
-        <v>656</v>
+        <v>688</v>
       </c>
       <c r="E9" t="n">
         <v>3042.86</v>
       </c>
       <c r="F9" t="n">
-        <v>638390.9399999999</v>
+        <v>655669.53</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>405782.47</v>
+        <v>460835.86</v>
       </c>
       <c r="D10" t="n">
-        <v>756</v>
+        <v>887</v>
       </c>
       <c r="E10" t="n">
         <v>15124.55</v>
       </c>
       <c r="F10" t="n">
-        <v>390657.92</v>
+        <v>445711.31</v>
       </c>
     </row>
     <row r="11">
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>297465.9</v>
+        <v>307465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>112993.9</v>
       </c>
       <c r="F12" t="n">
-        <v>184472</v>
+        <v>194472</v>
       </c>
     </row>
     <row r="13">
@@ -6636,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29297.61</v>
+        <v>31217.61</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
         <v>8434.360000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>20863.25</v>
+        <v>22783.25</v>
       </c>
     </row>
   </sheetData>
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1047216.27</v>
+        <v>1119548.25</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6771,7 +6771,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>297465.9</v>
+        <v>307465.9</v>
       </c>
       <c r="C6" t="n">
         <v>152021.9</v>
@@ -6815,13 +6815,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="F6" t="n">
         <v>150004</v>
       </c>
       <c r="G6" t="n">
-        <v>50.43</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="7">
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29297.61</v>
+        <v>31217.61</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,25 +528,25 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>317655</v>
+        <v>431274</v>
       </c>
       <c r="E2" t="n">
-        <v>134066</v>
+        <v>134123</v>
       </c>
       <c r="F2" t="n">
-        <v>183589</v>
+        <v>297151</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+34.9%</t>
+          <t>+83.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+104.2%</t>
+          <t>+230.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2047</v>
       </c>
       <c r="E3" t="n">
         <v>17617</v>
       </c>
       <c r="F3" t="n">
-        <v>-15598</v>
+        <v>-15570</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -607,7 +607,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.3%</t>
+          <t>-87.1%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -615,7 +615,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+71.0%</t>
+          <t>+70.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,25 +638,25 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>474893</v>
+        <v>484315</v>
       </c>
       <c r="E4" t="n">
-        <v>124529</v>
+        <v>132703</v>
       </c>
       <c r="F4" t="n">
-        <v>350364</v>
+        <v>351611</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+31.5%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -672,7 +672,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+43.0%</t>
+          <t>+43.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,13 +695,13 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224419</v>
+        <v>224496</v>
       </c>
       <c r="E5" t="n">
-        <v>189822</v>
+        <v>197822</v>
       </c>
       <c r="F5" t="n">
-        <v>34596</v>
+        <v>26673</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -729,7 +729,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>-90.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,25 +752,25 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>381749</v>
+        <v>457528</v>
       </c>
       <c r="E6" t="n">
-        <v>44245</v>
+        <v>52496</v>
       </c>
       <c r="F6" t="n">
-        <v>337503</v>
+        <v>405031</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+88.0%</t>
+          <t>+125.4%</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -786,7 +786,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+132.2%</t>
+          <t>+178.7%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,25 +809,25 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>277672</v>
+        <v>311419</v>
       </c>
       <c r="E7" t="n">
-        <v>77690</v>
+        <v>78062</v>
       </c>
       <c r="F7" t="n">
-        <v>199982</v>
+        <v>233357</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -835,7 +835,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+20.5%</t>
+          <t>+35.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+35.9%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,25 +866,25 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>306180</v>
+        <v>349022</v>
       </c>
       <c r="E8" t="n">
-        <v>78238</v>
+        <v>78580</v>
       </c>
       <c r="F8" t="n">
-        <v>227942</v>
+        <v>270442</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -892,7 +892,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,25 +923,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>698349</v>
+        <v>728727</v>
       </c>
       <c r="E9" t="n">
         <v>258700</v>
       </c>
       <c r="F9" t="n">
-        <v>439649</v>
+        <v>470027</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+14.1%</t>
+          <t>+19.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -957,7 +957,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,13 +980,13 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1073626</v>
+        <v>1073645</v>
       </c>
       <c r="E10" t="n">
         <v>11308</v>
       </c>
       <c r="F10" t="n">
-        <v>1062318</v>
+        <v>1062337</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1017,13 +1017,13 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>426472</v>
+        <v>426491</v>
       </c>
       <c r="P10" t="n">
         <v>635845</v>
       </c>
       <c r="Q10" t="n">
-        <v>1000930</v>
+        <v>1000949</v>
       </c>
     </row>
     <row r="11">
@@ -1041,23 +1041,23 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>171155</v>
+        <v>172549</v>
       </c>
       <c r="E11" t="n">
-        <v>26399</v>
+        <v>36399</v>
       </c>
       <c r="F11" t="n">
-        <v>144755</v>
+        <v>136149</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1073,17 +1073,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>19758</v>
+        <v>20356</v>
       </c>
       <c r="P11" t="n">
-        <v>124787</v>
+        <v>115583</v>
       </c>
       <c r="Q11" t="n">
         <v>78787</v>
@@ -1104,23 +1104,23 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>330614</v>
+        <v>347513</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>300538</v>
+        <v>317437</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+72.1%</t>
+          <t>+80.9%</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1136,18 +1136,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+58.1%</t>
+          <t>+67.0%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>61879</v>
+        <v>62178</v>
       </c>
       <c r="P12" t="n">
-        <v>238659</v>
+        <v>255259</v>
       </c>
       <c r="Q12" t="n">
-        <v>28132</v>
+        <v>35031</v>
       </c>
     </row>
     <row r="13">
@@ -1165,23 +1165,23 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>408275</v>
+        <v>416207</v>
       </c>
       <c r="E13" t="n">
-        <v>44984</v>
+        <v>45013</v>
       </c>
       <c r="F13" t="n">
-        <v>363290</v>
+        <v>371194</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+36.9%</t>
+          <t>+39.5%</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1197,20 +1197,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+52.2%</t>
+          <t>+55.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26225</v>
+        <v>26376</v>
       </c>
       <c r="O13" t="n">
-        <v>11909</v>
+        <v>12661</v>
       </c>
       <c r="P13" t="n">
-        <v>325156</v>
+        <v>332156</v>
       </c>
       <c r="Q13" t="n">
-        <v>84024</v>
+        <v>91530</v>
       </c>
     </row>
     <row r="14">
@@ -1228,23 +1228,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>166999</v>
+        <v>192199</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>152133</v>
+        <v>177333</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1270,7 +1270,7 @@
         <v>40511</v>
       </c>
       <c r="P14" t="n">
-        <v>101688</v>
+        <v>126888</v>
       </c>
       <c r="Q14" t="n">
         <v>26373</v>
@@ -1291,23 +1291,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>99313</v>
+        <v>100210</v>
       </c>
       <c r="E15" t="n">
         <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>83437</v>
+        <v>84334</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1323,18 +1323,18 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7114</v>
+        <v>7613</v>
       </c>
       <c r="P15" t="n">
-        <v>76323</v>
+        <v>76721</v>
       </c>
       <c r="Q15" t="n">
-        <v>36461</v>
+        <v>36960</v>
       </c>
     </row>
     <row r="16">
@@ -1352,23 +1352,23 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>227549</v>
+        <v>239947</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>209151</v>
+        <v>221549</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>+10.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1384,15 +1384,15 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>8968</v>
+        <v>9366</v>
       </c>
       <c r="P16" t="n">
-        <v>200183</v>
+        <v>212183</v>
       </c>
       <c r="Q16" t="n">
         <v>41087</v>
@@ -1413,23 +1413,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>297284</v>
+        <v>327376</v>
       </c>
       <c r="E17" t="n">
-        <v>59158</v>
+        <v>88491</v>
       </c>
       <c r="F17" t="n">
-        <v>238126</v>
+        <v>238885</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+15.4%</t>
+          <t>+27.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1445,20 +1445,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+12.5%</t>
+          <t>+12.8%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>43803</v>
       </c>
       <c r="O17" t="n">
-        <v>4361</v>
+        <v>6055</v>
       </c>
       <c r="P17" t="n">
-        <v>190162</v>
+        <v>189226</v>
       </c>
       <c r="Q17" t="n">
-        <v>9778</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="18">
@@ -1476,23 +1476,23 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>735249</v>
+        <v>789443</v>
       </c>
       <c r="E18" t="n">
-        <v>77994</v>
+        <v>84494</v>
       </c>
       <c r="F18" t="n">
-        <v>657255</v>
+        <v>704949</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+80.6%</t>
+          <t>+93.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1508,20 +1508,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+84.8%</t>
+          <t>+98.2%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>215642</v>
+        <v>216040</v>
       </c>
       <c r="P18" t="n">
-        <v>440763</v>
+        <v>488059</v>
       </c>
       <c r="Q18" t="n">
-        <v>404367</v>
+        <v>409347</v>
       </c>
     </row>
     <row r="19">
@@ -1539,23 +1539,23 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>233196</v>
+        <v>254472</v>
       </c>
       <c r="E19" t="n">
         <v>361</v>
       </c>
       <c r="F19" t="n">
-        <v>232835</v>
+        <v>254111</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+15.5%</t>
+          <t>+26.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1571,20 +1571,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+316.1%</t>
+          <t>+354.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>8855</v>
       </c>
       <c r="O19" t="n">
-        <v>29888</v>
+        <v>35266</v>
       </c>
       <c r="P19" t="n">
-        <v>194292</v>
+        <v>210190</v>
       </c>
       <c r="Q19" t="n">
-        <v>72859</v>
+        <v>77839</v>
       </c>
     </row>
     <row r="20">
@@ -1602,23 +1602,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>283526</v>
+        <v>307469</v>
       </c>
       <c r="E20" t="n">
-        <v>47926</v>
+        <v>48215</v>
       </c>
       <c r="F20" t="n">
-        <v>235600</v>
+        <v>259254</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1634,18 +1634,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>87082</v>
+        <v>86736</v>
       </c>
       <c r="P20" t="n">
-        <v>148518</v>
+        <v>172518</v>
       </c>
       <c r="Q20" t="n">
-        <v>36444</v>
+        <v>36098</v>
       </c>
     </row>
     <row r="21">
@@ -1663,25 +1663,25 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>6724650</v>
+        <v>7224786</v>
       </c>
       <c r="E21" t="n">
-        <v>1285367</v>
+        <v>1361715</v>
       </c>
       <c r="F21" t="n">
-        <v>5439282</v>
+        <v>5863070</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+16.0%</t>
+          <t>+24.6%</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1697,20 +1697,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+16.2%</t>
+          <t>+25.3%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>89879</v>
+        <v>90031</v>
       </c>
       <c r="O21" t="n">
-        <v>2524987</v>
+        <v>2796048</v>
       </c>
       <c r="P21" t="n">
-        <v>2824815</v>
+        <v>2977390</v>
       </c>
       <c r="Q21" t="n">
-        <v>2965860</v>
+        <v>3266609</v>
       </c>
     </row>
   </sheetData>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>196</v>
+        <v>479</v>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>559.8</v>
+        <v>1341.9</v>
       </c>
       <c r="E2" t="n">
-        <v>120264</v>
+        <v>145922</v>
       </c>
     </row>
     <row r="3">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" t="n">
-        <v>1602.4</v>
+        <v>1272.3</v>
       </c>
       <c r="E3" t="n">
-        <v>1489</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="4">
@@ -1799,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>455</v>
+        <v>815</v>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="D4" t="n">
-        <v>1236.3</v>
+        <v>1533.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4418</v>
+        <v>2610</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1318383</v>
+        <v>1554975</v>
       </c>
       <c r="D2" t="n">
-        <v>-2</v>
+        <v>13722</v>
       </c>
       <c r="E2" t="n">
-        <v>995386</v>
+        <v>1244706</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>304409</v>
+        <v>334189</v>
       </c>
       <c r="D3" t="n">
-        <v>135240</v>
+        <v>135838</v>
       </c>
       <c r="E3" t="n">
-        <v>151997</v>
+        <v>176797</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>913585</v>
+        <v>923274</v>
       </c>
       <c r="D4" t="n">
-        <v>2676377</v>
+        <v>2814630</v>
       </c>
       <c r="E4" t="n">
-        <v>1819247</v>
+        <v>1845875</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>187184</v>
+        <v>287546</v>
       </c>
       <c r="D5" t="n">
-        <v>-3595</v>
+        <v>9605</v>
       </c>
       <c r="E5" t="n">
-        <v>184391</v>
+        <v>296957</v>
       </c>
     </row>
     <row r="6">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15733</v>
+        <v>-15705</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-5598</v>
+        <v>-5570</v>
       </c>
     </row>
     <row r="7">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342133</v>
+        <v>342856</v>
       </c>
       <c r="D7" t="n">
-        <v>8230</v>
+        <v>8755</v>
       </c>
       <c r="E7" t="n">
-        <v>332578</v>
+        <v>333825</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29408</v>
+        <v>21485</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-85563</v>
+        <v>-85486</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>330577</v>
+        <v>398105</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>269740</v>
+        <v>337268</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>198264</v>
+        <v>231639</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>105088</v>
+        <v>138463</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>246547</v>
+        <v>289047</v>
       </c>
       <c r="D11" t="n">
         <v>-18605</v>
       </c>
       <c r="E11" t="n">
-        <v>194748</v>
+        <v>229248</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>304409</v>
+        <v>334189</v>
       </c>
       <c r="D12" t="n">
-        <v>135240</v>
+        <v>135838</v>
       </c>
       <c r="E12" t="n">
-        <v>151997</v>
+        <v>176797</v>
       </c>
     </row>
     <row r="13">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>426472</v>
+        <v>426491</v>
       </c>
       <c r="D13" t="n">
         <v>635845</v>
       </c>
       <c r="E13" t="n">
-        <v>1000930</v>
+        <v>1000949</v>
       </c>
     </row>
     <row r="14">
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19758</v>
+        <v>20356</v>
       </c>
       <c r="D14" t="n">
-        <v>124787</v>
+        <v>115583</v>
       </c>
       <c r="E14" t="n">
         <v>78787</v>
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>61879</v>
+        <v>62178</v>
       </c>
       <c r="D15" t="n">
-        <v>238659</v>
+        <v>255259</v>
       </c>
       <c r="E15" t="n">
-        <v>28132</v>
+        <v>35031</v>
       </c>
     </row>
     <row r="16">
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11909</v>
+        <v>12661</v>
       </c>
       <c r="D16" t="n">
-        <v>325156</v>
+        <v>332156</v>
       </c>
       <c r="E16" t="n">
-        <v>84024</v>
+        <v>91530</v>
       </c>
     </row>
     <row r="17">
@@ -2182,7 +2182,7 @@
         <v>40511</v>
       </c>
       <c r="D17" t="n">
-        <v>101688</v>
+        <v>126888</v>
       </c>
       <c r="E17" t="n">
         <v>26373</v>
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7114</v>
+        <v>7613</v>
       </c>
       <c r="D18" t="n">
-        <v>76323</v>
+        <v>76721</v>
       </c>
       <c r="E18" t="n">
-        <v>36461</v>
+        <v>36960</v>
       </c>
     </row>
     <row r="19">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8968</v>
+        <v>9366</v>
       </c>
       <c r="D19" t="n">
-        <v>200183</v>
+        <v>212183</v>
       </c>
       <c r="E19" t="n">
         <v>41087</v>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4361</v>
+        <v>6055</v>
       </c>
       <c r="D20" t="n">
-        <v>190162</v>
+        <v>189226</v>
       </c>
       <c r="E20" t="n">
-        <v>9778</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>215642</v>
+        <v>216040</v>
       </c>
       <c r="D21" t="n">
-        <v>440763</v>
+        <v>488059</v>
       </c>
       <c r="E21" t="n">
-        <v>404367</v>
+        <v>409347</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>29888</v>
+        <v>35266</v>
       </c>
       <c r="D22" t="n">
-        <v>194292</v>
+        <v>210190</v>
       </c>
       <c r="E22" t="n">
-        <v>72859</v>
+        <v>77839</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>87082</v>
+        <v>86736</v>
       </c>
       <c r="D23" t="n">
-        <v>148518</v>
+        <v>172518</v>
       </c>
       <c r="E23" t="n">
-        <v>36444</v>
+        <v>36098</v>
       </c>
     </row>
     <row r="24">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-11391</v>
+        <v>-16391</v>
       </c>
       <c r="D24" t="n">
         <v>13200</v>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2524987</v>
+        <v>2796048</v>
       </c>
       <c r="D25" t="n">
-        <v>2824815</v>
+        <v>2977390</v>
       </c>
       <c r="E25" t="n">
-        <v>2965860</v>
+        <v>3266609</v>
       </c>
     </row>
   </sheetData>
@@ -2437,19 +2437,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>119400</v>
+        <v>156416</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>81273.34</v>
+        <v>118289.34</v>
       </c>
     </row>
     <row r="3">
@@ -2479,19 +2479,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>6960</v>
+        <v>62520</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2499,11 +2499,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>278.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-12429</v>
+        <v>43131</v>
       </c>
     </row>
     <row r="4">
@@ -2521,19 +2521,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>43658</v>
+        <v>48638</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-902</v>
+        <v>4078</v>
       </c>
     </row>
     <row r="5">
@@ -2563,19 +2563,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>64780</v>
+        <v>74740</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>58382.5</v>
+        <v>68342.5</v>
       </c>
     </row>
     <row r="6">
@@ -2605,19 +2605,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>43400</v>
+        <v>48380</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41720</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="7">
@@ -2689,19 +2689,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>21540</v>
+        <v>54340</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2709,11 +2709,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>218.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-25610</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="9">
@@ -2731,19 +2731,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>36480</v>
+        <v>43080</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31501</v>
+        <v>38101</v>
       </c>
     </row>
     <row r="10">
@@ -2857,19 +2857,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>59110</v>
+        <v>64090</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>52510</v>
+        <v>57490</v>
       </c>
     </row>
     <row r="13">
@@ -3025,19 +3025,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>60136</v>
+        <v>60734</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3045,11 +3045,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>23736</v>
+        <v>24334</v>
       </c>
     </row>
     <row r="17">
@@ -3277,19 +3277,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>26400</v>
+        <v>51200</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3297,11 +3297,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>18800</v>
+        <v>43600</v>
       </c>
     </row>
     <row r="23">
@@ -3457,19 +3457,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13766</v>
+        <v>18746</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>128450</v>
+        <v>123470</v>
       </c>
     </row>
     <row r="27">
@@ -3613,19 +3613,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>67720</v>
+        <v>72700</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>50740</v>
+        <v>55720</v>
       </c>
     </row>
     <row r="31">
@@ -3655,19 +3655,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>163474</v>
+        <v>173434</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>116594</v>
+        <v>126554</v>
       </c>
     </row>
     <row r="32">
@@ -3697,19 +3697,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>73680</v>
+        <v>78660</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3717,11 +3717,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>69700</v>
+        <v>74680</v>
       </c>
     </row>
     <row r="33">
@@ -3739,19 +3739,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>57382</v>
+        <v>62362</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>32602</v>
+        <v>37582</v>
       </c>
     </row>
     <row r="34">
@@ -3781,19 +3781,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>58019</v>
+        <v>67979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>54419</v>
+        <v>64379</v>
       </c>
     </row>
     <row r="35">
@@ -3823,19 +3823,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>57710</v>
+        <v>72650</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>57710</v>
+        <v>72650</v>
       </c>
     </row>
     <row r="36">
@@ -3865,31 +3865,31 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>62318</v>
+        <v>82238</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>58338</v>
+        <v>74278</v>
       </c>
     </row>
     <row r="37">
@@ -3907,19 +3907,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>63096</v>
+        <v>83016</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3927,11 +3927,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>55136</v>
+        <v>75056</v>
       </c>
     </row>
     <row r="38">
@@ -4045,19 +4045,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>8780</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41">
@@ -4075,19 +4075,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>33860</v>
+        <v>48800</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4095,11 +4095,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>32180</v>
+        <v>47120</v>
       </c>
     </row>
   </sheetData>
@@ -4173,11 +4173,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>214823.3</v>
+        <v>215574.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>174956.63</v>
+        <v>175708.03</v>
       </c>
     </row>
     <row r="3">
@@ -4241,11 +4241,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60169.8</v>
+        <v>60567.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60169.8</v>
+        <v>60567.8</v>
       </c>
     </row>
     <row r="5">
@@ -4309,11 +4309,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>50890.16</v>
+        <v>57490.16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>50890.16</v>
+        <v>57490.16</v>
       </c>
     </row>
     <row r="7">
@@ -4377,11 +4377,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26108.11</v>
+        <v>26506.11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26108.11</v>
+        <v>26506.11</v>
       </c>
     </row>
     <row r="9">
@@ -4445,11 +4445,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>54266.7</v>
+        <v>62266.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>54266.7</v>
+        <v>62266.7</v>
       </c>
     </row>
     <row r="11">
@@ -4513,11 +4513,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>102907.7</v>
+        <v>110805.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>102907.7</v>
+        <v>110805.7</v>
       </c>
     </row>
     <row r="13">
@@ -4615,11 +4615,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>36188</v>
+        <v>48188</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4627,11 +4627,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>26990</v>
+        <v>38990</v>
       </c>
     </row>
     <row r="16">
@@ -4649,11 +4649,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>75982</v>
+        <v>76380</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4661,11 +4661,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>66782</v>
+        <v>67180</v>
       </c>
     </row>
     <row r="17">
@@ -4717,11 +4717,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>10310.6</v>
+        <v>35510.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10310.6</v>
+        <v>35510.6</v>
       </c>
     </row>
     <row r="19">
@@ -4887,11 +4887,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>90778</v>
+        <v>114778</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>90778</v>
+        <v>114778</v>
       </c>
     </row>
     <row r="24">
@@ -5091,11 +5091,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>84178</v>
+        <v>85174</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>77178</v>
+        <v>78174</v>
       </c>
     </row>
     <row r="30">
@@ -5129,19 +5129,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38176</v>
+        <v>28176</v>
       </c>
     </row>
     <row r="31">
@@ -5159,11 +5159,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>12098</v>
+        <v>12496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12098</v>
+        <v>12496</v>
       </c>
     </row>
     <row r="32">
@@ -5227,11 +5227,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>94773.64</v>
+        <v>124069.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5239,11 +5239,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>60973.64</v>
+        <v>90269.64</v>
       </c>
     </row>
     <row r="34">
@@ -5265,19 +5265,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>14500</v>
+        <v>39833.4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>76943.25</v>
+        <v>51609.85</v>
       </c>
     </row>
     <row r="35">
@@ -5333,19 +5333,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>200</v>
+        <v>6200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>42788</v>
+        <v>36788</v>
       </c>
     </row>
     <row r="37">
@@ -5363,23 +5363,23 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38">
@@ -5465,23 +5465,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>461410</v>
+        <v>483008</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>59800</v>
+        <v>66300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>401610</v>
+        <v>416708</v>
       </c>
     </row>
     <row r="41">
@@ -5499,11 +5499,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>69389</v>
+        <v>101189</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>69389</v>
+        <v>101189</v>
       </c>
     </row>
     <row r="42">
@@ -5533,11 +5533,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>117770</v>
+        <v>118566</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5545,11 +5545,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110170</v>
+        <v>110966</v>
       </c>
     </row>
     <row r="43">
@@ -5975,11 +5975,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>90393</v>
+        <v>96993</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5987,11 +5987,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>80393</v>
+        <v>86993</v>
       </c>
     </row>
     <row r="56">
@@ -6009,11 +6009,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>31194</v>
+        <v>41194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6021,11 +6021,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>26194</v>
+        <v>36194</v>
       </c>
     </row>
     <row r="57">
@@ -6179,11 +6179,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>27368</v>
+        <v>37368</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>27368</v>
+        <v>37368</v>
       </c>
     </row>
     <row r="62">
@@ -6213,11 +6213,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>61073</v>
+        <v>51572</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6225,11 +6225,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>45273</v>
+        <v>35772</v>
       </c>
     </row>
     <row r="63">
@@ -6247,11 +6247,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9472</v>
+        <v>9870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>157.9%</t>
+          <t>164.5%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9472</v>
+        <v>9870</v>
       </c>
     </row>
   </sheetData>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1603908.8</v>
+        <v>1819191.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8132</v>
+        <v>8542</v>
       </c>
       <c r="E2" t="n">
-        <v>1398507.8</v>
+        <v>1590121.8</v>
       </c>
       <c r="F2" t="n">
-        <v>205401</v>
+        <v>229070</v>
       </c>
     </row>
     <row r="3">
@@ -6348,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1382230</v>
+        <v>1583350</v>
       </c>
       <c r="D3" t="n">
-        <v>371</v>
+        <v>410</v>
       </c>
       <c r="E3" t="n">
-        <v>1192187</v>
+        <v>1369667</v>
       </c>
       <c r="F3" t="n">
-        <v>190043</v>
+        <v>213683</v>
       </c>
     </row>
     <row r="4">
@@ -6372,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>221678.8</v>
+        <v>235841.8</v>
       </c>
       <c r="D4" t="n">
-        <v>7761</v>
+        <v>8132</v>
       </c>
       <c r="E4" t="n">
-        <v>206320.8</v>
+        <v>220454.8</v>
       </c>
       <c r="F4" t="n">
-        <v>15358</v>
+        <v>15387</v>
       </c>
     </row>
     <row r="5">
@@ -6396,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2866890</v>
+        <v>3048762</v>
       </c>
       <c r="D5" t="n">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="E5" t="n">
-        <v>742696</v>
+        <v>757270</v>
       </c>
       <c r="F5" t="n">
-        <v>2124194</v>
+        <v>2291492</v>
       </c>
     </row>
     <row r="6">
@@ -6420,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1823248</v>
+        <v>1988954</v>
       </c>
       <c r="D6" t="n">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="E6" t="n">
-        <v>57218</v>
+        <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>1766030</v>
+        <v>1931138</v>
       </c>
     </row>
     <row r="7">
@@ -6444,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1033642</v>
+        <v>1049808</v>
       </c>
       <c r="D7" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E7" t="n">
-        <v>685478</v>
+        <v>699454</v>
       </c>
       <c r="F7" t="n">
-        <v>348164</v>
+        <v>350354</v>
       </c>
     </row>
     <row r="8">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1119548.25</v>
+        <v>1123240.05</v>
       </c>
       <c r="D8" t="n">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="E8" t="n">
-        <v>18167.41</v>
+        <v>20472.81</v>
       </c>
       <c r="F8" t="n">
-        <v>1101380.84</v>
+        <v>1102767.24</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>658712.39</v>
+        <v>659769.1899999999</v>
       </c>
       <c r="D9" t="n">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E9" t="n">
-        <v>3042.86</v>
+        <v>3548.26</v>
       </c>
       <c r="F9" t="n">
-        <v>655669.53</v>
+        <v>656220.9300000001</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>460835.86</v>
+        <v>463470.86</v>
       </c>
       <c r="D10" t="n">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="E10" t="n">
-        <v>15124.55</v>
+        <v>16924.55</v>
       </c>
       <c r="F10" t="n">
-        <v>445711.31</v>
+        <v>446546.31</v>
       </c>
     </row>
     <row r="11">
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>397600</v>
+        <v>492800</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>123000</v>
+        <v>218200</v>
       </c>
       <c r="F11" t="n">
         <v>274600</v>
@@ -6636,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>31217.61</v>
+        <v>35306.61</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
-        <v>8434.360000000001</v>
+        <v>10632.36</v>
       </c>
       <c r="F15" t="n">
-        <v>22783.25</v>
+        <v>24674.25</v>
       </c>
     </row>
   </sheetData>
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1603908.8</v>
+        <v>1819191.8</v>
       </c>
       <c r="C2" t="n">
-        <v>365562.06</v>
+        <v>379236.86</v>
       </c>
       <c r="D2" t="n">
-        <v>35641</v>
+        <v>45346</v>
       </c>
       <c r="E2" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="F2" t="n">
-        <v>329921.06</v>
+        <v>333890.86</v>
       </c>
       <c r="G2" t="n">
-        <v>20.57</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="3">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2866890</v>
+        <v>3048762</v>
       </c>
       <c r="C3" t="n">
-        <v>383467.98</v>
+        <v>442301.38</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>383467.98</v>
+        <v>442301.38</v>
       </c>
       <c r="G3" t="n">
-        <v>13.38</v>
+        <v>14.51</v>
       </c>
     </row>
     <row r="4">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1119548.25</v>
+        <v>1123240.05</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>397600</v>
+        <v>492800</v>
       </c>
       <c r="C5" t="n">
         <v>91200</v>
@@ -6796,7 +6796,7 @@
         <v>91200</v>
       </c>
       <c r="G5" t="n">
-        <v>22.94</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="6">
@@ -6809,7 +6809,7 @@
         <v>307465.9</v>
       </c>
       <c r="C6" t="n">
-        <v>152021.9</v>
+        <v>154862.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6818,10 +6818,10 @@
         <v>0.66</v>
       </c>
       <c r="F6" t="n">
-        <v>150004</v>
+        <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>48.79</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="7">
@@ -6881,16 +6881,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31217.61</v>
+        <v>35306.61</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="C2" t="n">
-        <v>793881.65</v>
+        <v>833431.05</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="C3" t="n">
-        <v>253105.4</v>
+        <v>262180.4</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>96163</v>
+        <v>105163</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C5" t="n">
+        <v>69200</v>
+      </c>
+      <c r="D5" t="n">
         <v>18</v>
-      </c>
-      <c r="C5" t="n">
-        <v>54700</v>
-      </c>
-      <c r="D5" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>29007</v>
+        <v>29026</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -7018,33 +7018,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>20926.9</v>
+        <v>23276.66</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>20251.66</v>
+        <v>21982.7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>16601</v>
+        <v>16687</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>104254</v>
+        <v>112254</v>
       </c>
     </row>
     <row r="8">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>72238</v>
+        <v>72257</v>
       </c>
     </row>
     <row r="13">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>20725.5</v>
+        <v>20763.5</v>
       </c>
     </row>
     <row r="15">
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>62956</v>
+        <v>63116</v>
       </c>
     </row>
     <row r="23">
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="D23" t="n">
-        <v>26947</v>
+        <v>33855</v>
       </c>
     </row>
     <row r="24">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>5596</v>
+        <v>5647</v>
       </c>
     </row>
     <row r="26">
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D26" t="n">
-        <v>4070</v>
+        <v>5087.8</v>
       </c>
     </row>
     <row r="27">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2490</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="28">
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D28" t="n">
-        <v>647</v>
+        <v>666</v>
       </c>
     </row>
     <row r="29">
@@ -7654,109 +7654,109 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>95</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>62592</v>
+        <v>58733.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>14876</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>362</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>247</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>161</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>77918</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>38</v>
+        <v>77918</v>
       </c>
     </row>
     <row r="37">
@@ -7785,56 +7785,56 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>57996</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>14839</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7843,142 +7843,142 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="D40" t="n">
-        <v>3769</v>
+        <v>62744</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>598</v>
+        <v>14895</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>394</v>
+        <v>381</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D44" t="n">
-        <v>38</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>36400</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D46" t="n">
-        <v>22500</v>
+        <v>57996</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>200</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7987,208 +7987,208 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>29</v>
+        <v>4084</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>29</v>
+        <v>598</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>38327</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>9000</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>342</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="D53" t="n">
-        <v>143</v>
+        <v>25720.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="D54" t="n">
-        <v>57</v>
+        <v>16461</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D55" t="n">
-        <v>57</v>
+        <v>8742</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D56" t="n">
-        <v>33494.67</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D57" t="n">
-        <v>6500</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>4691</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>299</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60">
@@ -8199,20 +8199,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>24357.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8221,172 +8221,172 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="D61" t="n">
-        <v>12443</v>
+        <v>38327</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>5872</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D63" t="n">
-        <v>1269</v>
+        <v>641</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>209</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>19</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>15019</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D69" t="n">
-        <v>15009</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>48</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71">
@@ -8419,142 +8419,142 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>8000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73" t="n">
-        <v>18000</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>398</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>10000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>6289</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1328</v>
+        <v>398</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>9000</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>6800</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8563,16 +8563,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>76</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8581,88 +8581,88 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>9318</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>5500</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D83" t="n">
-        <v>29</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>19</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>10621</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8671,16 +8671,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>2490</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8689,16 +8689,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>10009</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8710,13 +8710,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8728,42 +8728,114 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>299</v>
+        <v>29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>318</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="n">
+        <v>10009</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>武汉</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
         <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C95" t="n">
         <v>4</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D95" t="n">
         <v>43</v>
       </c>
     </row>
@@ -8805,10 +8877,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>315097.98</v>
+        <v>373931.38</v>
       </c>
     </row>
     <row r="3">
@@ -8831,10 +8903,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>154494.16</v>
+        <v>163454.16</v>
       </c>
     </row>
     <row r="5">
@@ -8966,36 +9038,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C2" t="n">
-        <v>181124.33</v>
+        <v>187957.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="C3" t="n">
-        <v>142553.5</v>
+        <v>165101.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>135645</v>
+        <v>142582.5</v>
       </c>
     </row>
     <row r="5">
@@ -9005,10 +9077,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C5" t="n">
-        <v>110610.98</v>
+        <v>126483.98</v>
       </c>
     </row>
     <row r="6">
@@ -9018,10 +9090,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>108867</v>
+        <v>108943</v>
       </c>
     </row>
     <row r="7">
@@ -9031,10 +9103,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>66656</v>
+        <v>69497</v>
       </c>
     </row>
     <row r="8">
@@ -9044,36 +9116,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>65985</v>
+        <v>66014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C9" t="n">
-        <v>62903</v>
+        <v>64791.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C10" t="n">
-        <v>62018</v>
+        <v>62941</v>
       </c>
     </row>
     <row r="11">
@@ -9083,10 +9155,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11" t="n">
-        <v>54163</v>
+        <v>54252</v>
       </c>
     </row>
     <row r="12">
@@ -9148,10 +9220,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C16" t="n">
-        <v>26903</v>
+        <v>26969</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,41 +528,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>431274</v>
+        <v>455793</v>
       </c>
       <c r="E2" t="n">
-        <v>134123</v>
+        <v>135997</v>
       </c>
       <c r="F2" t="n">
-        <v>297151</v>
+        <v>319796</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>235559</v>
+        <v>246140</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+83.1%</t>
+          <t>+85.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>89887</v>
+        <v>95148</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+230.6%</t>
+          <t>+236.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -585,13 +585,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2047</v>
+        <v>2079</v>
       </c>
       <c r="E3" t="n">
-        <v>17617</v>
+        <v>17636</v>
       </c>
       <c r="F3" t="n">
-        <v>-15570</v>
+        <v>-15557</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15909</v>
+        <v>16352</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.1%</t>
+          <t>-87.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-9120</v>
+        <v>-10682</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+70.7%</t>
+          <t>+45.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -638,20 +638,20 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>484315</v>
+        <v>485207</v>
       </c>
       <c r="E4" t="n">
-        <v>132703</v>
+        <v>133581</v>
       </c>
       <c r="F4" t="n">
-        <v>351611</v>
+        <v>351625</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>361124</v>
+        <v>398547</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+21.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>245078</v>
+        <v>276427</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+43.5%</t>
+          <t>+27.2%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -695,13 +695,13 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224496</v>
+        <v>224458</v>
       </c>
       <c r="E5" t="n">
         <v>197822</v>
       </c>
       <c r="F5" t="n">
-        <v>26673</v>
+        <v>26635</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>391449</v>
+        <v>399527</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-43.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>285397</v>
+        <v>293351</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-90.7%</t>
+          <t>-90.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -752,41 +752,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>457528</v>
+        <v>502221</v>
       </c>
       <c r="E6" t="n">
-        <v>52496</v>
+        <v>52715</v>
       </c>
       <c r="F6" t="n">
-        <v>405031</v>
+        <v>449505</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>203014</v>
+        <v>212784</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+125.4%</t>
+          <t>+136.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>145339</v>
+        <v>149326</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+178.7%</t>
+          <t>+201.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -809,41 +809,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>311419</v>
+        <v>337080</v>
       </c>
       <c r="E7" t="n">
-        <v>78062</v>
+        <v>81455</v>
       </c>
       <c r="F7" t="n">
-        <v>233357</v>
+        <v>255625</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>230370</v>
+        <v>245788</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+35.2%</t>
+          <t>+37.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>171689</v>
+        <v>184174</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+35.9%</t>
+          <t>+38.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -866,41 +866,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>349022</v>
+        <v>354005</v>
       </c>
       <c r="E8" t="n">
-        <v>78580</v>
+        <v>83945</v>
       </c>
       <c r="F8" t="n">
-        <v>270442</v>
+        <v>270060</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>280445</v>
+        <v>294504</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+24.5%</t>
+          <t>+20.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>247322</v>
+        <v>261201</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>+3.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -923,41 +923,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>728727</v>
+        <v>824467</v>
       </c>
       <c r="E9" t="n">
-        <v>258700</v>
+        <v>286700</v>
       </c>
       <c r="F9" t="n">
-        <v>470027</v>
+        <v>537767</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>612148</v>
+        <v>670556</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+19.0%</t>
+          <t>+23.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>471224</v>
+        <v>523632</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -980,50 +980,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1073645</v>
+        <v>1328416</v>
       </c>
       <c r="E10" t="n">
-        <v>11308</v>
+        <v>22808</v>
       </c>
       <c r="F10" t="n">
-        <v>1062337</v>
+        <v>1305608</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1014789</v>
+        <v>1094883</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>+21.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1014789</v>
+        <v>1094883</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+4.7%</t>
+          <t>+19.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>426491</v>
+        <v>494845</v>
       </c>
       <c r="P10" t="n">
-        <v>635845</v>
+        <v>810762</v>
       </c>
       <c r="Q10" t="n">
-        <v>1000949</v>
+        <v>1254322</v>
       </c>
     </row>
     <row r="11">
@@ -1041,52 +1041,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>172549</v>
+        <v>206143</v>
       </c>
       <c r="E11" t="n">
         <v>36399</v>
       </c>
       <c r="F11" t="n">
-        <v>136149</v>
+        <v>169743</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>192897</v>
+        <v>230497</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>167789</v>
+        <v>205389</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>20356</v>
+        <v>31552</v>
       </c>
       <c r="P11" t="n">
-        <v>115583</v>
+        <v>137981</v>
       </c>
       <c r="Q11" t="n">
-        <v>78787</v>
+        <v>78987</v>
       </c>
     </row>
     <row r="12">
@@ -1104,50 +1104,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>347513</v>
+        <v>365307</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>317437</v>
+        <v>335231</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>192100</v>
+        <v>192896</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+80.9%</t>
+          <t>+89.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>190121</v>
+        <v>190898</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+67.0%</t>
+          <t>+75.6%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>62178</v>
+        <v>68877</v>
       </c>
       <c r="P12" t="n">
-        <v>255259</v>
+        <v>266354</v>
       </c>
       <c r="Q12" t="n">
-        <v>35031</v>
+        <v>41631</v>
       </c>
     </row>
     <row r="13">
@@ -1165,52 +1165,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>416207</v>
+        <v>469457</v>
       </c>
       <c r="E13" t="n">
         <v>45013</v>
       </c>
       <c r="F13" t="n">
-        <v>371194</v>
+        <v>424443</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>298276</v>
+        <v>336875</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+39.5%</t>
+          <t>+39.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>238715</v>
+        <v>271114</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+55.5%</t>
+          <t>+56.6%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>26376</v>
+        <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>12661</v>
+        <v>12674</v>
       </c>
       <c r="P13" t="n">
-        <v>332156</v>
+        <v>380554</v>
       </c>
       <c r="Q13" t="n">
-        <v>91530</v>
+        <v>96983</v>
       </c>
     </row>
     <row r="14">
@@ -1228,52 +1228,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>192199</v>
+        <v>197921</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>177333</v>
+        <v>183055</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>212952</v>
+        <v>216621</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>194574</v>
+        <v>198243</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>9934</v>
+        <v>13845</v>
       </c>
       <c r="O14" t="n">
-        <v>40511</v>
+        <v>31326</v>
       </c>
       <c r="P14" t="n">
-        <v>126888</v>
+        <v>137884</v>
       </c>
       <c r="Q14" t="n">
-        <v>26373</v>
+        <v>30303</v>
       </c>
     </row>
     <row r="15">
@@ -1291,50 +1291,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>100210</v>
+        <v>110728</v>
       </c>
       <c r="E15" t="n">
         <v>15876</v>
       </c>
       <c r="F15" t="n">
-        <v>84334</v>
+        <v>94852</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>134157</v>
+        <v>164073</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>118851</v>
+        <v>148767</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7613</v>
+        <v>7632</v>
       </c>
       <c r="P15" t="n">
-        <v>76721</v>
+        <v>87220</v>
       </c>
       <c r="Q15" t="n">
-        <v>36960</v>
+        <v>37478</v>
       </c>
     </row>
     <row r="16">
@@ -1352,50 +1352,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>239947</v>
+        <v>265280</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>221549</v>
+        <v>246882</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>216446</v>
+        <v>221434</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+10.9%</t>
+          <t>+19.8%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>206246</v>
+        <v>211234</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>9366</v>
+        <v>32709</v>
       </c>
       <c r="P16" t="n">
-        <v>212183</v>
+        <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>41087</v>
+        <v>44232</v>
       </c>
     </row>
     <row r="17">
@@ -1413,52 +1413,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>327376</v>
+        <v>431788</v>
       </c>
       <c r="E17" t="n">
-        <v>88491</v>
+        <v>88462</v>
       </c>
       <c r="F17" t="n">
-        <v>238885</v>
+        <v>343326</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>257611</v>
+        <v>288451</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+27.1%</t>
+          <t>+49.7%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>211745</v>
+        <v>242585</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+12.8%</t>
+          <t>+41.5%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>43803</v>
+        <v>69029</v>
       </c>
       <c r="O17" t="n">
-        <v>6055</v>
+        <v>42482</v>
       </c>
       <c r="P17" t="n">
-        <v>189226</v>
+        <v>232014</v>
       </c>
       <c r="Q17" t="n">
-        <v>11870</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="18">
@@ -1476,52 +1476,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>789443</v>
+        <v>895353</v>
       </c>
       <c r="E18" t="n">
-        <v>84494</v>
+        <v>98495</v>
       </c>
       <c r="F18" t="n">
-        <v>704949</v>
+        <v>796858</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>407163</v>
+        <v>439972</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+93.9%</t>
+          <t>+103.5%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>355607</v>
+        <v>388416</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+98.2%</t>
+          <t>+105.2%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>216040</v>
+        <v>218371</v>
       </c>
       <c r="P18" t="n">
-        <v>488059</v>
+        <v>577637</v>
       </c>
       <c r="Q18" t="n">
-        <v>409347</v>
+        <v>494460</v>
       </c>
     </row>
     <row r="19">
@@ -1539,52 +1539,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>254472</v>
+        <v>301622</v>
       </c>
       <c r="E19" t="n">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>254111</v>
+        <v>301276</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>201959</v>
+        <v>224526</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+34.3%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>55961</v>
+        <v>78499</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+354.1%</t>
+          <t>+283.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>8855</v>
+        <v>21106</v>
       </c>
       <c r="O19" t="n">
-        <v>35266</v>
+        <v>41184</v>
       </c>
       <c r="P19" t="n">
-        <v>210190</v>
+        <v>239186</v>
       </c>
       <c r="Q19" t="n">
-        <v>77839</v>
+        <v>91710</v>
       </c>
     </row>
     <row r="20">
@@ -1602,50 +1602,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>307469</v>
+        <v>361182</v>
       </c>
       <c r="E20" t="n">
-        <v>48215</v>
+        <v>49262</v>
       </c>
       <c r="F20" t="n">
-        <v>259254</v>
+        <v>311920</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>339326</v>
+        <v>340122</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>+6.2%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>278326</v>
+        <v>279122</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+11.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>86736</v>
+        <v>86603</v>
       </c>
       <c r="P20" t="n">
-        <v>172518</v>
+        <v>225317</v>
       </c>
       <c r="Q20" t="n">
-        <v>36098</v>
+        <v>40964</v>
       </c>
     </row>
     <row r="21">
@@ -1663,54 +1663,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>7224786</v>
+        <v>8133434</v>
       </c>
       <c r="E21" t="n">
-        <v>1361715</v>
+        <v>1427967</v>
       </c>
       <c r="F21" t="n">
-        <v>5863070</v>
+        <v>6705466</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>5797703</v>
+        <v>6234556</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+24.6%</t>
+          <t>+30.5%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4679549</v>
+        <v>5081735</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+25.3%</t>
+          <t>+32.0%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>90031</v>
+        <v>136256</v>
       </c>
       <c r="O21" t="n">
-        <v>2796048</v>
+        <v>3089104</v>
       </c>
       <c r="P21" t="n">
-        <v>2977390</v>
+        <v>3480505</v>
       </c>
       <c r="Q21" t="n">
-        <v>3266609</v>
+        <v>3870628</v>
       </c>
     </row>
   </sheetData>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>479</v>
+        <v>203</v>
       </c>
       <c r="C2" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>1341.9</v>
+        <v>345.5</v>
       </c>
       <c r="E2" t="n">
-        <v>145922</v>
+        <v>89148</v>
       </c>
     </row>
     <row r="3">
@@ -1780,16 +1780,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1272.3</v>
+        <v>64.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4641</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4">
@@ -1799,16 +1799,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>815</v>
+        <v>514</v>
       </c>
       <c r="C4" t="n">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="D4" t="n">
-        <v>1533.8</v>
+        <v>895.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2610</v>
+        <v>2517</v>
       </c>
     </row>
   </sheetData>
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1554975</v>
+        <v>1643708</v>
       </c>
       <c r="D2" t="n">
-        <v>13722</v>
+        <v>13983</v>
       </c>
       <c r="E2" t="n">
-        <v>1244706</v>
+        <v>1327884</v>
       </c>
     </row>
     <row r="3">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>334189</v>
+        <v>393529</v>
       </c>
       <c r="D3" t="n">
-        <v>135838</v>
+        <v>144238</v>
       </c>
       <c r="E3" t="n">
-        <v>176797</v>
+        <v>228717</v>
       </c>
     </row>
     <row r="4">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>923274</v>
+        <v>1068257</v>
       </c>
       <c r="D4" t="n">
-        <v>2814630</v>
+        <v>3309084</v>
       </c>
       <c r="E4" t="n">
-        <v>1845875</v>
+        <v>2314796</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>287546</v>
+        <v>310162</v>
       </c>
       <c r="D5" t="n">
-        <v>9605</v>
+        <v>9634</v>
       </c>
       <c r="E5" t="n">
-        <v>296957</v>
+        <v>318806</v>
       </c>
     </row>
     <row r="6">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15705</v>
+        <v>-15692</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-5570</v>
+        <v>-5557</v>
       </c>
     </row>
     <row r="7">
@@ -1969,13 +1969,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342856</v>
+        <v>342638</v>
       </c>
       <c r="D7" t="n">
-        <v>8755</v>
+        <v>8987</v>
       </c>
       <c r="E7" t="n">
-        <v>333825</v>
+        <v>333839</v>
       </c>
     </row>
     <row r="8">
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21485</v>
+        <v>21447</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-85486</v>
+        <v>-85524</v>
       </c>
     </row>
     <row r="9">
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>398105</v>
+        <v>442579</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>337268</v>
+        <v>371742</v>
       </c>
     </row>
     <row r="10">
@@ -2032,13 +2032,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>231639</v>
+        <v>253907</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>138463</v>
+        <v>165711</v>
       </c>
     </row>
     <row r="11">
@@ -2053,13 +2053,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>289047</v>
+        <v>288665</v>
       </c>
       <c r="D11" t="n">
         <v>-18605</v>
       </c>
       <c r="E11" t="n">
-        <v>229248</v>
+        <v>228866</v>
       </c>
     </row>
     <row r="12">
@@ -2074,13 +2074,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>334189</v>
+        <v>393529</v>
       </c>
       <c r="D12" t="n">
-        <v>135838</v>
+        <v>144238</v>
       </c>
       <c r="E12" t="n">
-        <v>176797</v>
+        <v>228717</v>
       </c>
     </row>
     <row r="13">
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>426491</v>
+        <v>494845</v>
       </c>
       <c r="D13" t="n">
-        <v>635845</v>
+        <v>810762</v>
       </c>
       <c r="E13" t="n">
-        <v>1000949</v>
+        <v>1254322</v>
       </c>
     </row>
     <row r="14">
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20356</v>
+        <v>31552</v>
       </c>
       <c r="D14" t="n">
-        <v>115583</v>
+        <v>137981</v>
       </c>
       <c r="E14" t="n">
-        <v>78787</v>
+        <v>78987</v>
       </c>
     </row>
     <row r="15">
@@ -2137,13 +2137,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>62178</v>
+        <v>68877</v>
       </c>
       <c r="D15" t="n">
-        <v>255259</v>
+        <v>266354</v>
       </c>
       <c r="E15" t="n">
-        <v>35031</v>
+        <v>41631</v>
       </c>
     </row>
     <row r="16">
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12661</v>
+        <v>12674</v>
       </c>
       <c r="D16" t="n">
-        <v>332156</v>
+        <v>380554</v>
       </c>
       <c r="E16" t="n">
-        <v>91530</v>
+        <v>96983</v>
       </c>
     </row>
     <row r="17">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>40511</v>
+        <v>31326</v>
       </c>
       <c r="D17" t="n">
-        <v>126888</v>
+        <v>137884</v>
       </c>
       <c r="E17" t="n">
-        <v>26373</v>
+        <v>30303</v>
       </c>
     </row>
     <row r="18">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7613</v>
+        <v>7632</v>
       </c>
       <c r="D18" t="n">
-        <v>76721</v>
+        <v>87220</v>
       </c>
       <c r="E18" t="n">
-        <v>36960</v>
+        <v>37478</v>
       </c>
     </row>
     <row r="19">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9366</v>
+        <v>32709</v>
       </c>
       <c r="D19" t="n">
-        <v>212183</v>
+        <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>41087</v>
+        <v>44232</v>
       </c>
     </row>
     <row r="20">
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6055</v>
+        <v>42482</v>
       </c>
       <c r="D20" t="n">
-        <v>189226</v>
+        <v>232014</v>
       </c>
       <c r="E20" t="n">
-        <v>11870</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="21">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>216040</v>
+        <v>218371</v>
       </c>
       <c r="D21" t="n">
-        <v>488059</v>
+        <v>577637</v>
       </c>
       <c r="E21" t="n">
-        <v>409347</v>
+        <v>494460</v>
       </c>
     </row>
     <row r="22">
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35266</v>
+        <v>41184</v>
       </c>
       <c r="D22" t="n">
-        <v>210190</v>
+        <v>239186</v>
       </c>
       <c r="E22" t="n">
-        <v>77839</v>
+        <v>91710</v>
       </c>
     </row>
     <row r="23">
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>86736</v>
+        <v>86603</v>
       </c>
       <c r="D23" t="n">
-        <v>172518</v>
+        <v>225317</v>
       </c>
       <c r="E23" t="n">
-        <v>36098</v>
+        <v>40964</v>
       </c>
     </row>
     <row r="24">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2796048</v>
+        <v>3089104</v>
       </c>
       <c r="D25" t="n">
-        <v>2977390</v>
+        <v>3480505</v>
       </c>
       <c r="E25" t="n">
-        <v>3266609</v>
+        <v>3870628</v>
       </c>
     </row>
   </sheetData>
@@ -2437,19 +2437,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>156416</v>
+        <v>169152</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>118289.34</v>
+        <v>131025.34</v>
       </c>
     </row>
     <row r="3">
@@ -2521,19 +2521,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>48638</v>
+        <v>45698</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4078</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5">
@@ -2563,19 +2563,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>74740</v>
+        <v>84700</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2583,11 +2583,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>68342.5</v>
+        <v>78302.5</v>
       </c>
     </row>
     <row r="6">
@@ -2605,19 +2605,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>48380</v>
+        <v>52340</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>46700</v>
+        <v>50660</v>
       </c>
     </row>
     <row r="7">
@@ -2659,19 +2659,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10000</v>
+        <v>14980</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>64740</v>
+        <v>59760</v>
       </c>
     </row>
     <row r="8">
@@ -2689,19 +2689,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>54340</v>
+        <v>56320</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2709,11 +2709,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7190</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="9">
@@ -2857,19 +2857,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>64090</v>
+        <v>78910</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>57490</v>
+        <v>72310</v>
       </c>
     </row>
     <row r="13">
@@ -2899,31 +2899,31 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>141338</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>176.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>165.4%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9000</v>
+        <v>33800</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>132338</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -3025,19 +3025,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>60734</v>
+        <v>70634</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3045,11 +3045,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>24334</v>
+        <v>34234</v>
       </c>
     </row>
     <row r="17">
@@ -3067,19 +3067,19 @@
         <v>80000</v>
       </c>
       <c r="D17" t="n">
-        <v>27820</v>
+        <v>28020</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -3087,11 +3087,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>187.3%</t>
+          <t>185.9%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-24280</v>
+        <v>-24080</v>
       </c>
     </row>
     <row r="18">
@@ -3109,31 +3109,31 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>14980</v>
+        <v>21580</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>17000</v>
+        <v>20200</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>-2020</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="19">
@@ -3151,19 +3151,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67520</v>
+        <v>67720</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3171,11 +3171,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33520</v>
+        <v>33720</v>
       </c>
     </row>
     <row r="20">
@@ -3193,19 +3193,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>69220</v>
+        <v>87820</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>69220</v>
+        <v>87820</v>
       </c>
     </row>
     <row r="21">
@@ -3361,31 +3361,31 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>30600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>34.8%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>30600</v>
       </c>
     </row>
     <row r="25">
@@ -3445,19 +3445,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>142216</v>
+        <v>138236</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3465,11 +3465,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>123470</v>
+        <v>119490</v>
       </c>
     </row>
     <row r="27">
@@ -3655,19 +3655,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>173434</v>
+        <v>183394</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>114.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3675,11 +3675,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>126554</v>
+        <v>136514</v>
       </c>
     </row>
     <row r="32">
@@ -3697,19 +3697,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>78660</v>
+        <v>105180</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3717,11 +3717,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>74680</v>
+        <v>101200</v>
       </c>
     </row>
     <row r="33">
@@ -3739,19 +3739,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>62362</v>
+        <v>67342</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>37582</v>
+        <v>42562</v>
       </c>
     </row>
     <row r="34">
@@ -3781,19 +3781,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>67979</v>
+        <v>77979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3801,11 +3801,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>64379</v>
+        <v>74379</v>
       </c>
     </row>
     <row r="35">
@@ -3907,19 +3907,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>83016</v>
+        <v>87996</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3927,11 +3927,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>75056</v>
+        <v>80036</v>
       </c>
     </row>
     <row r="38">
@@ -4075,31 +4075,31 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>48800</v>
+        <v>58760</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1680</v>
+        <v>4997</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>47120</v>
+        <v>53763</v>
       </c>
     </row>
   </sheetData>
@@ -4173,11 +4173,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>215574.7</v>
+        <v>229174.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>175708.03</v>
+        <v>189307.93</v>
       </c>
     </row>
     <row r="3">
@@ -4275,11 +4275,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>15015.1</v>
+        <v>42388.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4287,11 +4287,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12415.1</v>
+        <v>39788.8</v>
       </c>
     </row>
     <row r="6">
@@ -4309,11 +4309,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>57490.16</v>
+        <v>69150.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>57490.16</v>
+        <v>69150.06</v>
       </c>
     </row>
     <row r="7">
@@ -4343,11 +4343,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>11194</v>
+        <v>12194</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11194</v>
+        <v>12194</v>
       </c>
     </row>
     <row r="8">
@@ -4377,11 +4377,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>26506.11</v>
+        <v>27601.93</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>26506.11</v>
+        <v>27601.93</v>
       </c>
     </row>
     <row r="9">
@@ -4411,11 +4411,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>34038.64</v>
+        <v>35270.96</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>33838.64</v>
+        <v>35070.96</v>
       </c>
     </row>
     <row r="10">
@@ -4445,11 +4445,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62266.7</v>
+        <v>83675.61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62266.7</v>
+        <v>83675.61</v>
       </c>
     </row>
     <row r="11">
@@ -4479,11 +4479,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>11700</v>
+        <v>12500</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11700</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="12">
@@ -4513,11 +4513,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>110805.7</v>
+        <v>128205.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>110805.7</v>
+        <v>128205.7</v>
       </c>
     </row>
     <row r="13">
@@ -4581,11 +4581,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>96372</v>
+        <v>96770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96372</v>
+        <v>96770</v>
       </c>
     </row>
     <row r="15">
@@ -4615,11 +4615,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>48188</v>
+        <v>51760</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4627,11 +4627,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>38990</v>
+        <v>42562</v>
       </c>
     </row>
     <row r="16">
@@ -4649,11 +4649,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>76380</v>
+        <v>96976</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4661,11 +4661,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>67180</v>
+        <v>87776</v>
       </c>
     </row>
     <row r="17">
@@ -4683,11 +4683,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>18788</v>
+        <v>19584</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>18788</v>
+        <v>19584</v>
       </c>
     </row>
     <row r="18">
@@ -4717,11 +4717,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>35510.6</v>
+        <v>38158</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>35510.6</v>
+        <v>38158</v>
       </c>
     </row>
     <row r="19">
@@ -4785,11 +4785,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>76035.8</v>
+        <v>77727.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4797,11 +4797,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>72035.8</v>
+        <v>73727.8</v>
       </c>
     </row>
     <row r="21">
@@ -4819,11 +4819,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>9314</v>
+        <v>10279.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9314</v>
+        <v>10279.8</v>
       </c>
     </row>
     <row r="22">
@@ -4853,23 +4853,23 @@
         <v>60000</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="23">
@@ -4887,11 +4887,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>114778</v>
+        <v>163558</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>114778</v>
+        <v>163558</v>
       </c>
     </row>
     <row r="24">
@@ -4921,11 +4921,11 @@
         <v>150000</v>
       </c>
       <c r="D24" t="n">
-        <v>3590</v>
+        <v>8590</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3590</v>
+        <v>8590</v>
       </c>
     </row>
     <row r="25">
@@ -5091,11 +5091,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>85174</v>
+        <v>97572</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5103,11 +5103,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>78174</v>
+        <v>90572</v>
       </c>
     </row>
     <row r="30">
@@ -5159,11 +5159,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>12496</v>
+        <v>22496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>12496</v>
+        <v>22496</v>
       </c>
     </row>
     <row r="32">
@@ -5193,11 +5193,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>10796</v>
+        <v>21792</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -5209,7 +5209,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>10796</v>
+        <v>21792</v>
       </c>
     </row>
     <row r="33">
@@ -5227,11 +5227,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>124069.64</v>
+        <v>160069.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5239,11 +5239,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>90269.64</v>
+        <v>126269.64</v>
       </c>
     </row>
     <row r="34">
@@ -5261,11 +5261,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>91443.25</v>
+        <v>142265.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5273,11 +5273,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>51609.85</v>
+        <v>102431.73</v>
       </c>
     </row>
     <row r="35">
@@ -5295,11 +5295,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>56446.92</v>
+        <v>67044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5307,11 +5307,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>49846.92</v>
+        <v>60444.92</v>
       </c>
     </row>
     <row r="36">
@@ -5329,11 +5329,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>42988</v>
+        <v>49980</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5341,11 +5341,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>36788</v>
+        <v>43780</v>
       </c>
     </row>
     <row r="37">
@@ -5431,11 +5431,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>48472</v>
+        <v>68472</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>48472</v>
+        <v>68472</v>
       </c>
     </row>
     <row r="40">
@@ -5465,23 +5465,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>483008</v>
+        <v>496884</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>106.4%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>66300</v>
+        <v>71300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>416708</v>
+        <v>425584</v>
       </c>
     </row>
     <row r="41">
@@ -5499,11 +5499,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>101189</v>
+        <v>102869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>101189</v>
+        <v>102869</v>
       </c>
     </row>
     <row r="42">
@@ -5567,23 +5567,23 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>35751</v>
+        <v>106151</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>35751</v>
+        <v>97151</v>
       </c>
     </row>
     <row r="44">
@@ -5635,11 +5635,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>75876.64000000001</v>
+        <v>98466.64000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>75876.64000000001</v>
+        <v>98466.64000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5669,11 +5669,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>25476</v>
+        <v>31103</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>25476</v>
+        <v>31103</v>
       </c>
     </row>
     <row r="47">
@@ -5703,11 +5703,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>130600</v>
+        <v>157308</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>130600</v>
+        <v>157308</v>
       </c>
     </row>
     <row r="48">
@@ -5737,11 +5737,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>77268</v>
+        <v>108869</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>77268</v>
+        <v>108869</v>
       </c>
     </row>
     <row r="49">
@@ -5771,11 +5771,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>148555.04</v>
+        <v>219861.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>148555.04</v>
+        <v>219861.04</v>
       </c>
     </row>
     <row r="50">
@@ -5805,11 +5805,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>398</v>
+        <v>1996</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>398</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="51">
@@ -5873,11 +5873,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>229564.64</v>
+        <v>299056.64</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>229564.64</v>
+        <v>299056.64</v>
       </c>
     </row>
     <row r="53">
@@ -5907,11 +5907,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>61756.10000000001</v>
+        <v>141525.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>61756.10000000001</v>
+        <v>141525.1</v>
       </c>
     </row>
     <row r="54">
@@ -5941,11 +5941,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>201951</v>
+        <v>209949</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>201951</v>
+        <v>209949</v>
       </c>
     </row>
     <row r="55">
@@ -5975,11 +5975,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>96993</v>
+        <v>107789</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5987,11 +5987,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>86993</v>
+        <v>97789</v>
       </c>
     </row>
     <row r="56">
@@ -6043,11 +6043,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>54456</v>
+        <v>54854</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>54456</v>
+        <v>54854</v>
       </c>
     </row>
     <row r="58">
@@ -6111,11 +6111,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>106206</v>
+        <v>112806</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>163.7%</t>
+          <t>174.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6123,11 +6123,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>98206</v>
+        <v>104806</v>
       </c>
     </row>
     <row r="60">
@@ -6213,11 +6213,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>51572</v>
+        <v>52071</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6225,11 +6225,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>35772</v>
+        <v>36271</v>
       </c>
     </row>
     <row r="63">
@@ -6247,11 +6247,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>9870</v>
+        <v>19870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>164.5%</t>
+          <t>331.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9870</v>
+        <v>19870</v>
       </c>
     </row>
   </sheetData>
@@ -6324,16 +6324,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1819191.8</v>
+        <v>1973367.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8542</v>
+        <v>8973</v>
       </c>
       <c r="E2" t="n">
-        <v>1590121.8</v>
+        <v>1722850.8</v>
       </c>
       <c r="F2" t="n">
-        <v>229070</v>
+        <v>250517</v>
       </c>
     </row>
     <row r="3">
@@ -6348,16 +6348,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1583350</v>
+        <v>1729700</v>
       </c>
       <c r="D3" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="E3" t="n">
-        <v>1369667</v>
+        <v>1494038</v>
       </c>
       <c r="F3" t="n">
-        <v>213683</v>
+        <v>235662</v>
       </c>
     </row>
     <row r="4">
@@ -6372,16 +6372,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>235841.8</v>
+        <v>243667.8</v>
       </c>
       <c r="D4" t="n">
-        <v>8132</v>
+        <v>8536</v>
       </c>
       <c r="E4" t="n">
-        <v>220454.8</v>
+        <v>228812.8</v>
       </c>
       <c r="F4" t="n">
-        <v>15387</v>
+        <v>14855</v>
       </c>
     </row>
     <row r="5">
@@ -6396,16 +6396,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3048762</v>
+        <v>3316840</v>
       </c>
       <c r="D5" t="n">
-        <v>577</v>
+        <v>641</v>
       </c>
       <c r="E5" t="n">
-        <v>757270</v>
+        <v>782106</v>
       </c>
       <c r="F5" t="n">
-        <v>2291492</v>
+        <v>2534734</v>
       </c>
     </row>
     <row r="6">
@@ -6420,16 +6420,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1988954</v>
+        <v>2203122</v>
       </c>
       <c r="D6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>1931138</v>
+        <v>2145306</v>
       </c>
     </row>
     <row r="7">
@@ -6444,16 +6444,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1049808</v>
+        <v>1103718</v>
       </c>
       <c r="D7" t="n">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="E7" t="n">
-        <v>699454</v>
+        <v>724290</v>
       </c>
       <c r="F7" t="n">
-        <v>350354</v>
+        <v>379428</v>
       </c>
     </row>
     <row r="8">
@@ -6468,16 +6468,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1123240.05</v>
+        <v>1421855.15</v>
       </c>
       <c r="D8" t="n">
-        <v>1584</v>
+        <v>1950</v>
       </c>
       <c r="E8" t="n">
-        <v>20472.81</v>
+        <v>24790.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1102767.24</v>
+        <v>1397064.54</v>
       </c>
     </row>
     <row r="9">
@@ -6492,16 +6492,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>659769.1899999999</v>
+        <v>887675.0699999999</v>
       </c>
       <c r="D9" t="n">
-        <v>693</v>
+        <v>832</v>
       </c>
       <c r="E9" t="n">
-        <v>3548.26</v>
+        <v>5628.16</v>
       </c>
       <c r="F9" t="n">
-        <v>656220.9300000001</v>
+        <v>882046.91</v>
       </c>
     </row>
     <row r="10">
@@ -6516,16 +6516,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>463470.86</v>
+        <v>534180.08</v>
       </c>
       <c r="D10" t="n">
-        <v>891</v>
+        <v>1118</v>
       </c>
       <c r="E10" t="n">
-        <v>16924.55</v>
+        <v>19162.45</v>
       </c>
       <c r="F10" t="n">
-        <v>446546.31</v>
+        <v>515017.63</v>
       </c>
     </row>
     <row r="11">
@@ -6540,16 +6540,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>492800</v>
+        <v>589000</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>274600</v>
+        <v>370800</v>
       </c>
     </row>
     <row r="12">
@@ -6564,16 +6564,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>307465.9</v>
+        <v>317465.9</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>112993.9</v>
       </c>
       <c r="F12" t="n">
-        <v>194472</v>
+        <v>204472</v>
       </c>
     </row>
     <row r="13">
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>291100</v>
+        <v>324700</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>261320</v>
+        <v>294920</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -6612,16 +6612,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>106920</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
         <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>89100</v>
+        <v>93060</v>
       </c>
     </row>
     <row r="15">
@@ -6636,16 +6636,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>35306.61</v>
+        <v>79325.61</v>
       </c>
       <c r="D15" t="n">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E15" t="n">
-        <v>10632.36</v>
+        <v>11631.36</v>
       </c>
       <c r="F15" t="n">
-        <v>24674.25</v>
+        <v>67694.25</v>
       </c>
     </row>
   </sheetData>
@@ -6706,22 +6706,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1819191.8</v>
+        <v>1973367.8</v>
       </c>
       <c r="C2" t="n">
-        <v>379236.86</v>
+        <v>390988.86</v>
       </c>
       <c r="D2" t="n">
-        <v>45346</v>
+        <v>48763</v>
       </c>
       <c r="E2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="F2" t="n">
-        <v>333890.86</v>
+        <v>342225.86</v>
       </c>
       <c r="G2" t="n">
-        <v>18.35</v>
+        <v>17.34</v>
       </c>
     </row>
     <row r="3">
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3048762</v>
+        <v>3316840</v>
       </c>
       <c r="C3" t="n">
-        <v>442301.38</v>
+        <v>472001.38</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6743,10 +6743,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>442301.38</v>
+        <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.51</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="4">
@@ -6756,7 +6756,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1123240.05</v>
+        <v>1421855.15</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6771,7 +6771,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>492800</v>
+        <v>589000</v>
       </c>
       <c r="C5" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6793,10 +6793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>18.51</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="6">
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>307465.9</v>
+        <v>317465.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -6815,13 +6815,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>49.71</v>
+        <v>48.15</v>
       </c>
     </row>
     <row r="7">
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>291100</v>
+        <v>324700</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -6840,13 +6840,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>18.21</v>
+        <v>16.32</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>81.51000000000001</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106920</v>
+        <v>110880</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35306.61</v>
+        <v>79325.61</v>
       </c>
       <c r="C9" t="n">
         <v>999</v>
@@ -6890,7 +6890,7 @@
         <v>999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.83</v>
+        <v>1.26</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6942,13 +6942,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C2" t="n">
-        <v>833431.05</v>
+        <v>847454.05</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -6958,13 +6958,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>564</v>
+        <v>611</v>
       </c>
       <c r="C3" t="n">
-        <v>262180.4</v>
+        <v>267939.4</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>105163</v>
+        <v>129982</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>69200</v>
+        <v>90200</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -7022,10 +7022,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C7" t="n">
-        <v>23276.66</v>
+        <v>23727.66</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>21982.7</v>
+        <v>22039.7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>16687</v>
+        <v>16792</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7159,10 +7159,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>193200</v>
+        <v>196400</v>
       </c>
     </row>
     <row r="3">
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>36400</v>
+        <v>61200</v>
       </c>
     </row>
     <row r="4">
@@ -7339,10 +7339,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="n">
-        <v>72257</v>
+        <v>72276</v>
       </c>
     </row>
     <row r="13">
@@ -7353,14 +7353,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>21780</v>
+        <v>22214.5</v>
       </c>
     </row>
     <row r="14">
@@ -7371,14 +7371,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>20763.5</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="15">
@@ -7411,10 +7411,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>7614.66</v>
+        <v>7932.66</v>
       </c>
     </row>
     <row r="17">
@@ -7429,10 +7429,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>394</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18">
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -7519,10 +7519,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D22" t="n">
-        <v>63116</v>
+        <v>63305</v>
       </c>
     </row>
     <row r="23">
@@ -7537,10 +7537,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="D23" t="n">
-        <v>33855</v>
+        <v>34449</v>
       </c>
     </row>
     <row r="24">
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>5647</v>
+        <v>5685</v>
       </c>
     </row>
     <row r="26">
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" t="n">
-        <v>5087.8</v>
+        <v>5106.8</v>
       </c>
     </row>
     <row r="27">
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D28" t="n">
-        <v>666</v>
+        <v>704</v>
       </c>
     </row>
     <row r="29">
@@ -7654,7 +7654,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7663,16 +7663,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>58733.4</v>
+        <v>77900</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>20500</v>
@@ -7690,37 +7690,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>9000</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -7731,14 +7731,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>29</v>
+        <v>58733.4</v>
       </c>
     </row>
     <row r="35">
@@ -7749,56 +7749,56 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>29</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>77918</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>6500</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7807,28 +7807,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="D39" t="n">
-        <v>38</v>
+        <v>62893</v>
       </c>
     </row>
     <row r="40">
@@ -7839,14 +7839,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="D40" t="n">
-        <v>62744</v>
+        <v>19987</v>
       </c>
     </row>
     <row r="41">
@@ -7857,14 +7857,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>14895</v>
+        <v>429</v>
       </c>
     </row>
     <row r="42">
@@ -7875,14 +7875,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D42" t="n">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="43">
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>361</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44">
@@ -7911,14 +7911,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>161</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
@@ -7929,14 +7929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -7951,10 +7951,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
-        <v>57996</v>
+        <v>58034</v>
       </c>
     </row>
     <row r="47">
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D48" t="n">
-        <v>4084</v>
+        <v>7439</v>
       </c>
     </row>
     <row r="49">
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D53" t="n">
-        <v>25720.9</v>
+        <v>25892.9</v>
       </c>
     </row>
     <row r="54">
@@ -8095,10 +8095,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>16461</v>
+        <v>16470</v>
       </c>
     </row>
     <row r="55">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>8742</v>
+        <v>8761</v>
       </c>
     </row>
     <row r="56">
@@ -8131,10 +8131,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D56" t="n">
-        <v>1269</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="57">
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D61" t="n">
-        <v>38327</v>
+        <v>39336</v>
       </c>
     </row>
     <row r="62">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D63" t="n">
-        <v>641</v>
+        <v>660</v>
       </c>
     </row>
     <row r="64">
@@ -8275,10 +8275,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
-        <v>133</v>
+        <v>152</v>
       </c>
     </row>
     <row r="65">
@@ -8482,7 +8482,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8491,52 +8491,52 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>18000</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>398</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>10621</v>
+        <v>299</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8545,88 +8545,88 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>5000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>2490</v>
+        <v>398</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>10000</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>6289</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1328</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8638,121 +8638,121 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>6800</v>
+        <v>6289</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>76</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>9318</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>5500</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>29</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8761,16 +8761,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" t="n">
-        <v>10009</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8782,13 +8782,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8800,25 +8800,25 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>299</v>
+        <v>29</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>318</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95">
@@ -8829,14 +8829,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>其他/未说明</t>
         </is>
       </c>
-      <c r="C95" t="n">
-        <v>4</v>
-      </c>
-      <c r="D95" t="n">
-        <v>43</v>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8877,10 +8895,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>373931.38</v>
+        <v>403631.38</v>
       </c>
     </row>
     <row r="3">
@@ -8903,10 +8921,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>163454.16</v>
+        <v>171751.16</v>
       </c>
     </row>
     <row r="5">
@@ -8942,10 +8960,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>91200</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="8">
@@ -9038,10 +9056,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C2" t="n">
-        <v>187957.33</v>
+        <v>189559.33</v>
       </c>
     </row>
     <row r="3">
@@ -9051,10 +9069,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C3" t="n">
-        <v>165101.4</v>
+        <v>161699.4</v>
       </c>
     </row>
     <row r="4">
@@ -9064,10 +9082,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>142582.5</v>
+        <v>142639.5</v>
       </c>
     </row>
     <row r="5">
@@ -9077,10 +9095,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C5" t="n">
-        <v>126483.98</v>
+        <v>141661.98</v>
       </c>
     </row>
     <row r="6">
@@ -9090,36 +9108,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C6" t="n">
-        <v>108943</v>
+        <v>126680</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>69497</v>
+        <v>92094</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>66014</v>
+        <v>69497</v>
       </c>
     </row>
     <row r="9">
@@ -9129,10 +9147,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>64791.8</v>
+        <v>64848.8</v>
       </c>
     </row>
     <row r="10">
@@ -9142,10 +9160,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C10" t="n">
-        <v>62941</v>
+        <v>62998</v>
       </c>
     </row>
     <row r="11">
@@ -9155,10 +9173,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11" t="n">
-        <v>54252</v>
+        <v>54405</v>
       </c>
     </row>
     <row r="12">
@@ -9181,10 +9199,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>37200</v>
+        <v>37219</v>
       </c>
     </row>
     <row r="14">
@@ -9194,10 +9212,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>31756</v>
+        <v>31775</v>
       </c>
     </row>
     <row r="15">
@@ -9220,10 +9238,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>26969</v>
+        <v>27035</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款服务类型" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款省份" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电话" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新老客" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协同" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新老客" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,11 +538,11 @@
         <v>319796</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -647,11 +648,11 @@
         <v>351625</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -704,11 +705,11 @@
         <v>26635</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -761,11 +762,11 @@
         <v>449505</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1672,11 +1673,11 @@
         <v>6705466</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>256182</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1822,6 +1823,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>协同金额(元)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>课程3组</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>课程5组</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>49820</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>课程4组</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>173964</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>课程1组</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10398</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2524,11 +2591,11 @@
         <v>45698</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3406,11 +3473,11 @@
         <v>31114</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3616,11 +3683,11 @@
         <v>72700</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3826,11 +3893,11 @@
         <v>72650</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3994,11 +4061,11 @@
         <v>86228</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>455793</v>
+        <v>461959</v>
       </c>
       <c r="E2" t="n">
-        <v>135997</v>
+        <v>136120</v>
       </c>
       <c r="F2" t="n">
-        <v>319796</v>
+        <v>325839</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>246140</v>
+        <v>299086</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+85.2%</t>
+          <t>+54.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>95148</v>
+        <v>143626</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+236.1%</t>
+          <t>+126.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2079</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>17636</v>
+        <v>14980</v>
       </c>
       <c r="F3" t="n">
-        <v>-15557</v>
+        <v>-14961</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16352</v>
+        <v>16390</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.3%</t>
+          <t>-99.9%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-10682</v>
+        <v>-14030</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+45.6%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>485207</v>
+        <v>452826</v>
       </c>
       <c r="E4" t="n">
-        <v>133581</v>
+        <v>137973</v>
       </c>
       <c r="F4" t="n">
-        <v>351625</v>
+        <v>314852</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>398547</v>
+        <v>411191</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+21.7%</t>
+          <t>+10.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>276427</v>
+        <v>288019</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+27.2%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224458</v>
+        <v>218577</v>
       </c>
       <c r="E5" t="n">
-        <v>197822</v>
+        <v>197841</v>
       </c>
       <c r="F5" t="n">
-        <v>26635</v>
+        <v>20735</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>399527</v>
+        <v>399845</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-43.8%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>293351</v>
+        <v>293669</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-90.9%</t>
+          <t>-92.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>502221</v>
+        <v>493990</v>
       </c>
       <c r="E6" t="n">
-        <v>52715</v>
+        <v>57758</v>
       </c>
       <c r="F6" t="n">
-        <v>449505</v>
+        <v>436231</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>212784</v>
+        <v>257410</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+136.0%</t>
+          <t>+91.9%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>149326</v>
+        <v>193211</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+201.0%</t>
+          <t>+125.8%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>337080</v>
+        <v>355575</v>
       </c>
       <c r="E7" t="n">
-        <v>81455</v>
+        <v>81615</v>
       </c>
       <c r="F7" t="n">
-        <v>255625</v>
+        <v>273960</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>245788</v>
+        <v>258264</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+37.1%</t>
+          <t>+37.7%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>184174</v>
+        <v>196014</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+38.8%</t>
+          <t>+39.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>354005</v>
+        <v>347770</v>
       </c>
       <c r="E8" t="n">
-        <v>83945</v>
+        <v>97470</v>
       </c>
       <c r="F8" t="n">
-        <v>270060</v>
+        <v>250300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>294504</v>
+        <v>296470</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+20.2%</t>
+          <t>+17.3%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>261201</v>
+        <v>262996</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,25 +924,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>824467</v>
+        <v>833538</v>
       </c>
       <c r="E9" t="n">
         <v>286700</v>
       </c>
       <c r="F9" t="n">
-        <v>537767</v>
+        <v>546838</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -950,15 +950,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+23.0%</t>
+          <t>+24.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>523632</v>
+        <v>510432</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+7.1%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1328416</v>
+        <v>1424373</v>
       </c>
       <c r="E10" t="n">
         <v>22808</v>
       </c>
       <c r="F10" t="n">
-        <v>1305608</v>
+        <v>1401565</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1094883</v>
+        <v>1120687</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+21.3%</t>
+          <t>+27.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1094883</v>
+        <v>1120687</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+19.2%</t>
+          <t>+25.1%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>494845</v>
+        <v>529674</v>
       </c>
       <c r="P10" t="n">
-        <v>810762</v>
+        <v>871890</v>
       </c>
       <c r="Q10" t="n">
-        <v>1254322</v>
+        <v>1350677</v>
       </c>
     </row>
     <row r="11">
@@ -1042,52 +1042,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>206143</v>
+        <v>204306</v>
       </c>
       <c r="E11" t="n">
         <v>36399</v>
       </c>
       <c r="F11" t="n">
-        <v>169743</v>
+        <v>167906</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>230497</v>
+        <v>247516</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>205389</v>
+        <v>222408</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>31552</v>
+        <v>31514</v>
       </c>
       <c r="P11" t="n">
-        <v>137981</v>
+        <v>136181</v>
       </c>
       <c r="Q11" t="n">
-        <v>78987</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>365307</v>
+        <v>344701</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>335231</v>
+        <v>314625</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>192896</v>
+        <v>237094</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+89.4%</t>
+          <t>+45.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>190898</v>
+        <v>235096</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+75.6%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>68877</v>
+        <v>38669</v>
       </c>
       <c r="P12" t="n">
-        <v>266354</v>
+        <v>275956</v>
       </c>
       <c r="Q12" t="n">
-        <v>41631</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="13">
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>469457</v>
+        <v>473605</v>
       </c>
       <c r="E13" t="n">
         <v>45013</v>
       </c>
       <c r="F13" t="n">
-        <v>424443</v>
+        <v>428591</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>336875</v>
+        <v>379795</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+39.4%</t>
+          <t>+24.7%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>271114</v>
+        <v>303286</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+56.6%</t>
+          <t>+41.3%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>12674</v>
+        <v>18924</v>
       </c>
       <c r="P13" t="n">
-        <v>380554</v>
+        <v>378452</v>
       </c>
       <c r="Q13" t="n">
-        <v>96983</v>
+        <v>96637</v>
       </c>
     </row>
     <row r="14">
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>197921</v>
+        <v>241898</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>183055</v>
+        <v>227032</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>216621</v>
+        <v>217019</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>+11.5%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>198243</v>
+        <v>195641</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>+16.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>13845</v>
+        <v>16354</v>
       </c>
       <c r="O14" t="n">
-        <v>31326</v>
+        <v>29346</v>
       </c>
       <c r="P14" t="n">
-        <v>137884</v>
+        <v>181332</v>
       </c>
       <c r="Q14" t="n">
-        <v>30303</v>
+        <v>64480</v>
       </c>
     </row>
     <row r="15">
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>110728</v>
+        <v>109890</v>
       </c>
       <c r="E15" t="n">
-        <v>15876</v>
+        <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>94852</v>
+        <v>94033</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>164073</v>
+        <v>164471</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>148767</v>
+        <v>149165</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-37.0%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7632</v>
+        <v>7594</v>
       </c>
       <c r="P15" t="n">
-        <v>87220</v>
+        <v>86439</v>
       </c>
       <c r="Q15" t="n">
-        <v>37478</v>
+        <v>36659</v>
       </c>
     </row>
     <row r="16">
@@ -1353,13 +1353,13 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265280</v>
+        <v>265261</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>246882</v>
+        <v>246863</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1373,30 +1373,30 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>221434</v>
+        <v>221833</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+19.8%</t>
+          <t>+19.6%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>211234</v>
+        <v>178833</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+38.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>32709</v>
+        <v>32690</v>
       </c>
       <c r="P16" t="n">
         <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>44232</v>
+        <v>44213</v>
       </c>
     </row>
     <row r="17">
@@ -1414,52 +1414,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>431788</v>
+        <v>454157</v>
       </c>
       <c r="E17" t="n">
-        <v>88462</v>
+        <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>343326</v>
+        <v>365724</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>288451</v>
+        <v>296047</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+49.7%</t>
+          <t>+53.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>242585</v>
+        <v>250181</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+41.5%</t>
+          <t>+46.2%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>69029</v>
       </c>
       <c r="O17" t="n">
-        <v>42482</v>
+        <v>42282</v>
       </c>
       <c r="P17" t="n">
-        <v>232014</v>
+        <v>254612</v>
       </c>
       <c r="Q17" t="n">
-        <v>103721</v>
+        <v>103521</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>895353</v>
+        <v>878621</v>
       </c>
       <c r="E18" t="n">
         <v>98495</v>
       </c>
       <c r="F18" t="n">
-        <v>796858</v>
+        <v>780126</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>439972</v>
+        <v>441189</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+103.5%</t>
+          <t>+99.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>388416</v>
+        <v>325647</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+105.2%</t>
+          <t>+139.6%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>218371</v>
+        <v>178402</v>
       </c>
       <c r="P18" t="n">
-        <v>577637</v>
+        <v>600874</v>
       </c>
       <c r="Q18" t="n">
-        <v>494460</v>
+        <v>451528</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>301622</v>
+        <v>313911</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>301276</v>
+        <v>313565</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>224526</v>
+        <v>232443</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+34.3%</t>
+          <t>+35.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>78499</v>
+        <v>86416</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+283.8%</t>
+          <t>+262.9%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>21106</v>
+        <v>21537</v>
       </c>
       <c r="O19" t="n">
-        <v>41184</v>
+        <v>41946</v>
       </c>
       <c r="P19" t="n">
-        <v>239186</v>
+        <v>250282</v>
       </c>
       <c r="Q19" t="n">
-        <v>91710</v>
+        <v>92103</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>361182</v>
+        <v>338526</v>
       </c>
       <c r="E20" t="n">
-        <v>49262</v>
+        <v>49290</v>
       </c>
       <c r="F20" t="n">
-        <v>311920</v>
+        <v>289236</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>340122</v>
+        <v>357516</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+6.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>279122</v>
+        <v>293516</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+11.8%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>86603</v>
+        <v>34879</v>
       </c>
       <c r="P20" t="n">
-        <v>225317</v>
+        <v>254357</v>
       </c>
       <c r="Q20" t="n">
-        <v>40964</v>
+        <v>39276</v>
       </c>
     </row>
     <row r="21">
@@ -1664,54 +1664,54 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>8133434</v>
+        <v>8228430</v>
       </c>
       <c r="E21" t="n">
-        <v>1427967</v>
+        <v>1448553</v>
       </c>
       <c r="F21" t="n">
-        <v>6705466</v>
+        <v>6779876</v>
       </c>
       <c r="G21" t="n">
         <v>256182</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6234556</v>
+        <v>6524830</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+30.5%</t>
+          <t>+26.1%</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5081735</v>
+        <v>5234821</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+32.0%</t>
+          <t>+29.5%</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>136256</v>
+        <v>139196</v>
       </c>
       <c r="O21" t="n">
-        <v>3089104</v>
+        <v>2993089</v>
       </c>
       <c r="P21" t="n">
-        <v>3480505</v>
+        <v>3647990</v>
       </c>
       <c r="Q21" t="n">
-        <v>3870628</v>
+        <v>3923841</v>
       </c>
     </row>
   </sheetData>
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>203</v>
+        <v>503</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="D2" t="n">
-        <v>345.5</v>
+        <v>1129.1</v>
       </c>
       <c r="E2" t="n">
-        <v>89148</v>
+        <v>129848</v>
       </c>
     </row>
     <row r="3">
@@ -1781,16 +1781,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>64.5</v>
+        <v>1082.8</v>
       </c>
       <c r="E3" t="n">
-        <v>396</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="4">
@@ -1800,16 +1800,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>514</v>
+        <v>870</v>
       </c>
       <c r="C4" t="n">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>895.6</v>
+        <v>1572.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2517</v>
+        <v>2434</v>
       </c>
     </row>
   </sheetData>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1643708</v>
+        <v>1593156</v>
       </c>
       <c r="D2" t="n">
-        <v>13983</v>
+        <v>13802</v>
       </c>
       <c r="E2" t="n">
-        <v>1327884</v>
+        <v>1288753</v>
       </c>
     </row>
     <row r="3">
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>393529</v>
+        <v>430400</v>
       </c>
       <c r="D3" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="E3" t="n">
-        <v>228717</v>
+        <v>237788</v>
       </c>
     </row>
     <row r="4">
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1068257</v>
+        <v>985923</v>
       </c>
       <c r="D4" t="n">
-        <v>3309084</v>
+        <v>3504550</v>
       </c>
       <c r="E4" t="n">
-        <v>2314796</v>
+        <v>2398069</v>
       </c>
     </row>
     <row r="5">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>310162</v>
+        <v>316205</v>
       </c>
       <c r="D5" t="n">
         <v>9634</v>
       </c>
       <c r="E5" t="n">
-        <v>318806</v>
+        <v>324849</v>
       </c>
     </row>
     <row r="6">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-15692</v>
+        <v>-14961</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-5557</v>
+        <v>-4961</v>
       </c>
     </row>
     <row r="7">
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>342638</v>
+        <v>306046</v>
       </c>
       <c r="D7" t="n">
-        <v>8987</v>
+        <v>8806</v>
       </c>
       <c r="E7" t="n">
-        <v>333839</v>
+        <v>307464</v>
       </c>
     </row>
     <row r="8">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21447</v>
+        <v>15547</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-85524</v>
+        <v>-91424</v>
       </c>
     </row>
     <row r="9">
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>442579</v>
+        <v>429305</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>371742</v>
+        <v>370070</v>
       </c>
     </row>
     <row r="10">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>253907</v>
+        <v>272242</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>165711</v>
+        <v>173648</v>
       </c>
     </row>
     <row r="11">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>288665</v>
+        <v>268770</v>
       </c>
       <c r="D11" t="n">
-        <v>-18605</v>
+        <v>-18470</v>
       </c>
       <c r="E11" t="n">
-        <v>228866</v>
+        <v>209106</v>
       </c>
     </row>
     <row r="12">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>393529</v>
+        <v>430400</v>
       </c>
       <c r="D12" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="E12" t="n">
-        <v>228717</v>
+        <v>237788</v>
       </c>
     </row>
     <row r="13">
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>494845</v>
+        <v>529674</v>
       </c>
       <c r="D13" t="n">
-        <v>810762</v>
+        <v>871890</v>
       </c>
       <c r="E13" t="n">
-        <v>1254322</v>
+        <v>1350677</v>
       </c>
     </row>
     <row r="14">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31552</v>
+        <v>31514</v>
       </c>
       <c r="D14" t="n">
-        <v>137981</v>
+        <v>136181</v>
       </c>
       <c r="E14" t="n">
-        <v>78987</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="15">
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68877</v>
+        <v>38669</v>
       </c>
       <c r="D15" t="n">
-        <v>266354</v>
+        <v>275956</v>
       </c>
       <c r="E15" t="n">
-        <v>41631</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="16">
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12674</v>
+        <v>18924</v>
       </c>
       <c r="D16" t="n">
-        <v>380554</v>
+        <v>378452</v>
       </c>
       <c r="E16" t="n">
-        <v>96983</v>
+        <v>96637</v>
       </c>
     </row>
     <row r="17">
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31326</v>
+        <v>29346</v>
       </c>
       <c r="D17" t="n">
-        <v>137884</v>
+        <v>181332</v>
       </c>
       <c r="E17" t="n">
-        <v>30303</v>
+        <v>64480</v>
       </c>
     </row>
     <row r="18">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7632</v>
+        <v>7594</v>
       </c>
       <c r="D18" t="n">
-        <v>87220</v>
+        <v>86439</v>
       </c>
       <c r="E18" t="n">
-        <v>37478</v>
+        <v>36659</v>
       </c>
     </row>
     <row r="19">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32709</v>
+        <v>32690</v>
       </c>
       <c r="D19" t="n">
         <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>44232</v>
+        <v>44213</v>
       </c>
     </row>
     <row r="20">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42482</v>
+        <v>42282</v>
       </c>
       <c r="D20" t="n">
-        <v>232014</v>
+        <v>254612</v>
       </c>
       <c r="E20" t="n">
-        <v>103721</v>
+        <v>103521</v>
       </c>
     </row>
     <row r="21">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>218371</v>
+        <v>178402</v>
       </c>
       <c r="D21" t="n">
-        <v>577637</v>
+        <v>600874</v>
       </c>
       <c r="E21" t="n">
-        <v>494460</v>
+        <v>451528</v>
       </c>
     </row>
     <row r="22">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41184</v>
+        <v>41946</v>
       </c>
       <c r="D22" t="n">
-        <v>239186</v>
+        <v>250282</v>
       </c>
       <c r="E22" t="n">
-        <v>91710</v>
+        <v>92103</v>
       </c>
     </row>
     <row r="23">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>86603</v>
+        <v>34879</v>
       </c>
       <c r="D23" t="n">
-        <v>225317</v>
+        <v>254357</v>
       </c>
       <c r="E23" t="n">
-        <v>40964</v>
+        <v>39276</v>
       </c>
     </row>
     <row r="24">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3089104</v>
+        <v>2993089</v>
       </c>
       <c r="D25" t="n">
-        <v>3480505</v>
+        <v>3647990</v>
       </c>
       <c r="E25" t="n">
-        <v>3870628</v>
+        <v>3923841</v>
       </c>
     </row>
   </sheetData>
@@ -2504,19 +2504,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>169152</v>
+        <v>170432</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2524,11 +2524,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>131025.34</v>
+        <v>132305.34</v>
       </c>
     </row>
     <row r="3">
@@ -2588,19 +2588,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>45698</v>
+        <v>40718</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2608,11 +2608,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1138</v>
+        <v>-3842</v>
       </c>
     </row>
     <row r="5">
@@ -2630,19 +2630,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>84700</v>
+        <v>89680</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2650,11 +2650,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>78302.5</v>
+        <v>83282.5</v>
       </c>
     </row>
     <row r="6">
@@ -2768,19 +2768,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>47150</v>
+        <v>51333</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9170</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="9">
@@ -2810,19 +2810,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4979</v>
+        <v>11579</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>38101</v>
+        <v>31501</v>
       </c>
     </row>
     <row r="10">
@@ -2840,19 +2840,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>77196</v>
+        <v>72216</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2860,11 +2860,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>69237</v>
+        <v>64257</v>
       </c>
     </row>
     <row r="11">
@@ -2924,19 +2924,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>78910</v>
+        <v>118510</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>134.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2944,11 +2944,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>72310</v>
+        <v>111910</v>
       </c>
     </row>
     <row r="13">
@@ -2966,19 +2966,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>154178</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>192.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>150.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2986,11 +2986,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>120378</v>
       </c>
     </row>
     <row r="14">
@@ -3218,19 +3218,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67720</v>
+        <v>39920</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33720</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="20">
@@ -3470,19 +3470,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>31114</v>
+        <v>30716</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3490,11 +3490,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13064</v>
+        <v>12666</v>
       </c>
     </row>
     <row r="26">
@@ -3512,19 +3512,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>138236</v>
+        <v>131596</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3532,11 +3532,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>119490</v>
+        <v>112850</v>
       </c>
     </row>
     <row r="27">
@@ -3554,19 +3554,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>33580</v>
+        <v>28600</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>33580</v>
+        <v>28600</v>
       </c>
     </row>
     <row r="28">
@@ -3596,19 +3596,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>39840</v>
+        <v>36840</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3616,11 +3616,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>21240</v>
+        <v>18240</v>
       </c>
     </row>
     <row r="29">
@@ -3638,31 +3638,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>61380</v>
+        <v>56400</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>12940</v>
+        <v>17123</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>48440</v>
+        <v>39277</v>
       </c>
     </row>
     <row r="30">
@@ -3680,19 +3680,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>72700</v>
+        <v>64740</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3700,11 +3700,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>55720</v>
+        <v>47760</v>
       </c>
     </row>
     <row r="31">
@@ -3722,19 +3722,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>183394</v>
+        <v>189994</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>114.6%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>136514</v>
+        <v>143114</v>
       </c>
     </row>
     <row r="32">
@@ -3764,19 +3764,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>105180</v>
+        <v>93578</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3784,11 +3784,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>101200</v>
+        <v>89598</v>
       </c>
     </row>
     <row r="33">
@@ -3806,19 +3806,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>67342</v>
+        <v>77740</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3826,11 +3826,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>42562</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="34">
@@ -3848,19 +3848,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>77979</v>
+        <v>73999</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3868,11 +3868,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>74379</v>
+        <v>70399</v>
       </c>
     </row>
     <row r="35">
@@ -3932,19 +3932,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>82238</v>
+        <v>87218</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3952,11 +3952,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>74278</v>
+        <v>79258</v>
       </c>
     </row>
     <row r="37">
@@ -4058,19 +4058,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>86228</v>
+        <v>84168</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4078,11 +4078,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>69332</v>
+        <v>67272</v>
       </c>
     </row>
     <row r="40">
@@ -4100,19 +4100,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>8780</v>
+        <v>4980</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4120,11 +4120,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>160.6%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>780</v>
+        <v>-3020</v>
       </c>
     </row>
     <row r="41">
@@ -4142,19 +4142,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>58760</v>
+        <v>59760</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>53763</v>
+        <v>54763</v>
       </c>
     </row>
   </sheetData>
@@ -4274,11 +4274,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>53844.1</v>
+        <v>59644.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53844.1</v>
+        <v>59644.1</v>
       </c>
     </row>
     <row r="4">
@@ -4308,11 +4308,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60567.8</v>
+        <v>53067.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60567.8</v>
+        <v>53067.8</v>
       </c>
     </row>
     <row r="5">
@@ -4342,11 +4342,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>42388.8</v>
+        <v>43184.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4354,11 +4354,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>39788.8</v>
+        <v>40584.8</v>
       </c>
     </row>
     <row r="6">
@@ -4376,11 +4376,11 @@
         <v>100000</v>
       </c>
       <c r="D6" t="n">
-        <v>69150.06</v>
+        <v>74548.06</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>69150.06</v>
+        <v>74548.06</v>
       </c>
     </row>
     <row r="7">
@@ -4444,11 +4444,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>27601.93</v>
+        <v>28110.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>27601.93</v>
+        <v>28110.39</v>
       </c>
     </row>
     <row r="9">
@@ -4478,11 +4478,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>35270.96</v>
+        <v>37343.66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4490,11 +4490,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>35070.96</v>
+        <v>37143.66</v>
       </c>
     </row>
     <row r="10">
@@ -4512,11 +4512,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>83675.61</v>
+        <v>84275.32000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>83675.61</v>
+        <v>84275.32000000001</v>
       </c>
     </row>
     <row r="11">
@@ -4546,11 +4546,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>12500</v>
+        <v>20000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12500</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12">
@@ -4580,11 +4580,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>128205.7</v>
+        <v>129805.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>128205.7</v>
+        <v>129805.7</v>
       </c>
     </row>
     <row r="13">
@@ -4784,11 +4784,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>38158</v>
+        <v>48556</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>38158</v>
+        <v>48556</v>
       </c>
     </row>
     <row r="19">
@@ -4818,11 +4818,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>70733.89999999999</v>
+        <v>112391.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4830,11 +4830,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>65733.89999999999</v>
+        <v>107391.9</v>
       </c>
     </row>
     <row r="20">
@@ -4852,11 +4852,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>77727.8</v>
+        <v>77568.60000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>73727.8</v>
+        <v>73568.60000000001</v>
       </c>
     </row>
     <row r="21">
@@ -4886,11 +4886,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10279.8</v>
+        <v>2359.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10279.8</v>
+        <v>2359.8</v>
       </c>
     </row>
     <row r="22">
@@ -4954,11 +4954,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>163558</v>
+        <v>152164</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>163558</v>
+        <v>152164</v>
       </c>
     </row>
     <row r="24">
@@ -5022,11 +5022,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>79584</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5034,11 +5034,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>69784</v>
       </c>
     </row>
     <row r="26">
@@ -5090,11 +5090,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>35752</v>
+        <v>26150</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>35752</v>
+        <v>26150</v>
       </c>
     </row>
     <row r="28">
@@ -5158,11 +5158,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>97572</v>
+        <v>96170</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5170,11 +5170,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>90572</v>
+        <v>89170</v>
       </c>
     </row>
     <row r="30">
@@ -5226,11 +5226,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22496</v>
+        <v>22098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22496</v>
+        <v>22098</v>
       </c>
     </row>
     <row r="32">
@@ -5294,11 +5294,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160069.64</v>
+        <v>160269.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126269.64</v>
+        <v>126469.64</v>
       </c>
     </row>
     <row r="34">
@@ -5362,11 +5362,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>67044.92</v>
+        <v>79044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5374,11 +5374,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>60444.92</v>
+        <v>72444.92</v>
       </c>
     </row>
     <row r="36">
@@ -5464,11 +5464,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>10897</v>
+        <v>21295</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5480,7 +5480,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10897</v>
+        <v>21295</v>
       </c>
     </row>
     <row r="39">
@@ -5498,11 +5498,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>68472</v>
+        <v>75072</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5514,7 +5514,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>68472</v>
+        <v>75072</v>
       </c>
     </row>
     <row r="40">
@@ -5532,11 +5532,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>496884</v>
+        <v>467484</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>106.4%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5544,11 +5544,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>425584</v>
+        <v>396184</v>
       </c>
     </row>
     <row r="41">
@@ -5566,11 +5566,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>102869</v>
+        <v>100889</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>102869</v>
+        <v>100889</v>
       </c>
     </row>
     <row r="42">
@@ -5600,11 +5600,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>118566</v>
+        <v>128566</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5612,11 +5612,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>110966</v>
+        <v>120966</v>
       </c>
     </row>
     <row r="43">
@@ -5634,11 +5634,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106151</v>
+        <v>104171</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97151</v>
+        <v>95171</v>
       </c>
     </row>
     <row r="44">
@@ -5702,11 +5702,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>98466.64000000001</v>
+        <v>102303.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>98466.64000000001</v>
+        <v>102303.64</v>
       </c>
     </row>
     <row r="46">
@@ -5736,11 +5736,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>31103</v>
+        <v>31803</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>31103</v>
+        <v>31803</v>
       </c>
     </row>
     <row r="47">
@@ -5770,11 +5770,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>157308</v>
+        <v>174767</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>157308</v>
+        <v>174767</v>
       </c>
     </row>
     <row r="48">
@@ -5804,11 +5804,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>108869</v>
+        <v>114357</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>108869</v>
+        <v>114357</v>
       </c>
     </row>
     <row r="49">
@@ -5838,11 +5838,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>219861.04</v>
+        <v>231661.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>219861.04</v>
+        <v>231661.04</v>
       </c>
     </row>
     <row r="50">
@@ -5872,11 +5872,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1996</v>
+        <v>1598</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1996</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="51">
@@ -5940,11 +5940,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>299056.64</v>
+        <v>319909.65</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>299056.64</v>
+        <v>319909.65</v>
       </c>
     </row>
     <row r="53">
@@ -5974,11 +5974,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>141525.1</v>
+        <v>144428.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>141525.1</v>
+        <v>144428.1</v>
       </c>
     </row>
     <row r="54">
@@ -6008,11 +6008,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>209949</v>
+        <v>232767</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>209949</v>
+        <v>232767</v>
       </c>
     </row>
     <row r="55">
@@ -6076,11 +6076,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41194</v>
+        <v>10398</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36194</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="57">
@@ -6178,11 +6178,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>112806</v>
+        <v>122806</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>174.7%</t>
+          <t>191.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6190,11 +6190,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>104806</v>
+        <v>114806</v>
       </c>
     </row>
     <row r="60">
@@ -6280,11 +6280,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52071</v>
+        <v>52570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6292,11 +6292,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36271</v>
+        <v>36770</v>
       </c>
     </row>
     <row r="63">
@@ -6314,11 +6314,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>19870</v>
+        <v>18590</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>331.2%</t>
+          <t>309.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19870</v>
+        <v>18590</v>
       </c>
     </row>
   </sheetData>
@@ -6391,16 +6391,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1973367.8</v>
+        <v>2005960.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8973</v>
+        <v>8969</v>
       </c>
       <c r="E2" t="n">
-        <v>1722850.8</v>
+        <v>1748632.8</v>
       </c>
       <c r="F2" t="n">
-        <v>250517</v>
+        <v>257328</v>
       </c>
     </row>
     <row r="3">
@@ -6415,16 +6415,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1729700</v>
+        <v>1760384</v>
       </c>
       <c r="D3" t="n">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E3" t="n">
-        <v>1494038</v>
+        <v>1515981</v>
       </c>
       <c r="F3" t="n">
-        <v>235662</v>
+        <v>244403</v>
       </c>
     </row>
     <row r="4">
@@ -6439,16 +6439,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>243667.8</v>
+        <v>245576.8</v>
       </c>
       <c r="D4" t="n">
         <v>8536</v>
       </c>
       <c r="E4" t="n">
-        <v>228812.8</v>
+        <v>232651.8</v>
       </c>
       <c r="F4" t="n">
-        <v>14855</v>
+        <v>12925</v>
       </c>
     </row>
     <row r="5">
@@ -6463,16 +6463,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3316840</v>
+        <v>3338036</v>
       </c>
       <c r="D5" t="n">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="E5" t="n">
-        <v>782106</v>
+        <v>770504</v>
       </c>
       <c r="F5" t="n">
-        <v>2534734</v>
+        <v>2567532</v>
       </c>
     </row>
     <row r="6">
@@ -6487,16 +6487,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2203122</v>
+        <v>2303734</v>
       </c>
       <c r="D6" t="n">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>2145306</v>
+        <v>2245918</v>
       </c>
     </row>
     <row r="7">
@@ -6511,16 +6511,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1103718</v>
+        <v>1024302</v>
       </c>
       <c r="D7" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E7" t="n">
-        <v>724290</v>
+        <v>712688</v>
       </c>
       <c r="F7" t="n">
-        <v>379428</v>
+        <v>311614</v>
       </c>
     </row>
     <row r="8">
@@ -6535,16 +6535,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1421855.15</v>
+        <v>1519353.76</v>
       </c>
       <c r="D8" t="n">
-        <v>1950</v>
+        <v>2048</v>
       </c>
       <c r="E8" t="n">
-        <v>24790.61</v>
+        <v>23214.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1397064.54</v>
+        <v>1496139.15</v>
       </c>
     </row>
     <row r="9">
@@ -6559,16 +6559,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>887675.0699999999</v>
+        <v>944562.33</v>
       </c>
       <c r="D9" t="n">
-        <v>832</v>
+        <v>861</v>
       </c>
       <c r="E9" t="n">
-        <v>5628.16</v>
+        <v>5428.16</v>
       </c>
       <c r="F9" t="n">
-        <v>882046.91</v>
+        <v>939134.17</v>
       </c>
     </row>
     <row r="10">
@@ -6583,16 +6583,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>534180.08</v>
+        <v>574791.4300000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1118</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="n">
-        <v>19162.45</v>
+        <v>17786.45</v>
       </c>
       <c r="F10" t="n">
-        <v>515017.63</v>
+        <v>557004.98</v>
       </c>
     </row>
     <row r="11">
@@ -6607,16 +6607,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>589000</v>
+        <v>544400</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>370800</v>
+        <v>326200</v>
       </c>
     </row>
     <row r="12">
@@ -6631,16 +6631,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>317465.9</v>
+        <v>355153.9</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="n">
-        <v>112993.9</v>
+        <v>111093.9</v>
       </c>
       <c r="F12" t="n">
-        <v>204472</v>
+        <v>244060</v>
       </c>
     </row>
     <row r="13">
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>324700</v>
+        <v>298880</v>
       </c>
       <c r="D13" t="n">
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>294920</v>
+        <v>269100</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -6679,16 +6679,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>87120</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
-        <v>17820</v>
+        <v>11880</v>
       </c>
       <c r="F14" t="n">
-        <v>93060</v>
+        <v>75240</v>
       </c>
     </row>
     <row r="15">
@@ -6703,16 +6703,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79325.61</v>
+        <v>79525.61</v>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E15" t="n">
         <v>11631.36</v>
       </c>
       <c r="F15" t="n">
-        <v>67694.25</v>
+        <v>67894.25</v>
       </c>
     </row>
   </sheetData>
@@ -6773,22 +6773,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1973367.8</v>
+        <v>2005960.8</v>
       </c>
       <c r="C2" t="n">
-        <v>390988.86</v>
+        <v>411574.86</v>
       </c>
       <c r="D2" t="n">
-        <v>48763</v>
+        <v>50157</v>
       </c>
       <c r="E2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="F2" t="n">
-        <v>342225.86</v>
+        <v>361417.86</v>
       </c>
       <c r="G2" t="n">
-        <v>17.34</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="3">
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3316840</v>
+        <v>3338036</v>
       </c>
       <c r="C3" t="n">
         <v>472001.38</v>
@@ -6813,7 +6813,7 @@
         <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.23</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="4">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1421855.15</v>
+        <v>1519353.76</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6838,7 +6838,7 @@
         <v>2800</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="5">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>589000</v>
+        <v>544400</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -6863,7 +6863,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>19.69</v>
+        <v>21.31</v>
       </c>
     </row>
     <row r="6">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>317465.9</v>
+        <v>355153.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -6882,13 +6882,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>48.15</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="7">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>324700</v>
+        <v>298880</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -6907,13 +6907,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32</v>
+        <v>17.73</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>73.06999999999999</v>
+        <v>79.39</v>
       </c>
     </row>
     <row r="8">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110880</v>
+        <v>87120</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79325.61</v>
+        <v>79525.61</v>
       </c>
       <c r="C9" t="n">
         <v>999</v>
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="C2" t="n">
-        <v>847454.05</v>
+        <v>851959.05</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -7025,13 +7025,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="C3" t="n">
-        <v>267939.4</v>
+        <v>283147.4</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -7089,10 +7089,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>23727.66</v>
+        <v>24121.66</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>22039.7</v>
+        <v>22442.7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -7121,10 +7121,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>16792</v>
+        <v>16849</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7153,10 +7153,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>112254</v>
+        <v>112273</v>
       </c>
     </row>
     <row r="8">
@@ -7397,7 +7397,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7406,16 +7406,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>72276</v>
+        <v>67545</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7424,16 +7424,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="D13" t="n">
-        <v>22214.5</v>
+        <v>34487</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7442,88 +7442,88 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>21780</v>
+        <v>21785</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>11200</v>
+        <v>5742</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>7932.66</v>
+        <v>5106.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>442</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>761</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7546,14 +7546,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>72342</v>
       </c>
     </row>
     <row r="21">
@@ -7564,92 +7564,92 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>22252.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>155</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>63305</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>34449</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>21785</v>
+        <v>7932.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>5685</v>
+        <v>442</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7658,64 +7658,64 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>5106.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2509</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>704</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
@@ -7793,91 +7793,91 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>116</v>
       </c>
       <c r="D34" t="n">
-        <v>58733.4</v>
+        <v>75004</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D35" t="n">
-        <v>20500</v>
+        <v>20054</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>9000</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>200</v>
+        <v>418</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D38" t="n">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39">
@@ -7888,14 +7888,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>62893</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
@@ -7906,104 +7906,104 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>19987</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>429</v>
+        <v>58733.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>399</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>161</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="46">
@@ -8014,14 +8014,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>58034</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="47">
@@ -8032,14 +8032,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="D47" t="n">
-        <v>14839</v>
+        <v>7486</v>
       </c>
     </row>
     <row r="48">
@@ -8050,14 +8050,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>7439</v>
+        <v>598</v>
       </c>
     </row>
     <row r="49">
@@ -8068,14 +8068,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>598</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50">
@@ -8086,14 +8086,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>394</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51">
@@ -8104,14 +8104,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
     </row>
     <row r="52">
@@ -8122,14 +8122,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D53" t="n">
-        <v>25892.9</v>
+        <v>30204.9</v>
       </c>
     </row>
     <row r="54">
@@ -8162,10 +8162,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D54" t="n">
-        <v>16470</v>
+        <v>16508</v>
       </c>
     </row>
     <row r="55">
@@ -8180,10 +8180,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D55" t="n">
-        <v>8761</v>
+        <v>9079</v>
       </c>
     </row>
     <row r="56">
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D56" t="n">
-        <v>1288</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="57">
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D61" t="n">
-        <v>39336</v>
+        <v>39345</v>
       </c>
     </row>
     <row r="62">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D63" t="n">
-        <v>660</v>
+        <v>679</v>
       </c>
     </row>
     <row r="64">
@@ -8693,7 +8693,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8705,43 +8705,43 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>10000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>6289</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>3</v>
       </c>
       <c r="D86" t="n">
-        <v>1328</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
@@ -8752,68 +8752,68 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>19</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>9000</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D89" t="n">
-        <v>6800</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>76</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="91">
@@ -8824,14 +8824,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>9318</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92">
@@ -8842,85 +8842,49 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>5500</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>29</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2</v>
-      </c>
-      <c r="D96" t="n">
         <v>28</v>
       </c>
     </row>
@@ -8988,10 +8952,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" t="n">
-        <v>171751.16</v>
+        <v>184267.16</v>
       </c>
     </row>
     <row r="5">
@@ -9014,10 +8978,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>135360</v>
+        <v>141960</v>
       </c>
     </row>
     <row r="7">
@@ -9123,10 +9087,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C2" t="n">
-        <v>189559.33</v>
+        <v>193875.33</v>
       </c>
     </row>
     <row r="3">
@@ -9136,10 +9100,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C3" t="n">
-        <v>161699.4</v>
+        <v>162045.4</v>
       </c>
     </row>
     <row r="4">
@@ -9149,10 +9113,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>142639.5</v>
+        <v>146789.5</v>
       </c>
     </row>
     <row r="5">
@@ -9162,10 +9126,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C5" t="n">
-        <v>141661.98</v>
+        <v>141775.98</v>
       </c>
     </row>
     <row r="6">
@@ -9175,10 +9139,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C6" t="n">
-        <v>126680</v>
+        <v>130920</v>
       </c>
     </row>
     <row r="7">
@@ -9188,10 +9152,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>92094</v>
+        <v>92113</v>
       </c>
     </row>
     <row r="8">
@@ -9201,10 +9165,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>69497</v>
+        <v>69516</v>
       </c>
     </row>
     <row r="9">
@@ -9214,10 +9178,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>64848.8</v>
+        <v>64885.8</v>
       </c>
     </row>
     <row r="10">
@@ -9227,10 +9191,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C10" t="n">
-        <v>62998</v>
+        <v>63411</v>
       </c>
     </row>
     <row r="11">
@@ -9240,10 +9204,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C11" t="n">
-        <v>54405</v>
+        <v>54462</v>
       </c>
     </row>
     <row r="12">
@@ -9279,10 +9243,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>31775</v>
+        <v>31794</v>
       </c>
     </row>
     <row r="15">
@@ -9305,10 +9269,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C16" t="n">
-        <v>27035</v>
+        <v>27130</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,25 +529,25 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>461959</v>
+        <v>470209</v>
       </c>
       <c r="E2" t="n">
         <v>136120</v>
       </c>
       <c r="F2" t="n">
-        <v>325839</v>
+        <v>334089</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+54.5%</t>
+          <t>+57.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+126.9%</t>
+          <t>+132.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>1318</v>
       </c>
       <c r="E3" t="n">
         <v>14980</v>
       </c>
       <c r="F3" t="n">
-        <v>-14961</v>
+        <v>-13662</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-99.9%</t>
+          <t>-92.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -616,7 +616,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,25 +639,25 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>452826</v>
+        <v>493912</v>
       </c>
       <c r="E4" t="n">
         <v>137973</v>
       </c>
       <c r="F4" t="n">
-        <v>314852</v>
+        <v>355938</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+10.1%</t>
+          <t>+20.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,25 +696,25 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>218577</v>
+        <v>226501</v>
       </c>
       <c r="E5" t="n">
         <v>197841</v>
       </c>
       <c r="F5" t="n">
-        <v>20735</v>
+        <v>28659</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-92.9%</t>
+          <t>-90.2%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,25 +753,25 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>493990</v>
+        <v>511626</v>
       </c>
       <c r="E6" t="n">
         <v>57758</v>
       </c>
       <c r="F6" t="n">
-        <v>436231</v>
+        <v>453867</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+91.9%</t>
+          <t>+98.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+125.8%</t>
+          <t>+134.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,25 +810,25 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>355575</v>
+        <v>360310</v>
       </c>
       <c r="E7" t="n">
         <v>81615</v>
       </c>
       <c r="F7" t="n">
-        <v>273960</v>
+        <v>278695</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>100.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+37.7%</t>
+          <t>+39.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+39.8%</t>
+          <t>+42.2%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,25 +867,25 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>347770</v>
+        <v>355003</v>
       </c>
       <c r="E8" t="n">
         <v>97470</v>
       </c>
       <c r="F8" t="n">
-        <v>250300</v>
+        <v>257533</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+17.3%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,25 +924,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>833538</v>
+        <v>864067</v>
       </c>
       <c r="E9" t="n">
         <v>286700</v>
       </c>
       <c r="F9" t="n">
-        <v>546838</v>
+        <v>577367</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+24.3%</t>
+          <t>+28.9%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+7.1%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,23 +981,23 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1424373</v>
+        <v>1429049</v>
       </c>
       <c r="E10" t="n">
         <v>22808</v>
       </c>
       <c r="F10" t="n">
-        <v>1401565</v>
+        <v>1406241</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+27.1%</t>
+          <t>+27.5%</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1013,18 +1013,18 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+25.1%</t>
+          <t>+25.5%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>529674</v>
+        <v>534350</v>
       </c>
       <c r="P10" t="n">
         <v>871890</v>
       </c>
       <c r="Q10" t="n">
-        <v>1350677</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="11">
@@ -1042,23 +1042,23 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>204306</v>
+        <v>206523</v>
       </c>
       <c r="E11" t="n">
         <v>36399</v>
       </c>
       <c r="F11" t="n">
-        <v>167906</v>
+        <v>170123</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1074,20 +1074,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>31514</v>
+        <v>31533</v>
       </c>
       <c r="P11" t="n">
-        <v>136181</v>
+        <v>138379</v>
       </c>
       <c r="Q11" t="n">
-        <v>77150</v>
+        <v>78969</v>
       </c>
     </row>
     <row r="12">
@@ -1105,23 +1105,23 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>344701</v>
+        <v>375497</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>314625</v>
+        <v>345421</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+45.4%</t>
+          <t>+58.4%</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1137,15 +1137,15 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+46.9%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>38669</v>
+        <v>69067</v>
       </c>
       <c r="P12" t="n">
-        <v>275956</v>
+        <v>276354</v>
       </c>
       <c r="Q12" t="n">
         <v>41821</v>
@@ -1166,23 +1166,23 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>473605</v>
+        <v>481680</v>
       </c>
       <c r="E13" t="n">
         <v>45013</v>
       </c>
       <c r="F13" t="n">
-        <v>428591</v>
+        <v>436666</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+24.7%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1198,20 +1198,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+41.3%</t>
+          <t>+44.0%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>18924</v>
+        <v>19299</v>
       </c>
       <c r="P13" t="n">
-        <v>378452</v>
+        <v>386152</v>
       </c>
       <c r="Q13" t="n">
-        <v>96637</v>
+        <v>97212</v>
       </c>
     </row>
     <row r="14">
@@ -1229,23 +1229,23 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>241898</v>
+        <v>250416</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>227032</v>
+        <v>235550</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+11.5%</t>
+          <t>+15.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1261,20 +1261,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+16.0%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>16354</v>
       </c>
       <c r="O14" t="n">
-        <v>29346</v>
+        <v>31326</v>
       </c>
       <c r="P14" t="n">
-        <v>181332</v>
+        <v>187870</v>
       </c>
       <c r="Q14" t="n">
-        <v>64480</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="15">
@@ -1292,23 +1292,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>109890</v>
+        <v>111208</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>94033</v>
+        <v>95351</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1324,18 +1324,18 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7594</v>
+        <v>7632</v>
       </c>
       <c r="P15" t="n">
-        <v>86439</v>
+        <v>87719</v>
       </c>
       <c r="Q15" t="n">
-        <v>36659</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="16">
@@ -1353,13 +1353,13 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265261</v>
+        <v>265290</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>246863</v>
+        <v>246892</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1385,18 +1385,18 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+38.0%</t>
+          <t>+38.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>32690</v>
+        <v>32719</v>
       </c>
       <c r="P16" t="n">
         <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>44213</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="17">
@@ -1414,23 +1414,23 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454157</v>
+        <v>454755</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>365724</v>
+        <v>366322</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+53.4%</t>
+          <t>+53.6%</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1446,20 +1446,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+46.2%</t>
+          <t>+46.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>69029</v>
       </c>
       <c r="O17" t="n">
-        <v>42282</v>
+        <v>42482</v>
       </c>
       <c r="P17" t="n">
-        <v>254612</v>
+        <v>255010</v>
       </c>
       <c r="Q17" t="n">
-        <v>103521</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="18">
@@ -1477,23 +1477,23 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>878621</v>
+        <v>928588</v>
       </c>
       <c r="E18" t="n">
         <v>98495</v>
       </c>
       <c r="F18" t="n">
-        <v>780126</v>
+        <v>830093</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+99.1%</t>
+          <t>+110.5%</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1509,20 +1509,20 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+139.6%</t>
+          <t>+154.9%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>178402</v>
+        <v>226389</v>
       </c>
       <c r="P18" t="n">
-        <v>600874</v>
+        <v>602854</v>
       </c>
       <c r="Q18" t="n">
-        <v>451528</v>
+        <v>501097</v>
       </c>
     </row>
     <row r="19">
@@ -1540,23 +1540,23 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>313911</v>
+        <v>321930</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>313565</v>
+        <v>321584</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+35.0%</t>
+          <t>+38.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+262.9%</t>
+          <t>+272.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>21537</v>
       </c>
       <c r="O19" t="n">
-        <v>41946</v>
+        <v>41965</v>
       </c>
       <c r="P19" t="n">
-        <v>250282</v>
+        <v>258282</v>
       </c>
       <c r="Q19" t="n">
-        <v>92103</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="20">
@@ -1603,23 +1603,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>338526</v>
+        <v>372221</v>
       </c>
       <c r="E20" t="n">
         <v>49290</v>
       </c>
       <c r="F20" t="n">
-        <v>289236</v>
+        <v>322931</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1635,18 +1635,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>34879</v>
+        <v>36196</v>
       </c>
       <c r="P20" t="n">
-        <v>254357</v>
+        <v>286735</v>
       </c>
       <c r="Q20" t="n">
-        <v>39276</v>
+        <v>41577</v>
       </c>
     </row>
     <row r="21">
@@ -1664,25 +1664,25 @@
         <v>13000000</v>
       </c>
       <c r="D21" t="n">
-        <v>8228430</v>
+        <v>8495030</v>
       </c>
       <c r="E21" t="n">
         <v>1448553</v>
       </c>
       <c r="F21" t="n">
-        <v>6779876</v>
+        <v>7046476</v>
       </c>
       <c r="G21" t="n">
         <v>256182</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>+26.1%</t>
+          <t>+30.2%</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1698,20 +1698,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+29.5%</t>
+          <t>+34.6%</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>139196</v>
       </c>
       <c r="O21" t="n">
-        <v>2993089</v>
+        <v>3170800</v>
       </c>
       <c r="P21" t="n">
-        <v>3647990</v>
+        <v>3736879</v>
       </c>
       <c r="Q21" t="n">
-        <v>3923841</v>
+        <v>4088163</v>
       </c>
     </row>
   </sheetData>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1593156</v>
+        <v>1681100</v>
       </c>
       <c r="D2" t="n">
-        <v>13802</v>
+        <v>14021</v>
       </c>
       <c r="E2" t="n">
-        <v>1288753</v>
+        <v>1354518</v>
       </c>
     </row>
     <row r="3">
@@ -1952,13 +1952,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>430400</v>
+        <v>433129</v>
       </c>
       <c r="D3" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="E3" t="n">
-        <v>237788</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="4">
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>985923</v>
+        <v>1072961</v>
       </c>
       <c r="D4" t="n">
-        <v>3504550</v>
+        <v>3565420</v>
       </c>
       <c r="E4" t="n">
-        <v>2398069</v>
+        <v>2466097</v>
       </c>
     </row>
     <row r="5">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>316205</v>
+        <v>324455</v>
       </c>
       <c r="D5" t="n">
         <v>9634</v>
       </c>
       <c r="E5" t="n">
-        <v>324849</v>
+        <v>333099</v>
       </c>
     </row>
     <row r="6">
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-14961</v>
+        <v>-13662</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-4961</v>
+        <v>-3662</v>
       </c>
     </row>
     <row r="7">
@@ -2036,13 +2036,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>306046</v>
+        <v>346913</v>
       </c>
       <c r="D7" t="n">
-        <v>8806</v>
+        <v>9025</v>
       </c>
       <c r="E7" t="n">
-        <v>307464</v>
+        <v>338152</v>
       </c>
     </row>
     <row r="8">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15547</v>
+        <v>23471</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-91424</v>
+        <v>-83500</v>
       </c>
     </row>
     <row r="9">
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>429305</v>
+        <v>446941</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>370070</v>
+        <v>375706</v>
       </c>
     </row>
     <row r="10">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>272242</v>
+        <v>276977</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>173648</v>
+        <v>178383</v>
       </c>
     </row>
     <row r="11">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>268770</v>
+        <v>276003</v>
       </c>
       <c r="D11" t="n">
         <v>-18470</v>
       </c>
       <c r="E11" t="n">
-        <v>209106</v>
+        <v>216339</v>
       </c>
     </row>
     <row r="12">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>430400</v>
+        <v>433129</v>
       </c>
       <c r="D12" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="E12" t="n">
-        <v>237788</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="13">
@@ -2162,13 +2162,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>529674</v>
+        <v>534350</v>
       </c>
       <c r="D13" t="n">
         <v>871890</v>
       </c>
       <c r="E13" t="n">
-        <v>1350677</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="14">
@@ -2183,13 +2183,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31514</v>
+        <v>31533</v>
       </c>
       <c r="D14" t="n">
-        <v>136181</v>
+        <v>138379</v>
       </c>
       <c r="E14" t="n">
-        <v>77150</v>
+        <v>78969</v>
       </c>
     </row>
     <row r="15">
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38669</v>
+        <v>69067</v>
       </c>
       <c r="D15" t="n">
-        <v>275956</v>
+        <v>276354</v>
       </c>
       <c r="E15" t="n">
         <v>41821</v>
@@ -2225,13 +2225,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18924</v>
+        <v>19299</v>
       </c>
       <c r="D16" t="n">
-        <v>378452</v>
+        <v>386152</v>
       </c>
       <c r="E16" t="n">
-        <v>96637</v>
+        <v>97212</v>
       </c>
     </row>
     <row r="17">
@@ -2246,13 +2246,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29346</v>
+        <v>31326</v>
       </c>
       <c r="D17" t="n">
-        <v>181332</v>
+        <v>187870</v>
       </c>
       <c r="E17" t="n">
-        <v>64480</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="18">
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7594</v>
+        <v>7632</v>
       </c>
       <c r="D18" t="n">
-        <v>86439</v>
+        <v>87719</v>
       </c>
       <c r="E18" t="n">
-        <v>36659</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="19">
@@ -2288,13 +2288,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32690</v>
+        <v>32719</v>
       </c>
       <c r="D19" t="n">
         <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>44213</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="20">
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42282</v>
+        <v>42482</v>
       </c>
       <c r="D20" t="n">
-        <v>254612</v>
+        <v>255010</v>
       </c>
       <c r="E20" t="n">
-        <v>103521</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="21">
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>178402</v>
+        <v>226389</v>
       </c>
       <c r="D21" t="n">
-        <v>600874</v>
+        <v>602854</v>
       </c>
       <c r="E21" t="n">
-        <v>451528</v>
+        <v>501097</v>
       </c>
     </row>
     <row r="22">
@@ -2351,13 +2351,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41946</v>
+        <v>41965</v>
       </c>
       <c r="D22" t="n">
-        <v>250282</v>
+        <v>258282</v>
       </c>
       <c r="E22" t="n">
-        <v>92103</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="23">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>34879</v>
+        <v>36196</v>
       </c>
       <c r="D23" t="n">
-        <v>254357</v>
+        <v>286735</v>
       </c>
       <c r="E23" t="n">
-        <v>39276</v>
+        <v>41577</v>
       </c>
     </row>
     <row r="24">
@@ -2414,13 +2414,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2993089</v>
+        <v>3170800</v>
       </c>
       <c r="D25" t="n">
-        <v>3647990</v>
+        <v>3736879</v>
       </c>
       <c r="E25" t="n">
-        <v>3923841</v>
+        <v>4088163</v>
       </c>
     </row>
   </sheetData>
@@ -2588,19 +2588,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>40718</v>
+        <v>45698</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2608,11 +2608,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-3842</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5">
@@ -2840,19 +2840,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>72216</v>
+        <v>77196</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2860,11 +2860,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>64257</v>
+        <v>69237</v>
       </c>
     </row>
     <row r="11">
@@ -2966,19 +2966,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>154178</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>192.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>150.5%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2986,11 +2986,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>120378</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -3218,19 +3218,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>39920</v>
+        <v>67720</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>5920</v>
+        <v>33720</v>
       </c>
     </row>
     <row r="20">
@@ -3470,19 +3470,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>30716</v>
+        <v>31114</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3490,11 +3490,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>12666</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="26">
@@ -3512,19 +3512,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>131596</v>
+        <v>145576</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3532,11 +3532,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>112850</v>
+        <v>126830</v>
       </c>
     </row>
     <row r="27">
@@ -3554,19 +3554,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>28600</v>
+        <v>33580</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>28600</v>
+        <v>33580</v>
       </c>
     </row>
     <row r="28">
@@ -3596,19 +3596,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>36840</v>
+        <v>41820</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3616,11 +3616,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>18240</v>
+        <v>23220</v>
       </c>
     </row>
     <row r="29">
@@ -3638,19 +3638,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>56400</v>
+        <v>61380</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3658,11 +3658,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>39277</v>
+        <v>44257</v>
       </c>
     </row>
     <row r="30">
@@ -3680,19 +3680,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>64740</v>
+        <v>72700</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3700,11 +3700,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>47760</v>
+        <v>55720</v>
       </c>
     </row>
     <row r="31">
@@ -3764,19 +3764,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>93578</v>
+        <v>105578</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3784,11 +3784,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>89598</v>
+        <v>101598</v>
       </c>
     </row>
     <row r="33">
@@ -3848,19 +3848,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>73999</v>
+        <v>77979</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3868,11 +3868,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>70399</v>
+        <v>74379</v>
       </c>
     </row>
     <row r="35">
@@ -4058,19 +4058,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>84168</v>
+        <v>88128</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4078,11 +4078,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>67272</v>
+        <v>71232</v>
       </c>
     </row>
     <row r="40">
@@ -4100,19 +4100,19 @@
         <v>40000</v>
       </c>
       <c r="D40" t="n">
-        <v>4980</v>
+        <v>8780</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -4120,11 +4120,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>160.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>-3020</v>
+        <v>780</v>
       </c>
     </row>
     <row r="41">
@@ -4142,19 +4142,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>59760</v>
+        <v>63740</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4162,11 +4162,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>54763</v>
+        <v>58743</v>
       </c>
     </row>
   </sheetData>
@@ -4240,11 +4240,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>229174.6</v>
+        <v>229374.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>189307.93</v>
+        <v>189507.93</v>
       </c>
     </row>
     <row r="3">
@@ -4308,11 +4308,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>53067.8</v>
+        <v>60567.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>53067.8</v>
+        <v>60567.8</v>
       </c>
     </row>
     <row r="5">
@@ -4478,11 +4478,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>37343.66</v>
+        <v>45343.66</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4490,11 +4490,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>37143.66</v>
+        <v>45143.66</v>
       </c>
     </row>
     <row r="10">
@@ -4852,11 +4852,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>77568.60000000001</v>
+        <v>78166.60000000001</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>73568.60000000001</v>
+        <v>74166.60000000001</v>
       </c>
     </row>
     <row r="21">
@@ -4886,11 +4886,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>2359.8</v>
+        <v>10279.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2359.8</v>
+        <v>10279.8</v>
       </c>
     </row>
     <row r="22">
@@ -4954,11 +4954,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>152164</v>
+        <v>173558</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>152164</v>
+        <v>173558</v>
       </c>
     </row>
     <row r="24">
@@ -5022,11 +5022,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>79584</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5034,11 +5034,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>69784</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -5090,11 +5090,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>26150</v>
+        <v>36150</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26150</v>
+        <v>36150</v>
       </c>
     </row>
     <row r="28">
@@ -5158,11 +5158,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>96170</v>
+        <v>97970</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5170,11 +5170,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>89170</v>
+        <v>90970</v>
       </c>
     </row>
     <row r="30">
@@ -5226,11 +5226,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22098</v>
+        <v>22496</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22098</v>
+        <v>22496</v>
       </c>
     </row>
     <row r="32">
@@ -5294,11 +5294,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160269.64</v>
+        <v>160667.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126469.64</v>
+        <v>126867.64</v>
       </c>
     </row>
     <row r="34">
@@ -5532,11 +5532,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>467484</v>
+        <v>513482</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>110.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5544,11 +5544,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>396184</v>
+        <v>442182</v>
       </c>
     </row>
     <row r="41">
@@ -5566,11 +5566,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>100889</v>
+        <v>102869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>100889</v>
+        <v>102869</v>
       </c>
     </row>
     <row r="42">
@@ -5634,11 +5634,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>104171</v>
+        <v>106151</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95171</v>
+        <v>97151</v>
       </c>
     </row>
     <row r="44">
@@ -5736,11 +5736,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>31803</v>
+        <v>33783</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>31803</v>
+        <v>33783</v>
       </c>
     </row>
     <row r="47">
@@ -5872,11 +5872,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1598</v>
+        <v>1996</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1598</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="51">
@@ -6008,11 +6008,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>232767</v>
+        <v>234747</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>232767</v>
+        <v>234747</v>
       </c>
     </row>
     <row r="55">
@@ -6076,11 +6076,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>10398</v>
+        <v>41194</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6088,11 +6088,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>5398</v>
+        <v>36194</v>
       </c>
     </row>
     <row r="57">
@@ -6314,11 +6314,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>18590</v>
+        <v>19870</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>309.8%</t>
+          <t>331.2%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>18590</v>
+        <v>19870</v>
       </c>
     </row>
   </sheetData>
@@ -6391,16 +6391,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2005960.8</v>
+        <v>2064246.8</v>
       </c>
       <c r="D2" t="n">
-        <v>8969</v>
+        <v>9481</v>
       </c>
       <c r="E2" t="n">
-        <v>1748632.8</v>
+        <v>1804310.8</v>
       </c>
       <c r="F2" t="n">
-        <v>257328</v>
+        <v>259936</v>
       </c>
     </row>
     <row r="3">
@@ -6415,16 +6415,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1760384</v>
+        <v>1805279</v>
       </c>
       <c r="D3" t="n">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E3" t="n">
-        <v>1515981</v>
+        <v>1560857</v>
       </c>
       <c r="F3" t="n">
-        <v>244403</v>
+        <v>244422</v>
       </c>
     </row>
     <row r="4">
@@ -6439,16 +6439,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>245576.8</v>
+        <v>258967.8</v>
       </c>
       <c r="D4" t="n">
-        <v>8536</v>
+        <v>9032</v>
       </c>
       <c r="E4" t="n">
-        <v>232651.8</v>
+        <v>243453.8</v>
       </c>
       <c r="F4" t="n">
-        <v>12925</v>
+        <v>15514</v>
       </c>
     </row>
     <row r="5">
@@ -6463,16 +6463,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3338036</v>
+        <v>3440314</v>
       </c>
       <c r="D5" t="n">
-        <v>652</v>
+        <v>673</v>
       </c>
       <c r="E5" t="n">
-        <v>770504</v>
+        <v>792902</v>
       </c>
       <c r="F5" t="n">
-        <v>2567532</v>
+        <v>2647412</v>
       </c>
     </row>
     <row r="6">
@@ -6487,16 +6487,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2303734</v>
+        <v>2351424</v>
       </c>
       <c r="D6" t="n">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="E6" t="n">
         <v>57816</v>
       </c>
       <c r="F6" t="n">
-        <v>2245918</v>
+        <v>2293608</v>
       </c>
     </row>
     <row r="7">
@@ -6511,16 +6511,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1024302</v>
+        <v>1078890</v>
       </c>
       <c r="D7" t="n">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E7" t="n">
-        <v>712688</v>
+        <v>735086</v>
       </c>
       <c r="F7" t="n">
-        <v>311614</v>
+        <v>343804</v>
       </c>
     </row>
     <row r="8">
@@ -6535,16 +6535,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1519353.76</v>
+        <v>1524429.76</v>
       </c>
       <c r="D8" t="n">
-        <v>2048</v>
+        <v>2057</v>
       </c>
       <c r="E8" t="n">
-        <v>23214.61</v>
+        <v>26290.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1496139.15</v>
+        <v>1498139.15</v>
       </c>
     </row>
     <row r="9">
@@ -6559,16 +6559,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>944562.33</v>
+        <v>946762.33</v>
       </c>
       <c r="D9" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="E9" t="n">
-        <v>5428.16</v>
+        <v>5628.16</v>
       </c>
       <c r="F9" t="n">
-        <v>939134.17</v>
+        <v>941134.17</v>
       </c>
     </row>
     <row r="10">
@@ -6583,13 +6583,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>574791.4300000001</v>
+        <v>577667.4300000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="E10" t="n">
-        <v>17786.45</v>
+        <v>20662.45</v>
       </c>
       <c r="F10" t="n">
         <v>557004.98</v>
@@ -6607,16 +6607,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>544400</v>
+        <v>590000</v>
       </c>
       <c r="D11" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
         <v>218200</v>
       </c>
       <c r="F11" t="n">
-        <v>326200</v>
+        <v>371800</v>
       </c>
     </row>
     <row r="12">
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>355153.9</v>
+        <v>358953.9</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>111093.9</v>
+        <v>114893.9</v>
       </c>
       <c r="F12" t="n">
         <v>244060</v>
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>298880</v>
+        <v>326680</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>269100</v>
+        <v>296900</v>
       </c>
       <c r="F13" t="n">
         <v>29780</v>
@@ -6679,16 +6679,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>87120</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E14" t="n">
-        <v>11880</v>
+        <v>17820</v>
       </c>
       <c r="F14" t="n">
-        <v>75240</v>
+        <v>93060</v>
       </c>
     </row>
     <row r="15">
@@ -6706,7 +6706,7 @@
         <v>79525.61</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" t="n">
         <v>11631.36</v>
@@ -6773,7 +6773,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2005960.8</v>
+        <v>2064246.8</v>
       </c>
       <c r="C2" t="n">
         <v>411574.86</v>
@@ -6782,13 +6782,13 @@
         <v>50157</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="F2" t="n">
         <v>361417.86</v>
       </c>
       <c r="G2" t="n">
-        <v>18.02</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="3">
@@ -6798,7 +6798,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3338036</v>
+        <v>3440314</v>
       </c>
       <c r="C3" t="n">
         <v>472001.38</v>
@@ -6813,7 +6813,7 @@
         <v>472001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.14</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="4">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1519353.76</v>
+        <v>1524429.76</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>544400</v>
+        <v>590000</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -6863,7 +6863,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>21.31</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="6">
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>355153.9</v>
+        <v>358953.9</v>
       </c>
       <c r="C6" t="n">
         <v>154862.9</v>
@@ -6882,13 +6882,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" t="n">
         <v>152845</v>
       </c>
       <c r="G6" t="n">
-        <v>43.04</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="7">
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>298880</v>
+        <v>326680</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -6907,13 +6907,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>17.73</v>
+        <v>16.22</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>79.39</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="8">
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87120</v>
+        <v>110880</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1652,65 +1652,110 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>未映射</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14920</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18111</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3191</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
+        <v>-16391</v>
+      </c>
+      <c r="P21" t="n">
+        <v>13200</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-770</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>南区合计</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C22" t="n">
         <v>13000000</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D22" t="n">
         <v>8495030</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E22" t="n">
         <v>1448553</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F22" t="n">
         <v>7046476</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G22" t="n">
         <v>256182</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>56.2%</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>6524830</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>+30.2%</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>5234821</v>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>+34.6%</t>
         </is>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>139196</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O22" t="n">
         <v>3170800</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P22" t="n">
         <v>3736879</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q22" t="n">
         <v>4088163</v>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>143626</v>
+        <v>143627</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-14030</v>
+        <v>-14031</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>493912</v>
       </c>
       <c r="E4" t="n">
-        <v>137973</v>
+        <v>137974</v>
       </c>
       <c r="F4" t="n">
         <v>355938</v>
@@ -699,7 +699,7 @@
         <v>226501</v>
       </c>
       <c r="E5" t="n">
-        <v>197841</v>
+        <v>197842</v>
       </c>
       <c r="F5" t="n">
         <v>28659</v>
@@ -756,10 +756,10 @@
         <v>511626</v>
       </c>
       <c r="E6" t="n">
-        <v>57758</v>
+        <v>57759</v>
       </c>
       <c r="F6" t="n">
-        <v>453867</v>
+        <v>453868</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>257410</v>
+        <v>257411</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>193211</v>
+        <v>193212</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -810,13 +810,13 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360310</v>
+        <v>360311</v>
       </c>
       <c r="E7" t="n">
         <v>81615</v>
       </c>
       <c r="F7" t="n">
-        <v>278695</v>
+        <v>278696</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355003</v>
+        <v>355004</v>
       </c>
       <c r="E8" t="n">
         <v>97470</v>
       </c>
       <c r="F8" t="n">
-        <v>257533</v>
+        <v>257534</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>296470</v>
+        <v>296471</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>262996</v>
+        <v>262997</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1120687</v>
+        <v>1120688</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1120687</v>
+        <v>1120688</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>534350</v>
       </c>
       <c r="P10" t="n">
-        <v>871890</v>
+        <v>871891</v>
       </c>
       <c r="Q10" t="n">
         <v>1354955</v>
@@ -1045,7 +1045,7 @@
         <v>206523</v>
       </c>
       <c r="E11" t="n">
-        <v>36399</v>
+        <v>36400</v>
       </c>
       <c r="F11" t="n">
         <v>170123</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>247516</v>
+        <v>247517</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>222408</v>
+        <v>222409</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>31533</v>
+        <v>31534</v>
       </c>
       <c r="P11" t="n">
         <v>138379</v>
@@ -1169,10 +1169,10 @@
         <v>481680</v>
       </c>
       <c r="E13" t="n">
-        <v>45013</v>
+        <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>436666</v>
+        <v>436667</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>379795</v>
+        <v>379796</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>303286</v>
+        <v>303287</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>19299</v>
+        <v>19300</v>
       </c>
       <c r="P13" t="n">
         <v>386152</v>
       </c>
       <c r="Q13" t="n">
-        <v>97212</v>
+        <v>97213</v>
       </c>
     </row>
     <row r="14">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>221833</v>
+        <v>221834</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>178833</v>
+        <v>178834</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454755</v>
+        <v>454756</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>296047</v>
+        <v>296048</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>250181</v>
+        <v>250182</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>69029</v>
+        <v>69030</v>
       </c>
       <c r="O17" t="n">
         <v>42482</v>
       </c>
       <c r="P17" t="n">
-        <v>255010</v>
+        <v>255011</v>
       </c>
       <c r="Q17" t="n">
-        <v>103721</v>
+        <v>103722</v>
       </c>
     </row>
     <row r="18">
@@ -1477,13 +1477,13 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>928588</v>
+        <v>928589</v>
       </c>
       <c r="E18" t="n">
         <v>98495</v>
       </c>
       <c r="F18" t="n">
-        <v>830093</v>
+        <v>830094</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>441189</v>
+        <v>441190</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>325647</v>
+        <v>325648</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1519,10 +1519,10 @@
         <v>226389</v>
       </c>
       <c r="P18" t="n">
-        <v>602854</v>
+        <v>602855</v>
       </c>
       <c r="Q18" t="n">
-        <v>501097</v>
+        <v>501098</v>
       </c>
     </row>
     <row r="19">
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>232443</v>
+        <v>232444</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>86416</v>
+        <v>86417</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1603,13 +1603,13 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>372221</v>
+        <v>372222</v>
       </c>
       <c r="E20" t="n">
         <v>49290</v>
       </c>
       <c r="F20" t="n">
-        <v>322931</v>
+        <v>322932</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>357516</v>
+        <v>357517</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>293516</v>
+        <v>293517</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1640,13 +1640,13 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>36196</v>
+        <v>36197</v>
       </c>
       <c r="P20" t="n">
         <v>286735</v>
       </c>
       <c r="Q20" t="n">
-        <v>41577</v>
+        <v>41578</v>
       </c>
     </row>
     <row r="21">
@@ -1712,7 +1712,7 @@
         <v>8495030</v>
       </c>
       <c r="E22" t="n">
-        <v>1448553</v>
+        <v>1448554</v>
       </c>
       <c r="F22" t="n">
         <v>7046476</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6524830</v>
+        <v>6524831</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>139196</v>
+        <v>139195</v>
       </c>
       <c r="O22" t="n">
         <v>3170800</v>
       </c>
       <c r="P22" t="n">
-        <v>3736879</v>
+        <v>3736880</v>
       </c>
       <c r="Q22" t="n">
         <v>4088163</v>
@@ -2108,7 +2108,7 @@
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-83500</v>
+        <v>-83501</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>446941</v>
+        <v>446942</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>375706</v>
+        <v>375707</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>276977</v>
+        <v>276978</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>178383</v>
+        <v>178384</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>276003</v>
+        <v>276004</v>
       </c>
       <c r="D11" t="n">
         <v>-18470</v>
       </c>
       <c r="E11" t="n">
-        <v>216339</v>
+        <v>216340</v>
       </c>
     </row>
     <row r="12">
@@ -2210,7 +2210,7 @@
         <v>534350</v>
       </c>
       <c r="D13" t="n">
-        <v>871890</v>
+        <v>871891</v>
       </c>
       <c r="E13" t="n">
         <v>1354955</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31533</v>
+        <v>31534</v>
       </c>
       <c r="D14" t="n">
         <v>138379</v>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19299</v>
+        <v>19300</v>
       </c>
       <c r="D16" t="n">
         <v>386152</v>
       </c>
       <c r="E16" t="n">
-        <v>97212</v>
+        <v>97213</v>
       </c>
     </row>
     <row r="17">
@@ -2357,10 +2357,10 @@
         <v>42482</v>
       </c>
       <c r="D20" t="n">
-        <v>255010</v>
+        <v>255011</v>
       </c>
       <c r="E20" t="n">
-        <v>103721</v>
+        <v>103722</v>
       </c>
     </row>
     <row r="21">
@@ -2378,10 +2378,10 @@
         <v>226389</v>
       </c>
       <c r="D21" t="n">
-        <v>602854</v>
+        <v>602855</v>
       </c>
       <c r="E21" t="n">
-        <v>501097</v>
+        <v>501098</v>
       </c>
     </row>
     <row r="22">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36196</v>
+        <v>36197</v>
       </c>
       <c r="D23" t="n">
         <v>286735</v>
       </c>
       <c r="E23" t="n">
-        <v>41577</v>
+        <v>41578</v>
       </c>
     </row>
     <row r="24">
@@ -2462,7 +2462,7 @@
         <v>3170800</v>
       </c>
       <c r="D25" t="n">
-        <v>3736879</v>
+        <v>3736880</v>
       </c>
       <c r="E25" t="n">
         <v>4088163</v>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -639,25 +639,25 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>493912</v>
+        <v>494663</v>
       </c>
       <c r="E4" t="n">
         <v>137974</v>
       </c>
       <c r="F4" t="n">
-        <v>355938</v>
+        <v>356689</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+20.1%</t>
+          <t>+20.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>+23.8%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -810,13 +810,13 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360311</v>
+        <v>360320</v>
       </c>
       <c r="E7" t="n">
         <v>81615</v>
       </c>
       <c r="F7" t="n">
-        <v>278696</v>
+        <v>278705</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355004</v>
+        <v>355042</v>
       </c>
       <c r="E8" t="n">
         <v>97470</v>
       </c>
       <c r="F8" t="n">
-        <v>257534</v>
+        <v>257572</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+19.8%</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -924,25 +924,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>864067</v>
+        <v>838247</v>
       </c>
       <c r="E9" t="n">
         <v>286700</v>
       </c>
       <c r="F9" t="n">
-        <v>577367</v>
+        <v>551547</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+28.9%</t>
+          <t>+25.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,13 +981,13 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429049</v>
+        <v>1429077</v>
       </c>
       <c r="E10" t="n">
         <v>22808</v>
       </c>
       <c r="F10" t="n">
-        <v>1406241</v>
+        <v>1406269</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1018,13 +1018,13 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>534350</v>
+        <v>534378</v>
       </c>
       <c r="P10" t="n">
         <v>871891</v>
       </c>
       <c r="Q10" t="n">
-        <v>1354955</v>
+        <v>1354983</v>
       </c>
     </row>
     <row r="11">
@@ -1105,13 +1105,13 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375497</v>
+        <v>375545</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>345421</v>
+        <v>345469</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1142,13 +1142,13 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="P12" t="n">
         <v>276354</v>
       </c>
       <c r="Q12" t="n">
-        <v>41821</v>
+        <v>41869</v>
       </c>
     </row>
     <row r="13">
@@ -1166,13 +1166,13 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>481680</v>
+        <v>482017</v>
       </c>
       <c r="E13" t="n">
         <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>436667</v>
+        <v>437004</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>+26.9%</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1198,20 +1198,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+44.0%</t>
+          <t>+44.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>19300</v>
+        <v>19637</v>
       </c>
       <c r="P13" t="n">
         <v>386152</v>
       </c>
       <c r="Q13" t="n">
-        <v>97213</v>
+        <v>97550</v>
       </c>
     </row>
     <row r="14">
@@ -1229,13 +1229,13 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250416</v>
+        <v>250435</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>235550</v>
+        <v>235569</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1268,13 +1268,13 @@
         <v>16354</v>
       </c>
       <c r="O14" t="n">
-        <v>31326</v>
+        <v>31345</v>
       </c>
       <c r="P14" t="n">
         <v>187870</v>
       </c>
       <c r="Q14" t="n">
-        <v>72400</v>
+        <v>72419</v>
       </c>
     </row>
     <row r="15">
@@ -1292,23 +1292,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>111208</v>
+        <v>121227</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>95351</v>
+        <v>105370</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1324,18 +1324,18 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7632</v>
+        <v>7651</v>
       </c>
       <c r="P15" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="Q15" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="16">
@@ -1353,13 +1353,13 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265290</v>
+        <v>265309</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>246892</v>
+        <v>246911</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1390,13 +1390,13 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>32719</v>
+        <v>32738</v>
       </c>
       <c r="P16" t="n">
         <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="17">
@@ -1414,13 +1414,13 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454756</v>
+        <v>454785</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>366322</v>
+        <v>366351</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1453,13 +1453,13 @@
         <v>69030</v>
       </c>
       <c r="O17" t="n">
-        <v>42482</v>
+        <v>42511</v>
       </c>
       <c r="P17" t="n">
         <v>255011</v>
       </c>
       <c r="Q17" t="n">
-        <v>103722</v>
+        <v>103751</v>
       </c>
     </row>
     <row r="18">
@@ -1540,13 +1540,13 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321930</v>
+        <v>321964</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>321584</v>
+        <v>321618</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+272.1%</t>
+          <t>+272.2%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>21537</v>
       </c>
       <c r="O19" t="n">
-        <v>41965</v>
+        <v>41999</v>
       </c>
       <c r="P19" t="n">
         <v>258282</v>
       </c>
       <c r="Q19" t="n">
-        <v>92122</v>
+        <v>92156</v>
       </c>
     </row>
     <row r="20">
@@ -1603,23 +1603,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>372222</v>
+        <v>365698</v>
       </c>
       <c r="E20" t="n">
         <v>49290</v>
       </c>
       <c r="F20" t="n">
-        <v>322932</v>
+        <v>316408</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1635,18 +1635,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+10.0%</t>
+          <t>+7.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>36197</v>
+        <v>29673</v>
       </c>
       <c r="P20" t="n">
         <v>286735</v>
       </c>
       <c r="Q20" t="n">
-        <v>41578</v>
+        <v>35054</v>
       </c>
     </row>
     <row r="21">
@@ -1709,25 +1709,25 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>8495030</v>
+        <v>8474017</v>
       </c>
       <c r="E22" t="n">
         <v>1448554</v>
       </c>
       <c r="F22" t="n">
-        <v>7046476</v>
+        <v>7025463</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+30.2%</t>
+          <t>+29.9%</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+34.6%</t>
+          <t>+34.2%</t>
         </is>
       </c>
       <c r="N22" t="n">
         <v>139195</v>
       </c>
       <c r="O22" t="n">
-        <v>3170800</v>
+        <v>3167587</v>
       </c>
       <c r="P22" t="n">
-        <v>3736880</v>
+        <v>3719080</v>
       </c>
       <c r="Q22" t="n">
-        <v>4088163</v>
+        <v>4057150</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1681100</v>
+        <v>1681898</v>
       </c>
       <c r="D2" t="n">
         <v>14021</v>
       </c>
       <c r="E2" t="n">
-        <v>1354518</v>
+        <v>1355316</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>433129</v>
+        <v>435109</v>
       </c>
       <c r="D3" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="E3" t="n">
-        <v>268317</v>
+        <v>242497</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1072961</v>
+        <v>1066970</v>
       </c>
       <c r="D4" t="n">
-        <v>3565420</v>
+        <v>3575420</v>
       </c>
       <c r="E4" t="n">
-        <v>2466097</v>
+        <v>2460106</v>
       </c>
     </row>
     <row r="5">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>346913</v>
+        <v>347664</v>
       </c>
       <c r="D7" t="n">
         <v>9025</v>
       </c>
       <c r="E7" t="n">
-        <v>338152</v>
+        <v>338903</v>
       </c>
     </row>
     <row r="8">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>276978</v>
+        <v>276987</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>178384</v>
+        <v>178393</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>276004</v>
+        <v>276042</v>
       </c>
       <c r="D11" t="n">
         <v>-18470</v>
       </c>
       <c r="E11" t="n">
-        <v>216340</v>
+        <v>216378</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>433129</v>
+        <v>435109</v>
       </c>
       <c r="D12" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="E12" t="n">
-        <v>268317</v>
+        <v>242497</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>534350</v>
+        <v>534378</v>
       </c>
       <c r="D13" t="n">
         <v>871891</v>
       </c>
       <c r="E13" t="n">
-        <v>1354955</v>
+        <v>1354983</v>
       </c>
     </row>
     <row r="14">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="D15" t="n">
         <v>276354</v>
       </c>
       <c r="E15" t="n">
-        <v>41821</v>
+        <v>41869</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19300</v>
+        <v>19637</v>
       </c>
       <c r="D16" t="n">
         <v>386152</v>
       </c>
       <c r="E16" t="n">
-        <v>97213</v>
+        <v>97550</v>
       </c>
     </row>
     <row r="17">
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31326</v>
+        <v>31345</v>
       </c>
       <c r="D17" t="n">
         <v>187870</v>
       </c>
       <c r="E17" t="n">
-        <v>72400</v>
+        <v>72419</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7632</v>
+        <v>7651</v>
       </c>
       <c r="D18" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="E18" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="19">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32719</v>
+        <v>32738</v>
       </c>
       <c r="D19" t="n">
         <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="20">
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42482</v>
+        <v>42511</v>
       </c>
       <c r="D20" t="n">
         <v>255011</v>
       </c>
       <c r="E20" t="n">
-        <v>103722</v>
+        <v>103751</v>
       </c>
     </row>
     <row r="21">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41965</v>
+        <v>41999</v>
       </c>
       <c r="D22" t="n">
         <v>258282</v>
       </c>
       <c r="E22" t="n">
-        <v>92122</v>
+        <v>92156</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36197</v>
+        <v>29673</v>
       </c>
       <c r="D23" t="n">
         <v>286735</v>
       </c>
       <c r="E23" t="n">
-        <v>41578</v>
+        <v>35054</v>
       </c>
     </row>
     <row r="24">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3170800</v>
+        <v>3167587</v>
       </c>
       <c r="D25" t="n">
-        <v>3736880</v>
+        <v>3719080</v>
       </c>
       <c r="E25" t="n">
-        <v>4088163</v>
+        <v>4057150</v>
       </c>
     </row>
   </sheetData>
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>158138</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>197.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>155.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>124338</v>
       </c>
     </row>
     <row r="14">
@@ -3431,19 +3431,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>59560</v>
+        <v>31760</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3451,11 +3451,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>52960</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="24">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>74964</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>65164</v>
       </c>
     </row>
     <row r="26">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52570</v>
+        <v>62570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36770</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -639,25 +639,25 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>494663</v>
+        <v>493912</v>
       </c>
       <c r="E4" t="n">
         <v>137974</v>
       </c>
       <c r="F4" t="n">
-        <v>356689</v>
+        <v>355938</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+20.3%</t>
+          <t>+20.1%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+23.8%</t>
+          <t>+23.6%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -810,13 +810,13 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360320</v>
+        <v>360311</v>
       </c>
       <c r="E7" t="n">
         <v>81615</v>
       </c>
       <c r="F7" t="n">
-        <v>278705</v>
+        <v>278696</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -867,13 +867,13 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355042</v>
+        <v>355004</v>
       </c>
       <c r="E8" t="n">
         <v>97470</v>
       </c>
       <c r="F8" t="n">
-        <v>257572</v>
+        <v>257534</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+19.8%</t>
+          <t>+19.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -924,25 +924,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>838247</v>
+        <v>864067</v>
       </c>
       <c r="E9" t="n">
         <v>286700</v>
       </c>
       <c r="F9" t="n">
-        <v>551547</v>
+        <v>577367</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+25.0%</t>
+          <t>+28.9%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+13.1%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,13 +981,13 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429077</v>
+        <v>1429049</v>
       </c>
       <c r="E10" t="n">
         <v>22808</v>
       </c>
       <c r="F10" t="n">
-        <v>1406269</v>
+        <v>1406241</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1018,13 +1018,13 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>534378</v>
+        <v>534350</v>
       </c>
       <c r="P10" t="n">
         <v>871891</v>
       </c>
       <c r="Q10" t="n">
-        <v>1354983</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="11">
@@ -1105,13 +1105,13 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375545</v>
+        <v>375497</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>345469</v>
+        <v>345421</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
@@ -1142,13 +1142,13 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69115</v>
+        <v>69067</v>
       </c>
       <c r="P12" t="n">
         <v>276354</v>
       </c>
       <c r="Q12" t="n">
-        <v>41869</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="13">
@@ -1166,13 +1166,13 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>482017</v>
+        <v>481680</v>
       </c>
       <c r="E13" t="n">
         <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>437004</v>
+        <v>436667</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+26.9%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -1198,20 +1198,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+44.1%</t>
+          <t>+44.0%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>19637</v>
+        <v>19300</v>
       </c>
       <c r="P13" t="n">
         <v>386152</v>
       </c>
       <c r="Q13" t="n">
-        <v>97550</v>
+        <v>97213</v>
       </c>
     </row>
     <row r="14">
@@ -1229,13 +1229,13 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250435</v>
+        <v>250416</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>235569</v>
+        <v>235550</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
@@ -1268,13 +1268,13 @@
         <v>16354</v>
       </c>
       <c r="O14" t="n">
-        <v>31345</v>
+        <v>31326</v>
       </c>
       <c r="P14" t="n">
         <v>187870</v>
       </c>
       <c r="Q14" t="n">
-        <v>72419</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="15">
@@ -1292,23 +1292,23 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>121227</v>
+        <v>111208</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>105370</v>
+        <v>95351</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -1324,18 +1324,18 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7651</v>
+        <v>7632</v>
       </c>
       <c r="P15" t="n">
-        <v>97719</v>
+        <v>87719</v>
       </c>
       <c r="Q15" t="n">
-        <v>37996</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="16">
@@ -1353,13 +1353,13 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265309</v>
+        <v>265290</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>246911</v>
+        <v>246892</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
@@ -1390,13 +1390,13 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>32738</v>
+        <v>32719</v>
       </c>
       <c r="P16" t="n">
         <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>44261</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="17">
@@ -1414,13 +1414,13 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454785</v>
+        <v>454756</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>366351</v>
+        <v>366322</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
@@ -1453,13 +1453,13 @@
         <v>69030</v>
       </c>
       <c r="O17" t="n">
-        <v>42511</v>
+        <v>42482</v>
       </c>
       <c r="P17" t="n">
         <v>255011</v>
       </c>
       <c r="Q17" t="n">
-        <v>103751</v>
+        <v>103722</v>
       </c>
     </row>
     <row r="18">
@@ -1540,13 +1540,13 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321964</v>
+        <v>321930</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>321618</v>
+        <v>321584</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -1572,20 +1572,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+272.2%</t>
+          <t>+272.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>21537</v>
       </c>
       <c r="O19" t="n">
-        <v>41999</v>
+        <v>41965</v>
       </c>
       <c r="P19" t="n">
         <v>258282</v>
       </c>
       <c r="Q19" t="n">
-        <v>92156</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="20">
@@ -1603,23 +1603,23 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>365698</v>
+        <v>372222</v>
       </c>
       <c r="E20" t="n">
         <v>49290</v>
       </c>
       <c r="F20" t="n">
-        <v>316408</v>
+        <v>322932</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1635,18 +1635,18 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+7.8%</t>
+          <t>+10.0%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>29673</v>
+        <v>36197</v>
       </c>
       <c r="P20" t="n">
         <v>286735</v>
       </c>
       <c r="Q20" t="n">
-        <v>35054</v>
+        <v>41578</v>
       </c>
     </row>
     <row r="21">
@@ -1709,25 +1709,25 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>8474017</v>
+        <v>8495030</v>
       </c>
       <c r="E22" t="n">
         <v>1448554</v>
       </c>
       <c r="F22" t="n">
-        <v>7025463</v>
+        <v>7046476</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+29.9%</t>
+          <t>+30.2%</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1743,20 +1743,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+34.2%</t>
+          <t>+34.6%</t>
         </is>
       </c>
       <c r="N22" t="n">
         <v>139195</v>
       </c>
       <c r="O22" t="n">
-        <v>3167587</v>
+        <v>3170800</v>
       </c>
       <c r="P22" t="n">
-        <v>3719080</v>
+        <v>3736880</v>
       </c>
       <c r="Q22" t="n">
-        <v>4057150</v>
+        <v>4088163</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1681898</v>
+        <v>1681100</v>
       </c>
       <c r="D2" t="n">
         <v>14021</v>
       </c>
       <c r="E2" t="n">
-        <v>1355316</v>
+        <v>1354518</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>435109</v>
+        <v>433129</v>
       </c>
       <c r="D3" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="E3" t="n">
-        <v>242497</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1066970</v>
+        <v>1072961</v>
       </c>
       <c r="D4" t="n">
-        <v>3575420</v>
+        <v>3565420</v>
       </c>
       <c r="E4" t="n">
-        <v>2460106</v>
+        <v>2466097</v>
       </c>
     </row>
     <row r="5">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>347664</v>
+        <v>346913</v>
       </c>
       <c r="D7" t="n">
         <v>9025</v>
       </c>
       <c r="E7" t="n">
-        <v>338903</v>
+        <v>338152</v>
       </c>
     </row>
     <row r="8">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>276987</v>
+        <v>276978</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>178393</v>
+        <v>178384</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>276042</v>
+        <v>276004</v>
       </c>
       <c r="D11" t="n">
         <v>-18470</v>
       </c>
       <c r="E11" t="n">
-        <v>216378</v>
+        <v>216340</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>435109</v>
+        <v>433129</v>
       </c>
       <c r="D12" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="E12" t="n">
-        <v>242497</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>534378</v>
+        <v>534350</v>
       </c>
       <c r="D13" t="n">
         <v>871891</v>
       </c>
       <c r="E13" t="n">
-        <v>1354983</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="14">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69115</v>
+        <v>69067</v>
       </c>
       <c r="D15" t="n">
         <v>276354</v>
       </c>
       <c r="E15" t="n">
-        <v>41869</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19637</v>
+        <v>19300</v>
       </c>
       <c r="D16" t="n">
         <v>386152</v>
       </c>
       <c r="E16" t="n">
-        <v>97550</v>
+        <v>97213</v>
       </c>
     </row>
     <row r="17">
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31345</v>
+        <v>31326</v>
       </c>
       <c r="D17" t="n">
         <v>187870</v>
       </c>
       <c r="E17" t="n">
-        <v>72419</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7651</v>
+        <v>7632</v>
       </c>
       <c r="D18" t="n">
-        <v>97719</v>
+        <v>87719</v>
       </c>
       <c r="E18" t="n">
-        <v>37996</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="19">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32738</v>
+        <v>32719</v>
       </c>
       <c r="D19" t="n">
         <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>44261</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="20">
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42511</v>
+        <v>42482</v>
       </c>
       <c r="D20" t="n">
         <v>255011</v>
       </c>
       <c r="E20" t="n">
-        <v>103751</v>
+        <v>103722</v>
       </c>
     </row>
     <row r="21">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41999</v>
+        <v>41965</v>
       </c>
       <c r="D22" t="n">
         <v>258282</v>
       </c>
       <c r="E22" t="n">
-        <v>92156</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>29673</v>
+        <v>36197</v>
       </c>
       <c r="D23" t="n">
         <v>286735</v>
       </c>
       <c r="E23" t="n">
-        <v>35054</v>
+        <v>41578</v>
       </c>
     </row>
     <row r="24">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3167587</v>
+        <v>3170800</v>
       </c>
       <c r="D25" t="n">
-        <v>3719080</v>
+        <v>3736880</v>
       </c>
       <c r="E25" t="n">
-        <v>4057150</v>
+        <v>4088163</v>
       </c>
     </row>
   </sheetData>
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>158138</v>
+        <v>156158</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>197.7%</t>
+          <t>195.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>155.4%</t>
+          <t>152.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>124338</v>
+        <v>122358</v>
       </c>
     </row>
     <row r="14">
@@ -3431,19 +3431,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>31760</v>
+        <v>59560</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3451,11 +3451,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25160</v>
+        <v>52960</v>
       </c>
     </row>
     <row r="24">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>74964</v>
+        <v>81564</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65164</v>
+        <v>71764</v>
       </c>
     </row>
     <row r="26">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>62570</v>
+        <v>52570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>46770</v>
+        <v>36770</v>
       </c>
     </row>
     <row r="63">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>470209</v>
+        <v>536976</v>
       </c>
       <c r="E2" t="n">
-        <v>136120</v>
+        <v>136571</v>
       </c>
       <c r="F2" t="n">
-        <v>334089</v>
+        <v>400405</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>299086</v>
+        <v>312462</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+57.2%</t>
+          <t>+71.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>143627</v>
+        <v>127165</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+132.6%</t>
+          <t>+214.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1318</v>
+        <v>2019</v>
       </c>
       <c r="E3" t="n">
         <v>14980</v>
       </c>
       <c r="F3" t="n">
-        <v>-13662</v>
+        <v>-12961</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16390</v>
+        <v>16437</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-92.0%</t>
+          <t>-87.7%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-14031</v>
+        <v>-14003</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>493912</v>
+        <v>592959</v>
       </c>
       <c r="E4" t="n">
-        <v>137974</v>
+        <v>142095</v>
       </c>
       <c r="F4" t="n">
-        <v>355938</v>
+        <v>450864</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>411191</v>
+        <v>438279</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+20.1%</t>
+          <t>+35.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>288019</v>
+        <v>314294</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+23.6%</t>
+          <t>+43.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>226501</v>
+        <v>230387</v>
       </c>
       <c r="E5" t="n">
-        <v>197842</v>
+        <v>239928</v>
       </c>
       <c r="F5" t="n">
-        <v>28659</v>
+        <v>-9541</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>399845</v>
+        <v>410348</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>-43.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>293669</v>
+        <v>304172</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-90.2%</t>
+          <t>-103.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>511626</v>
+        <v>550501</v>
       </c>
       <c r="E6" t="n">
-        <v>57759</v>
+        <v>66617</v>
       </c>
       <c r="F6" t="n">
-        <v>453868</v>
+        <v>483885</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>257411</v>
+        <v>274769</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+98.8%</t>
+          <t>+100.4%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>193212</v>
+        <v>209849</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+134.9%</t>
+          <t>+130.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360311</v>
+        <v>384192</v>
       </c>
       <c r="E7" t="n">
-        <v>81615</v>
+        <v>87008</v>
       </c>
       <c r="F7" t="n">
-        <v>278696</v>
+        <v>297184</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>258264</v>
+        <v>282047</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+39.5%</t>
+          <t>+36.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>196014</v>
+        <v>219402</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+42.2%</t>
+          <t>+35.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355004</v>
+        <v>414738</v>
       </c>
       <c r="E8" t="n">
-        <v>97470</v>
+        <v>101687</v>
       </c>
       <c r="F8" t="n">
-        <v>257534</v>
+        <v>313051</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>296471</v>
+        <v>308441</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+19.7%</t>
+          <t>+34.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>262997</v>
+        <v>243215</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+28.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>864067</v>
+        <v>863847</v>
       </c>
       <c r="E9" t="n">
-        <v>286700</v>
+        <v>295700</v>
       </c>
       <c r="F9" t="n">
-        <v>577367</v>
+        <v>568147</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>670556</v>
+        <v>707036</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+28.9%</t>
+          <t>+22.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>510432</v>
+        <v>536912</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+13.1%</t>
+          <t>+5.8%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429049</v>
+        <v>1503178</v>
       </c>
       <c r="E10" t="n">
-        <v>22808</v>
+        <v>29808</v>
       </c>
       <c r="F10" t="n">
-        <v>1406241</v>
+        <v>1473370</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1120688</v>
+        <v>1157254</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+27.5%</t>
+          <t>+29.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1120688</v>
+        <v>1157254</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+25.5%</t>
+          <t>+27.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>534350</v>
+        <v>554088</v>
       </c>
       <c r="P10" t="n">
-        <v>871891</v>
+        <v>919282</v>
       </c>
       <c r="Q10" t="n">
-        <v>1354955</v>
+        <v>1429084</v>
       </c>
     </row>
     <row r="11">
@@ -1042,52 +1042,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>206523</v>
+        <v>229338</v>
       </c>
       <c r="E11" t="n">
         <v>36400</v>
       </c>
       <c r="F11" t="n">
-        <v>170123</v>
+        <v>192938</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>247517</v>
+        <v>248536</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>222409</v>
+        <v>223428</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>210</v>
       </c>
       <c r="O11" t="n">
-        <v>31534</v>
+        <v>44747</v>
       </c>
       <c r="P11" t="n">
-        <v>138379</v>
+        <v>147981</v>
       </c>
       <c r="Q11" t="n">
-        <v>78969</v>
+        <v>78988</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375497</v>
+        <v>375246</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>345421</v>
+        <v>345170</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>237094</v>
+        <v>237890</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+58.4%</t>
+          <t>+57.7%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>235096</v>
+        <v>235892</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+46.9%</t>
+          <t>+46.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="P12" t="n">
-        <v>276354</v>
+        <v>276055</v>
       </c>
       <c r="Q12" t="n">
-        <v>41821</v>
+        <v>41570</v>
       </c>
     </row>
     <row r="13">
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>481680</v>
+        <v>490573</v>
       </c>
       <c r="E13" t="n">
         <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>436667</v>
+        <v>445560</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>379796</v>
+        <v>441162</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>+11.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>303287</v>
+        <v>364653</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+44.0%</t>
+          <t>+22.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>19300</v>
+        <v>20454</v>
       </c>
       <c r="P13" t="n">
-        <v>386152</v>
+        <v>393891</v>
       </c>
       <c r="Q13" t="n">
-        <v>97213</v>
+        <v>105310</v>
       </c>
     </row>
     <row r="14">
@@ -1229,46 +1229,46 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250416</v>
+        <v>260814</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>235550</v>
+        <v>245948</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>217019</v>
+        <v>278542</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>+15.4%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>195641</v>
+        <v>257164</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>16354</v>
       </c>
       <c r="O14" t="n">
-        <v>31326</v>
+        <v>41724</v>
       </c>
       <c r="P14" t="n">
         <v>187870</v>
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>111208</v>
+        <v>121625</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>95351</v>
+        <v>105768</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>164471</v>
+        <v>164869</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>149165</v>
+        <v>149563</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>7632</v>
+        <v>8049</v>
       </c>
       <c r="P15" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="Q15" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="16">
@@ -1353,50 +1353,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265290</v>
+        <v>273707</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>246892</v>
+        <v>255309</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>221834</v>
+        <v>235032</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+19.6%</t>
+          <t>+16.5%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>178834</v>
+        <v>192032</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+38.1%</t>
+          <t>+33.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>32719</v>
+        <v>41136</v>
       </c>
       <c r="P16" t="n">
         <v>214173</v>
       </c>
       <c r="Q16" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="17">
@@ -1414,52 +1414,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454756</v>
+        <v>501583</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>366322</v>
+        <v>413149</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>296048</v>
+        <v>325646</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+53.6%</t>
+          <t>+54.0%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>250182</v>
+        <v>273280</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+46.4%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>69030</v>
       </c>
       <c r="O17" t="n">
-        <v>42482</v>
+        <v>42911</v>
       </c>
       <c r="P17" t="n">
-        <v>255011</v>
+        <v>301409</v>
       </c>
       <c r="Q17" t="n">
-        <v>103722</v>
+        <v>104151</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>928589</v>
+        <v>925449</v>
       </c>
       <c r="E18" t="n">
-        <v>98495</v>
+        <v>99495</v>
       </c>
       <c r="F18" t="n">
-        <v>830094</v>
+        <v>825954</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>441190</v>
+        <v>477388</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+110.5%</t>
+          <t>+93.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>325648</v>
+        <v>349401</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+154.9%</t>
+          <t>+136.4%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>226389</v>
+        <v>226862</v>
       </c>
       <c r="P18" t="n">
-        <v>602855</v>
+        <v>598242</v>
       </c>
       <c r="Q18" t="n">
-        <v>501098</v>
+        <v>497162</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321930</v>
+        <v>325449</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>321584</v>
+        <v>325103</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>232444</v>
+        <v>245042</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+38.5%</t>
+          <t>+32.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>86417</v>
+        <v>99015</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+272.1%</t>
+          <t>+228.3%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>21537</v>
+        <v>24605</v>
       </c>
       <c r="O19" t="n">
-        <v>41965</v>
+        <v>42018</v>
       </c>
       <c r="P19" t="n">
-        <v>258282</v>
+        <v>258680</v>
       </c>
       <c r="Q19" t="n">
-        <v>92122</v>
+        <v>95243</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>372222</v>
+        <v>366770</v>
       </c>
       <c r="E20" t="n">
-        <v>49290</v>
+        <v>54328</v>
       </c>
       <c r="F20" t="n">
-        <v>322932</v>
+        <v>312442</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>357517</v>
+        <v>382115</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>293517</v>
+        <v>318115</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+10.0%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>36197</v>
+        <v>81129</v>
       </c>
       <c r="P20" t="n">
-        <v>286735</v>
+        <v>231313</v>
       </c>
       <c r="Q20" t="n">
-        <v>41578</v>
+        <v>35092</v>
       </c>
     </row>
     <row r="21">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>8495030</v>
+        <v>8964272</v>
       </c>
       <c r="E22" t="n">
-        <v>1448554</v>
+        <v>1535718</v>
       </c>
       <c r="F22" t="n">
-        <v>7046476</v>
+        <v>7428554</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>6524831</v>
+        <v>6943294</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+30.2%</t>
+          <t>+29.1%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5234821</v>
+        <v>5560802</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+34.6%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>139195</v>
+        <v>142263</v>
       </c>
       <c r="O22" t="n">
-        <v>3170800</v>
+        <v>3494819</v>
       </c>
       <c r="P22" t="n">
-        <v>3736880</v>
+        <v>3791872</v>
       </c>
       <c r="Q22" t="n">
-        <v>4088163</v>
+        <v>4397470</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>503</v>
+        <v>374</v>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="n">
-        <v>1129.1</v>
+        <v>1270.3</v>
       </c>
       <c r="E2" t="n">
-        <v>129848</v>
+        <v>178384</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>1082.8</v>
+        <v>1274.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1444</v>
+        <v>60542</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>870</v>
+        <v>797</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D4" t="n">
-        <v>1572.6</v>
+        <v>1546.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2434</v>
+        <v>2841</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1681100</v>
+        <v>1908467</v>
       </c>
       <c r="D2" t="n">
-        <v>14021</v>
+        <v>14419</v>
       </c>
       <c r="E2" t="n">
-        <v>1354518</v>
+        <v>1564885</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>433129</v>
+        <v>430509</v>
       </c>
       <c r="D3" t="n">
-        <v>144238</v>
+        <v>137638</v>
       </c>
       <c r="E3" t="n">
-        <v>268317</v>
+        <v>292097</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1072961</v>
+        <v>1172233</v>
       </c>
       <c r="D4" t="n">
-        <v>3565420</v>
+        <v>3626614</v>
       </c>
       <c r="E4" t="n">
-        <v>2466097</v>
+        <v>2541256</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>324455</v>
+        <v>390771</v>
       </c>
       <c r="D5" t="n">
         <v>9634</v>
       </c>
       <c r="E5" t="n">
-        <v>333099</v>
+        <v>399415</v>
       </c>
     </row>
     <row r="6">
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-13662</v>
+        <v>-13096</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-3662</v>
+        <v>-2961</v>
       </c>
     </row>
     <row r="7">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>346913</v>
+        <v>441641</v>
       </c>
       <c r="D7" t="n">
-        <v>9025</v>
+        <v>9223</v>
       </c>
       <c r="E7" t="n">
-        <v>338152</v>
+        <v>432680</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23471</v>
+        <v>-14729</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-83501</v>
+        <v>-121701</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>446942</v>
+        <v>476959</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>375707</v>
+        <v>405724</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>276978</v>
+        <v>295466</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>178384</v>
+        <v>179872</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>276004</v>
+        <v>331456</v>
       </c>
       <c r="D11" t="n">
-        <v>-18470</v>
+        <v>-18405</v>
       </c>
       <c r="E11" t="n">
-        <v>216340</v>
+        <v>271857</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>433129</v>
+        <v>430509</v>
       </c>
       <c r="D12" t="n">
-        <v>144238</v>
+        <v>137638</v>
       </c>
       <c r="E12" t="n">
-        <v>268317</v>
+        <v>292097</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>534350</v>
+        <v>554088</v>
       </c>
       <c r="D13" t="n">
-        <v>871891</v>
+        <v>919282</v>
       </c>
       <c r="E13" t="n">
-        <v>1354955</v>
+        <v>1429084</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>31534</v>
+        <v>44747</v>
       </c>
       <c r="D14" t="n">
-        <v>138379</v>
+        <v>147981</v>
       </c>
       <c r="E14" t="n">
-        <v>78969</v>
+        <v>78988</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="D15" t="n">
-        <v>276354</v>
+        <v>276055</v>
       </c>
       <c r="E15" t="n">
-        <v>41821</v>
+        <v>41570</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19300</v>
+        <v>20454</v>
       </c>
       <c r="D16" t="n">
-        <v>386152</v>
+        <v>393891</v>
       </c>
       <c r="E16" t="n">
-        <v>97213</v>
+        <v>105310</v>
       </c>
     </row>
     <row r="17">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>31326</v>
+        <v>41724</v>
       </c>
       <c r="D17" t="n">
         <v>187870</v>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7632</v>
+        <v>8049</v>
       </c>
       <c r="D18" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="E18" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="19">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>32719</v>
+        <v>41136</v>
       </c>
       <c r="D19" t="n">
         <v>214173</v>
       </c>
       <c r="E19" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="20">
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42482</v>
+        <v>42911</v>
       </c>
       <c r="D20" t="n">
-        <v>255011</v>
+        <v>301409</v>
       </c>
       <c r="E20" t="n">
-        <v>103722</v>
+        <v>104151</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>226389</v>
+        <v>226862</v>
       </c>
       <c r="D21" t="n">
-        <v>602855</v>
+        <v>598242</v>
       </c>
       <c r="E21" t="n">
-        <v>501098</v>
+        <v>497162</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>41965</v>
+        <v>42018</v>
       </c>
       <c r="D22" t="n">
-        <v>258282</v>
+        <v>258680</v>
       </c>
       <c r="E22" t="n">
-        <v>92122</v>
+        <v>95243</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36197</v>
+        <v>81129</v>
       </c>
       <c r="D23" t="n">
-        <v>286735</v>
+        <v>231313</v>
       </c>
       <c r="E23" t="n">
-        <v>41578</v>
+        <v>35092</v>
       </c>
     </row>
     <row r="24">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3170800</v>
+        <v>3494819</v>
       </c>
       <c r="D25" t="n">
-        <v>3736880</v>
+        <v>3791872</v>
       </c>
       <c r="E25" t="n">
-        <v>4088163</v>
+        <v>4397470</v>
       </c>
     </row>
   </sheetData>
@@ -2549,19 +2549,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>170432</v>
+        <v>225012</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2569,11 +2569,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>132305.34</v>
+        <v>186885.34</v>
       </c>
     </row>
     <row r="3">
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>89680</v>
+        <v>94660</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>83282.5</v>
+        <v>88262.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,19 +2717,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>52340</v>
+        <v>57320</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50660</v>
+        <v>55640</v>
       </c>
     </row>
     <row r="7">
@@ -2759,31 +2759,31 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>74740</v>
+        <v>109600</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14980</v>
+        <v>19130</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>59760</v>
+        <v>90470</v>
       </c>
     </row>
     <row r="8">
@@ -2801,19 +2801,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>56320</v>
+        <v>81220</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2821,11 +2821,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4987</v>
+        <v>29887</v>
       </c>
     </row>
     <row r="9">
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>156158</v>
+        <v>207738</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>195.2%</t>
+          <t>259.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>152.9%</t>
+          <t>217.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>122358</v>
+        <v>173938</v>
       </c>
     </row>
     <row r="14">
@@ -3065,19 +3065,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>69600</v>
+        <v>78600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>44820</v>
+        <v>35820</v>
       </c>
     </row>
     <row r="15">
@@ -3137,19 +3137,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>70634</v>
+        <v>77234</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3157,11 +3157,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>34234</v>
+        <v>40834</v>
       </c>
     </row>
     <row r="17">
@@ -3431,19 +3431,19 @@
         <v>80000</v>
       </c>
       <c r="D23" t="n">
-        <v>59560</v>
+        <v>31760</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3451,11 +3451,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>52960</v>
+        <v>25160</v>
       </c>
     </row>
     <row r="24">
@@ -3473,19 +3473,19 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>30600</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>30600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3515,19 +3515,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>31114</v>
+        <v>41074</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13064</v>
+        <v>23024</v>
       </c>
     </row>
     <row r="26">
@@ -3557,19 +3557,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>145576</v>
+        <v>176956</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>110.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>126830</v>
+        <v>158210</v>
       </c>
     </row>
     <row r="27">
@@ -3599,31 +3599,31 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>33580</v>
+        <v>43540</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>33580</v>
+        <v>39840</v>
       </c>
     </row>
     <row r="28">
@@ -3641,19 +3641,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>41820</v>
+        <v>56760</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3661,11 +3661,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>23220</v>
+        <v>38160</v>
       </c>
     </row>
     <row r="29">
@@ -3683,19 +3683,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>61380</v>
+        <v>71738</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>44257</v>
+        <v>54615</v>
       </c>
     </row>
     <row r="30">
@@ -3725,19 +3725,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>72700</v>
+        <v>87640</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>55720</v>
+        <v>70660</v>
       </c>
     </row>
     <row r="31">
@@ -3767,31 +3767,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>189994</v>
+        <v>208594</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>130.4%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>46880</v>
+        <v>51860</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>143114</v>
+        <v>156734</v>
       </c>
     </row>
     <row r="32">
@@ -3821,19 +3821,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3980</v>
+        <v>7960</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>101598</v>
+        <v>97618</v>
       </c>
     </row>
     <row r="33">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>77740</v>
+        <v>82740</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>52960</v>
+        <v>57960</v>
       </c>
     </row>
     <row r="34">
@@ -3893,31 +3893,31 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>77979</v>
+        <v>87939</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3600</v>
+        <v>7500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>74379</v>
+        <v>80439</v>
       </c>
     </row>
     <row r="35">
@@ -3977,19 +3977,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>87218</v>
+        <v>105958</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>79258</v>
+        <v>97998</v>
       </c>
     </row>
     <row r="37">
@@ -4019,19 +4019,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>87996</v>
+        <v>92976</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4039,11 +4039,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>80036</v>
+        <v>85016</v>
       </c>
     </row>
     <row r="38">
@@ -4103,31 +4103,31 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>88128</v>
+        <v>91928</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>16896</v>
+        <v>54073</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>71232</v>
+        <v>37855</v>
       </c>
     </row>
     <row r="40">
@@ -4285,11 +4285,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>229374.6</v>
+        <v>230370.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>189507.93</v>
+        <v>190503.93</v>
       </c>
     </row>
     <row r="3">
@@ -4455,11 +4455,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>12194</v>
+        <v>18794</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>12194</v>
+        <v>18794</v>
       </c>
     </row>
     <row r="8">
@@ -4557,11 +4557,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>84275.32000000001</v>
+        <v>87740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>84275.32000000001</v>
+        <v>87740.48</v>
       </c>
     </row>
     <row r="11">
@@ -4727,11 +4727,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>51760</v>
+        <v>60158</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>42562</v>
+        <v>50960</v>
       </c>
     </row>
     <row r="16">
@@ -4863,11 +4863,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>112391.9</v>
+        <v>122391.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>107391.9</v>
+        <v>117391.9</v>
       </c>
     </row>
     <row r="20">
@@ -4931,11 +4931,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10279.8</v>
+        <v>10677.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10279.8</v>
+        <v>10677.8</v>
       </c>
     </row>
     <row r="22">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>81564</v>
+        <v>75562</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>71764</v>
+        <v>65762</v>
       </c>
     </row>
     <row r="26">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>36150</v>
+        <v>36548</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36150</v>
+        <v>36548</v>
       </c>
     </row>
     <row r="28">
@@ -5169,11 +5169,11 @@
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>14788</v>
+        <v>15186</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5181,11 +5181,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>131.2%</t>
+          <t>127.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4611.98</v>
+        <v>-4213.98</v>
       </c>
     </row>
     <row r="29">
@@ -5203,11 +5203,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>97970</v>
+        <v>110368</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5215,11 +5215,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>90970</v>
+        <v>103368</v>
       </c>
     </row>
     <row r="30">
@@ -5237,11 +5237,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>38176</v>
+        <v>48176</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5249,11 +5249,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>28176</v>
+        <v>38176</v>
       </c>
     </row>
     <row r="31">
@@ -5373,11 +5373,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>142265.13</v>
+        <v>164265.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5385,11 +5385,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>102431.73</v>
+        <v>124431.73</v>
       </c>
     </row>
     <row r="35">
@@ -5407,11 +5407,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>79044.92</v>
+        <v>91044.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5419,11 +5419,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>72444.92</v>
+        <v>84444.92</v>
       </c>
     </row>
     <row r="36">
@@ -5441,11 +5441,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>49980</v>
+        <v>62778</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5453,11 +5453,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43780</v>
+        <v>56578</v>
       </c>
     </row>
     <row r="37">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>513482</v>
+        <v>503080</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>110.5%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>442182</v>
+        <v>431780</v>
       </c>
     </row>
     <row r="41">
@@ -5645,11 +5645,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>128566</v>
+        <v>135166</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5657,11 +5657,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>120966</v>
+        <v>127566</v>
       </c>
     </row>
     <row r="43">
@@ -5679,11 +5679,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106151</v>
+        <v>106549</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5691,11 +5691,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97151</v>
+        <v>97549</v>
       </c>
     </row>
     <row r="44">
@@ -5717,19 +5717,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>102303.64</v>
+        <v>144607.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>102303.64</v>
+        <v>144607.64</v>
       </c>
     </row>
     <row r="46">
@@ -5781,11 +5781,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>33783</v>
+        <v>43783</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>33783</v>
+        <v>43783</v>
       </c>
     </row>
     <row r="47">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>174767</v>
+        <v>187909</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>174767</v>
+        <v>187909</v>
       </c>
     </row>
     <row r="48">
@@ -5883,11 +5883,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>231661.04</v>
+        <v>241661.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>231661.04</v>
+        <v>241661.04</v>
       </c>
     </row>
     <row r="50">
@@ -5917,11 +5917,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>1996</v>
+        <v>4469</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1996</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="51">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>319909.65</v>
+        <v>320773.65</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>319909.65</v>
+        <v>320773.65</v>
       </c>
     </row>
     <row r="53">
@@ -6053,11 +6053,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>234747</v>
+        <v>235826</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>234747</v>
+        <v>235826</v>
       </c>
     </row>
     <row r="55">
@@ -6291,11 +6291,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>37368</v>
+        <v>37766</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37368</v>
+        <v>37766</v>
       </c>
     </row>
     <row r="62">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>52570</v>
+        <v>62570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36770</v>
+        <v>46770</v>
       </c>
     </row>
     <row r="63">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2064246.8</v>
+        <v>892008</v>
       </c>
       <c r="D2" t="n">
-        <v>9481</v>
+        <v>2690</v>
       </c>
       <c r="E2" t="n">
-        <v>1804310.8</v>
+        <v>765825</v>
       </c>
       <c r="F2" t="n">
-        <v>259936</v>
+        <v>126183</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1805279</v>
+        <v>819147</v>
       </c>
       <c r="D3" t="n">
-        <v>449</v>
+        <v>154</v>
       </c>
       <c r="E3" t="n">
-        <v>1560857</v>
+        <v>695370</v>
       </c>
       <c r="F3" t="n">
-        <v>244422</v>
+        <v>123777</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>258967.8</v>
+        <v>72861</v>
       </c>
       <c r="D4" t="n">
-        <v>9032</v>
+        <v>2536</v>
       </c>
       <c r="E4" t="n">
-        <v>243453.8</v>
+        <v>70455</v>
       </c>
       <c r="F4" t="n">
-        <v>15514</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3440314</v>
+        <v>1041076</v>
       </c>
       <c r="D5" t="n">
-        <v>673</v>
+        <v>240</v>
       </c>
       <c r="E5" t="n">
-        <v>792902</v>
+        <v>242360</v>
       </c>
       <c r="F5" t="n">
-        <v>2647412</v>
+        <v>798716</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2351424</v>
+        <v>726900</v>
       </c>
       <c r="D6" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="E6" t="n">
-        <v>57816</v>
+        <v>42598</v>
       </c>
       <c r="F6" t="n">
-        <v>2293608</v>
+        <v>684302</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1078890</v>
+        <v>301176</v>
       </c>
       <c r="D7" t="n">
-        <v>243</v>
+        <v>88</v>
       </c>
       <c r="E7" t="n">
-        <v>735086</v>
+        <v>199762</v>
       </c>
       <c r="F7" t="n">
-        <v>343804</v>
+        <v>101414</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1524429.76</v>
+        <v>1526886.8</v>
       </c>
       <c r="D8" t="n">
-        <v>2057</v>
+        <v>2044</v>
       </c>
       <c r="E8" t="n">
-        <v>26290.61</v>
+        <v>11310.73</v>
       </c>
       <c r="F8" t="n">
-        <v>1498139.15</v>
+        <v>1515576.07</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946762.33</v>
+        <v>942636.61</v>
       </c>
       <c r="D9" t="n">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E9" t="n">
-        <v>5628.16</v>
+        <v>2945.64</v>
       </c>
       <c r="F9" t="n">
-        <v>941134.17</v>
+        <v>939690.97</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>577667.4300000001</v>
+        <v>584250.1899999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="E10" t="n">
-        <v>20662.45</v>
+        <v>8365.09</v>
       </c>
       <c r="F10" t="n">
-        <v>557004.98</v>
+        <v>575885.1</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>590000</v>
+        <v>382800</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E11" t="n">
-        <v>218200</v>
+        <v>194400</v>
       </c>
       <c r="F11" t="n">
-        <v>371800</v>
+        <v>188400</v>
       </c>
     </row>
     <row r="12">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>358953.9</v>
+        <v>74788</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>114893.9</v>
+        <v>15200</v>
       </c>
       <c r="F12" t="n">
-        <v>244060</v>
+        <v>59588</v>
       </c>
     </row>
     <row r="13">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>326680</v>
+        <v>59340</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>296900</v>
+        <v>59340</v>
       </c>
       <c r="F13" t="n">
-        <v>29780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>7920</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>17820</v>
+        <v>1980</v>
       </c>
       <c r="F14" t="n">
-        <v>93060</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="15">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>79525.61</v>
+        <v>57187.24</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="E15" t="n">
-        <v>11631.36</v>
+        <v>8092</v>
       </c>
       <c r="F15" t="n">
-        <v>67894.25</v>
+        <v>49095.24</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2064246.8</v>
+        <v>892008</v>
       </c>
       <c r="C2" t="n">
-        <v>411574.86</v>
+        <v>434481.86</v>
       </c>
       <c r="D2" t="n">
-        <v>50157</v>
+        <v>60716</v>
       </c>
       <c r="E2" t="n">
-        <v>2.43</v>
+        <v>6.81</v>
       </c>
       <c r="F2" t="n">
-        <v>361417.86</v>
+        <v>373765.86</v>
       </c>
       <c r="G2" t="n">
-        <v>17.51</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3440314</v>
+        <v>1041076</v>
       </c>
       <c r="C3" t="n">
-        <v>472001.38</v>
+        <v>494001.38</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>472001.38</v>
+        <v>493001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>13.72</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="4">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1524429.76</v>
+        <v>1526886.8</v>
       </c>
       <c r="C4" t="n">
         <v>2849</v>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>590000</v>
+        <v>382800</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -6908,7 +6908,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>19.66</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="6">
@@ -6918,22 +6918,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>358953.9</v>
+        <v>74788</v>
       </c>
       <c r="C6" t="n">
-        <v>154862.9</v>
+        <v>196919.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="F6" t="n">
-        <v>152845</v>
+        <v>194902</v>
       </c>
       <c r="G6" t="n">
-        <v>42.58</v>
+        <v>260.61</v>
       </c>
     </row>
     <row r="7">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>326680</v>
+        <v>59340</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -6952,13 +6952,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>16.22</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>72.63</v>
+        <v>399.84</v>
       </c>
     </row>
     <row r="8">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110880</v>
+        <v>7920</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6993,16 +6993,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79525.61</v>
+        <v>57187.24</v>
       </c>
       <c r="C9" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="D9" t="n">
-        <v>999</v>
+        <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C2" t="n">
-        <v>851959.05</v>
+        <v>916933.05</v>
       </c>
       <c r="D2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>629</v>
+        <v>660</v>
       </c>
       <c r="C3" t="n">
-        <v>283147.4</v>
+        <v>296368.4</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>90200</v>
+        <v>98200</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>29026</v>
+        <v>29045</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>24121.66</v>
+        <v>24235.66</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>22442.7</v>
+        <v>22960.7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>16849</v>
+        <v>17167</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>196400</v>
+        <v>205400</v>
       </c>
     </row>
     <row r="3">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>112273</v>
+        <v>154330</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>85493</v>
+        <v>85522</v>
       </c>
     </row>
     <row r="9">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>67545</v>
+        <v>67554</v>
       </c>
     </row>
     <row r="13">
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="D13" t="n">
-        <v>34487</v>
+        <v>38300</v>
       </c>
     </row>
     <row r="14">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>5106.8</v>
+        <v>5405.8</v>
       </c>
     </row>
     <row r="17">
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D21" t="n">
-        <v>22252.5</v>
+        <v>22646.5</v>
       </c>
     </row>
     <row r="22">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>7932.66</v>
+        <v>7989.66</v>
       </c>
     </row>
     <row r="25">
@@ -7766,61 +7766,61 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="D30" t="n">
-        <v>77900</v>
+        <v>79221</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D31" t="n">
-        <v>20500</v>
+        <v>20054</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34">
@@ -7843,14 +7843,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>116</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>75004</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35">
@@ -7861,14 +7861,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>20054</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
@@ -7879,65 +7879,65 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>1757</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>418</v>
+        <v>77900</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>161</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
         <v>57</v>
@@ -7946,19 +7946,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>58100</v>
+        <v>63080</v>
       </c>
     </row>
     <row r="46">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D47" t="n">
-        <v>7486</v>
+        <v>7861</v>
       </c>
     </row>
     <row r="48">
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>413</v>
+        <v>432</v>
       </c>
     </row>
     <row r="50">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51">
@@ -8189,10 +8189,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D53" t="n">
-        <v>30204.9</v>
+        <v>34578.9</v>
       </c>
     </row>
     <row r="54">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D54" t="n">
-        <v>16508</v>
+        <v>20436</v>
       </c>
     </row>
     <row r="55">
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D55" t="n">
-        <v>9079</v>
+        <v>9117</v>
       </c>
     </row>
     <row r="56">
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56" t="n">
-        <v>1663</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="57">
@@ -8261,10 +8261,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>209</v>
+        <v>508</v>
       </c>
     </row>
     <row r="58">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -8333,10 +8333,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D61" t="n">
-        <v>39345</v>
+        <v>44345</v>
       </c>
     </row>
     <row r="62">
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
-        <v>679</v>
+        <v>698</v>
       </c>
     </row>
     <row r="64">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8599,14 +8599,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>14509</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="77">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>8000</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="78">
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>403631.38</v>
+        <v>424631.38</v>
       </c>
     </row>
     <row r="3">
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C4" t="n">
-        <v>184267.16</v>
+        <v>201077.16</v>
       </c>
     </row>
     <row r="5">
@@ -9010,10 +9010,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>146216</v>
+        <v>188273</v>
       </c>
     </row>
     <row r="6">
@@ -9049,10 +9049,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>49900</v>
+        <v>50900</v>
       </c>
     </row>
     <row r="9">
@@ -9132,62 +9132,62 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="C2" t="n">
-        <v>193875.33</v>
+        <v>211902.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
-        <v>162045.4</v>
+        <v>173752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="C4" t="n">
-        <v>146789.5</v>
+        <v>162131.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>176</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>141775.98</v>
+        <v>147008.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="C6" t="n">
-        <v>130920</v>
+        <v>146774.98</v>
       </c>
     </row>
     <row r="7">
@@ -9197,10 +9197,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>92113</v>
+        <v>92412</v>
       </c>
     </row>
     <row r="8">
@@ -9223,10 +9223,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>64885.8</v>
+        <v>64942.8</v>
       </c>
     </row>
     <row r="10">
@@ -9236,10 +9236,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>63411</v>
+        <v>63729</v>
       </c>
     </row>
     <row r="11">
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C11" t="n">
-        <v>54462</v>
+        <v>54500</v>
       </c>
     </row>
     <row r="12">
@@ -9262,10 +9262,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>49985</v>
+        <v>50004</v>
       </c>
     </row>
     <row r="13">
@@ -9284,40 +9284,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C14" t="n">
-        <v>31794</v>
+        <v>34187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>29838</v>
+        <v>31775</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>27130</v>
+        <v>29838</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>536976</v>
+        <v>541467</v>
       </c>
       <c r="E2" t="n">
-        <v>136571</v>
+        <v>150423</v>
       </c>
       <c r="F2" t="n">
-        <v>400405</v>
+        <v>391044</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>312462</v>
+        <v>338479</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+71.9%</t>
+          <t>+60.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>127165</v>
+        <v>152715</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+214.9%</t>
+          <t>+156.1%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>592959</v>
+        <v>626869</v>
       </c>
       <c r="E4" t="n">
-        <v>142095</v>
+        <v>152074</v>
       </c>
       <c r="F4" t="n">
-        <v>450864</v>
+        <v>474796</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>438279</v>
+        <v>510984</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+35.3%</t>
+          <t>+22.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>314294</v>
+        <v>386071</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+43.5%</t>
+          <t>+23.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,13 +696,13 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>230387</v>
+        <v>230425</v>
       </c>
       <c r="E5" t="n">
         <v>239928</v>
       </c>
       <c r="F5" t="n">
-        <v>-9541</v>
+        <v>-9503</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>410348</v>
+        <v>410463</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>304172</v>
+        <v>304287</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>550501</v>
+        <v>588342</v>
       </c>
       <c r="E6" t="n">
-        <v>66617</v>
+        <v>69646</v>
       </c>
       <c r="F6" t="n">
-        <v>483885</v>
+        <v>518697</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>274769</v>
+        <v>277717</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+100.4%</t>
+          <t>+111.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>209849</v>
+        <v>212501</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+130.6%</t>
+          <t>+144.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>384192</v>
+        <v>390131</v>
       </c>
       <c r="E7" t="n">
-        <v>87008</v>
+        <v>92083</v>
       </c>
       <c r="F7" t="n">
-        <v>297184</v>
+        <v>298048</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>282047</v>
+        <v>285196</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+36.2%</t>
+          <t>+36.8%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>219402</v>
+        <v>222418</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+35.5%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>414738</v>
+        <v>423881</v>
       </c>
       <c r="E8" t="n">
-        <v>101687</v>
+        <v>106828</v>
       </c>
       <c r="F8" t="n">
-        <v>313051</v>
+        <v>317053</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>308441</v>
+        <v>318508</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+34.5%</t>
+          <t>+33.1%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>243215</v>
+        <v>253158</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+28.7%</t>
+          <t>+25.2%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>863847</v>
+        <v>843372</v>
       </c>
       <c r="E9" t="n">
-        <v>295700</v>
+        <v>315500</v>
       </c>
       <c r="F9" t="n">
-        <v>568147</v>
+        <v>527872</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>707036</v>
+        <v>729456</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+22.2%</t>
+          <t>+15.6%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>536912</v>
+        <v>559332</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+5.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,13 +981,13 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1503178</v>
+        <v>1503391</v>
       </c>
       <c r="E10" t="n">
         <v>29808</v>
       </c>
       <c r="F10" t="n">
-        <v>1473370</v>
+        <v>1473583</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
@@ -1001,30 +1001,30 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1157254</v>
+        <v>1273695</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+29.9%</t>
+          <t>+18.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1157254</v>
+        <v>1273695</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+27.3%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>554088</v>
+        <v>555301</v>
       </c>
       <c r="P10" t="n">
-        <v>919282</v>
+        <v>918282</v>
       </c>
       <c r="Q10" t="n">
-        <v>1429084</v>
+        <v>1429297</v>
       </c>
     </row>
     <row r="11">
@@ -1042,52 +1042,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>229338</v>
+        <v>239150</v>
       </c>
       <c r="E11" t="n">
         <v>36400</v>
       </c>
       <c r="F11" t="n">
-        <v>192938</v>
+        <v>202750</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248536</v>
+        <v>249401</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>223428</v>
+        <v>224293</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="O11" t="n">
-        <v>44747</v>
+        <v>51745</v>
       </c>
       <c r="P11" t="n">
-        <v>147981</v>
+        <v>150781</v>
       </c>
       <c r="Q11" t="n">
-        <v>78988</v>
+        <v>87402</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375246</v>
+        <v>375683</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>345170</v>
+        <v>345607</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>237890</v>
+        <v>277909</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+57.7%</t>
+          <t>+35.2%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>235892</v>
+        <v>275911</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+46.3%</t>
+          <t>+25.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69115</v>
+        <v>69552</v>
       </c>
       <c r="P12" t="n">
         <v>276055</v>
       </c>
       <c r="Q12" t="n">
-        <v>41570</v>
+        <v>41609</v>
       </c>
     </row>
     <row r="13">
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>490573</v>
+        <v>527733</v>
       </c>
       <c r="E13" t="n">
         <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>445560</v>
+        <v>482720</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>441162</v>
+        <v>475420</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+11.2%</t>
+          <t>+11.0%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>364653</v>
+        <v>398911</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+22.2%</t>
+          <t>+21.0%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31214</v>
       </c>
       <c r="O13" t="n">
-        <v>20454</v>
+        <v>29618</v>
       </c>
       <c r="P13" t="n">
-        <v>393891</v>
+        <v>421887</v>
       </c>
       <c r="Q13" t="n">
-        <v>105310</v>
+        <v>105378</v>
       </c>
     </row>
     <row r="14">
@@ -1229,43 +1229,43 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>260814</v>
+        <v>263538</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>245948</v>
+        <v>248672</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>278542</v>
+        <v>279426</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>257164</v>
+        <v>248048</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>16354</v>
+        <v>19078</v>
       </c>
       <c r="O14" t="n">
         <v>41724</v>
@@ -1274,7 +1274,7 @@
         <v>187870</v>
       </c>
       <c r="Q14" t="n">
-        <v>72400</v>
+        <v>75124</v>
       </c>
     </row>
     <row r="15">
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>121625</v>
+        <v>122055</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>105768</v>
+        <v>106198</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>164869</v>
+        <v>165267</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>149563</v>
+        <v>149961</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8049</v>
+        <v>8081</v>
       </c>
       <c r="P15" t="n">
-        <v>97719</v>
+        <v>98117</v>
       </c>
       <c r="Q15" t="n">
-        <v>37996</v>
+        <v>38028</v>
       </c>
     </row>
     <row r="16">
@@ -1353,50 +1353,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>273707</v>
+        <v>291483</v>
       </c>
       <c r="E16" t="n">
         <v>18398</v>
       </c>
       <c r="F16" t="n">
-        <v>255309</v>
+        <v>273085</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>235032</v>
+        <v>235449</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+23.8%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>192032</v>
+        <v>192449</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+33.0%</t>
+          <t>+41.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>41136</v>
+        <v>41534</v>
       </c>
       <c r="P16" t="n">
-        <v>214173</v>
+        <v>231551</v>
       </c>
       <c r="Q16" t="n">
-        <v>44261</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="17">
@@ -1414,52 +1414,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>501583</v>
+        <v>532408</v>
       </c>
       <c r="E17" t="n">
         <v>88433</v>
       </c>
       <c r="F17" t="n">
-        <v>413149</v>
+        <v>443974</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>325646</v>
+        <v>363747</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+54.0%</t>
+          <t>+46.4%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>273280</v>
+        <v>311381</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+42.6%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>69030</v>
       </c>
       <c r="O17" t="n">
-        <v>42911</v>
+        <v>43338</v>
       </c>
       <c r="P17" t="n">
-        <v>301409</v>
+        <v>331807</v>
       </c>
       <c r="Q17" t="n">
-        <v>104151</v>
+        <v>104180</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>925449</v>
+        <v>981600</v>
       </c>
       <c r="E18" t="n">
         <v>99495</v>
       </c>
       <c r="F18" t="n">
-        <v>825954</v>
+        <v>882105</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>477388</v>
+        <v>509037</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+93.9%</t>
+          <t>+92.8%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>349401</v>
+        <v>381031</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+136.4%</t>
+          <t>+131.5%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>226862</v>
+        <v>237298</v>
       </c>
       <c r="P18" t="n">
-        <v>598242</v>
+        <v>643957</v>
       </c>
       <c r="Q18" t="n">
-        <v>497162</v>
+        <v>542915</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>325449</v>
+        <v>386469</v>
       </c>
       <c r="E19" t="n">
         <v>346</v>
       </c>
       <c r="F19" t="n">
-        <v>325103</v>
+        <v>386123</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>245042</v>
+        <v>270276</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+32.8%</t>
+          <t>+43.0%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>99015</v>
+        <v>124249</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+228.3%</t>
+          <t>+210.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>24605</v>
+        <v>58125</v>
       </c>
       <c r="O19" t="n">
         <v>42018</v>
       </c>
       <c r="P19" t="n">
-        <v>258680</v>
+        <v>286180</v>
       </c>
       <c r="Q19" t="n">
-        <v>95243</v>
+        <v>128763</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>366770</v>
+        <v>389754</v>
       </c>
       <c r="E20" t="n">
-        <v>54328</v>
+        <v>56427</v>
       </c>
       <c r="F20" t="n">
-        <v>312442</v>
+        <v>333327</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>382115</v>
+        <v>446313</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>318115</v>
+        <v>382313</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>81129</v>
+        <v>82614</v>
       </c>
       <c r="P20" t="n">
-        <v>231313</v>
+        <v>250713</v>
       </c>
       <c r="Q20" t="n">
-        <v>35092</v>
+        <v>34777</v>
       </c>
     </row>
     <row r="21">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>8964272</v>
+        <v>9274691</v>
       </c>
       <c r="E22" t="n">
-        <v>1535718</v>
+        <v>1594693</v>
       </c>
       <c r="F22" t="n">
-        <v>7428554</v>
+        <v>7679998</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>61.0%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>59.1%</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
       <c r="J22" t="n">
-        <v>6943294</v>
+        <v>7433180</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+29.1%</t>
+          <t>+24.8%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5560802</v>
+        <v>6038721</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+27.2%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>142263</v>
+        <v>178521</v>
       </c>
       <c r="O22" t="n">
-        <v>3494819</v>
+        <v>3538421</v>
       </c>
       <c r="P22" t="n">
-        <v>3791872</v>
+        <v>3963456</v>
       </c>
       <c r="Q22" t="n">
-        <v>4397470</v>
+        <v>4564201</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="C2" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>1270.3</v>
+        <v>1205.6</v>
       </c>
       <c r="E2" t="n">
-        <v>178384</v>
+        <v>104519</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D3" t="n">
-        <v>1274.9</v>
+        <v>1369.1</v>
       </c>
       <c r="E3" t="n">
-        <v>60542</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>797</v>
+        <v>618</v>
       </c>
       <c r="C4" t="n">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n">
-        <v>1546.6</v>
+        <v>1053.3</v>
       </c>
       <c r="E4" t="n">
-        <v>2841</v>
+        <v>1897</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1908467</v>
+        <v>1961754</v>
       </c>
       <c r="D2" t="n">
-        <v>14419</v>
+        <v>15418</v>
       </c>
       <c r="E2" t="n">
-        <v>1564885</v>
+        <v>1613794</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>430509</v>
+        <v>390233</v>
       </c>
       <c r="D3" t="n">
         <v>137638</v>
       </c>
       <c r="E3" t="n">
-        <v>292097</v>
+        <v>317461</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1172233</v>
+        <v>1202823</v>
       </c>
       <c r="D4" t="n">
-        <v>3626614</v>
+        <v>3797199</v>
       </c>
       <c r="E4" t="n">
-        <v>2541256</v>
+        <v>2633713</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>390771</v>
+        <v>380411</v>
       </c>
       <c r="D5" t="n">
-        <v>9634</v>
+        <v>10633</v>
       </c>
       <c r="E5" t="n">
-        <v>399415</v>
+        <v>399656</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>441641</v>
+        <v>465572</v>
       </c>
       <c r="D7" t="n">
         <v>9223</v>
       </c>
       <c r="E7" t="n">
-        <v>432680</v>
+        <v>456612</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-14729</v>
+        <v>-14691</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-121701</v>
+        <v>-121663</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>476959</v>
+        <v>511771</v>
       </c>
       <c r="D9" t="n">
         <v>6926</v>
       </c>
       <c r="E9" t="n">
-        <v>405724</v>
+        <v>430536</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>295466</v>
+        <v>296330</v>
       </c>
       <c r="D10" t="n">
         <v>1718</v>
       </c>
       <c r="E10" t="n">
-        <v>179872</v>
+        <v>175756</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>331456</v>
+        <v>335458</v>
       </c>
       <c r="D11" t="n">
         <v>-18405</v>
       </c>
       <c r="E11" t="n">
-        <v>271857</v>
+        <v>275859</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>430509</v>
+        <v>390234</v>
       </c>
       <c r="D12" t="n">
         <v>137638</v>
       </c>
       <c r="E12" t="n">
-        <v>292097</v>
+        <v>317462</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>554088</v>
+        <v>555301</v>
       </c>
       <c r="D13" t="n">
-        <v>919282</v>
+        <v>918282</v>
       </c>
       <c r="E13" t="n">
-        <v>1429084</v>
+        <v>1429297</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>44747</v>
+        <v>51745</v>
       </c>
       <c r="D14" t="n">
-        <v>147981</v>
+        <v>150781</v>
       </c>
       <c r="E14" t="n">
-        <v>78988</v>
+        <v>87402</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69115</v>
+        <v>69552</v>
       </c>
       <c r="D15" t="n">
         <v>276055</v>
       </c>
       <c r="E15" t="n">
-        <v>41570</v>
+        <v>41609</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20454</v>
+        <v>29618</v>
       </c>
       <c r="D16" t="n">
-        <v>393891</v>
+        <v>421887</v>
       </c>
       <c r="E16" t="n">
-        <v>105310</v>
+        <v>105378</v>
       </c>
     </row>
     <row r="17">
@@ -2297,7 +2297,7 @@
         <v>187870</v>
       </c>
       <c r="E17" t="n">
-        <v>72400</v>
+        <v>75124</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8049</v>
+        <v>8081</v>
       </c>
       <c r="D18" t="n">
-        <v>97719</v>
+        <v>98117</v>
       </c>
       <c r="E18" t="n">
-        <v>37996</v>
+        <v>38028</v>
       </c>
     </row>
     <row r="19">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41136</v>
+        <v>41534</v>
       </c>
       <c r="D19" t="n">
-        <v>214173</v>
+        <v>231551</v>
       </c>
       <c r="E19" t="n">
-        <v>44261</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="20">
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>42911</v>
+        <v>43338</v>
       </c>
       <c r="D20" t="n">
-        <v>301409</v>
+        <v>331807</v>
       </c>
       <c r="E20" t="n">
-        <v>104151</v>
+        <v>104180</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>226862</v>
+        <v>237298</v>
       </c>
       <c r="D21" t="n">
-        <v>598242</v>
+        <v>643957</v>
       </c>
       <c r="E21" t="n">
-        <v>497162</v>
+        <v>542915</v>
       </c>
     </row>
     <row r="22">
@@ -2399,10 +2399,10 @@
         <v>42018</v>
       </c>
       <c r="D22" t="n">
-        <v>258680</v>
+        <v>286180</v>
       </c>
       <c r="E22" t="n">
-        <v>95243</v>
+        <v>128763</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>81129</v>
+        <v>82614</v>
       </c>
       <c r="D23" t="n">
-        <v>231313</v>
+        <v>250713</v>
       </c>
       <c r="E23" t="n">
-        <v>35092</v>
+        <v>34777</v>
       </c>
     </row>
     <row r="24">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3494819</v>
+        <v>3538421</v>
       </c>
       <c r="D25" t="n">
-        <v>3791872</v>
+        <v>3963456</v>
       </c>
       <c r="E25" t="n">
-        <v>4397470</v>
+        <v>4564201</v>
       </c>
     </row>
   </sheetData>
@@ -2549,31 +2549,31 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>225012</v>
+        <v>224312</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>38126.66</v>
+        <v>41598.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>186885.34</v>
+        <v>182713.34</v>
       </c>
     </row>
     <row r="3">
@@ -2591,19 +2591,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>62520</v>
+        <v>64200</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2611,11 +2611,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>43131</v>
+        <v>44811</v>
       </c>
     </row>
     <row r="4">
@@ -2633,19 +2633,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>45698</v>
+        <v>52036</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1138</v>
+        <v>7476</v>
       </c>
     </row>
     <row r="5">
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>94660</v>
+        <v>96640</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>88262.5</v>
+        <v>90242.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,31 +2717,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>57320</v>
+        <v>53360</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1680</v>
+        <v>11680</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>55640</v>
+        <v>41680</v>
       </c>
     </row>
     <row r="7">
@@ -2759,19 +2759,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>109600</v>
+        <v>104620</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>90470</v>
+        <v>85490</v>
       </c>
     </row>
     <row r="8">
@@ -2801,19 +2801,19 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>81220</v>
+        <v>86200</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2821,11 +2821,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29887</v>
+        <v>34867</v>
       </c>
     </row>
     <row r="9">
@@ -2885,19 +2885,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>77196</v>
+        <v>83796</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>69237</v>
+        <v>75837</v>
       </c>
     </row>
     <row r="11">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3980</v>
+        <v>8960</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>56538</v>
+        <v>51558</v>
       </c>
     </row>
     <row r="12">
@@ -2969,19 +2969,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>118510</v>
+        <v>91690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>134.7%</t>
+          <t>104.2%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2989,11 +2989,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>111910</v>
+        <v>85090</v>
       </c>
     </row>
     <row r="13">
@@ -3053,19 +3053,19 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>114420</v>
+        <v>75600</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -3073,11 +3073,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>104.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>35820</v>
+        <v>-3000</v>
       </c>
     </row>
     <row r="15">
@@ -3137,31 +3137,31 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>77234</v>
+        <v>122834</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>36400</v>
+        <v>43000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>40834</v>
+        <v>79834</v>
       </c>
     </row>
     <row r="17">
@@ -3221,19 +3221,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>21580</v>
+        <v>20580</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1380</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19">
@@ -3359,19 +3359,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>38600</v>
+        <v>25400</v>
       </c>
     </row>
     <row r="22">
@@ -3515,19 +3515,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>41074</v>
+        <v>51034</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>23024</v>
+        <v>32984</v>
       </c>
     </row>
     <row r="26">
@@ -3599,14 +3599,14 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>43540</v>
+        <v>48520</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3615,11 +3615,11 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3700</v>
+        <v>8680</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3683,19 +3683,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>71738</v>
+        <v>83318</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>54615</v>
+        <v>66195</v>
       </c>
     </row>
     <row r="30">
@@ -3725,14 +3725,14 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>87640</v>
+        <v>92620</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3741,11 +3741,11 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16980</v>
+        <v>21960</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3767,19 +3767,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>208594</v>
+        <v>213574</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>130.4%</t>
+          <t>133.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3787,11 +3787,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>156734</v>
+        <v>161714</v>
       </c>
     </row>
     <row r="32">
@@ -3809,19 +3809,19 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>105578</v>
+        <v>140358</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>97618</v>
+        <v>132398</v>
       </c>
     </row>
     <row r="33">
@@ -4199,19 +4199,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4997</v>
+        <v>9977</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>58743</v>
+        <v>53763</v>
       </c>
     </row>
   </sheetData>
@@ -4285,11 +4285,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>230370.6</v>
+        <v>258166.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>190503.93</v>
+        <v>218299.93</v>
       </c>
     </row>
     <row r="3">
@@ -4319,11 +4319,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>59644.1</v>
+        <v>67944.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59644.1</v>
+        <v>67944.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -4387,11 +4387,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>43184.8</v>
+        <v>43782.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>40584.8</v>
+        <v>41182.8</v>
       </c>
     </row>
     <row r="6">
@@ -4455,11 +4455,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>18794</v>
+        <v>19192</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>18794</v>
+        <v>19192</v>
       </c>
     </row>
     <row r="8">
@@ -4489,11 +4489,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>28110.39</v>
+        <v>29790.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>28110.39</v>
+        <v>29790.39</v>
       </c>
     </row>
     <row r="9">
@@ -4523,11 +4523,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>45343.66</v>
+        <v>65864.13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4535,11 +4535,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>45143.66</v>
+        <v>65664.13</v>
       </c>
     </row>
     <row r="10">
@@ -4557,11 +4557,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>87740.48</v>
+        <v>120740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>120.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>87740.48</v>
+        <v>120740.48</v>
       </c>
     </row>
     <row r="11">
@@ -4625,11 +4625,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>129805.7</v>
+        <v>137305.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>129805.7</v>
+        <v>137305.7</v>
       </c>
     </row>
     <row r="13">
@@ -4693,11 +4693,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>96770</v>
+        <v>106770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96770</v>
+        <v>106770</v>
       </c>
     </row>
     <row r="15">
@@ -4727,11 +4727,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>60158</v>
+        <v>65954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50960</v>
+        <v>56756</v>
       </c>
     </row>
     <row r="16">
@@ -4761,11 +4761,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>96976</v>
+        <v>98956</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>87776</v>
+        <v>89756</v>
       </c>
     </row>
     <row r="17">
@@ -4863,11 +4863,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>122391.9</v>
+        <v>125115.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>117391.9</v>
+        <v>120115.5</v>
       </c>
     </row>
     <row r="20">
@@ -5101,11 +5101,11 @@
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>31552</v>
+        <v>51552</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>31552</v>
+        <v>51552</v>
       </c>
     </row>
     <row r="27">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>36548</v>
+        <v>39428</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>36548</v>
+        <v>39428</v>
       </c>
     </row>
     <row r="28">
@@ -5203,11 +5203,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>110368</v>
+        <v>112168</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5215,11 +5215,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>103368</v>
+        <v>105168</v>
       </c>
     </row>
     <row r="30">
@@ -5271,11 +5271,11 @@
         <v>60000</v>
       </c>
       <c r="D31" t="n">
-        <v>22496</v>
+        <v>22894</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22496</v>
+        <v>22894</v>
       </c>
     </row>
     <row r="32">
@@ -5305,11 +5305,11 @@
         <v>30000</v>
       </c>
       <c r="D32" t="n">
-        <v>21792</v>
+        <v>28392</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>21792</v>
+        <v>28392</v>
       </c>
     </row>
     <row r="33">
@@ -5441,11 +5441,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>62778</v>
+        <v>82778</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5453,11 +5453,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>56578</v>
+        <v>76578</v>
       </c>
     </row>
     <row r="37">
@@ -5475,11 +5475,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>796</v>
+        <v>11592</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>796</v>
+        <v>11592</v>
       </c>
     </row>
     <row r="38">
@@ -5543,11 +5543,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>75072</v>
+        <v>85470</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>75072</v>
+        <v>85470</v>
       </c>
     </row>
     <row r="40">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>503080</v>
+        <v>548680</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>431780</v>
+        <v>477380</v>
       </c>
     </row>
     <row r="41">
@@ -5781,11 +5781,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>43783</v>
+        <v>44181</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>43783</v>
+        <v>44181</v>
       </c>
     </row>
     <row r="47">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>187909</v>
+        <v>187307</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>187909</v>
+        <v>187307</v>
       </c>
     </row>
     <row r="48">
@@ -6155,11 +6155,11 @@
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>54854</v>
+        <v>55252</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>54854</v>
+        <v>55252</v>
       </c>
     </row>
     <row r="58">
@@ -6359,11 +6359,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>19870</v>
+        <v>20268</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>331.2%</t>
+          <t>337.8%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>19870</v>
+        <v>20268</v>
       </c>
     </row>
   </sheetData>
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>892008</v>
+        <v>858325</v>
       </c>
       <c r="D2" t="n">
-        <v>2690</v>
+        <v>2572</v>
       </c>
       <c r="E2" t="n">
-        <v>765825</v>
+        <v>726343</v>
       </c>
       <c r="F2" t="n">
-        <v>126183</v>
+        <v>131982</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>819147</v>
+        <v>786587</v>
       </c>
       <c r="D3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E3" t="n">
-        <v>695370</v>
+        <v>656210</v>
       </c>
       <c r="F3" t="n">
-        <v>123777</v>
+        <v>130377</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72861</v>
+        <v>71738</v>
       </c>
       <c r="D4" t="n">
-        <v>2536</v>
+        <v>2426</v>
       </c>
       <c r="E4" t="n">
-        <v>70455</v>
+        <v>70133</v>
       </c>
       <c r="F4" t="n">
-        <v>2406</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1041076</v>
+        <v>997436</v>
       </c>
       <c r="D5" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E5" t="n">
-        <v>242360</v>
+        <v>133900</v>
       </c>
       <c r="F5" t="n">
-        <v>798716</v>
+        <v>863536</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>726900</v>
+        <v>761820</v>
       </c>
       <c r="D6" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E6" t="n">
-        <v>42598</v>
+        <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>684302</v>
+        <v>739222</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>301176</v>
+        <v>215616</v>
       </c>
       <c r="D7" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
-        <v>199762</v>
+        <v>111302</v>
       </c>
       <c r="F7" t="n">
-        <v>101414</v>
+        <v>104314</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1526886.8</v>
+        <v>1533282.74</v>
       </c>
       <c r="D8" t="n">
-        <v>2044</v>
+        <v>2071</v>
       </c>
       <c r="E8" t="n">
-        <v>11310.73</v>
+        <v>12251.53</v>
       </c>
       <c r="F8" t="n">
-        <v>1515576.07</v>
+        <v>1521031.21</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>942636.61</v>
+        <v>946289.28</v>
       </c>
       <c r="D9" t="n">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="E9" t="n">
         <v>2945.64</v>
       </c>
       <c r="F9" t="n">
-        <v>939690.97</v>
+        <v>943343.64</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>584250.1899999999</v>
+        <v>586993.46</v>
       </c>
       <c r="D10" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="E10" t="n">
-        <v>8365.09</v>
+        <v>9305.889999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>575885.1</v>
+        <v>577687.5699999999</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>382800</v>
+        <v>474000</v>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>194400</v>
+        <v>240000</v>
       </c>
       <c r="F11" t="n">
-        <v>188400</v>
+        <v>234000</v>
       </c>
     </row>
     <row r="12">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>74788</v>
+        <v>100788</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>15200</v>
       </c>
       <c r="F12" t="n">
-        <v>59588</v>
+        <v>85588</v>
       </c>
     </row>
     <row r="13">
@@ -6700,13 +6700,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -6724,13 +6724,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7920</v>
+        <v>5940</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>5940</v>
@@ -6748,13 +6748,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57187.24</v>
+        <v>57887.24</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>8092</v>
+        <v>8792</v>
       </c>
       <c r="F15" t="n">
         <v>49095.24</v>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>892008</v>
+        <v>858325</v>
       </c>
       <c r="C2" t="n">
-        <v>434481.86</v>
+        <v>481656.86</v>
       </c>
       <c r="D2" t="n">
-        <v>60716</v>
+        <v>77320</v>
       </c>
       <c r="E2" t="n">
-        <v>6.81</v>
+        <v>9.01</v>
       </c>
       <c r="F2" t="n">
-        <v>373765.86</v>
+        <v>404336.86</v>
       </c>
       <c r="G2" t="n">
-        <v>41.9</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="3">
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1041076</v>
+        <v>997436</v>
       </c>
       <c r="C3" t="n">
-        <v>494001.38</v>
+        <v>504001.38</v>
       </c>
       <c r="D3" t="n">
         <v>1000</v>
@@ -6855,10 +6855,10 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>493001.38</v>
+        <v>503001.38</v>
       </c>
       <c r="G3" t="n">
-        <v>47.35</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="4">
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1526886.8</v>
+        <v>1533282.74</v>
       </c>
       <c r="C4" t="n">
-        <v>2849</v>
+        <v>4649</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -6880,10 +6880,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2800</v>
+        <v>4600</v>
       </c>
       <c r="G4" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>382800</v>
+        <v>474000</v>
       </c>
       <c r="C5" t="n">
         <v>116000</v>
@@ -6908,7 +6908,7 @@
         <v>116000</v>
       </c>
       <c r="G5" t="n">
-        <v>30.3</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74788</v>
+        <v>100788</v>
       </c>
       <c r="C6" t="n">
         <v>196919.9</v>
@@ -6927,13 +6927,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>194902</v>
       </c>
       <c r="G6" t="n">
-        <v>260.61</v>
+        <v>193.38</v>
       </c>
     </row>
     <row r="7">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59340</v>
+        <v>45480</v>
       </c>
       <c r="C7" t="n">
         <v>290266.67</v>
@@ -6952,13 +6952,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>89.31999999999999</v>
+        <v>116.53</v>
       </c>
       <c r="F7" t="n">
         <v>237266.67</v>
       </c>
       <c r="G7" t="n">
-        <v>399.84</v>
+        <v>521.6900000000001</v>
       </c>
     </row>
     <row r="8">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7920</v>
+        <v>5940</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57187.24</v>
+        <v>57887.24</v>
       </c>
       <c r="C9" t="n">
         <v>1199</v>
@@ -7002,7 +7002,7 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="C2" t="n">
-        <v>916933.05</v>
+        <v>952308.05</v>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="C3" t="n">
-        <v>296368.4</v>
+        <v>310663.4</v>
       </c>
       <c r="D3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
@@ -7086,13 +7086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>129982</v>
+        <v>136582</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>98200</v>
+        <v>100200</v>
       </c>
       <c r="D5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>24235.66</v>
+        <v>24636.66</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>22960.7</v>
+        <v>23179.7</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>17167</v>
+        <v>17233</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7214,10 +7214,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>205400</v>
+        <v>218600</v>
       </c>
     </row>
     <row r="3">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>61200</v>
+        <v>67800</v>
       </c>
     </row>
     <row r="4">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D12" t="n">
-        <v>67554</v>
+        <v>72534</v>
       </c>
     </row>
     <row r="13">
@@ -7469,10 +7469,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D13" t="n">
-        <v>38300</v>
+        <v>43299</v>
       </c>
     </row>
     <row r="14">
@@ -7595,10 +7595,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>72342</v>
+        <v>80379</v>
       </c>
     </row>
     <row r="21">
@@ -7613,10 +7613,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>22646.5</v>
+        <v>24543.5</v>
       </c>
     </row>
     <row r="22">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>11200</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="24">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D24" t="n">
-        <v>7989.66</v>
+        <v>9707.66</v>
       </c>
     </row>
     <row r="25">
@@ -7703,10 +7703,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>95</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27">
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D30" t="n">
-        <v>79221</v>
+        <v>79297</v>
       </c>
     </row>
     <row r="31">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D31" t="n">
-        <v>20054</v>
+        <v>25081</v>
       </c>
     </row>
     <row r="32">
@@ -7829,10 +7829,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" t="n">
-        <v>418</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -7892,19 +7892,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>77900</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -7915,14 +7915,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D38" t="n">
-        <v>21500</v>
+        <v>77900</v>
       </c>
     </row>
     <row r="39">
@@ -7933,14 +7933,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>57</v>
+        <v>21500</v>
       </c>
     </row>
     <row r="40">
@@ -7951,86 +7951,86 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>58733.4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D42" t="n">
-        <v>20500</v>
+        <v>63118</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>9000</v>
+        <v>14839</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D44" t="n">
-        <v>200</v>
+        <v>12860</v>
       </c>
     </row>
     <row r="45">
@@ -8041,14 +8041,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>63080</v>
+        <v>598</v>
       </c>
     </row>
     <row r="46">
@@ -8059,14 +8059,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>14839</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47">
@@ -8077,14 +8077,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>7861</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48">
@@ -8095,14 +8095,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>598</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49">
@@ -8113,86 +8113,86 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>432</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>122</v>
+        <v>58733.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>57</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>34578.9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54">
@@ -8203,14 +8203,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="D54" t="n">
-        <v>20436</v>
+        <v>35102.9</v>
       </c>
     </row>
     <row r="55">
@@ -8221,14 +8221,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="D55" t="n">
-        <v>9117</v>
+        <v>24529</v>
       </c>
     </row>
     <row r="56">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D56" t="n">
-        <v>1863</v>
+        <v>7482</v>
       </c>
     </row>
     <row r="57">
@@ -8257,14 +8257,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D57" t="n">
-        <v>508</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="58">
@@ -8275,14 +8275,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D58" t="n">
-        <v>57</v>
+        <v>555</v>
       </c>
     </row>
     <row r="59">
@@ -8293,14 +8293,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -8311,32 +8311,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>44345</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -8347,14 +8347,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D62" t="n">
-        <v>9000</v>
+        <v>44345</v>
       </c>
     </row>
     <row r="63">
@@ -8365,14 +8365,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>698</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="64">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D64" t="n">
-        <v>152</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="65">
@@ -8401,14 +8401,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D65" t="n">
-        <v>76</v>
+        <v>451</v>
       </c>
     </row>
     <row r="66">
@@ -8419,32 +8419,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>33494.67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -8455,14 +8455,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>6500</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="69">
@@ -8473,14 +8473,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>4691</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="70">
@@ -8491,32 +8491,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D70" t="n">
-        <v>328</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>18399.98</v>
+        <v>328</v>
       </c>
     </row>
     <row r="72">
@@ -8527,32 +8527,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>18000</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>15019</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="74">
@@ -8563,14 +8563,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>15009</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="75">
@@ -8581,32 +8581,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>48</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>15000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -8617,14 +8617,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>14509</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="78">
@@ -8635,32 +8635,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>299</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>18000</v>
+        <v>299</v>
       </c>
     </row>
     <row r="80">
@@ -8671,32 +8671,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D80" t="n">
-        <v>398</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>10621</v>
+        <v>398</v>
       </c>
     </row>
     <row r="82">
@@ -8707,14 +8707,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>5000</v>
+        <v>10621</v>
       </c>
     </row>
     <row r="83">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>2490</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>9000</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="85">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>6800</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="86">
@@ -8779,32 +8779,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>57</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D87" t="n">
-        <v>10000</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
@@ -8815,32 +8815,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>4980</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程2组</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>9318</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="90">
@@ -8851,14 +8851,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>5500</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="91">
@@ -8869,14 +8869,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>29</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="92">
@@ -8887,32 +8887,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>318</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
@@ -8923,13 +8923,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>2</v>
       </c>
       <c r="D94" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
         <v>28</v>
       </c>
     </row>
@@ -8971,10 +8989,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="n">
-        <v>424631.38</v>
+        <v>432631.38</v>
       </c>
     </row>
     <row r="3">
@@ -8997,10 +9015,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C4" t="n">
-        <v>201077.16</v>
+        <v>226769.16</v>
       </c>
     </row>
     <row r="5">
@@ -9023,10 +9041,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>141960</v>
+        <v>161760</v>
       </c>
     </row>
     <row r="7">
@@ -9049,10 +9067,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>50900</v>
+        <v>54700</v>
       </c>
     </row>
     <row r="9">
@@ -9132,10 +9150,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C2" t="n">
-        <v>211902.33</v>
+        <v>221281.33</v>
       </c>
     </row>
     <row r="3">
@@ -9145,10 +9163,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C3" t="n">
-        <v>173752</v>
+        <v>188932</v>
       </c>
     </row>
     <row r="4">
@@ -9158,36 +9176,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C4" t="n">
-        <v>162131.4</v>
+        <v>169006.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="C5" t="n">
-        <v>147008.5</v>
+        <v>147073.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
-        <v>146774.98</v>
+        <v>147008.5</v>
       </c>
     </row>
     <row r="7">
@@ -9197,10 +9215,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>92412</v>
+        <v>105612</v>
       </c>
     </row>
     <row r="8">
@@ -9210,36 +9228,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>69516</v>
+        <v>71308</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>64942.8</v>
+        <v>70404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="C10" t="n">
-        <v>63729</v>
+        <v>64999.8</v>
       </c>
     </row>
     <row r="11">
@@ -9249,10 +9267,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" t="n">
-        <v>54500</v>
+        <v>59527</v>
       </c>
     </row>
     <row r="12">
@@ -9288,10 +9306,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C14" t="n">
-        <v>34187</v>
+        <v>34250</v>
       </c>
     </row>
     <row r="15">
@@ -9301,10 +9319,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>31775</v>
+        <v>31794</v>
       </c>
     </row>
     <row r="16">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>541467</v>
+        <v>311994</v>
       </c>
       <c r="E2" t="n">
-        <v>150423</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>391044</v>
+        <v>311994</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>338479</v>
+        <v>354727</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+60.0%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>152715</v>
+        <v>168693</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+156.1%</t>
+          <t>+84.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -586,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="E3" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-12961</v>
+        <v>2000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16437</v>
+        <v>16494</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.7%</t>
+          <t>-87.9%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-14003</v>
+        <v>-18935</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-110.6%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>626869</v>
+        <v>447038</v>
       </c>
       <c r="E4" t="n">
-        <v>152074</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>474796</v>
+        <v>447038</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>510984</v>
+        <v>522172</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+22.7%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>386071</v>
+        <v>396710</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+23.0%</t>
+          <t>+12.7%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>230425</v>
+        <v>176054</v>
       </c>
       <c r="E5" t="n">
-        <v>239928</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-9503</v>
+        <v>176054</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>410463</v>
+        <v>410568</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-43.9%</t>
+          <t>-57.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>304287</v>
+        <v>304373</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-103.1%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>588342</v>
+        <v>377840</v>
       </c>
       <c r="E6" t="n">
-        <v>69646</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>518697</v>
+        <v>377840</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>277717</v>
+        <v>284457</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+111.8%</t>
+          <t>+32.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>212501</v>
+        <v>214395</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+144.1%</t>
+          <t>+76.2%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>390131</v>
+        <v>276080</v>
       </c>
       <c r="E7" t="n">
-        <v>92083</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>298048</v>
+        <v>276080</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>285196</v>
+        <v>288360</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+36.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>222418</v>
+        <v>224628</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>423881</v>
+        <v>302772</v>
       </c>
       <c r="E8" t="n">
-        <v>106828</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>317053</v>
+        <v>302772</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>318508</v>
+        <v>325321</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+33.1%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>253158</v>
+        <v>259933</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+25.2%</t>
+          <t>+16.5%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>843372</v>
+        <v>910888</v>
       </c>
       <c r="E9" t="n">
-        <v>315500</v>
+        <v>377900</v>
       </c>
       <c r="F9" t="n">
-        <v>527872</v>
+        <v>532988</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>729456</v>
+        <v>763334</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+15.6%</t>
+          <t>+19.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>559332</v>
+        <v>593210</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1503391</v>
+        <v>1540234</v>
       </c>
       <c r="E10" t="n">
         <v>29808</v>
       </c>
       <c r="F10" t="n">
-        <v>1473583</v>
+        <v>1510426</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1273695</v>
+        <v>1408891</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+18.0%</t>
+          <t>+9.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1273695</v>
+        <v>1408891</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+7.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>555301</v>
+        <v>560593</v>
       </c>
       <c r="P10" t="n">
-        <v>918282</v>
+        <v>949833</v>
       </c>
       <c r="Q10" t="n">
-        <v>1429297</v>
+        <v>1466140</v>
       </c>
     </row>
     <row r="11">
@@ -1042,13 +1042,13 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>239150</v>
+        <v>239169</v>
       </c>
       <c r="E11" t="n">
         <v>36400</v>
       </c>
       <c r="F11" t="n">
-        <v>202750</v>
+        <v>202769</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1062,32 +1062,32 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>249401</v>
+        <v>258197</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>224293</v>
+        <v>233089</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>224</v>
       </c>
       <c r="O11" t="n">
-        <v>51745</v>
+        <v>51764</v>
       </c>
       <c r="P11" t="n">
         <v>150781</v>
       </c>
       <c r="Q11" t="n">
-        <v>87402</v>
+        <v>87421</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375683</v>
+        <v>386380</v>
       </c>
       <c r="E12" t="n">
         <v>30076</v>
       </c>
       <c r="F12" t="n">
-        <v>345607</v>
+        <v>356304</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>277909</v>
+        <v>284509</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+35.2%</t>
+          <t>+35.8%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>275911</v>
+        <v>282511</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+25.3%</t>
+          <t>+26.1%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69552</v>
+        <v>69851</v>
       </c>
       <c r="P12" t="n">
-        <v>276055</v>
+        <v>286453</v>
       </c>
       <c r="Q12" t="n">
-        <v>41609</v>
+        <v>41908</v>
       </c>
     </row>
     <row r="13">
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>527733</v>
+        <v>559255</v>
       </c>
       <c r="E13" t="n">
         <v>45014</v>
       </c>
       <c r="F13" t="n">
-        <v>482720</v>
+        <v>514242</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>475420</v>
+        <v>502164</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+11.0%</t>
+          <t>+11.4%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>398911</v>
+        <v>425655</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+21.0%</t>
+          <t>+20.8%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>31214</v>
+        <v>31692</v>
       </c>
       <c r="O13" t="n">
-        <v>29618</v>
+        <v>29647</v>
       </c>
       <c r="P13" t="n">
-        <v>421887</v>
+        <v>452902</v>
       </c>
       <c r="Q13" t="n">
-        <v>105378</v>
+        <v>106104</v>
       </c>
     </row>
     <row r="14">
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>263538</v>
+        <v>265863</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>248672</v>
+        <v>250997</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>279426</v>
+        <v>334008</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>248048</v>
+        <v>302630</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>19078</v>
+        <v>20407</v>
       </c>
       <c r="O14" t="n">
-        <v>41724</v>
+        <v>42322</v>
       </c>
       <c r="P14" t="n">
-        <v>187870</v>
+        <v>188268</v>
       </c>
       <c r="Q14" t="n">
-        <v>75124</v>
+        <v>76453</v>
       </c>
     </row>
     <row r="15">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>165267</v>
+        <v>169746</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>149961</v>
+        <v>154440</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1353,47 +1353,47 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>291483</v>
+        <v>311483</v>
       </c>
       <c r="E16" t="n">
-        <v>18398</v>
+        <v>48398</v>
       </c>
       <c r="F16" t="n">
-        <v>273085</v>
+        <v>263085</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>235449</v>
+        <v>253449</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+23.8%</t>
+          <t>+22.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>192449</v>
+        <v>210449</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+41.9%</t>
+          <t>+25.0%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>41534</v>
+        <v>21534</v>
       </c>
       <c r="P16" t="n">
-        <v>231551</v>
+        <v>241551</v>
       </c>
       <c r="Q16" t="n">
         <v>46241</v>
@@ -1414,52 +1414,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>532408</v>
+        <v>534173</v>
       </c>
       <c r="E17" t="n">
-        <v>88433</v>
+        <v>105631</v>
       </c>
       <c r="F17" t="n">
-        <v>443974</v>
+        <v>428542</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>363747</v>
+        <v>381164</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+46.4%</t>
+          <t>+40.1%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>311381</v>
+        <v>322298</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+42.6%</t>
+          <t>+33.0%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>69030</v>
+        <v>69599</v>
       </c>
       <c r="O17" t="n">
-        <v>43338</v>
+        <v>43538</v>
       </c>
       <c r="P17" t="n">
-        <v>331807</v>
+        <v>315605</v>
       </c>
       <c r="Q17" t="n">
-        <v>104180</v>
+        <v>87949</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>981600</v>
+        <v>999753</v>
       </c>
       <c r="E18" t="n">
-        <v>99495</v>
+        <v>108845</v>
       </c>
       <c r="F18" t="n">
-        <v>882105</v>
+        <v>890908</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>509037</v>
+        <v>535187</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+92.8%</t>
+          <t>+86.8%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>381031</v>
+        <v>407181</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+131.5%</t>
+          <t>+118.8%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>237298</v>
+        <v>228297</v>
       </c>
       <c r="P18" t="n">
-        <v>643957</v>
+        <v>661761</v>
       </c>
       <c r="Q18" t="n">
-        <v>542915</v>
+        <v>536922</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>386469</v>
+        <v>411284</v>
       </c>
       <c r="E19" t="n">
-        <v>346</v>
+        <v>30346</v>
       </c>
       <c r="F19" t="n">
-        <v>386123</v>
+        <v>380938</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>270276</v>
+        <v>300393</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+43.0%</t>
+          <t>+36.9%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>124249</v>
+        <v>154366</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+210.8%</t>
+          <t>+146.8%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>58125</v>
       </c>
       <c r="O19" t="n">
-        <v>42018</v>
+        <v>42416</v>
       </c>
       <c r="P19" t="n">
-        <v>286180</v>
+        <v>280597</v>
       </c>
       <c r="Q19" t="n">
-        <v>128763</v>
+        <v>128782</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>389754</v>
+        <v>401888</v>
       </c>
       <c r="E20" t="n">
-        <v>56427</v>
+        <v>56436</v>
       </c>
       <c r="F20" t="n">
-        <v>333327</v>
+        <v>345452</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>446313</v>
+        <v>451711</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>382313</v>
+        <v>387711</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>82614</v>
+        <v>83059</v>
       </c>
       <c r="P20" t="n">
-        <v>250713</v>
+        <v>262393</v>
       </c>
       <c r="Q20" t="n">
-        <v>34777</v>
+        <v>36504</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14920</v>
+        <v>1110893</v>
       </c>
       <c r="E21" t="n">
-        <v>18111</v>
+        <v>802688</v>
       </c>
       <c r="F21" t="n">
-        <v>-3191</v>
+        <v>308205</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-16391</v>
+        <v>376722</v>
       </c>
       <c r="P21" t="n">
-        <v>13200</v>
+        <v>-68516</v>
       </c>
       <c r="Q21" t="n">
-        <v>-770</v>
+        <v>266673</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>9274691</v>
+        <v>9687096</v>
       </c>
       <c r="E22" t="n">
-        <v>1594693</v>
+        <v>1702265</v>
       </c>
       <c r="F22" t="n">
-        <v>7679998</v>
+        <v>7984831</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7433180</v>
+        <v>7844851</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+24.8%</t>
+          <t>+23.5%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6038721</v>
+        <v>6432227</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+27.2%</t>
+          <t>+24.1%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>178521</v>
+        <v>180897</v>
       </c>
       <c r="O22" t="n">
-        <v>3538421</v>
+        <v>3726579</v>
       </c>
       <c r="P22" t="n">
-        <v>3963456</v>
+        <v>4077757</v>
       </c>
       <c r="Q22" t="n">
-        <v>4564201</v>
+        <v>4712641</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>417</v>
+        <v>194</v>
       </c>
       <c r="C2" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>1205.6</v>
+        <v>524.2</v>
       </c>
       <c r="E2" t="n">
-        <v>104519</v>
+        <v>46865</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" t="n">
-        <v>1369.1</v>
+        <v>1055.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1701</v>
+        <v>3247</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>618</v>
+        <v>469</v>
       </c>
       <c r="C4" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="D4" t="n">
-        <v>1053.3</v>
+        <v>978</v>
       </c>
       <c r="E4" t="n">
-        <v>1897</v>
+        <v>10706</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1961754</v>
+        <v>1773404</v>
       </c>
       <c r="D2" t="n">
-        <v>15418</v>
+        <v>120373</v>
       </c>
       <c r="E2" t="n">
-        <v>1613794</v>
+        <v>1523753</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>390233</v>
+        <v>395349</v>
       </c>
       <c r="D3" t="n">
         <v>137638</v>
       </c>
       <c r="E3" t="n">
-        <v>317461</v>
+        <v>269761</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1202823</v>
+        <v>1181102</v>
       </c>
       <c r="D4" t="n">
-        <v>3797199</v>
+        <v>3888260</v>
       </c>
       <c r="E4" t="n">
-        <v>2633713</v>
+        <v>2652451</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>380411</v>
+        <v>310870</v>
       </c>
       <c r="D5" t="n">
-        <v>10633</v>
+        <v>1124</v>
       </c>
       <c r="E5" t="n">
-        <v>399656</v>
+        <v>301596</v>
       </c>
     </row>
     <row r="6">
@@ -2060,13 +2060,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-13096</v>
+        <v>1865</v>
       </c>
       <c r="D6" t="n">
         <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>-2961</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>465572</v>
+        <v>421008</v>
       </c>
       <c r="D7" t="n">
-        <v>9223</v>
+        <v>26030</v>
       </c>
       <c r="E7" t="n">
-        <v>456612</v>
+        <v>390252</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-14691</v>
+        <v>132666</v>
       </c>
       <c r="D8" t="n">
-        <v>5188</v>
+        <v>43388</v>
       </c>
       <c r="E8" t="n">
-        <v>-121663</v>
+        <v>98414</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>511771</v>
+        <v>370876</v>
       </c>
       <c r="D9" t="n">
-        <v>6926</v>
+        <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>430536</v>
+        <v>310048</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>296330</v>
+        <v>244581</v>
       </c>
       <c r="D10" t="n">
-        <v>1718</v>
+        <v>31499</v>
       </c>
       <c r="E10" t="n">
-        <v>175756</v>
+        <v>161866</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>335458</v>
+        <v>291539</v>
       </c>
       <c r="D11" t="n">
-        <v>-18405</v>
+        <v>11233</v>
       </c>
       <c r="E11" t="n">
-        <v>275859</v>
+        <v>259578</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>390234</v>
+        <v>395350</v>
       </c>
       <c r="D12" t="n">
         <v>137638</v>
       </c>
       <c r="E12" t="n">
-        <v>317462</v>
+        <v>269762</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>555301</v>
+        <v>560593</v>
       </c>
       <c r="D13" t="n">
-        <v>918282</v>
+        <v>949833</v>
       </c>
       <c r="E13" t="n">
-        <v>1429297</v>
+        <v>1466140</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51745</v>
+        <v>51764</v>
       </c>
       <c r="D14" t="n">
         <v>150781</v>
       </c>
       <c r="E14" t="n">
-        <v>87402</v>
+        <v>87421</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69552</v>
+        <v>69851</v>
       </c>
       <c r="D15" t="n">
-        <v>276055</v>
+        <v>286453</v>
       </c>
       <c r="E15" t="n">
-        <v>41609</v>
+        <v>41908</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29618</v>
+        <v>29647</v>
       </c>
       <c r="D16" t="n">
-        <v>421887</v>
+        <v>452902</v>
       </c>
       <c r="E16" t="n">
-        <v>105378</v>
+        <v>106104</v>
       </c>
     </row>
     <row r="17">
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>41724</v>
+        <v>42322</v>
       </c>
       <c r="D17" t="n">
-        <v>187870</v>
+        <v>188268</v>
       </c>
       <c r="E17" t="n">
-        <v>75124</v>
+        <v>76453</v>
       </c>
     </row>
     <row r="18">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41534</v>
+        <v>21534</v>
       </c>
       <c r="D19" t="n">
-        <v>231551</v>
+        <v>241551</v>
       </c>
       <c r="E19" t="n">
         <v>46241</v>
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43338</v>
+        <v>43538</v>
       </c>
       <c r="D20" t="n">
-        <v>331807</v>
+        <v>315605</v>
       </c>
       <c r="E20" t="n">
-        <v>104180</v>
+        <v>87949</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>237298</v>
+        <v>228297</v>
       </c>
       <c r="D21" t="n">
-        <v>643957</v>
+        <v>661761</v>
       </c>
       <c r="E21" t="n">
-        <v>542915</v>
+        <v>536922</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42018</v>
+        <v>42416</v>
       </c>
       <c r="D22" t="n">
-        <v>286180</v>
+        <v>280597</v>
       </c>
       <c r="E22" t="n">
-        <v>128763</v>
+        <v>128782</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>82614</v>
+        <v>83059</v>
       </c>
       <c r="D23" t="n">
-        <v>250713</v>
+        <v>262393</v>
       </c>
       <c r="E23" t="n">
-        <v>34777</v>
+        <v>36504</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-16391</v>
+        <v>376722</v>
       </c>
       <c r="D24" t="n">
-        <v>13200</v>
+        <v>-68516</v>
       </c>
       <c r="E24" t="n">
-        <v>-770</v>
+        <v>266673</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3538421</v>
+        <v>3726579</v>
       </c>
       <c r="D25" t="n">
-        <v>3963456</v>
+        <v>4077757</v>
       </c>
       <c r="E25" t="n">
-        <v>4564201</v>
+        <v>4712641</v>
       </c>
     </row>
   </sheetData>
@@ -2549,19 +2549,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>224312</v>
+        <v>230912</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2569,11 +2569,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>182713.34</v>
+        <v>189313.34</v>
       </c>
     </row>
     <row r="3">
@@ -2717,19 +2717,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>53360</v>
+        <v>78160</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>41680</v>
+        <v>66480</v>
       </c>
     </row>
     <row r="7">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>51333</v>
+        <v>53125</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>34867</v>
+        <v>33075</v>
       </c>
     </row>
     <row r="9">
@@ -2885,19 +2885,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>83796</v>
+        <v>91956</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>75837</v>
+        <v>83997</v>
       </c>
     </row>
     <row r="11">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8960</v>
+        <v>13940</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51558</v>
+        <v>46578</v>
       </c>
     </row>
     <row r="12">
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>207738</v>
+        <v>182938</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>259.7%</t>
+          <t>228.7%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>217.4%</t>
+          <t>186.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>173938</v>
+        <v>149138</v>
       </c>
     </row>
     <row r="14">
@@ -3053,31 +3053,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>75600</v>
+        <v>83700</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>78600</v>
+        <v>124200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>104.0%</t>
+          <t>148.4%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-3000</v>
+        <v>-40500</v>
       </c>
     </row>
     <row r="15">
@@ -3221,19 +3221,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>20580</v>
+        <v>98196</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>111.6%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>380</v>
+        <v>77996</v>
       </c>
     </row>
     <row r="19">
@@ -3275,19 +3275,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>34000</v>
+        <v>50800</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33720</v>
+        <v>16920</v>
       </c>
     </row>
     <row r="20">
@@ -3347,19 +3347,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>38600</v>
+        <v>45200</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>25400</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="22">
@@ -3557,19 +3557,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>176956</v>
+        <v>181936</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>110.6%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>102.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>158210</v>
+        <v>163190</v>
       </c>
     </row>
     <row r="27">
@@ -3599,19 +3599,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>48520</v>
+        <v>53500</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3619,11 +3619,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>39840</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="28">
@@ -3725,19 +3725,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>92620</v>
+        <v>104560</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>70660</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="31">
@@ -3767,31 +3767,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>213574</v>
+        <v>218554</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>133.5%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>102.6%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>51860</v>
+        <v>54340</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>161714</v>
+        <v>164214</v>
       </c>
     </row>
     <row r="32">
@@ -3809,31 +3809,31 @@
         <v>160000</v>
       </c>
       <c r="D32" t="n">
-        <v>140358</v>
+        <v>196958</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7960</v>
+        <v>20940</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>132398</v>
+        <v>176018</v>
       </c>
     </row>
     <row r="33">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>82740</v>
+        <v>83138</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>57960</v>
+        <v>58358</v>
       </c>
     </row>
     <row r="34">
@@ -4019,19 +4019,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>92976</v>
+        <v>100936</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>97.1%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>89.4%</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>81.7%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4039,11 +4039,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>85016</v>
+        <v>92976</v>
       </c>
     </row>
     <row r="38">
@@ -4103,19 +4103,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>91928</v>
+        <v>96908</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4123,11 +4123,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>37855</v>
+        <v>42835</v>
       </c>
     </row>
     <row r="40">
@@ -4285,11 +4285,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>258166.6</v>
+        <v>270650</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>100.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>218299.93</v>
+        <v>230783.33</v>
       </c>
     </row>
     <row r="3">
@@ -4353,11 +4353,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>60567.8</v>
+        <v>75267.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>60567.8</v>
+        <v>75267.8</v>
       </c>
     </row>
     <row r="5">
@@ -4387,11 +4387,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>43782.8</v>
+        <v>47480.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>41182.8</v>
+        <v>44880.8</v>
       </c>
     </row>
     <row r="6">
@@ -4455,11 +4455,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19192</v>
+        <v>19590</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19192</v>
+        <v>19590</v>
       </c>
     </row>
     <row r="8">
@@ -4489,11 +4489,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>29790.39</v>
+        <v>30586.39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>29790.39</v>
+        <v>30586.39</v>
       </c>
     </row>
     <row r="9">
@@ -4557,11 +4557,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>120740.48</v>
+        <v>144740.48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>144.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>120740.48</v>
+        <v>144740.48</v>
       </c>
     </row>
     <row r="11">
@@ -4697,19 +4697,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>106770</v>
+        <v>96770</v>
       </c>
     </row>
     <row r="15">
@@ -4727,7 +4727,7 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>65954</v>
+        <v>85954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4735,11 +4735,11 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9198</v>
+        <v>29198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -4829,11 +4829,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>48556</v>
+        <v>48954</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48556</v>
+        <v>48954</v>
       </c>
     </row>
     <row r="19">
@@ -4863,11 +4863,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>125115.5</v>
+        <v>125713.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>120115.5</v>
+        <v>120713.5</v>
       </c>
     </row>
     <row r="20">
@@ -4897,11 +4897,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>78166.60000000001</v>
+        <v>78896.89999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74166.60000000001</v>
+        <v>74896.89999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4931,11 +4931,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>10677.8</v>
+        <v>11276.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10677.8</v>
+        <v>11276.55</v>
       </c>
     </row>
     <row r="22">
@@ -4999,11 +4999,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>173558</v>
+        <v>173956</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>173558</v>
+        <v>173956</v>
       </c>
     </row>
     <row r="24">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>75562</v>
+        <v>77242</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>65762</v>
+        <v>67442</v>
       </c>
     </row>
     <row r="26">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>39428</v>
+        <v>44428</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>39428</v>
+        <v>44428</v>
       </c>
     </row>
     <row r="28">
@@ -5373,11 +5373,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>164265.13</v>
+        <v>164863.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>124431.73</v>
+        <v>125029.73</v>
       </c>
     </row>
     <row r="35">
@@ -5407,11 +5407,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>91044.92</v>
+        <v>91642.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>84444.92</v>
+        <v>85042.92</v>
       </c>
     </row>
     <row r="36">
@@ -5445,19 +5445,19 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6200</v>
+        <v>6598</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>76578</v>
+        <v>76180</v>
       </c>
     </row>
     <row r="37">
@@ -5577,23 +5577,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>548680</v>
+        <v>565476</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>119.3%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>71300</v>
+        <v>78650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>477380</v>
+        <v>486826</v>
       </c>
     </row>
     <row r="41">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>144607.64</v>
+        <v>149519.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>144607.64</v>
+        <v>149519.64</v>
       </c>
     </row>
     <row r="46">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>187307</v>
+        <v>188544</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>187307</v>
+        <v>188544</v>
       </c>
     </row>
     <row r="48">
@@ -5849,11 +5849,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>114357</v>
+        <v>118397</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>114357</v>
+        <v>118397</v>
       </c>
     </row>
     <row r="49">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>320773.65</v>
+        <v>337792.15</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>320773.65</v>
+        <v>337792.15</v>
       </c>
     </row>
     <row r="53">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>144428.1</v>
+        <v>149610.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>144428.1</v>
+        <v>149610.3</v>
       </c>
     </row>
     <row r="54">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>107789</v>
+        <v>117789</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6099,11 +6099,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>97789</v>
+        <v>107789</v>
       </c>
     </row>
     <row r="56">
@@ -6257,11 +6257,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>25398</v>
+        <v>25796</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>127.0%</t>
+          <t>129.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25398</v>
+        <v>25796</v>
       </c>
     </row>
     <row r="61">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>858325</v>
+        <v>945493.9399999999</v>
       </c>
       <c r="D2" t="n">
-        <v>2572</v>
+        <v>2918</v>
       </c>
       <c r="E2" t="n">
-        <v>726343</v>
+        <v>92429</v>
       </c>
       <c r="F2" t="n">
-        <v>131982</v>
+        <v>853064.9399999999</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>786587</v>
+        <v>859547</v>
       </c>
       <c r="D3" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="E3" t="n">
-        <v>656210</v>
+        <v>92400</v>
       </c>
       <c r="F3" t="n">
-        <v>130377</v>
+        <v>767147</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71738</v>
+        <v>85946.94</v>
       </c>
       <c r="D4" t="n">
-        <v>2426</v>
+        <v>2756</v>
       </c>
       <c r="E4" t="n">
-        <v>70133</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>1605</v>
+        <v>85917.94</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>997436</v>
+        <v>1229826</v>
       </c>
       <c r="D5" t="n">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="E5" t="n">
-        <v>133900</v>
+        <v>85812</v>
       </c>
       <c r="F5" t="n">
-        <v>863536</v>
+        <v>1144014</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>761820</v>
+        <v>907204</v>
       </c>
       <c r="D6" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>739222</v>
+        <v>884606</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>215616</v>
+        <v>302622</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E7" t="n">
-        <v>111302</v>
+        <v>63214</v>
       </c>
       <c r="F7" t="n">
-        <v>104314</v>
+        <v>239408</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1533282.74</v>
+        <v>1574530.64</v>
       </c>
       <c r="D8" t="n">
-        <v>2071</v>
+        <v>2160</v>
       </c>
       <c r="E8" t="n">
-        <v>12251.53</v>
+        <v>8284.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1521031.21</v>
+        <v>1566246.17</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>946289.28</v>
+        <v>979701.9399999999</v>
       </c>
       <c r="D9" t="n">
-        <v>877</v>
+        <v>947</v>
       </c>
       <c r="E9" t="n">
-        <v>2945.64</v>
+        <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>943343.64</v>
+        <v>977901.9399999999</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>586993.46</v>
+        <v>594828.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1194</v>
+        <v>1213</v>
       </c>
       <c r="E10" t="n">
-        <v>9305.889999999999</v>
+        <v>6484.47</v>
       </c>
       <c r="F10" t="n">
-        <v>577687.5699999999</v>
+        <v>588344.23</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>474000</v>
+        <v>523600</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="F11" t="n">
-        <v>234000</v>
+        <v>403600</v>
       </c>
     </row>
     <row r="12">
@@ -6682,10 +6682,10 @@
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>15200</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>85588</v>
+        <v>100788</v>
       </c>
     </row>
     <row r="13">
@@ -6706,10 +6706,10 @@
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>45480</v>
+        <v>33600</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="14">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57887.24</v>
+        <v>59885.24</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>8792</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>49095.24</v>
+        <v>59885.24</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>858325</v>
+        <v>945493.9399999999</v>
       </c>
       <c r="C2" t="n">
-        <v>481656.86</v>
+        <v>486680.76</v>
       </c>
       <c r="D2" t="n">
-        <v>77320</v>
+        <v>83539</v>
       </c>
       <c r="E2" t="n">
-        <v>9.01</v>
+        <v>8.84</v>
       </c>
       <c r="F2" t="n">
-        <v>404336.86</v>
+        <v>403141.76</v>
       </c>
       <c r="G2" t="n">
-        <v>47.11</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>997436</v>
+        <v>1229826</v>
       </c>
       <c r="C3" t="n">
-        <v>504001.38</v>
+        <v>579999.38</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="F3" t="n">
-        <v>503001.38</v>
+        <v>572399.38</v>
       </c>
       <c r="G3" t="n">
-        <v>50.43</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="4">
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1533282.74</v>
+        <v>1574530.64</v>
       </c>
       <c r="C4" t="n">
-        <v>4649</v>
+        <v>28799</v>
       </c>
       <c r="D4" t="n">
         <v>49</v>
@@ -6880,10 +6880,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4600</v>
+        <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="5">
@@ -6893,10 +6893,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>474000</v>
+        <v>523600</v>
       </c>
       <c r="C5" t="n">
-        <v>116000</v>
+        <v>140800</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6905,10 +6905,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>116000</v>
+        <v>140800</v>
       </c>
       <c r="G5" t="n">
-        <v>24.47</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="6">
@@ -6921,7 +6921,7 @@
         <v>100788</v>
       </c>
       <c r="C6" t="n">
-        <v>196919.9</v>
+        <v>156919.9</v>
       </c>
       <c r="D6" t="n">
         <v>2017.9</v>
@@ -6930,10 +6930,10 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>194902</v>
+        <v>154902</v>
       </c>
       <c r="G6" t="n">
-        <v>193.38</v>
+        <v>153.69</v>
       </c>
     </row>
     <row r="7">
@@ -6946,7 +6946,7 @@
         <v>45480</v>
       </c>
       <c r="C7" t="n">
-        <v>290266.67</v>
+        <v>291066.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
@@ -6955,10 +6955,10 @@
         <v>116.53</v>
       </c>
       <c r="F7" t="n">
-        <v>237266.67</v>
+        <v>238066.67</v>
       </c>
       <c r="G7" t="n">
-        <v>521.6900000000001</v>
+        <v>523.45</v>
       </c>
     </row>
     <row r="8">
@@ -6993,22 +6993,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57887.24</v>
+        <v>59885.24</v>
       </c>
       <c r="C9" t="n">
-        <v>1199</v>
+        <v>17999</v>
       </c>
       <c r="D9" t="n">
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>28.05</v>
       </c>
     </row>
   </sheetData>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="C2" t="n">
-        <v>952308.05</v>
+        <v>980466.05</v>
       </c>
       <c r="D2" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>688</v>
+        <v>714</v>
       </c>
       <c r="C3" t="n">
-        <v>310663.4</v>
+        <v>314567.3</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -7086,13 +7086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>136582</v>
+        <v>199001</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -7102,61 +7102,61 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" t="n">
+        <v>102200</v>
+      </c>
+      <c r="D5" t="n">
         <v>27</v>
-      </c>
-      <c r="C5" t="n">
-        <v>100200</v>
-      </c>
-      <c r="D5" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>29045</v>
+        <v>35255.7</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>24636.66</v>
+        <v>29045</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>23179.7</v>
+        <v>23670.66</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>17233</v>
+        <v>17214</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7262,7 +7262,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7271,124 +7271,124 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="D2" t="n">
-        <v>218600</v>
+        <v>390970</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>667</v>
       </c>
       <c r="D3" t="n">
-        <v>67800</v>
+        <v>291998.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>14900</v>
+        <v>43603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>13200</v>
+        <v>28045</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>22455.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>154330</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D8" t="n">
-        <v>85522</v>
+        <v>7960.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -7397,88 +7397,88 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>18.9</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>161</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>72534</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>43299</v>
+        <v>218600</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -7487,52 +7487,52 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>21785</v>
+        <v>130200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5742</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>5405.8</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7541,106 +7541,106 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2509</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>761</v>
+        <v>85250</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>80379</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>24543.5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>21780</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7649,52 +7649,52 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>13200</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9707.66</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>442</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -7703,430 +7703,430 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>295</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>44354</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>79297</v>
+        <v>451</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>25081</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>1757</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>437</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>161</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>57</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
-        <v>77900</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>21500</v>
+        <v>18399.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>57</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>18028</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>63118</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>14839</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D44" t="n">
-        <v>12860</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>598</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>432</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>141</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>76</v>
+        <v>14509</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8135,820 +8135,118 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>58733.4</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>20500</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>9000</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>200</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>35102.9</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>24529</v>
+        <v>29</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>7482</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>28</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>15</v>
-      </c>
-      <c r="D58" t="n">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3</v>
-      </c>
-      <c r="D59" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>价格问题</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
         <v>19</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>15</v>
-      </c>
-      <c r="D62" t="n">
-        <v>44345</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>23</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>9</v>
-      </c>
-      <c r="D65" t="n">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>4</v>
-      </c>
-      <c r="D66" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>6</v>
-      </c>
-      <c r="D68" t="n">
-        <v>33494.67</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="n">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>10</v>
-      </c>
-      <c r="D70" t="n">
-        <v>4691</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>2</v>
-      </c>
-      <c r="D71" t="n">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>4</v>
-      </c>
-      <c r="D72" t="n">
-        <v>18399.98</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>6</v>
-      </c>
-      <c r="D73" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" t="n">
-        <v>15019</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>3</v>
-      </c>
-      <c r="D75" t="n">
-        <v>15009</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>2</v>
-      </c>
-      <c r="D76" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>4</v>
-      </c>
-      <c r="D77" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>3</v>
-      </c>
-      <c r="D78" t="n">
-        <v>14509</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="n">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2</v>
-      </c>
-      <c r="D80" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="n">
-        <v>10621</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="n">
-        <v>6800</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>课程2组</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="n">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>4</v>
-      </c>
-      <c r="D90" t="n">
-        <v>9318</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>1</v>
-      </c>
-      <c r="D92" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2</v>
-      </c>
-      <c r="D94" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8989,10 +8287,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C2" t="n">
-        <v>432631.38</v>
+        <v>482029.38</v>
       </c>
     </row>
     <row r="3">
@@ -9002,10 +8300,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>254866.67</v>
+        <v>255666.67</v>
       </c>
     </row>
     <row r="4">
@@ -9015,36 +8313,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>226769.16</v>
+        <v>228761.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>188273</v>
+        <v>161760</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>161760</v>
+        <v>148273</v>
       </c>
     </row>
     <row r="7">
@@ -9057,7 +8355,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>116000</v>
+        <v>140800</v>
       </c>
     </row>
     <row r="8">
@@ -9067,49 +8365,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>54700</v>
+        <v>74700</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>31200</v>
+        <v>32041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>26400</v>
+        <v>31200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>25441</v>
+        <v>26400</v>
       </c>
     </row>
   </sheetData>
@@ -9150,10 +8448,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C2" t="n">
-        <v>221281.33</v>
+        <v>247213.33</v>
       </c>
     </row>
     <row r="3">
@@ -9163,10 +8461,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C3" t="n">
-        <v>188932</v>
+        <v>197269</v>
       </c>
     </row>
     <row r="4">
@@ -9176,10 +8474,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C4" t="n">
-        <v>169006.4</v>
+        <v>186268.4</v>
       </c>
     </row>
     <row r="5">
@@ -9189,10 +8487,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C5" t="n">
-        <v>147073.98</v>
+        <v>149448.98</v>
       </c>
     </row>
     <row r="6">
@@ -9202,10 +8500,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="n">
-        <v>147008.5</v>
+        <v>107046.5</v>
       </c>
     </row>
     <row r="7">
@@ -9215,127 +8513,127 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>105612</v>
+        <v>100632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>71308</v>
+        <v>89565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>70404</v>
+        <v>77374.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>64999.8</v>
+        <v>71327.89999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="C11" t="n">
-        <v>59527</v>
+        <v>67661</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>50004</v>
+        <v>48829</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="C13" t="n">
-        <v>37219</v>
+        <v>41657</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>34250</v>
+        <v>37219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏回族自治区</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>31794</v>
+        <v>31819.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>29838</v>
+        <v>31786</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,25 +529,25 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>311994</v>
+        <v>559704</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>123625</v>
       </c>
       <c r="F2" t="n">
-        <v>311994</v>
+        <v>436079</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>+57.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+84.9%</t>
+          <t>+158.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -639,25 +639,25 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>447038</v>
+        <v>622556</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>103159</v>
       </c>
       <c r="F4" t="n">
-        <v>447038</v>
+        <v>519397</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>+19.2%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -673,7 +673,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+12.7%</t>
+          <t>+30.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,25 +696,25 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176054</v>
+        <v>234954</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>157581</v>
       </c>
       <c r="F5" t="n">
-        <v>176054</v>
+        <v>77373</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-57.1%</t>
+          <t>-42.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -730,7 +730,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,25 +753,25 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>377840</v>
+        <v>627658</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>44360</v>
       </c>
       <c r="F6" t="n">
-        <v>377840</v>
+        <v>583298</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+32.8%</t>
+          <t>+120.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+76.2%</t>
+          <t>+172.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,25 +810,25 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>276080</v>
+        <v>386796</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>89097</v>
       </c>
       <c r="F7" t="n">
-        <v>276080</v>
+        <v>297699</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -844,7 +844,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+22.9%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,25 +867,25 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>302772</v>
+        <v>418672</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>105733</v>
       </c>
       <c r="F8" t="n">
-        <v>302772</v>
+        <v>312939</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+28.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+16.5%</t>
+          <t>+20.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1110893</v>
+        <v>152331</v>
       </c>
       <c r="E21" t="n">
-        <v>802688</v>
+        <v>179132</v>
       </c>
       <c r="F21" t="n">
-        <v>308205</v>
+        <v>-26802</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>376722</v>
+        <v>-62345</v>
       </c>
       <c r="P21" t="n">
-        <v>-68516</v>
+        <v>35544</v>
       </c>
       <c r="Q21" t="n">
-        <v>266673</v>
+        <v>-26752</v>
       </c>
     </row>
     <row r="22">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1773404</v>
+        <v>2212470</v>
       </c>
       <c r="D2" t="n">
-        <v>120373</v>
+        <v>16313</v>
       </c>
       <c r="E2" t="n">
-        <v>1523753</v>
+        <v>1817178</v>
       </c>
     </row>
     <row r="3">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>310870</v>
+        <v>426735</v>
       </c>
       <c r="D5" t="n">
-        <v>1124</v>
+        <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>301596</v>
+        <v>444691</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>421008</v>
+        <v>505367</v>
       </c>
       <c r="D7" t="n">
-        <v>26030</v>
+        <v>14030</v>
       </c>
       <c r="E7" t="n">
-        <v>390252</v>
+        <v>486213</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>132666</v>
+        <v>72185</v>
       </c>
       <c r="D8" t="n">
-        <v>43388</v>
+        <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>98414</v>
+        <v>-34787</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>370876</v>
+        <v>576334</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>310048</v>
+        <v>472308</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>244581</v>
+        <v>298480</v>
       </c>
       <c r="D10" t="n">
-        <v>31499</v>
+        <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>161866</v>
+        <v>175009</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>291539</v>
+        <v>331506</v>
       </c>
       <c r="D11" t="n">
-        <v>11233</v>
+        <v>-18567</v>
       </c>
       <c r="E11" t="n">
-        <v>259578</v>
+        <v>271745</v>
       </c>
     </row>
     <row r="12">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>376722</v>
+        <v>-62345</v>
       </c>
       <c r="D24" t="n">
-        <v>-68516</v>
+        <v>35544</v>
       </c>
       <c r="E24" t="n">
-        <v>266673</v>
+        <v>-26752</v>
       </c>
     </row>
     <row r="25">
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7262,7 +7262,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7271,82 +7271,82 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>454</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>390970</v>
+        <v>218600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>667</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>291998.3</v>
+        <v>130200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>43603</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>28045</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>班主任</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>22455.66</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -7357,14 +7357,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>13200</v>
+        <v>91646</v>
       </c>
     </row>
     <row r="8">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>631</v>
       </c>
       <c r="D8" t="n">
-        <v>7960.7</v>
+        <v>50589.8</v>
       </c>
     </row>
     <row r="9">
@@ -7393,14 +7393,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>158</v>
       </c>
       <c r="D9" t="n">
-        <v>3610</v>
+        <v>13689</v>
       </c>
     </row>
     <row r="10">
@@ -7411,14 +7411,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>617</v>
+        <v>10735</v>
       </c>
     </row>
     <row r="11">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>190</v>
+        <v>7960.7</v>
       </c>
     </row>
     <row r="12">
@@ -7447,110 +7447,110 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>218600</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>130200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>14900</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>13200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1000</v>
+        <v>85388</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7559,304 +7559,304 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>85250</v>
+        <v>72193</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>23500</v>
+        <v>58829</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>21049.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>75533.39999999999</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>20500</v>
+        <v>8766.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>9000</v>
+        <v>85250</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>398</v>
+        <v>23500</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>200</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>44354</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D28" t="n">
-        <v>9000</v>
+        <v>76814</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>2498</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>451</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>48000</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>398</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7865,70 +7865,70 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D35" t="n">
-        <v>33494.67</v>
+        <v>52303</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>6500</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>4691</v>
+        <v>21766</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>328</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7937,160 +7937,160 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>18399.98</v>
+        <v>62620</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>18000</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>18028</v>
+        <v>11657</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D42" t="n">
-        <v>12000</v>
+        <v>44354</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>318</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D44" t="n">
-        <v>15019</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>15009</v>
+        <v>451</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>15000</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -8099,34 +8099,34 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>14509</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>299</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8135,34 +8135,34 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>9000</v>
+        <v>33494.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
-        <v>6800</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8171,81 +8171,387 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>57</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>9318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>5500</v>
+        <v>24460</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
-        <v>29</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="n">
+        <v>18399.98</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>18028</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15019</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15009</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>14509</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>普陀</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>深圳</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9318</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
         <is>
           <t>协商一致</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C73" t="n">
         <v>1</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D73" t="n">
         <v>19</v>
       </c>
     </row>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>559704</v>
+        <v>619464</v>
       </c>
       <c r="E2" t="n">
         <v>123625</v>
       </c>
       <c r="F2" t="n">
-        <v>436079</v>
+        <v>495839</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>354727</v>
+        <v>421255</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+57.8%</t>
+          <t>+47.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>168693</v>
+        <v>168911</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+158.5%</t>
+          <t>+193.6%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,15 +604,15 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16494</v>
+        <v>16663</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-87.9%</t>
+          <t>-88.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-18935</v>
+        <v>-18804</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>622556</v>
+        <v>632914</v>
       </c>
       <c r="E4" t="n">
         <v>103159</v>
       </c>
       <c r="F4" t="n">
-        <v>519397</v>
+        <v>529755</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>522172</v>
+        <v>673213</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+19.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>396710</v>
+        <v>500313</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+30.9%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>234954</v>
+        <v>241974</v>
       </c>
       <c r="E5" t="n">
         <v>157581</v>
       </c>
       <c r="F5" t="n">
-        <v>77373</v>
+        <v>84393</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>410568</v>
+        <v>473344</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-42.8%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>304373</v>
+        <v>362012</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>627658</v>
+        <v>688414</v>
       </c>
       <c r="E6" t="n">
-        <v>44360</v>
+        <v>46360</v>
       </c>
       <c r="F6" t="n">
-        <v>583298</v>
+        <v>642054</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>284457</v>
+        <v>323684</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+120.7%</t>
+          <t>+112.7%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>214395</v>
+        <v>242038</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+172.1%</t>
+          <t>+165.3%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>386796</v>
+        <v>433554</v>
       </c>
       <c r="E7" t="n">
         <v>89097</v>
       </c>
       <c r="F7" t="n">
-        <v>297699</v>
+        <v>344457</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>288360</v>
+        <v>331395</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+30.8%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>224628</v>
+        <v>224900</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+53.2%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>418672</v>
+        <v>421148</v>
       </c>
       <c r="E8" t="n">
-        <v>105733</v>
+        <v>109433</v>
       </c>
       <c r="F8" t="n">
-        <v>312939</v>
+        <v>311715</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>325321</v>
+        <v>373862</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+28.7%</t>
+          <t>+12.6%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>259933</v>
+        <v>292173</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+20.4%</t>
+          <t>+6.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>910888</v>
+        <v>927928</v>
       </c>
       <c r="E9" t="n">
-        <v>377900</v>
+        <v>388060</v>
       </c>
       <c r="F9" t="n">
-        <v>532988</v>
+        <v>539868</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>763334</v>
+        <v>907033</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+19.3%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>593210</v>
+        <v>687763</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1540234</v>
+        <v>1771164</v>
       </c>
       <c r="E10" t="n">
-        <v>29808</v>
+        <v>47508</v>
       </c>
       <c r="F10" t="n">
-        <v>1510426</v>
+        <v>1723656</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1408891</v>
+        <v>1534620</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+9.3%</t>
+          <t>+15.4%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1408891</v>
+        <v>1534620</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+7.2%</t>
+          <t>+12.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>560593</v>
+        <v>712253</v>
       </c>
       <c r="P10" t="n">
-        <v>949833</v>
+        <v>1011403</v>
       </c>
       <c r="Q10" t="n">
-        <v>1466140</v>
+        <v>1691672</v>
       </c>
     </row>
     <row r="11">
@@ -1042,52 +1042,52 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>239169</v>
+        <v>256386</v>
       </c>
       <c r="E11" t="n">
-        <v>36400</v>
+        <v>37233</v>
       </c>
       <c r="F11" t="n">
-        <v>202769</v>
+        <v>219153</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>258197</v>
+        <v>295709</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>233089</v>
+        <v>249801</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>224</v>
       </c>
       <c r="O11" t="n">
-        <v>51764</v>
+        <v>51348</v>
       </c>
       <c r="P11" t="n">
-        <v>150781</v>
+        <v>167581</v>
       </c>
       <c r="Q11" t="n">
-        <v>87421</v>
+        <v>104240</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>386380</v>
+        <v>410398</v>
       </c>
       <c r="E12" t="n">
-        <v>30076</v>
+        <v>30095</v>
       </c>
       <c r="F12" t="n">
-        <v>356304</v>
+        <v>380303</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>284509</v>
+        <v>325741</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+35.8%</t>
+          <t>+26.0%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>282511</v>
+        <v>323513</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+26.1%</t>
+          <t>+17.6%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>69851</v>
+        <v>65260</v>
       </c>
       <c r="P12" t="n">
-        <v>286453</v>
+        <v>315043</v>
       </c>
       <c r="Q12" t="n">
-        <v>41908</v>
+        <v>41927</v>
       </c>
     </row>
     <row r="13">
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>559255</v>
+        <v>566324</v>
       </c>
       <c r="E13" t="n">
-        <v>45014</v>
+        <v>50514</v>
       </c>
       <c r="F13" t="n">
-        <v>514242</v>
+        <v>515810</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>502164</v>
+        <v>553608</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+11.4%</t>
+          <t>+2.3%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>425655</v>
+        <v>476999</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+20.8%</t>
+          <t>+8.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>31692</v>
+        <v>31727</v>
       </c>
       <c r="O13" t="n">
-        <v>29647</v>
+        <v>30481</v>
       </c>
       <c r="P13" t="n">
-        <v>452902</v>
+        <v>453602</v>
       </c>
       <c r="Q13" t="n">
-        <v>106104</v>
+        <v>106176</v>
       </c>
     </row>
     <row r="14">
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>265863</v>
+        <v>296519</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>250997</v>
+        <v>281653</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>334008</v>
+        <v>370807</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>302630</v>
+        <v>325429</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>20407</v>
+        <v>20646</v>
       </c>
       <c r="O14" t="n">
-        <v>42322</v>
+        <v>52739</v>
       </c>
       <c r="P14" t="n">
-        <v>188268</v>
+        <v>208268</v>
       </c>
       <c r="Q14" t="n">
-        <v>76453</v>
+        <v>76711</v>
       </c>
     </row>
     <row r="15">
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>122055</v>
+        <v>141912</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>106198</v>
+        <v>126055</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>169746</v>
+        <v>193321</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>154440</v>
+        <v>178015</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8081</v>
+        <v>8119</v>
       </c>
       <c r="P15" t="n">
-        <v>98117</v>
+        <v>117936</v>
       </c>
       <c r="Q15" t="n">
-        <v>38028</v>
+        <v>38085</v>
       </c>
     </row>
     <row r="16">
@@ -1353,50 +1353,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>311483</v>
+        <v>320679</v>
       </c>
       <c r="E16" t="n">
-        <v>48398</v>
+        <v>68917</v>
       </c>
       <c r="F16" t="n">
-        <v>263085</v>
+        <v>251762</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>253449</v>
+        <v>312279</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+22.9%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>210449</v>
+        <v>259279</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+25.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>21534</v>
+        <v>12711</v>
       </c>
       <c r="P16" t="n">
-        <v>241551</v>
+        <v>239051</v>
       </c>
       <c r="Q16" t="n">
-        <v>46241</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="17">
@@ -1414,39 +1414,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>534173</v>
+        <v>580567</v>
       </c>
       <c r="E17" t="n">
         <v>105631</v>
       </c>
       <c r="F17" t="n">
-        <v>428542</v>
+        <v>474936</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>381164</v>
+        <v>392442</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+40.1%</t>
+          <t>+47.9%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>322298</v>
+        <v>296776</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+33.0%</t>
+          <t>+60.0%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1456,10 +1456,10 @@
         <v>43538</v>
       </c>
       <c r="P17" t="n">
-        <v>315605</v>
+        <v>361999</v>
       </c>
       <c r="Q17" t="n">
-        <v>87949</v>
+        <v>105549</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>999753</v>
+        <v>1046376</v>
       </c>
       <c r="E18" t="n">
-        <v>108845</v>
+        <v>117874</v>
       </c>
       <c r="F18" t="n">
-        <v>890908</v>
+        <v>928502</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>535187</v>
+        <v>629062</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+86.8%</t>
+          <t>+66.3%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>407181</v>
+        <v>476256</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+118.8%</t>
+          <t>+95.0%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>850</v>
       </c>
       <c r="O18" t="n">
-        <v>228297</v>
+        <v>229083</v>
       </c>
       <c r="P18" t="n">
-        <v>661761</v>
+        <v>698569</v>
       </c>
       <c r="Q18" t="n">
-        <v>536922</v>
+        <v>546720</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>411284</v>
+        <v>493397</v>
       </c>
       <c r="E19" t="n">
         <v>30346</v>
       </c>
       <c r="F19" t="n">
-        <v>380938</v>
+        <v>463051</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>300393</v>
+        <v>343485</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+36.9%</t>
+          <t>+43.6%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>154366</v>
+        <v>190458</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+146.8%</t>
+          <t>+143.1%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>58125</v>
+        <v>60001</v>
       </c>
       <c r="O19" t="n">
-        <v>42416</v>
+        <v>77753</v>
       </c>
       <c r="P19" t="n">
-        <v>280597</v>
+        <v>325497</v>
       </c>
       <c r="Q19" t="n">
-        <v>128782</v>
+        <v>135597</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>401888</v>
+        <v>413231</v>
       </c>
       <c r="E20" t="n">
-        <v>56436</v>
+        <v>99955</v>
       </c>
       <c r="F20" t="n">
-        <v>345452</v>
+        <v>313276</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>451711</v>
+        <v>585390</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>387711</v>
+        <v>502290</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>83059</v>
+        <v>58689</v>
       </c>
       <c r="P20" t="n">
-        <v>262393</v>
+        <v>254587</v>
       </c>
       <c r="Q20" t="n">
-        <v>36504</v>
+        <v>41634</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>152331</v>
+        <v>179277</v>
       </c>
       <c r="E21" t="n">
-        <v>179132</v>
+        <v>182489</v>
       </c>
       <c r="F21" t="n">
-        <v>-26802</v>
+        <v>-3213</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-62345</v>
+        <v>-39050</v>
       </c>
       <c r="P21" t="n">
-        <v>35544</v>
+        <v>35837</v>
       </c>
       <c r="Q21" t="n">
-        <v>-26752</v>
+        <v>-3163</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>9687096</v>
+        <v>10443626</v>
       </c>
       <c r="E22" t="n">
-        <v>1702265</v>
+        <v>1818601</v>
       </c>
       <c r="F22" t="n">
-        <v>7984831</v>
+        <v>8625025</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>7844851</v>
+        <v>9056913</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+23.5%</t>
+          <t>+15.3%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6432227</v>
+        <v>7272743</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+24.1%</t>
+          <t>+18.6%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>180897</v>
+        <v>183047</v>
       </c>
       <c r="O22" t="n">
-        <v>3726579</v>
+        <v>4099054</v>
       </c>
       <c r="P22" t="n">
-        <v>4077757</v>
+        <v>4343325</v>
       </c>
       <c r="Q22" t="n">
-        <v>4712641</v>
+        <v>5180133</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>524.2</v>
+        <v>160.4</v>
       </c>
       <c r="E2" t="n">
-        <v>46865</v>
+        <v>2669</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1055.1</v>
+        <v>8.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3247</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>469</v>
+        <v>754</v>
       </c>
       <c r="C4" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n">
-        <v>978</v>
+        <v>1365.8</v>
       </c>
       <c r="E4" t="n">
-        <v>10706</v>
+        <v>3816</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2212470</v>
+        <v>2393898</v>
       </c>
       <c r="D2" t="n">
         <v>16313</v>
       </c>
       <c r="E2" t="n">
-        <v>1817178</v>
+        <v>1972518</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>395349</v>
+        <v>402229</v>
       </c>
       <c r="D3" t="n">
         <v>137638</v>
       </c>
       <c r="E3" t="n">
-        <v>269761</v>
+        <v>276243</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1181102</v>
+        <v>1341974</v>
       </c>
       <c r="D4" t="n">
-        <v>3888260</v>
+        <v>4153535</v>
       </c>
       <c r="E4" t="n">
-        <v>2652451</v>
+        <v>2934533</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>426735</v>
+        <v>486495</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>444691</v>
+        <v>504451</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>505367</v>
+        <v>515725</v>
       </c>
       <c r="D7" t="n">
         <v>14030</v>
       </c>
       <c r="E7" t="n">
-        <v>486213</v>
+        <v>496173</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>72185</v>
+        <v>79205</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-34787</v>
+        <v>-39767</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>576334</v>
+        <v>635090</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>472308</v>
+        <v>530068</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>298480</v>
+        <v>345238</v>
       </c>
       <c r="D10" t="n">
         <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>175009</v>
+        <v>209869</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>331506</v>
+        <v>330282</v>
       </c>
       <c r="D11" t="n">
         <v>-18567</v>
       </c>
       <c r="E11" t="n">
-        <v>271745</v>
+        <v>269725</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>395350</v>
+        <v>402230</v>
       </c>
       <c r="D12" t="n">
         <v>137638</v>
       </c>
       <c r="E12" t="n">
-        <v>269762</v>
+        <v>276244</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>560593</v>
+        <v>712253</v>
       </c>
       <c r="D13" t="n">
-        <v>949833</v>
+        <v>1011403</v>
       </c>
       <c r="E13" t="n">
-        <v>1466140</v>
+        <v>1691672</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51764</v>
+        <v>51348</v>
       </c>
       <c r="D14" t="n">
-        <v>150781</v>
+        <v>167581</v>
       </c>
       <c r="E14" t="n">
-        <v>87421</v>
+        <v>104240</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>69851</v>
+        <v>65260</v>
       </c>
       <c r="D15" t="n">
-        <v>286453</v>
+        <v>315043</v>
       </c>
       <c r="E15" t="n">
-        <v>41908</v>
+        <v>41927</v>
       </c>
     </row>
     <row r="16">
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29647</v>
+        <v>30481</v>
       </c>
       <c r="D16" t="n">
-        <v>452902</v>
+        <v>453602</v>
       </c>
       <c r="E16" t="n">
-        <v>106104</v>
+        <v>106176</v>
       </c>
     </row>
     <row r="17">
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>42322</v>
+        <v>52739</v>
       </c>
       <c r="D17" t="n">
-        <v>188268</v>
+        <v>208268</v>
       </c>
       <c r="E17" t="n">
-        <v>76453</v>
+        <v>76711</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8081</v>
+        <v>8119</v>
       </c>
       <c r="D18" t="n">
-        <v>98117</v>
+        <v>117936</v>
       </c>
       <c r="E18" t="n">
-        <v>38028</v>
+        <v>38085</v>
       </c>
     </row>
     <row r="19">
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21534</v>
+        <v>12711</v>
       </c>
       <c r="D19" t="n">
-        <v>241551</v>
+        <v>239051</v>
       </c>
       <c r="E19" t="n">
-        <v>46241</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="20">
@@ -2357,10 +2357,10 @@
         <v>43538</v>
       </c>
       <c r="D20" t="n">
-        <v>315605</v>
+        <v>361999</v>
       </c>
       <c r="E20" t="n">
-        <v>87949</v>
+        <v>105549</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>228297</v>
+        <v>229083</v>
       </c>
       <c r="D21" t="n">
-        <v>661761</v>
+        <v>698569</v>
       </c>
       <c r="E21" t="n">
-        <v>536922</v>
+        <v>546720</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42416</v>
+        <v>77753</v>
       </c>
       <c r="D22" t="n">
-        <v>280597</v>
+        <v>325497</v>
       </c>
       <c r="E22" t="n">
-        <v>128782</v>
+        <v>135597</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>83059</v>
+        <v>58689</v>
       </c>
       <c r="D23" t="n">
-        <v>262393</v>
+        <v>254587</v>
       </c>
       <c r="E23" t="n">
-        <v>36504</v>
+        <v>41634</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-62345</v>
+        <v>-39050</v>
       </c>
       <c r="D24" t="n">
-        <v>35544</v>
+        <v>35837</v>
       </c>
       <c r="E24" t="n">
-        <v>-26752</v>
+        <v>-3163</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3726579</v>
+        <v>4099054</v>
       </c>
       <c r="D25" t="n">
-        <v>4077757</v>
+        <v>4343325</v>
       </c>
       <c r="E25" t="n">
-        <v>4712641</v>
+        <v>5180133</v>
       </c>
     </row>
   </sheetData>
@@ -2549,19 +2549,19 @@
         <v>240000</v>
       </c>
       <c r="D2" t="n">
-        <v>230912</v>
+        <v>250832</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>104.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -2569,11 +2569,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>189313.34</v>
+        <v>209233.34</v>
       </c>
     </row>
     <row r="3">
@@ -2591,19 +2591,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>64200</v>
+        <v>69180</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2611,11 +2611,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>44811</v>
+        <v>49791</v>
       </c>
     </row>
     <row r="4">
@@ -2633,19 +2633,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>52036</v>
+        <v>57016</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7476</v>
+        <v>12456</v>
       </c>
     </row>
     <row r="5">
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>96640</v>
+        <v>111580</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>90242.5</v>
+        <v>105182.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,19 +2717,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>78160</v>
+        <v>93100</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>66480</v>
+        <v>81420</v>
       </c>
     </row>
     <row r="7">
@@ -2759,19 +2759,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>104620</v>
+        <v>106300</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>85490</v>
+        <v>87170</v>
       </c>
     </row>
     <row r="8">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>53125</v>
+        <v>56825</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>33075</v>
+        <v>29375</v>
       </c>
     </row>
     <row r="9">
@@ -2885,19 +2885,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>91956</v>
+        <v>92752</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>83997</v>
+        <v>84793</v>
       </c>
     </row>
     <row r="11">
@@ -3023,19 +3023,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>186.4%</t>
+          <t>214.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>33800</v>
+        <v>10980</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>149138</v>
+        <v>171958</v>
       </c>
     </row>
     <row r="14">
@@ -3053,31 +3053,31 @@
         <v>96000</v>
       </c>
       <c r="D14" t="n">
-        <v>83700</v>
+        <v>84200</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-50.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>124200</v>
+        <v>132380</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>148.4%</t>
+          <t>157.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-40500</v>
+        <v>-48180</v>
       </c>
     </row>
     <row r="15">
@@ -3137,19 +3137,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>122834</v>
+        <v>123572</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>128.7%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3157,11 +3157,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>79834</v>
+        <v>80572</v>
       </c>
     </row>
     <row r="17">
@@ -3221,19 +3221,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>98196</v>
+        <v>107398</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>111.6%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>77996</v>
+        <v>87198</v>
       </c>
     </row>
     <row r="19">
@@ -3263,19 +3263,19 @@
         <v>88000</v>
       </c>
       <c r="D19" t="n">
-        <v>67720</v>
+        <v>74320</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -3283,11 +3283,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16920</v>
+        <v>23520</v>
       </c>
     </row>
     <row r="20">
@@ -3359,19 +3359,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>13200</v>
+        <v>38000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>32000</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="22">
@@ -3557,19 +3557,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>181936</v>
+        <v>186916</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>102.0%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>163190</v>
+        <v>168170</v>
       </c>
     </row>
     <row r="27">
@@ -3641,19 +3641,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>56760</v>
+        <v>57158</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3661,11 +3661,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>38160</v>
+        <v>38558</v>
       </c>
     </row>
     <row r="29">
@@ -3683,19 +3683,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>83318</v>
+        <v>88298</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>66195</v>
+        <v>71175</v>
       </c>
     </row>
     <row r="30">
@@ -3767,19 +3767,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>218554</v>
+        <v>238514</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>149.1%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>102.6%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3787,11 +3787,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>164214</v>
+        <v>184174</v>
       </c>
     </row>
     <row r="32">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>83138</v>
+        <v>89618</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>58358</v>
+        <v>64838</v>
       </c>
     </row>
     <row r="34">
@@ -3893,31 +3893,31 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>87939</v>
+        <v>97899</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>81.6%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>80439</v>
+        <v>88399</v>
       </c>
     </row>
     <row r="35">
@@ -3977,19 +3977,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>105958</v>
+        <v>126874</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>97998</v>
+        <v>118914</v>
       </c>
     </row>
     <row r="37">
@@ -4019,19 +4019,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>100936</v>
+        <v>130816</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4039,11 +4039,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>92976</v>
+        <v>122856</v>
       </c>
     </row>
     <row r="38">
@@ -4061,19 +4061,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>125860</v>
+        <v>137860</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>30352</v>
+        <v>42352</v>
       </c>
     </row>
     <row r="39">
@@ -4103,19 +4103,19 @@
         <v>240000</v>
       </c>
       <c r="D39" t="n">
-        <v>96908</v>
+        <v>91928</v>
       </c>
       <c r="E39" t="n">
         <v>173964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4123,11 +4123,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>42835</v>
+        <v>37855</v>
       </c>
     </row>
     <row r="40">
@@ -4187,19 +4187,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>63740</v>
+        <v>84058</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4207,11 +4207,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>53763</v>
+        <v>74081</v>
       </c>
     </row>
   </sheetData>
@@ -4319,23 +4319,23 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>67944.10000000001</v>
+        <v>71044.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67944.10000000001</v>
+        <v>65544.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -4353,11 +4353,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>75267.8</v>
+        <v>78800.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>75267.8</v>
+        <v>78800.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4455,11 +4455,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19590</v>
+        <v>19988</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19590</v>
+        <v>19988</v>
       </c>
     </row>
     <row r="8">
@@ -4489,11 +4489,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>30586.39</v>
+        <v>45937.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>30586.39</v>
+        <v>45937.21</v>
       </c>
     </row>
     <row r="9">
@@ -4523,11 +4523,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>65864.13</v>
+        <v>66076.69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65664.13</v>
+        <v>65876.69</v>
       </c>
     </row>
     <row r="10">
@@ -4557,11 +4557,11 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>144740.48</v>
+        <v>161172.17</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>144.7%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>144740.48</v>
+        <v>161172.17</v>
       </c>
     </row>
     <row r="11">
@@ -4625,11 +4625,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>137305.7</v>
+        <v>171205.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>137305.7</v>
+        <v>171205.7</v>
       </c>
     </row>
     <row r="13">
@@ -4659,23 +4659,23 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>15599.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>15599.23</v>
       </c>
     </row>
     <row r="14">
@@ -4697,19 +4697,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>10000</v>
+        <v>21500</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>96770</v>
+        <v>85270</v>
       </c>
     </row>
     <row r="15">
@@ -4727,11 +4727,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>85954</v>
+        <v>93954</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>56756</v>
+        <v>64756</v>
       </c>
     </row>
     <row r="16">
@@ -4765,19 +4765,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9200</v>
+        <v>18200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>89756</v>
+        <v>80756</v>
       </c>
     </row>
     <row r="17">
@@ -4795,11 +4795,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>19584</v>
+        <v>20780</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>19584</v>
+        <v>20780</v>
       </c>
     </row>
     <row r="18">
@@ -4829,11 +4829,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>48954</v>
+        <v>78954</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48954</v>
+        <v>78954</v>
       </c>
     </row>
     <row r="19">
@@ -4863,11 +4863,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>125713.5</v>
+        <v>126350.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>120713.5</v>
+        <v>121350.1</v>
       </c>
     </row>
     <row r="20">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77242</v>
+        <v>77640</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>67442</v>
+        <v>67840</v>
       </c>
     </row>
     <row r="26">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>44428</v>
+        <v>55204</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>110.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>44428</v>
+        <v>55204</v>
       </c>
     </row>
     <row r="28">
@@ -5203,11 +5203,11 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>112168</v>
+        <v>128968</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5215,11 +5215,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>105168</v>
+        <v>121968</v>
       </c>
     </row>
     <row r="30">
@@ -5373,11 +5373,11 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>164863.13</v>
+        <v>165461.13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -5385,11 +5385,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125029.73</v>
+        <v>125627.73</v>
       </c>
     </row>
     <row r="35">
@@ -5407,11 +5407,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>91642.92</v>
+        <v>104240.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5419,11 +5419,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>85042.92</v>
+        <v>97640.92</v>
       </c>
     </row>
     <row r="36">
@@ -5441,11 +5441,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>82778</v>
+        <v>105378</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5453,11 +5453,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>76180</v>
+        <v>98780</v>
       </c>
     </row>
     <row r="37">
@@ -5475,11 +5475,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>11592</v>
+        <v>12190</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>11592</v>
+        <v>12190</v>
       </c>
     </row>
     <row r="38">
@@ -5509,11 +5509,11 @@
         <v>30000</v>
       </c>
       <c r="D38" t="n">
-        <v>21295</v>
+        <v>31295</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>104.3%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>21295</v>
+        <v>31295</v>
       </c>
     </row>
     <row r="39">
@@ -5543,11 +5543,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>85470</v>
+        <v>85770</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>85470</v>
+        <v>85770</v>
       </c>
     </row>
     <row r="40">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>565476</v>
+        <v>590852</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>486826</v>
+        <v>512202</v>
       </c>
     </row>
     <row r="41">
@@ -5679,23 +5679,23 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>106549</v>
+        <v>126947</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>103.8%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>97549</v>
+        <v>108947</v>
       </c>
     </row>
     <row r="44">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>149519.64</v>
+        <v>199049.64</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>149519.64</v>
+        <v>199049.64</v>
       </c>
     </row>
     <row r="46">
@@ -5781,11 +5781,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>44181</v>
+        <v>44977</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>44181</v>
+        <v>44977</v>
       </c>
     </row>
     <row r="47">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>188544</v>
+        <v>222393</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>188544</v>
+        <v>222393</v>
       </c>
     </row>
     <row r="48">
@@ -5849,11 +5849,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>118397</v>
+        <v>145798.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>118397</v>
+        <v>145798.4</v>
       </c>
     </row>
     <row r="49">
@@ -5883,11 +5883,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>241661.04</v>
+        <v>274837.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>241661.04</v>
+        <v>274837.04</v>
       </c>
     </row>
     <row r="50">
@@ -5917,11 +5917,11 @@
         <v>80000</v>
       </c>
       <c r="D50" t="n">
-        <v>4469</v>
+        <v>8399</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4469</v>
+        <v>8399</v>
       </c>
     </row>
     <row r="51">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>337792.15</v>
+        <v>363630.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>337792.15</v>
+        <v>363630.97</v>
       </c>
     </row>
     <row r="53">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>149610.3</v>
+        <v>208911.3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>149610.3</v>
+        <v>208911.3</v>
       </c>
     </row>
     <row r="54">
@@ -6053,11 +6053,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>235826</v>
+        <v>266418</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>235826</v>
+        <v>266418</v>
       </c>
     </row>
     <row r="55">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>117789</v>
+        <v>139381</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>129.4%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6099,11 +6099,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>107789</v>
+        <v>129381</v>
       </c>
     </row>
     <row r="56">
@@ -6121,11 +6121,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41194</v>
+        <v>41990</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6133,11 +6133,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36194</v>
+        <v>36990</v>
       </c>
     </row>
     <row r="57">
@@ -6189,11 +6189,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>22078</v>
+        <v>22476</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -6201,11 +6201,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>15078</v>
+        <v>15476</v>
       </c>
     </row>
     <row r="59">
@@ -6223,11 +6223,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>122806</v>
+        <v>124000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>191.3%</t>
+          <t>193.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>114806</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="60">
@@ -6291,11 +6291,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>37766</v>
+        <v>57566</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>37766</v>
+        <v>57566</v>
       </c>
     </row>
     <row r="62">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>945493.9399999999</v>
+        <v>1152601.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2918</v>
+        <v>3508</v>
       </c>
       <c r="E2" t="n">
-        <v>92429</v>
+        <v>99369</v>
       </c>
       <c r="F2" t="n">
-        <v>853064.9399999999</v>
+        <v>1053232.5</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>859547</v>
+        <v>1046047</v>
       </c>
       <c r="D3" t="n">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
-        <v>92400</v>
+        <v>99340</v>
       </c>
       <c r="F3" t="n">
-        <v>767147</v>
+        <v>946707</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85946.94</v>
+        <v>106554.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2756</v>
+        <v>3308</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>85917.94</v>
+        <v>106525.5</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1229826</v>
+        <v>1499560</v>
       </c>
       <c r="D5" t="n">
-        <v>272</v>
+        <v>338</v>
       </c>
       <c r="E5" t="n">
-        <v>85812</v>
+        <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1144014</v>
+        <v>1413350</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>907204</v>
+        <v>1099480</v>
       </c>
       <c r="D6" t="n">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>884606</v>
+        <v>1076882</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>302622</v>
+        <v>380080</v>
       </c>
       <c r="D7" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E7" t="n">
-        <v>63214</v>
+        <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>239408</v>
+        <v>316468</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1574530.64</v>
+        <v>1841363.51</v>
       </c>
       <c r="D8" t="n">
-        <v>2160</v>
+        <v>2367</v>
       </c>
       <c r="E8" t="n">
-        <v>8284.469999999999</v>
+        <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1566246.17</v>
+        <v>1832579.04</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>979701.9399999999</v>
+        <v>1083856.96</v>
       </c>
       <c r="D9" t="n">
-        <v>947</v>
+        <v>1022</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>977901.9399999999</v>
+        <v>1082056.96</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>594828.7</v>
+        <v>757506.55</v>
       </c>
       <c r="D10" t="n">
-        <v>1213</v>
+        <v>1345</v>
       </c>
       <c r="E10" t="n">
-        <v>6484.47</v>
+        <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>588344.23</v>
+        <v>750522.08</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>523600</v>
+        <v>529608.4</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
-        <v>120000</v>
+        <v>129202</v>
       </c>
       <c r="F11" t="n">
-        <v>403600</v>
+        <v>400406.4</v>
       </c>
     </row>
     <row r="12">
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
     </row>
     <row r="15">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>945493.9399999999</v>
+        <v>1152601.5</v>
       </c>
       <c r="C2" t="n">
-        <v>486680.76</v>
+        <v>495823.76</v>
       </c>
       <c r="D2" t="n">
-        <v>83539</v>
+        <v>86522</v>
       </c>
       <c r="E2" t="n">
-        <v>8.84</v>
+        <v>7.51</v>
       </c>
       <c r="F2" t="n">
-        <v>403141.76</v>
+        <v>409301.76</v>
       </c>
       <c r="G2" t="n">
-        <v>42.64</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1229826</v>
+        <v>1499560</v>
       </c>
       <c r="C3" t="n">
-        <v>579999.38</v>
+        <v>677032.75</v>
       </c>
       <c r="D3" t="n">
         <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="F3" t="n">
-        <v>572399.38</v>
+        <v>669432.75</v>
       </c>
       <c r="G3" t="n">
-        <v>46.54</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="4">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1574530.64</v>
+        <v>1841363.51</v>
       </c>
       <c r="C4" t="n">
         <v>28799</v>
@@ -6883,7 +6883,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>523600</v>
+        <v>529608.4</v>
       </c>
       <c r="C5" t="n">
         <v>140800</v>
@@ -6908,7 +6908,7 @@
         <v>140800</v>
       </c>
       <c r="G5" t="n">
-        <v>26.89</v>
+        <v>26.59</v>
       </c>
     </row>
     <row r="6">
@@ -6946,7 +6946,7 @@
         <v>45480</v>
       </c>
       <c r="C7" t="n">
-        <v>291066.67</v>
+        <v>299246.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
@@ -6955,10 +6955,10 @@
         <v>116.53</v>
       </c>
       <c r="F7" t="n">
-        <v>238066.67</v>
+        <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>523.45</v>
+        <v>541.4400000000001</v>
       </c>
     </row>
     <row r="8">
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5940</v>
+        <v>8318</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="9">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59885.24</v>
+        <v>64354.24</v>
       </c>
       <c r="C9" t="n">
         <v>17999</v>
@@ -7002,13 +7002,13 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>28.05</v>
+        <v>26.11</v>
       </c>
     </row>
   </sheetData>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="C2" t="n">
-        <v>980466.05</v>
+        <v>1055652.42</v>
       </c>
       <c r="D2" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>714</v>
+        <v>769</v>
       </c>
       <c r="C3" t="n">
-        <v>314567.3</v>
+        <v>322121.3</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C5" t="n">
-        <v>102200</v>
+        <v>123400</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -7118,45 +7118,45 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C6" t="n">
-        <v>35255.7</v>
+        <v>36677.7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>29045</v>
+        <v>34549.66</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>23670.66</v>
+        <v>29064</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>17214</v>
+        <v>17271</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7214,10 +7214,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>218600</v>
+        <v>228760</v>
       </c>
     </row>
     <row r="3">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="D7" t="n">
-        <v>91646</v>
+        <v>91839</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>631</v>
+        <v>682</v>
       </c>
       <c r="D8" t="n">
-        <v>50589.8</v>
+        <v>52405.8</v>
       </c>
     </row>
     <row r="9">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D9" t="n">
-        <v>13689</v>
+        <v>13549</v>
       </c>
     </row>
     <row r="10">
@@ -7415,10 +7415,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>10735</v>
+        <v>10754</v>
       </c>
     </row>
     <row r="11">
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>7960.7</v>
+        <v>9353.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>3610</v>
+        <v>3667</v>
       </c>
     </row>
     <row r="13">
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -7685,10 +7685,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>23500</v>
+        <v>32500</v>
       </c>
     </row>
     <row r="26">
@@ -7730,19 +7730,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>76814</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -7753,20 +7753,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>28919</v>
+        <v>80514</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7778,7 +7778,7 @@
         <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>75533.39999999999</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="31">
@@ -7789,14 +7789,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>20500</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="32">
@@ -7807,14 +7807,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>9000</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="33">
@@ -7825,14 +7825,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>398</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="34">
@@ -7843,32 +7843,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>200</v>
+        <v>398</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>52303</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36">
@@ -7879,14 +7879,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>26600</v>
+        <v>52303</v>
       </c>
     </row>
     <row r="37">
@@ -7897,14 +7897,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>21766</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="38">
@@ -7915,68 +7915,68 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>2490</v>
+        <v>21766</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>62620</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D40" t="n">
-        <v>14820</v>
+        <v>87854</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>11657</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="42">
@@ -7987,14 +7987,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D42" t="n">
-        <v>44354</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="43">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>9000</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44">
@@ -8023,14 +8023,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>2498</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
@@ -8041,68 +8041,68 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>451</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>76</v>
+        <v>62620</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>48000</v>
+        <v>11657</v>
       </c>
     </row>
     <row r="49">
@@ -8113,50 +8113,50 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>398</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>33494.67</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>6500</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
@@ -8167,14 +8167,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>4691</v>
+        <v>38994.67</v>
       </c>
     </row>
     <row r="53">
@@ -8185,92 +8185,92 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>328</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D54" t="n">
-        <v>24460</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>19900</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D56" t="n">
-        <v>18399.98</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>18000</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8279,34 +8279,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>18028</v>
+        <v>9009</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" t="n">
-        <v>12000</v>
+        <v>24460</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8315,124 +8315,124 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D60" t="n">
-        <v>318</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
-        <v>15019</v>
+        <v>19233.35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D62" t="n">
-        <v>15009</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>48</v>
+        <v>18028</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>14509</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>299</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8441,52 +8441,52 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>9000</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>6800</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8495,46 +8495,46 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>9318</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>5500</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73">
@@ -8545,13 +8545,67 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="n">
+        <v>9318</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>咨询结案/好转</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>协商一致</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C76" t="n">
         <v>1</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D76" t="n">
         <v>19</v>
       </c>
     </row>
@@ -8593,10 +8647,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>482029.38</v>
+        <v>570062.75</v>
       </c>
     </row>
     <row r="3">
@@ -8619,10 +8673,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>228761.16</v>
+        <v>232461.16</v>
       </c>
     </row>
     <row r="5">
@@ -8671,36 +8725,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>74700</v>
+        <v>83700</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>32041</v>
+        <v>39380</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>31200</v>
+        <v>32041</v>
       </c>
     </row>
     <row r="11">
@@ -8754,10 +8808,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>247213.33</v>
+        <v>254651.33</v>
       </c>
     </row>
     <row r="3">
@@ -8767,10 +8821,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C3" t="n">
-        <v>197269</v>
+        <v>241585</v>
       </c>
     </row>
     <row r="4">
@@ -8780,10 +8834,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C4" t="n">
-        <v>186268.4</v>
+        <v>188699.4</v>
       </c>
     </row>
     <row r="5">
@@ -8793,10 +8847,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C5" t="n">
-        <v>149448.98</v>
+        <v>164404.98</v>
       </c>
     </row>
     <row r="6">
@@ -8806,36 +8860,36 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>107046.5</v>
+        <v>130736.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>100632</v>
+        <v>110147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>89565</v>
+        <v>102632</v>
       </c>
     </row>
     <row r="9">
@@ -8845,10 +8899,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>77374.8</v>
+        <v>73045.8</v>
       </c>
     </row>
     <row r="10">
@@ -8858,10 +8912,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>71327.89999999999</v>
+        <v>70748.89999999999</v>
       </c>
     </row>
     <row r="11">
@@ -8871,10 +8925,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C11" t="n">
-        <v>67661</v>
+        <v>68001</v>
       </c>
     </row>
     <row r="12">
@@ -8884,10 +8938,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>48829</v>
+        <v>49427</v>
       </c>
     </row>
     <row r="13">
@@ -8897,10 +8951,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C13" t="n">
-        <v>41657</v>
+        <v>41819</v>
       </c>
     </row>
     <row r="14">
@@ -8919,27 +8973,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>31819.9</v>
+        <v>33538</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>宁夏回族自治区</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>31786</v>
+        <v>31819.9</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -756,22 +756,22 @@
         <v>688414</v>
       </c>
       <c r="E6" t="n">
-        <v>46360</v>
+        <v>54490</v>
       </c>
       <c r="F6" t="n">
-        <v>642054</v>
+        <v>633924</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+165.3%</t>
+          <t>+161.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         <v>179277</v>
       </c>
       <c r="E21" t="n">
-        <v>182489</v>
+        <v>174360</v>
       </c>
       <c r="F21" t="n">
-        <v>-3213</v>
+        <v>4917</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-39050</v>
+        <v>-30920</v>
       </c>
       <c r="P21" t="n">
         <v>35837</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3163</v>
+        <v>4967</v>
       </c>
     </row>
     <row r="22">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2393898</v>
+        <v>2385768</v>
       </c>
       <c r="D2" t="n">
         <v>16313</v>
       </c>
       <c r="E2" t="n">
-        <v>1972518</v>
+        <v>1964388</v>
       </c>
     </row>
     <row r="3">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>635090</v>
+        <v>626960</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>530068</v>
+        <v>521938</v>
       </c>
     </row>
     <row r="10">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-39050</v>
+        <v>-30920</v>
       </c>
       <c r="D24" t="n">
         <v>35837</v>
       </c>
       <c r="E24" t="n">
-        <v>-3163</v>
+        <v>4967</v>
       </c>
     </row>
     <row r="25">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D7" t="n">
-        <v>91839</v>
+        <v>87859</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D8" t="n">
-        <v>52405.8</v>
+        <v>48255.8</v>
       </c>
     </row>
     <row r="9">
@@ -8162,7 +8162,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8171,28 +8171,28 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="n">
-        <v>38994.67</v>
+        <v>28440</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D53" t="n">
-        <v>6500</v>
+        <v>26050</v>
       </c>
     </row>
     <row r="54">
@@ -8203,14 +8203,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>4691</v>
+        <v>38994.67</v>
       </c>
     </row>
     <row r="55">
@@ -8221,50 +8221,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>328</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D56" t="n">
-        <v>27200</v>
+        <v>4691</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>11299</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58">
@@ -8275,50 +8275,50 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>9009</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>24460</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>21900</v>
+        <v>9009</v>
       </c>
     </row>
     <row r="61">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>619464</v>
+        <v>619862</v>
       </c>
       <c r="E2" t="n">
         <v>123625</v>
       </c>
       <c r="F2" t="n">
-        <v>495839</v>
+        <v>496237</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>421255</v>
+        <v>472619</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+47.1%</t>
+          <t>+31.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>168911</v>
+        <v>220057</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+193.6%</t>
+          <t>+125.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16663</v>
+        <v>16971</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>-88.2%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-18804</v>
+        <v>-18496</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-110.6%</t>
+          <t>-110.8%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>632914</v>
+        <v>639574</v>
       </c>
       <c r="E4" t="n">
         <v>103159</v>
       </c>
       <c r="F4" t="n">
-        <v>529755</v>
+        <v>536415</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>673213</v>
+        <v>691030</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>500313</v>
+        <v>515187</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+4.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>241974</v>
+        <v>243954</v>
       </c>
       <c r="E5" t="n">
         <v>157581</v>
       </c>
       <c r="F5" t="n">
-        <v>84393</v>
+        <v>86373</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>473344</v>
+        <v>479237</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>362012</v>
+        <v>351850</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>688414</v>
+        <v>695014</v>
       </c>
       <c r="E6" t="n">
         <v>54490</v>
       </c>
       <c r="F6" t="n">
-        <v>633924</v>
+        <v>640524</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>115.1%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>323684</v>
+        <v>396939</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+112.7%</t>
+          <t>+75.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>242038</v>
+        <v>291321</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+161.9%</t>
+          <t>+119.9%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>433554</v>
+        <v>438534</v>
       </c>
       <c r="E7" t="n">
         <v>89097</v>
       </c>
       <c r="F7" t="n">
-        <v>344457</v>
+        <v>349437</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>331395</v>
+        <v>352268</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+30.8%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>224900</v>
+        <v>244660</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+53.2%</t>
+          <t>+42.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>373862</v>
+        <v>376124</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+12.6%</t>
+          <t>+12.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>292173</v>
+        <v>294350</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+6.7%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>927928</v>
+        <v>934528</v>
       </c>
       <c r="E9" t="n">
         <v>388060</v>
       </c>
       <c r="F9" t="n">
-        <v>539868</v>
+        <v>546468</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>907033</v>
+        <v>949013</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>687763</v>
+        <v>712745</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1771164</v>
+        <v>1890334</v>
       </c>
       <c r="E10" t="n">
         <v>47508</v>
       </c>
       <c r="F10" t="n">
-        <v>1723656</v>
+        <v>1842826</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1534620</v>
+        <v>1576179</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+15.4%</t>
+          <t>+19.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1534620</v>
+        <v>1576179</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+12.3%</t>
+          <t>+16.9%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>712253</v>
+        <v>775873</v>
       </c>
       <c r="P10" t="n">
-        <v>1011403</v>
+        <v>1066952</v>
       </c>
       <c r="Q10" t="n">
-        <v>1691672</v>
+        <v>1810842</v>
       </c>
     </row>
     <row r="11">
@@ -1042,13 +1042,13 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256386</v>
+        <v>256605</v>
       </c>
       <c r="E11" t="n">
         <v>37233</v>
       </c>
       <c r="F11" t="n">
-        <v>219153</v>
+        <v>219372</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1062,32 +1062,32 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>295709</v>
+        <v>297145</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>249801</v>
+        <v>251218</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>224</v>
       </c>
       <c r="O11" t="n">
-        <v>51348</v>
+        <v>51367</v>
       </c>
       <c r="P11" t="n">
-        <v>167581</v>
+        <v>167781</v>
       </c>
       <c r="Q11" t="n">
-        <v>104240</v>
+        <v>104459</v>
       </c>
     </row>
     <row r="12">
@@ -1105,47 +1105,47 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>410398</v>
+        <v>431592</v>
       </c>
       <c r="E12" t="n">
         <v>30095</v>
       </c>
       <c r="F12" t="n">
-        <v>380303</v>
+        <v>401497</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>325741</v>
+        <v>357440</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+20.7%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>323513</v>
+        <v>355212</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+17.6%</t>
+          <t>+13.0%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>65260</v>
+        <v>65658</v>
       </c>
       <c r="P12" t="n">
-        <v>315043</v>
+        <v>335839</v>
       </c>
       <c r="Q12" t="n">
         <v>41927</v>
@@ -1166,39 +1166,39 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>566324</v>
+        <v>596939</v>
       </c>
       <c r="E13" t="n">
-        <v>50514</v>
+        <v>50533</v>
       </c>
       <c r="F13" t="n">
-        <v>515810</v>
+        <v>546406</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>553608</v>
+        <v>565894</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+2.3%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>476999</v>
+        <v>489285</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+8.1%</t>
+          <t>+11.7%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1208,7 +1208,7 @@
         <v>30481</v>
       </c>
       <c r="P13" t="n">
-        <v>453602</v>
+        <v>484198</v>
       </c>
       <c r="Q13" t="n">
         <v>106176</v>
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>296519</v>
+        <v>312841</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>281653</v>
+        <v>297975</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>370807</v>
+        <v>370826</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>325429</v>
+        <v>325448</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>20646</v>
+        <v>26968</v>
       </c>
       <c r="O14" t="n">
         <v>52739</v>
       </c>
       <c r="P14" t="n">
-        <v>208268</v>
+        <v>218268</v>
       </c>
       <c r="Q14" t="n">
-        <v>76711</v>
+        <v>83033</v>
       </c>
     </row>
     <row r="15">
@@ -1292,44 +1292,44 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>141912</v>
+        <v>142310</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>126055</v>
+        <v>126453</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>193321</v>
+        <v>193738</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>178015</v>
+        <v>178432</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8119</v>
+        <v>8517</v>
       </c>
       <c r="P15" t="n">
         <v>117936</v>
@@ -1353,50 +1353,50 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>320679</v>
+        <v>323355</v>
       </c>
       <c r="E16" t="n">
         <v>68917</v>
       </c>
       <c r="F16" t="n">
-        <v>251762</v>
+        <v>254438</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>312279</v>
+        <v>322279</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+2.7%</t>
+          <t>+0.3%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>259279</v>
+        <v>269279</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12711</v>
+        <v>5109</v>
       </c>
       <c r="P16" t="n">
-        <v>239051</v>
+        <v>249329</v>
       </c>
       <c r="Q16" t="n">
-        <v>46222</v>
+        <v>47902</v>
       </c>
     </row>
     <row r="17">
@@ -1434,19 +1434,19 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>392442</v>
+        <v>427840</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+47.9%</t>
+          <t>+35.7%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>296776</v>
+        <v>331174</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+60.0%</t>
+          <t>+43.4%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1046376</v>
+        <v>1067537</v>
       </c>
       <c r="E18" t="n">
         <v>117874</v>
       </c>
       <c r="F18" t="n">
-        <v>928502</v>
+        <v>949663</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>629062</v>
+        <v>637896</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+66.3%</t>
+          <t>+67.4%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>476256</v>
+        <v>485090</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+95.0%</t>
+          <t>+95.8%</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>850</v>
+        <v>7250</v>
       </c>
       <c r="O18" t="n">
-        <v>229083</v>
+        <v>230864</v>
       </c>
       <c r="P18" t="n">
-        <v>698569</v>
+        <v>711549</v>
       </c>
       <c r="Q18" t="n">
-        <v>546720</v>
+        <v>556881</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>493397</v>
+        <v>510448</v>
       </c>
       <c r="E19" t="n">
         <v>30346</v>
       </c>
       <c r="F19" t="n">
-        <v>463051</v>
+        <v>480102</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>343485</v>
+        <v>373985</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+43.6%</t>
+          <t>+36.5%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>190458</v>
+        <v>220958</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+143.1%</t>
+          <t>+117.3%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>60001</v>
+        <v>61252</v>
       </c>
       <c r="O19" t="n">
-        <v>77753</v>
+        <v>85253</v>
       </c>
       <c r="P19" t="n">
-        <v>325497</v>
+        <v>333797</v>
       </c>
       <c r="Q19" t="n">
-        <v>135597</v>
+        <v>136848</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>413231</v>
+        <v>450257</v>
       </c>
       <c r="E20" t="n">
         <v>99955</v>
       </c>
       <c r="F20" t="n">
-        <v>313276</v>
+        <v>350302</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>585390</v>
+        <v>623332</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>502290</v>
+        <v>540232</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>58689</v>
+        <v>65317</v>
       </c>
       <c r="P20" t="n">
-        <v>254587</v>
+        <v>284985</v>
       </c>
       <c r="Q20" t="n">
-        <v>41634</v>
+        <v>48262</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>179277</v>
+        <v>182908</v>
       </c>
       <c r="E21" t="n">
-        <v>174360</v>
+        <v>177578</v>
       </c>
       <c r="F21" t="n">
-        <v>4917</v>
+        <v>5329</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-30920</v>
+        <v>-30508</v>
       </c>
       <c r="P21" t="n">
         <v>35837</v>
       </c>
       <c r="Q21" t="n">
-        <v>4967</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>10443626</v>
+        <v>10740306</v>
       </c>
       <c r="E22" t="n">
-        <v>1818601</v>
+        <v>1821839</v>
       </c>
       <c r="F22" t="n">
-        <v>8625025</v>
+        <v>8918467</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9056913</v>
+        <v>9480755</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+15.3%</t>
+          <t>+13.3%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7272743</v>
+        <v>7634182</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+18.6%</t>
+          <t>+16.8%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>183047</v>
+        <v>197020</v>
       </c>
       <c r="O22" t="n">
-        <v>4099054</v>
+        <v>4197746</v>
       </c>
       <c r="P22" t="n">
-        <v>4343325</v>
+        <v>4524102</v>
       </c>
       <c r="Q22" t="n">
-        <v>5180133</v>
+        <v>5352796</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>160.4</v>
+        <v>204.3</v>
       </c>
       <c r="E2" t="n">
-        <v>2669</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="3">
@@ -1829,13 +1829,13 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>754</v>
+        <v>659</v>
       </c>
       <c r="C4" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D4" t="n">
-        <v>1365.8</v>
+        <v>979</v>
       </c>
       <c r="E4" t="n">
-        <v>3816</v>
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2385768</v>
+        <v>2404706</v>
       </c>
       <c r="D2" t="n">
-        <v>16313</v>
+        <v>17993</v>
       </c>
       <c r="E2" t="n">
-        <v>1964388</v>
+        <v>1984608</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>402229</v>
+        <v>408829</v>
       </c>
       <c r="D3" t="n">
         <v>137638</v>
       </c>
       <c r="E3" t="n">
-        <v>276243</v>
+        <v>282843</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1341974</v>
+        <v>1414716</v>
       </c>
       <c r="D4" t="n">
-        <v>4153535</v>
+        <v>4332633</v>
       </c>
       <c r="E4" t="n">
-        <v>2934533</v>
+        <v>3079963</v>
       </c>
     </row>
     <row r="5">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>486495</v>
+        <v>486893</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>515725</v>
+        <v>520705</v>
       </c>
       <c r="D7" t="n">
-        <v>14030</v>
+        <v>15710</v>
       </c>
       <c r="E7" t="n">
-        <v>496173</v>
+        <v>502833</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>79205</v>
+        <v>81185</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-39767</v>
+        <v>-37787</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>626960</v>
+        <v>633560</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>521938</v>
+        <v>528538</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>345238</v>
+        <v>350218</v>
       </c>
       <c r="D10" t="n">
         <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>209869</v>
+        <v>214849</v>
       </c>
     </row>
     <row r="11">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>402230</v>
+        <v>408830</v>
       </c>
       <c r="D12" t="n">
         <v>137638</v>
       </c>
       <c r="E12" t="n">
-        <v>276244</v>
+        <v>282844</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>712253</v>
+        <v>775873</v>
       </c>
       <c r="D13" t="n">
-        <v>1011403</v>
+        <v>1066952</v>
       </c>
       <c r="E13" t="n">
-        <v>1691672</v>
+        <v>1810842</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51348</v>
+        <v>51367</v>
       </c>
       <c r="D14" t="n">
-        <v>167581</v>
+        <v>167781</v>
       </c>
       <c r="E14" t="n">
-        <v>104240</v>
+        <v>104459</v>
       </c>
     </row>
     <row r="15">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65260</v>
+        <v>65658</v>
       </c>
       <c r="D15" t="n">
-        <v>315043</v>
+        <v>335839</v>
       </c>
       <c r="E15" t="n">
         <v>41927</v>
@@ -2273,7 +2273,7 @@
         <v>30481</v>
       </c>
       <c r="D16" t="n">
-        <v>453602</v>
+        <v>484198</v>
       </c>
       <c r="E16" t="n">
         <v>106176</v>
@@ -2294,10 +2294,10 @@
         <v>52739</v>
       </c>
       <c r="D17" t="n">
-        <v>208268</v>
+        <v>218268</v>
       </c>
       <c r="E17" t="n">
-        <v>76711</v>
+        <v>83033</v>
       </c>
     </row>
     <row r="18">
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8119</v>
+        <v>8517</v>
       </c>
       <c r="D18" t="n">
         <v>117936</v>
@@ -2333,13 +2333,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12711</v>
+        <v>5109</v>
       </c>
       <c r="D19" t="n">
-        <v>239051</v>
+        <v>249329</v>
       </c>
       <c r="E19" t="n">
-        <v>46222</v>
+        <v>47902</v>
       </c>
     </row>
     <row r="20">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>229083</v>
+        <v>230864</v>
       </c>
       <c r="D21" t="n">
-        <v>698569</v>
+        <v>711549</v>
       </c>
       <c r="E21" t="n">
-        <v>546720</v>
+        <v>556881</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>77753</v>
+        <v>85253</v>
       </c>
       <c r="D22" t="n">
-        <v>325497</v>
+        <v>333797</v>
       </c>
       <c r="E22" t="n">
-        <v>135597</v>
+        <v>136848</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>58689</v>
+        <v>65317</v>
       </c>
       <c r="D23" t="n">
-        <v>254587</v>
+        <v>284985</v>
       </c>
       <c r="E23" t="n">
-        <v>41634</v>
+        <v>48262</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-30920</v>
+        <v>-30508</v>
       </c>
       <c r="D24" t="n">
         <v>35837</v>
       </c>
       <c r="E24" t="n">
-        <v>4967</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4099054</v>
+        <v>4197746</v>
       </c>
       <c r="D25" t="n">
-        <v>4343325</v>
+        <v>4524102</v>
       </c>
       <c r="E25" t="n">
-        <v>5180133</v>
+        <v>5352796</v>
       </c>
     </row>
   </sheetData>
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>111580</v>
+        <v>111978</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>105182.5</v>
+        <v>105580.5</v>
       </c>
     </row>
     <row r="6">
@@ -3305,19 +3305,19 @@
         <v>88000</v>
       </c>
       <c r="D20" t="n">
-        <v>87820</v>
+        <v>94420</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3329,7 +3329,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87820</v>
+        <v>94420</v>
       </c>
     </row>
     <row r="21">
@@ -3515,19 +3515,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>51034</v>
+        <v>56014</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>32984</v>
+        <v>37964</v>
       </c>
     </row>
     <row r="26">
@@ -3641,19 +3641,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>57158</v>
+        <v>58838</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3661,11 +3661,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>38558</v>
+        <v>40238</v>
       </c>
     </row>
     <row r="29">
@@ -3767,19 +3767,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>238514</v>
+        <v>243494</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>149.1%</t>
+          <t>152.2%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>118.2%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3787,11 +3787,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>184174</v>
+        <v>189154</v>
       </c>
     </row>
     <row r="32">
@@ -3935,19 +3935,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>72650</v>
+        <v>79250</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>72650</v>
+        <v>79250</v>
       </c>
     </row>
     <row r="36">
@@ -4061,19 +4061,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>137860</v>
+        <v>139840</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>42352</v>
+        <v>44332</v>
       </c>
     </row>
     <row r="39">
@@ -4285,11 +4285,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>270650</v>
+        <v>288048</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>230783.33</v>
+        <v>248181.33</v>
       </c>
     </row>
     <row r="3">
@@ -4353,11 +4353,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>78800.67999999999</v>
+        <v>79998.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>78800.67999999999</v>
+        <v>79998.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4387,11 +4387,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>47480.8</v>
+        <v>59480.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>44880.8</v>
+        <v>56880.8</v>
       </c>
     </row>
     <row r="6">
@@ -4489,11 +4489,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>45937.21</v>
+        <v>46137.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>45937.21</v>
+        <v>46137.21</v>
       </c>
     </row>
     <row r="9">
@@ -4523,11 +4523,11 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>66076.69</v>
+        <v>66601.50999999999</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>65876.69</v>
+        <v>66401.50999999999</v>
       </c>
     </row>
     <row r="10">
@@ -4659,11 +4659,11 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>15599.23</v>
+        <v>31399.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>15599.23</v>
+        <v>31399.23</v>
       </c>
     </row>
     <row r="14">
@@ -4727,11 +4727,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>93954</v>
+        <v>96232</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>64756</v>
+        <v>67034</v>
       </c>
     </row>
     <row r="16">
@@ -4795,11 +4795,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>20780</v>
+        <v>21178</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>20780</v>
+        <v>21178</v>
       </c>
     </row>
     <row r="18">
@@ -4829,11 +4829,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>78954</v>
+        <v>79397</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>78954</v>
+        <v>79397</v>
       </c>
     </row>
     <row r="19">
@@ -4863,11 +4863,11 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>126350.1</v>
+        <v>129937.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4875,11 +4875,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>121350.1</v>
+        <v>124937.4</v>
       </c>
     </row>
     <row r="20">
@@ -4897,11 +4897,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>78896.89999999999</v>
+        <v>81188.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4909,11 +4909,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>74896.89999999999</v>
+        <v>77188.7</v>
       </c>
     </row>
     <row r="21">
@@ -4931,11 +4931,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>11276.55</v>
+        <v>21276.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>11276.55</v>
+        <v>21276.55</v>
       </c>
     </row>
     <row r="22">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>77640</v>
+        <v>107640</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>67840</v>
+        <v>97840</v>
       </c>
     </row>
     <row r="26">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>55204</v>
+        <v>62202</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>110.4%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>55204</v>
+        <v>62202</v>
       </c>
     </row>
     <row r="28">
@@ -5237,11 +5237,11 @@
         <v>60000</v>
       </c>
       <c r="D30" t="n">
-        <v>48176</v>
+        <v>48376</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5249,11 +5249,11 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38176</v>
+        <v>38376</v>
       </c>
     </row>
     <row r="31">
@@ -5543,11 +5543,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>85770</v>
+        <v>87750</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>85770</v>
+        <v>87750</v>
       </c>
     </row>
     <row r="40">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>590852</v>
+        <v>608834</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>132.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>512202</v>
+        <v>530184</v>
       </c>
     </row>
     <row r="41">
@@ -5611,11 +5611,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>102869</v>
+        <v>103869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>102869</v>
+        <v>103869</v>
       </c>
     </row>
     <row r="42">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>199049.64</v>
+        <v>223590.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>199049.64</v>
+        <v>223590.46</v>
       </c>
     </row>
     <row r="46">
@@ -5781,11 +5781,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>44977</v>
+        <v>56723</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>44977</v>
+        <v>56723</v>
       </c>
     </row>
     <row r="47">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>222393</v>
+        <v>226954</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>222393</v>
+        <v>226954</v>
       </c>
     </row>
     <row r="48">
@@ -5849,11 +5849,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>145798.4</v>
+        <v>152490.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>145798.4</v>
+        <v>152490.4</v>
       </c>
     </row>
     <row r="49">
@@ -5883,11 +5883,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>274837.04</v>
+        <v>286122.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>274837.04</v>
+        <v>286122.04</v>
       </c>
     </row>
     <row r="50">
@@ -5951,11 +5951,11 @@
         <v>80000</v>
       </c>
       <c r="D51" t="n">
-        <v>15940</v>
+        <v>16338</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>15940</v>
+        <v>16338</v>
       </c>
     </row>
     <row r="52">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>363630.97</v>
+        <v>384244.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>121.2%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>363630.97</v>
+        <v>384244.97</v>
       </c>
     </row>
     <row r="53">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>208911.3</v>
+        <v>227243.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>103.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>208911.3</v>
+        <v>227243.8</v>
       </c>
     </row>
     <row r="54">
@@ -6053,11 +6053,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>266418</v>
+        <v>287418</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>119.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>266418</v>
+        <v>287418</v>
       </c>
     </row>
     <row r="55">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>139381</v>
+        <v>139779</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>129.4%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>129381</v>
+        <v>129779</v>
       </c>
     </row>
     <row r="56">
@@ -6189,11 +6189,11 @@
         <v>60000</v>
       </c>
       <c r="D58" t="n">
-        <v>22476</v>
+        <v>33272</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -6201,11 +6201,11 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>15476</v>
+        <v>26272</v>
       </c>
     </row>
     <row r="59">
@@ -6223,11 +6223,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>124000</v>
+        <v>134000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>193.3%</t>
+          <t>210.0%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>116000</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="60">
@@ -6291,11 +6291,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>57566</v>
+        <v>57964</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57566</v>
+        <v>57964</v>
       </c>
     </row>
     <row r="62">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1152601.5</v>
+        <v>1189368.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3508</v>
+        <v>3600</v>
       </c>
       <c r="E2" t="n">
-        <v>99369</v>
+        <v>105969</v>
       </c>
       <c r="F2" t="n">
-        <v>1053232.5</v>
+        <v>1083399.5</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1046047</v>
+        <v>1079167</v>
       </c>
       <c r="D3" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="E3" t="n">
-        <v>99340</v>
+        <v>105940</v>
       </c>
       <c r="F3" t="n">
-        <v>946707</v>
+        <v>973227</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>106554.5</v>
+        <v>110201.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3308</v>
+        <v>3393</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>106525.5</v>
+        <v>110172.5</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1499560</v>
+        <v>1620340</v>
       </c>
       <c r="D5" t="n">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="E5" t="n">
         <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1413350</v>
+        <v>1534130</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1099480</v>
+        <v>1219168</v>
       </c>
       <c r="D6" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1076882</v>
+        <v>1196570</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380080</v>
+        <v>381172</v>
       </c>
       <c r="D7" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E7" t="n">
         <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>316468</v>
+        <v>317560</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1841363.51</v>
+        <v>1970376.27</v>
       </c>
       <c r="D8" t="n">
-        <v>2367</v>
+        <v>2531</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1832579.04</v>
+        <v>1961591.8</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1083856.96</v>
+        <v>1145798.69</v>
       </c>
       <c r="D9" t="n">
-        <v>1022</v>
+        <v>1111</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1082056.96</v>
+        <v>1143998.69</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>757506.55</v>
+        <v>824577.58</v>
       </c>
       <c r="D10" t="n">
-        <v>1345</v>
+        <v>1420</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>750522.08</v>
+        <v>817593.11</v>
       </c>
     </row>
     <row r="11">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>45480</v>
+        <v>47460</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>33600</v>
       </c>
       <c r="F13" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="14">
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="15">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1152601.5</v>
+        <v>1189368.5</v>
       </c>
       <c r="C2" t="n">
-        <v>495823.76</v>
+        <v>499061.76</v>
       </c>
       <c r="D2" t="n">
-        <v>86522</v>
+        <v>89798</v>
       </c>
       <c r="E2" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="F2" t="n">
-        <v>409301.76</v>
+        <v>409263.76</v>
       </c>
       <c r="G2" t="n">
-        <v>35.51</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="3">
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1499560</v>
+        <v>1620340</v>
       </c>
       <c r="C3" t="n">
         <v>677032.75</v>
@@ -6852,13 +6852,13 @@
         <v>7600</v>
       </c>
       <c r="E3" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="F3" t="n">
         <v>669432.75</v>
       </c>
       <c r="G3" t="n">
-        <v>44.64</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="4">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1841363.51</v>
+        <v>1970376.27</v>
       </c>
       <c r="C4" t="n">
         <v>28799</v>
@@ -6883,7 +6883,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="5">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45480</v>
+        <v>47460</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -6952,13 +6952,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>116.53</v>
+        <v>111.67</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>541.4400000000001</v>
+        <v>518.85</v>
       </c>
     </row>
     <row r="8">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8318</v>
+        <v>11880</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -6983,7 +6983,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>23.8</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="9">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64354.24</v>
+        <v>68932.24000000001</v>
       </c>
       <c r="C9" t="n">
         <v>17999</v>
@@ -7002,13 +7002,13 @@
         <v>1199</v>
       </c>
       <c r="E9" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>26.11</v>
+        <v>24.37</v>
       </c>
     </row>
   </sheetData>
@@ -7054,10 +7054,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C2" t="n">
-        <v>1055652.42</v>
+        <v>1055708.42</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="C3" t="n">
-        <v>322121.3</v>
+        <v>325151.3</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C6" t="n">
-        <v>36677.7</v>
+        <v>36696.7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>34549.66</v>
+        <v>34625.66</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>17271</v>
+        <v>17309</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D7" t="n">
-        <v>87859</v>
+        <v>87915</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="D8" t="n">
-        <v>48255.8</v>
+        <v>51266.8</v>
       </c>
     </row>
     <row r="9">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>13549</v>
+        <v>13625</v>
       </c>
     </row>
     <row r="10">
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
-        <v>9353.700000000001</v>
+        <v>9372.700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>3667</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="13">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D56" t="n">
-        <v>4691</v>
+        <v>4710</v>
       </c>
     </row>
     <row r="57">
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C2" t="n">
-        <v>254651.33</v>
+        <v>254727.33</v>
       </c>
     </row>
     <row r="3">
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>241585</v>
+        <v>241623</v>
       </c>
     </row>
     <row r="4">
@@ -8834,10 +8834,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C4" t="n">
-        <v>188699.4</v>
+        <v>190036.4</v>
       </c>
     </row>
     <row r="5">
@@ -8847,10 +8847,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C5" t="n">
-        <v>164404.98</v>
+        <v>165703.98</v>
       </c>
     </row>
     <row r="6">
@@ -8873,10 +8873,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>110147</v>
+        <v>110223</v>
       </c>
     </row>
     <row r="8">
@@ -8899,10 +8899,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" t="n">
-        <v>73045.8</v>
+        <v>73064.8</v>
       </c>
     </row>
     <row r="10">
@@ -8951,10 +8951,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C13" t="n">
-        <v>41819</v>
+        <v>42136</v>
       </c>
     </row>
     <row r="14">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>619862</v>
+        <v>632101</v>
       </c>
       <c r="E2" t="n">
-        <v>123625</v>
+        <v>129095</v>
       </c>
       <c r="F2" t="n">
-        <v>496237</v>
+        <v>503006</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>472619</v>
+        <v>483573</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+31.2%</t>
+          <t>+30.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>220057</v>
+        <v>229471</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+125.5%</t>
+          <t>+119.2%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16971</v>
+        <v>16999</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -612,11 +612,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-18496</v>
+        <v>-23766</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-110.8%</t>
+          <t>-108.4%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>639574</v>
+        <v>724154</v>
       </c>
       <c r="E4" t="n">
-        <v>103159</v>
+        <v>128972</v>
       </c>
       <c r="F4" t="n">
-        <v>536415</v>
+        <v>595181</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>691030</v>
+        <v>697652</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>515187</v>
+        <v>520819</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+4.1%</t>
+          <t>+14.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>243954</v>
+        <v>245934</v>
       </c>
       <c r="E5" t="n">
         <v>157581</v>
       </c>
       <c r="F5" t="n">
-        <v>86373</v>
+        <v>88353</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>479237</v>
+        <v>479572</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>351850</v>
+        <v>351366</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>695014</v>
+        <v>725312</v>
       </c>
       <c r="E6" t="n">
-        <v>54490</v>
+        <v>64470</v>
       </c>
       <c r="F6" t="n">
-        <v>640524</v>
+        <v>660842</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>396939</v>
+        <v>410768</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+75.1%</t>
+          <t>+76.6%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>291321</v>
+        <v>300599</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+119.9%</t>
+          <t>+119.8%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>438534</v>
+        <v>446634</v>
       </c>
       <c r="E7" t="n">
         <v>89097</v>
       </c>
       <c r="F7" t="n">
-        <v>349437</v>
+        <v>357537</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>352268</v>
+        <v>367717</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+24.5%</t>
+          <t>+21.5%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>244660</v>
+        <v>259858</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+42.8%</t>
+          <t>+37.6%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>421148</v>
+        <v>482608</v>
       </c>
       <c r="E8" t="n">
-        <v>109433</v>
+        <v>135030</v>
       </c>
       <c r="F8" t="n">
-        <v>311715</v>
+        <v>347578</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>376124</v>
+        <v>376338</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+12.0%</t>
+          <t>+28.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>294350</v>
+        <v>294132</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+18.2%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>934528</v>
+        <v>1007328</v>
       </c>
       <c r="E9" t="n">
-        <v>388060</v>
+        <v>419460</v>
       </c>
       <c r="F9" t="n">
-        <v>546468</v>
+        <v>587868</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>949013</v>
+        <v>962613</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>+4.6%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>712745</v>
+        <v>674845</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,39 +981,39 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1890334</v>
+        <v>1924783</v>
       </c>
       <c r="E10" t="n">
         <v>47508</v>
       </c>
       <c r="F10" t="n">
-        <v>1842826</v>
+        <v>1877275</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1576179</v>
+        <v>1638459</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+19.9%</t>
+          <t>+17.5%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1576179</v>
+        <v>1638459</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+16.9%</t>
+          <t>+14.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         <v>775873</v>
       </c>
       <c r="P10" t="n">
-        <v>1066952</v>
+        <v>1101401</v>
       </c>
       <c r="Q10" t="n">
-        <v>1810842</v>
+        <v>1845291</v>
       </c>
     </row>
     <row r="11">
@@ -1042,13 +1042,13 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256605</v>
+        <v>256615</v>
       </c>
       <c r="E11" t="n">
         <v>37233</v>
       </c>
       <c r="F11" t="n">
-        <v>219372</v>
+        <v>219382</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1062,23 +1062,23 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>297145</v>
+        <v>317752</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>251218</v>
+        <v>271825</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="O11" t="n">
         <v>51367</v>
@@ -1087,7 +1087,7 @@
         <v>167781</v>
       </c>
       <c r="Q11" t="n">
-        <v>104459</v>
+        <v>104469</v>
       </c>
     </row>
     <row r="12">
@@ -1105,47 +1105,47 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>431592</v>
+        <v>453582</v>
       </c>
       <c r="E12" t="n">
         <v>30095</v>
       </c>
       <c r="F12" t="n">
-        <v>401497</v>
+        <v>423487</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>357440</v>
+        <v>367839</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+20.7%</t>
+          <t>+23.3%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>355212</v>
+        <v>365611</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+13.0%</t>
+          <t>+15.8%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>65658</v>
+        <v>66852</v>
       </c>
       <c r="P12" t="n">
-        <v>335839</v>
+        <v>356635</v>
       </c>
       <c r="Q12" t="n">
         <v>41927</v>
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>596939</v>
+        <v>617720</v>
       </c>
       <c r="E13" t="n">
-        <v>50533</v>
+        <v>68262</v>
       </c>
       <c r="F13" t="n">
-        <v>546406</v>
+        <v>549458</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>565894</v>
+        <v>578560</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+5.5%</t>
+          <t>+6.8%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>489285</v>
+        <v>501751</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+11.7%</t>
+          <t>+9.5%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31727</v>
       </c>
       <c r="O13" t="n">
-        <v>30481</v>
+        <v>37952</v>
       </c>
       <c r="P13" t="n">
-        <v>484198</v>
+        <v>479779</v>
       </c>
       <c r="Q13" t="n">
-        <v>106176</v>
+        <v>106128</v>
       </c>
     </row>
     <row r="14">
@@ -1229,49 +1229,49 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>312841</v>
+        <v>323239</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>297975</v>
+        <v>308373</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>370826</v>
+        <v>427650</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>325448</v>
+        <v>350472</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="N14" t="n">
         <v>26968</v>
       </c>
       <c r="O14" t="n">
-        <v>52739</v>
+        <v>53137</v>
       </c>
       <c r="P14" t="n">
-        <v>218268</v>
+        <v>228268</v>
       </c>
       <c r="Q14" t="n">
         <v>83033</v>
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>142310</v>
+        <v>148328</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>126453</v>
+        <v>132471</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>193738</v>
+        <v>194534</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>178432</v>
+        <v>179209</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8517</v>
+        <v>8555</v>
       </c>
       <c r="P15" t="n">
-        <v>117936</v>
+        <v>123916</v>
       </c>
       <c r="Q15" t="n">
-        <v>38085</v>
+        <v>39123</v>
       </c>
     </row>
     <row r="16">
@@ -1353,47 +1353,47 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323355</v>
+        <v>354151</v>
       </c>
       <c r="E16" t="n">
         <v>68917</v>
       </c>
       <c r="F16" t="n">
-        <v>254438</v>
+        <v>285234</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>322279</v>
+        <v>322298</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+0.3%</t>
+          <t>+9.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>269279</v>
+        <v>269298</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>+5.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>5109</v>
+        <v>17507</v>
       </c>
       <c r="P16" t="n">
-        <v>249329</v>
+        <v>267727</v>
       </c>
       <c r="Q16" t="n">
         <v>47902</v>
@@ -1414,52 +1414,52 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>580567</v>
+        <v>619530</v>
       </c>
       <c r="E17" t="n">
         <v>105631</v>
       </c>
       <c r="F17" t="n">
-        <v>474936</v>
+        <v>513899</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>427840</v>
+        <v>439291</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+35.7%</t>
+          <t>+41.0%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>331174</v>
+        <v>342625</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+43.4%</t>
+          <t>+50.0%</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>69599</v>
+        <v>69668</v>
       </c>
       <c r="O17" t="n">
-        <v>43538</v>
+        <v>44534</v>
       </c>
       <c r="P17" t="n">
-        <v>361999</v>
+        <v>399897</v>
       </c>
       <c r="Q17" t="n">
-        <v>105549</v>
+        <v>141618</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1067537</v>
+        <v>1082656</v>
       </c>
       <c r="E18" t="n">
-        <v>117874</v>
+        <v>142696</v>
       </c>
       <c r="F18" t="n">
-        <v>949663</v>
+        <v>939959</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>637896</v>
+        <v>655530</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+67.4%</t>
+          <t>+65.2%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>485090</v>
+        <v>502724</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+95.8%</t>
+          <t>+87.0%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>7250</v>
       </c>
       <c r="O18" t="n">
-        <v>230864</v>
+        <v>229968</v>
       </c>
       <c r="P18" t="n">
-        <v>711549</v>
+        <v>702741</v>
       </c>
       <c r="Q18" t="n">
-        <v>556881</v>
+        <v>552808</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>510448</v>
+        <v>541588</v>
       </c>
       <c r="E19" t="n">
-        <v>30346</v>
+        <v>86946</v>
       </c>
       <c r="F19" t="n">
-        <v>480102</v>
+        <v>454642</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>373985</v>
+        <v>381027</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+36.5%</t>
+          <t>+42.1%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>220958</v>
+        <v>227981</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+117.3%</t>
+          <t>+99.4%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>61252</v>
+        <v>61392</v>
       </c>
       <c r="O19" t="n">
-        <v>85253</v>
+        <v>69553</v>
       </c>
       <c r="P19" t="n">
-        <v>333797</v>
+        <v>323897</v>
       </c>
       <c r="Q19" t="n">
-        <v>136848</v>
+        <v>136988</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>450257</v>
+        <v>468752</v>
       </c>
       <c r="E20" t="n">
-        <v>99955</v>
+        <v>105502</v>
       </c>
       <c r="F20" t="n">
-        <v>350302</v>
+        <v>363250</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>623332</v>
+        <v>623446</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>540232</v>
+        <v>540327</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-32.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>65317</v>
+        <v>60365</v>
       </c>
       <c r="P20" t="n">
-        <v>284985</v>
+        <v>302885</v>
       </c>
       <c r="Q20" t="n">
-        <v>48262</v>
+        <v>66710</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>182908</v>
+        <v>213095</v>
       </c>
       <c r="E21" t="n">
-        <v>177578</v>
+        <v>184810</v>
       </c>
       <c r="F21" t="n">
-        <v>5329</v>
+        <v>28285</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-30508</v>
+        <v>-14171</v>
       </c>
       <c r="P21" t="n">
-        <v>35837</v>
+        <v>42456</v>
       </c>
       <c r="Q21" t="n">
-        <v>5379</v>
+        <v>31733</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>10740306</v>
+        <v>11270109</v>
       </c>
       <c r="E22" t="n">
-        <v>1821839</v>
+        <v>2032029</v>
       </c>
       <c r="F22" t="n">
-        <v>8918467</v>
+        <v>9238080</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9480755</v>
+        <v>9741618</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+13.3%</t>
+          <t>+15.7%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7634182</v>
+        <v>7797605</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+16.8%</t>
+          <t>+18.5%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>197020</v>
+        <v>197239</v>
       </c>
       <c r="O22" t="n">
-        <v>4197746</v>
+        <v>4394827</v>
       </c>
       <c r="P22" t="n">
-        <v>4524102</v>
+        <v>4646415</v>
       </c>
       <c r="Q22" t="n">
-        <v>5352796</v>
+        <v>5621481</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>204.3</v>
+        <v>627.8</v>
       </c>
       <c r="E2" t="n">
-        <v>2730</v>
+        <v>12374</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>65.90000000000001</v>
+        <v>722</v>
       </c>
       <c r="E3" t="n">
-        <v>121</v>
+        <v>16377</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
       <c r="C4" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
-        <v>979</v>
+        <v>1423.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2025</v>
+        <v>2302</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2404706</v>
+        <v>2536503</v>
       </c>
       <c r="D2" t="n">
         <v>17993</v>
       </c>
       <c r="E2" t="n">
-        <v>1984608</v>
+        <v>2099507</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>408829</v>
+        <v>456829</v>
       </c>
       <c r="D3" t="n">
-        <v>137638</v>
+        <v>131038</v>
       </c>
       <c r="E3" t="n">
-        <v>282843</v>
+        <v>324243</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1414716</v>
+        <v>1415663</v>
       </c>
       <c r="D4" t="n">
-        <v>4332633</v>
+        <v>4454927</v>
       </c>
       <c r="E4" t="n">
-        <v>3079963</v>
+        <v>3165996</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>486893</v>
+        <v>493662</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>504451</v>
+        <v>511220</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>520705</v>
+        <v>579472</v>
       </c>
       <c r="D7" t="n">
         <v>15710</v>
       </c>
       <c r="E7" t="n">
-        <v>502833</v>
+        <v>561599</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>81185</v>
+        <v>83165</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-37787</v>
+        <v>-35807</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>633560</v>
+        <v>653878</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>528538</v>
+        <v>553458</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>350218</v>
+        <v>358318</v>
       </c>
       <c r="D10" t="n">
         <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>214849</v>
+        <v>221449</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>330282</v>
+        <v>366145</v>
       </c>
       <c r="D11" t="n">
         <v>-18567</v>
       </c>
       <c r="E11" t="n">
-        <v>269725</v>
+        <v>285588</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>408830</v>
+        <v>456830</v>
       </c>
       <c r="D12" t="n">
-        <v>137638</v>
+        <v>131038</v>
       </c>
       <c r="E12" t="n">
-        <v>282844</v>
+        <v>324244</v>
       </c>
     </row>
     <row r="13">
@@ -2210,10 +2210,10 @@
         <v>775873</v>
       </c>
       <c r="D13" t="n">
-        <v>1066952</v>
+        <v>1101401</v>
       </c>
       <c r="E13" t="n">
-        <v>1810842</v>
+        <v>1845291</v>
       </c>
     </row>
     <row r="14">
@@ -2234,7 +2234,7 @@
         <v>167781</v>
       </c>
       <c r="E14" t="n">
-        <v>104459</v>
+        <v>104469</v>
       </c>
     </row>
     <row r="15">
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65658</v>
+        <v>66852</v>
       </c>
       <c r="D15" t="n">
-        <v>335839</v>
+        <v>356635</v>
       </c>
       <c r="E15" t="n">
         <v>41927</v>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30481</v>
+        <v>37952</v>
       </c>
       <c r="D16" t="n">
-        <v>484198</v>
+        <v>479779</v>
       </c>
       <c r="E16" t="n">
-        <v>106176</v>
+        <v>106128</v>
       </c>
     </row>
     <row r="17">
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>52739</v>
+        <v>53137</v>
       </c>
       <c r="D17" t="n">
-        <v>218268</v>
+        <v>228268</v>
       </c>
       <c r="E17" t="n">
         <v>83033</v>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8517</v>
+        <v>8555</v>
       </c>
       <c r="D18" t="n">
-        <v>117936</v>
+        <v>123916</v>
       </c>
       <c r="E18" t="n">
-        <v>38085</v>
+        <v>39123</v>
       </c>
     </row>
     <row r="19">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5109</v>
+        <v>17507</v>
       </c>
       <c r="D19" t="n">
-        <v>249329</v>
+        <v>267727</v>
       </c>
       <c r="E19" t="n">
         <v>47902</v>
@@ -2354,13 +2354,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>43538</v>
+        <v>44534</v>
       </c>
       <c r="D20" t="n">
-        <v>361999</v>
+        <v>399897</v>
       </c>
       <c r="E20" t="n">
-        <v>105549</v>
+        <v>141618</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>230864</v>
+        <v>229968</v>
       </c>
       <c r="D21" t="n">
-        <v>711549</v>
+        <v>702741</v>
       </c>
       <c r="E21" t="n">
-        <v>556881</v>
+        <v>552808</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>85253</v>
+        <v>69553</v>
       </c>
       <c r="D22" t="n">
-        <v>333797</v>
+        <v>323897</v>
       </c>
       <c r="E22" t="n">
-        <v>136848</v>
+        <v>136988</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>65317</v>
+        <v>60365</v>
       </c>
       <c r="D23" t="n">
-        <v>284985</v>
+        <v>302885</v>
       </c>
       <c r="E23" t="n">
-        <v>48262</v>
+        <v>66710</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-30508</v>
+        <v>-14171</v>
       </c>
       <c r="D24" t="n">
-        <v>35837</v>
+        <v>42456</v>
       </c>
       <c r="E24" t="n">
-        <v>5379</v>
+        <v>31733</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4197746</v>
+        <v>4394827</v>
       </c>
       <c r="D25" t="n">
-        <v>4524102</v>
+        <v>4646415</v>
       </c>
       <c r="E25" t="n">
-        <v>5352796</v>
+        <v>5621481</v>
       </c>
     </row>
   </sheetData>
@@ -2591,19 +2591,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>69180</v>
+        <v>69479</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2611,11 +2611,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>49791</v>
+        <v>50090</v>
       </c>
     </row>
     <row r="4">
@@ -2633,19 +2633,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>57016</v>
+        <v>61996</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12456</v>
+        <v>17436</v>
       </c>
     </row>
     <row r="5">
@@ -2675,31 +2675,31 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>111978</v>
+        <v>116958</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6397.5</v>
+        <v>7887.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>105580.5</v>
+        <v>109070.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,31 +2717,31 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>93100</v>
+        <v>95080</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11680</v>
+        <v>15660</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>81420</v>
+        <v>79420</v>
       </c>
     </row>
     <row r="7">
@@ -2759,19 +2759,19 @@
         <v>120000</v>
       </c>
       <c r="D7" t="n">
-        <v>106300</v>
+        <v>116260</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -2779,11 +2779,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>87170</v>
+        <v>97130</v>
       </c>
     </row>
     <row r="8">
@@ -2813,19 +2813,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>56825</v>
+        <v>82422</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>29375</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="9">
@@ -2885,19 +2885,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>92752</v>
+        <v>119352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>84793</v>
+        <v>111393</v>
       </c>
     </row>
     <row r="11">
@@ -2927,19 +2927,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>60518</v>
+        <v>85418</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2947,11 +2947,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>46578</v>
+        <v>71478</v>
       </c>
     </row>
     <row r="12">
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>182938</v>
+        <v>242538</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>228.7%</t>
+          <t>303.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>214.9%</t>
+          <t>289.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>171958</v>
+        <v>231558</v>
       </c>
     </row>
     <row r="14">
@@ -3149,19 +3149,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>43000</v>
+        <v>67800</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>80572</v>
+        <v>55772</v>
       </c>
     </row>
     <row r="17">
@@ -3221,19 +3221,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>107398</v>
+        <v>113998</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>122.0%</t>
+          <t>129.5%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>106.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>87198</v>
+        <v>93798</v>
       </c>
     </row>
     <row r="19">
@@ -3317,19 +3317,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>94420</v>
+        <v>87820</v>
       </c>
     </row>
     <row r="21">
@@ -3473,19 +3473,19 @@
         <v>88000</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="25">
@@ -3515,19 +3515,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>56014</v>
+        <v>60994</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>37964</v>
+        <v>42944</v>
       </c>
     </row>
     <row r="26">
@@ -3557,31 +3557,31 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>186916</v>
+        <v>221696</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>138.6%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>119.6%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18746</v>
+        <v>30326</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>168170</v>
+        <v>191370</v>
       </c>
     </row>
     <row r="27">
@@ -3599,19 +3599,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>53500</v>
+        <v>63460</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3619,11 +3619,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44820</v>
+        <v>54780</v>
       </c>
     </row>
     <row r="28">
@@ -3641,31 +3641,31 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>58838</v>
+        <v>68798</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>18600</v>
+        <v>25200</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>40238</v>
+        <v>43598</v>
       </c>
     </row>
     <row r="29">
@@ -3683,31 +3683,31 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>88298</v>
+        <v>103238</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>17123</v>
+        <v>22103</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>71175</v>
+        <v>81135</v>
       </c>
     </row>
     <row r="30">
@@ -3725,31 +3725,31 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>104560</v>
+        <v>114520</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>21960</v>
+        <v>24613.4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>82600</v>
+        <v>89906.60000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3767,19 +3767,19 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>243494</v>
+        <v>250094</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>152.2%</t>
+          <t>156.3%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3787,11 +3787,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>189154</v>
+        <v>195754</v>
       </c>
     </row>
     <row r="32">
@@ -3821,19 +3821,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>20940</v>
+        <v>25940</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>176018</v>
+        <v>171018</v>
       </c>
     </row>
     <row r="33">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>89618</v>
+        <v>91118</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>64838</v>
+        <v>66338</v>
       </c>
     </row>
     <row r="34">
@@ -3893,19 +3893,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>97899</v>
+        <v>103217</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3913,11 +3913,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>88399</v>
+        <v>93717</v>
       </c>
     </row>
     <row r="35">
@@ -3935,19 +3935,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>79250</v>
+        <v>84230</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>79250</v>
+        <v>84230</v>
       </c>
     </row>
     <row r="36">
@@ -4019,31 +4019,31 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>130816</v>
+        <v>150816</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>145.0%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7960</v>
+        <v>12940</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>122856</v>
+        <v>137876</v>
       </c>
     </row>
     <row r="38">
@@ -4061,19 +4061,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>139840</v>
+        <v>141820</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>44332</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="39">
@@ -4285,23 +4285,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>288048</v>
+        <v>298048</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>39866.67</v>
+        <v>57366.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>248181.33</v>
+        <v>240681.33</v>
       </c>
     </row>
     <row r="3">
@@ -4353,11 +4353,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>79998.67999999999</v>
+        <v>90598.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>79998.67999999999</v>
+        <v>90598.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4489,11 +4489,11 @@
         <v>200000</v>
       </c>
       <c r="D8" t="n">
-        <v>46137.21</v>
+        <v>62137.21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>46137.21</v>
+        <v>62137.21</v>
       </c>
     </row>
     <row r="9">
@@ -4557,7 +4557,7 @@
         <v>100000</v>
       </c>
       <c r="D10" t="n">
-        <v>161172.17</v>
+        <v>161239.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>161172.17</v>
+        <v>161239.7</v>
       </c>
     </row>
     <row r="11">
@@ -4591,11 +4591,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>20000</v>
+        <v>27500</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20000</v>
+        <v>27500</v>
       </c>
     </row>
     <row r="12">
@@ -4625,23 +4625,23 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>171205.7</v>
+        <v>171278.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>56600</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>171205.7</v>
+        <v>114678.4</v>
       </c>
     </row>
     <row r="13">
@@ -4659,11 +4659,11 @@
         <v>100000</v>
       </c>
       <c r="D13" t="n">
-        <v>31399.23</v>
+        <v>38899.23</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>31399.23</v>
+        <v>38899.23</v>
       </c>
     </row>
     <row r="14">
@@ -4693,11 +4693,11 @@
         <v>120000</v>
       </c>
       <c r="D14" t="n">
-        <v>106770</v>
+        <v>118770</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4705,11 +4705,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>85270</v>
+        <v>97270</v>
       </c>
     </row>
     <row r="15">
@@ -4727,11 +4727,11 @@
         <v>120000</v>
       </c>
       <c r="D15" t="n">
-        <v>96232</v>
+        <v>106630</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4739,11 +4739,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>67034</v>
+        <v>77432</v>
       </c>
     </row>
     <row r="16">
@@ -4795,11 +4795,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>21178</v>
+        <v>29576</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>21178</v>
+        <v>29576</v>
       </c>
     </row>
     <row r="18">
@@ -4931,11 +4931,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>21276.55</v>
+        <v>31674.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>21276.55</v>
+        <v>31674.55</v>
       </c>
     </row>
     <row r="22">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>107640</v>
+        <v>124440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>97840</v>
+        <v>114640</v>
       </c>
     </row>
     <row r="26">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>62202</v>
+        <v>63822</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>62202</v>
+        <v>63822</v>
       </c>
     </row>
     <row r="28">
@@ -5373,7 +5373,7 @@
         <v>180000</v>
       </c>
       <c r="D34" t="n">
-        <v>165461.13</v>
+        <v>165530.37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125627.73</v>
+        <v>125696.97</v>
       </c>
     </row>
     <row r="35">
@@ -5441,11 +5441,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>105378</v>
+        <v>142174</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5453,11 +5453,11 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>98780</v>
+        <v>135576</v>
       </c>
     </row>
     <row r="37">
@@ -5475,11 +5475,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>12190</v>
+        <v>14288</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12190</v>
+        <v>14288</v>
       </c>
     </row>
     <row r="38">
@@ -5547,19 +5547,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>6600</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>87750</v>
+        <v>81150</v>
       </c>
     </row>
     <row r="40">
@@ -5577,23 +5577,23 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>608834</v>
+        <v>622406</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>134.9%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>78650</v>
+        <v>82650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>530184</v>
+        <v>539756</v>
       </c>
     </row>
     <row r="41">
@@ -5611,11 +5611,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>103869</v>
+        <v>104869</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>103869</v>
+        <v>104869</v>
       </c>
     </row>
     <row r="42">
@@ -5683,19 +5683,19 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>103.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>18000</v>
+        <v>32222.24</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>108947</v>
+        <v>94724.76000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>223590.46</v>
+        <v>233590.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>223590.46</v>
+        <v>233590.46</v>
       </c>
     </row>
     <row r="46">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>226954</v>
+        <v>228917</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>226954</v>
+        <v>228917</v>
       </c>
     </row>
     <row r="48">
@@ -5849,11 +5849,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>152490.4</v>
+        <v>162490.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>152490.4</v>
+        <v>162490.4</v>
       </c>
     </row>
     <row r="49">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>384244.97</v>
+        <v>386638.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.9%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>384244.97</v>
+        <v>386638.97</v>
       </c>
     </row>
     <row r="53">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>227243.8</v>
+        <v>237335.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>103.3%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>227243.8</v>
+        <v>237335.8</v>
       </c>
     </row>
     <row r="54">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>139779</v>
+        <v>140177</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>130.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6099,11 +6099,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>129779</v>
+        <v>130177</v>
       </c>
     </row>
     <row r="56">
@@ -6121,11 +6121,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>41990</v>
+        <v>42388</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6133,11 +6133,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>36990</v>
+        <v>37388</v>
       </c>
     </row>
     <row r="57">
@@ -6223,11 +6223,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>134000</v>
+        <v>134398</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>210.0%</t>
+          <t>210.7%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>126000</v>
+        <v>126398</v>
       </c>
     </row>
     <row r="60">
@@ -6257,11 +6257,11 @@
         <v>20000</v>
       </c>
       <c r="D60" t="n">
-        <v>25796</v>
+        <v>46592</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>129.0%</t>
+          <t>233.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25796</v>
+        <v>46592</v>
       </c>
     </row>
     <row r="61">
@@ -6291,11 +6291,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>57964</v>
+        <v>62944</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57964</v>
+        <v>62944</v>
       </c>
     </row>
     <row r="62">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>62570</v>
+        <v>63570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>46770</v>
+        <v>47770</v>
       </c>
     </row>
     <row r="63">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1189368.5</v>
+        <v>1354650.52</v>
       </c>
       <c r="D2" t="n">
-        <v>3600</v>
+        <v>3808</v>
       </c>
       <c r="E2" t="n">
-        <v>105969</v>
+        <v>119169</v>
       </c>
       <c r="F2" t="n">
-        <v>1083399.5</v>
+        <v>1235481.52</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1079167</v>
+        <v>1238526</v>
       </c>
       <c r="D3" t="n">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="E3" t="n">
-        <v>105940</v>
+        <v>119140</v>
       </c>
       <c r="F3" t="n">
-        <v>973227</v>
+        <v>1119386</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110201.5</v>
+        <v>116124.52</v>
       </c>
       <c r="D4" t="n">
-        <v>3393</v>
+        <v>3570</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>110172.5</v>
+        <v>116095.52</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1620340</v>
+        <v>1777488</v>
       </c>
       <c r="D5" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="E5" t="n">
         <v>86210</v>
       </c>
       <c r="F5" t="n">
-        <v>1534130</v>
+        <v>1691278</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1219168</v>
+        <v>1316136</v>
       </c>
       <c r="D6" t="n">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1196570</v>
+        <v>1293538</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>381172</v>
+        <v>441352</v>
       </c>
       <c r="D7" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="E7" t="n">
         <v>63612</v>
       </c>
       <c r="F7" t="n">
-        <v>317560</v>
+        <v>377740</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1970376.27</v>
+        <v>2023212.69</v>
       </c>
       <c r="D8" t="n">
-        <v>2531</v>
+        <v>2558</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1961591.8</v>
+        <v>2014428.22</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1145798.69</v>
+        <v>1198345.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1111</v>
+        <v>1130</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1143998.69</v>
+        <v>1196545.9</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>824577.58</v>
+        <v>824866.79</v>
       </c>
       <c r="D10" t="n">
-        <v>1420</v>
+        <v>1428</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>817593.11</v>
+        <v>817882.3199999999</v>
       </c>
     </row>
     <row r="11">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47460</v>
+        <v>140820</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>33600</v>
+        <v>93200</v>
       </c>
       <c r="F13" t="n">
-        <v>13860</v>
+        <v>47620</v>
       </c>
     </row>
     <row r="14">
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
     </row>
     <row r="15">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1189368.5</v>
+        <v>1354650.52</v>
       </c>
       <c r="C2" t="n">
-        <v>499061.76</v>
+        <v>552232.1800000001</v>
       </c>
       <c r="D2" t="n">
-        <v>89798</v>
+        <v>100988.02</v>
       </c>
       <c r="E2" t="n">
-        <v>7.55</v>
+        <v>7.45</v>
       </c>
       <c r="F2" t="n">
-        <v>409263.76</v>
+        <v>451244.16</v>
       </c>
       <c r="G2" t="n">
-        <v>34.41</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1620340</v>
+        <v>1777488</v>
       </c>
       <c r="C3" t="n">
-        <v>677032.75</v>
+        <v>783252.99</v>
       </c>
       <c r="D3" t="n">
-        <v>7600</v>
+        <v>45598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.47</v>
+        <v>2.57</v>
       </c>
       <c r="F3" t="n">
-        <v>669432.75</v>
+        <v>737654.99</v>
       </c>
       <c r="G3" t="n">
-        <v>41.31</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="4">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1970376.27</v>
+        <v>2023212.69</v>
       </c>
       <c r="C4" t="n">
-        <v>28799</v>
+        <v>28999</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>249</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="5">
@@ -6896,7 +6896,7 @@
         <v>529608.4</v>
       </c>
       <c r="C5" t="n">
-        <v>140800</v>
+        <v>190400</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6905,10 +6905,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>140800</v>
+        <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>26.59</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="6">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47460</v>
+        <v>140820</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -6952,13 +6952,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>111.67</v>
+        <v>37.64</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>518.85</v>
+        <v>174.87</v>
       </c>
     </row>
     <row r="8">
@@ -6968,7 +6968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11880</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="n">
         <v>1980</v>
@@ -6983,7 +6983,7 @@
         <v>1980</v>
       </c>
       <c r="G8" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="9">
@@ -6993,22 +6993,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68932.24000000001</v>
+        <v>128129.24</v>
       </c>
       <c r="C9" t="n">
-        <v>17999</v>
+        <v>18998</v>
       </c>
       <c r="D9" t="n">
-        <v>1199</v>
+        <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>24.37</v>
+        <v>13.11</v>
       </c>
     </row>
   </sheetData>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>563</v>
+        <v>592</v>
       </c>
       <c r="C2" t="n">
-        <v>1055708.42</v>
+        <v>1171572.82</v>
       </c>
       <c r="D2" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="C3" t="n">
-        <v>325151.3</v>
+        <v>354763.32</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
@@ -7086,13 +7086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>199001</v>
+        <v>230401</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -7102,42 +7102,42 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
-        <v>123400</v>
+        <v>141622.24</v>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>97</v>
+        <v>193</v>
       </c>
       <c r="C6" t="n">
-        <v>36696.7</v>
+        <v>41665.66</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>34625.66</v>
+        <v>37781.7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7166,13 +7166,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>17309</v>
+        <v>24275</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>228760</v>
+        <v>235360</v>
       </c>
     </row>
     <row r="3">
@@ -7289,10 +7289,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>130200</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="4">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="D7" t="n">
-        <v>87915</v>
+        <v>91046</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="D8" t="n">
-        <v>51266.8</v>
+        <v>53913.82</v>
       </c>
     </row>
     <row r="9">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D9" t="n">
-        <v>13625</v>
+        <v>13675</v>
       </c>
     </row>
     <row r="10">
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>9372.700000000001</v>
+        <v>10438.7</v>
       </c>
     </row>
     <row r="12">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>3705</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="13">
@@ -7568,7 +7568,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7577,70 +7577,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>58829</v>
+        <v>85250</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>21780</v>
+        <v>50722.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>21049.5</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>13200</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>8766.66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
@@ -7663,212 +7663,212 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>85250</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>32500</v>
+        <v>76331</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>58699</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>58829</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>25029.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>80514</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>28919</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>75533.39999999999</v>
+        <v>10256.66</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D32" t="n">
-        <v>20500</v>
+        <v>61556.4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>9000</v>
+        <v>36560</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>398</v>
+        <v>21766</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>200</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="36">
@@ -7879,104 +7879,104 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>52303</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>26600</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>21766</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>2490</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>87854</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>9000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -7987,14 +7987,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D42" t="n">
-        <v>2517</v>
+        <v>87854</v>
       </c>
     </row>
     <row r="43">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>451</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="44">
@@ -8023,14 +8023,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>76</v>
+        <v>5951</v>
       </c>
     </row>
     <row r="45">
@@ -8041,50 +8041,50 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D45" t="n">
-        <v>57</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>62620</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>14820</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
@@ -8095,92 +8095,92 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
-        <v>11657</v>
+        <v>62620</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>68500</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>398</v>
+        <v>11657</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>19</v>
+        <v>74628</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>28440</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8189,16 +8189,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>26050</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8210,31 +8210,31 @@
         <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>38994.67</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>6500</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>4710</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
@@ -8257,74 +8257,74 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>328</v>
+        <v>44494.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
-        <v>27200</v>
+        <v>16910</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>11299</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>9009</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -8333,118 +8333,118 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>19233.35</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>18000</v>
+        <v>31030</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>18028</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>12000</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>318</v>
+        <v>9009</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>15019</v>
+        <v>19233.35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>15009</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="68">
@@ -8455,14 +8455,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="n">
-        <v>48</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="69">
@@ -8473,50 +8473,50 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>9000</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>6800</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -8527,50 +8527,50 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>57</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>9318</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>5500</v>
+        <v>57</v>
       </c>
     </row>
     <row r="75">
@@ -8581,14 +8581,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>29</v>
+        <v>9318</v>
       </c>
     </row>
     <row r="76">
@@ -8599,13 +8599,49 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>时间/适配冲突</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>协商一致</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
         <v>19</v>
       </c>
     </row>
@@ -8647,75 +8683,75 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
-        <v>570062.75</v>
+        <v>630684.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>255666.67</v>
+        <v>256321.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>232461.16</v>
+        <v>255666.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>161760</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>心灯—长程课</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6" t="n">
-        <v>148273</v>
+        <v>188160</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>心灯—长程课</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>140800</v>
+        <v>148273</v>
       </c>
     </row>
     <row r="8">
@@ -8725,10 +8761,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>83700</v>
+        <v>129498</v>
       </c>
     </row>
     <row r="9">
@@ -8808,10 +8844,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="C2" t="n">
-        <v>254727.33</v>
+        <v>327025.35</v>
       </c>
     </row>
     <row r="3">
@@ -8821,36 +8857,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>241623</v>
+        <v>235820</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C4" t="n">
-        <v>190036.4</v>
+        <v>197139.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C5" t="n">
-        <v>165703.98</v>
+        <v>196563.4</v>
       </c>
     </row>
     <row r="6">
@@ -8863,72 +8899,72 @@
         <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>130736.5</v>
+        <v>138217.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>110223</v>
+        <v>127432</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>102632</v>
+        <v>113323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>73064.8</v>
+        <v>108229.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="C10" t="n">
-        <v>70748.89999999999</v>
+        <v>73492.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>68001</v>
+        <v>70748.89999999999</v>
       </c>
     </row>
     <row r="12">
@@ -8951,10 +8987,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C13" t="n">
-        <v>42136</v>
+        <v>47434</v>
       </c>
     </row>
     <row r="14">
@@ -8977,23 +9013,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>33538</v>
+        <v>33557</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>宁夏回族自治区</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>31819.9</v>
+        <v>31824</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -532,22 +532,22 @@
         <v>632101</v>
       </c>
       <c r="E2" t="n">
-        <v>129095</v>
+        <v>132095</v>
       </c>
       <c r="F2" t="n">
-        <v>503006</v>
+        <v>500006</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+119.2%</t>
+          <t>+117.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         <v>213095</v>
       </c>
       <c r="E21" t="n">
-        <v>184810</v>
+        <v>181810</v>
       </c>
       <c r="F21" t="n">
-        <v>28285</v>
+        <v>31285</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,7 +1685,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-14171</v>
+        <v>-11171</v>
       </c>
       <c r="P21" t="n">
         <v>42456</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2536503</v>
+        <v>2533503</v>
       </c>
       <c r="D2" t="n">
         <v>17993</v>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>493662</v>
+        <v>490662</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-14171</v>
+        <v>-11171</v>
       </c>
       <c r="D24" t="n">
         <v>42456</v>
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>41598.66</v>
+        <v>44598.66</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>209233.34</v>
+        <v>206233.34</v>
       </c>
     </row>
     <row r="3">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D7" t="n">
-        <v>91046</v>
+        <v>88046</v>
       </c>
     </row>
     <row r="8">
@@ -7721,10 +7721,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>58829</v>
+        <v>61829</v>
       </c>
     </row>
     <row r="28">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>632101</v>
+        <v>665361</v>
       </c>
       <c r="E2" t="n">
         <v>132095</v>
       </c>
       <c r="F2" t="n">
-        <v>500006</v>
+        <v>533266</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>483573</v>
+        <v>488983</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+30.7%</t>
+          <t>+36.1%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>229471</v>
+        <v>234758</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+117.9%</t>
+          <t>+127.2%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16999</v>
+        <v>17018</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>724154</v>
+        <v>753934</v>
       </c>
       <c r="E4" t="n">
-        <v>128972</v>
+        <v>138932</v>
       </c>
       <c r="F4" t="n">
-        <v>595181</v>
+        <v>615001</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>697652</v>
+        <v>707550</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+3.8%</t>
+          <t>+6.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>520819</v>
+        <v>530545</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+14.3%</t>
+          <t>+15.9%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -696,41 +696,41 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>245934</v>
+        <v>247834</v>
       </c>
       <c r="E5" t="n">
         <v>157581</v>
       </c>
       <c r="F5" t="n">
-        <v>88353</v>
+        <v>90253</v>
       </c>
       <c r="G5" t="n">
         <v>173964</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>479572</v>
+        <v>479630</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>351366</v>
+        <v>351424</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>725312</v>
+        <v>740292</v>
       </c>
       <c r="E6" t="n">
         <v>64470</v>
       </c>
       <c r="F6" t="n">
-        <v>660842</v>
+        <v>675822</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>410768</v>
+        <v>420439</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+76.6%</t>
+          <t>+76.1%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>300599</v>
+        <v>310042</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+119.8%</t>
+          <t>+118.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>446634</v>
+        <v>461634</v>
       </c>
       <c r="E7" t="n">
-        <v>89097</v>
+        <v>94077</v>
       </c>
       <c r="F7" t="n">
-        <v>357537</v>
+        <v>367557</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>367717</v>
+        <v>368797</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+21.5%</t>
+          <t>+25.2%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>259858</v>
+        <v>260573</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+37.6%</t>
+          <t>+41.1%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>482608</v>
+        <v>417948</v>
       </c>
       <c r="E8" t="n">
-        <v>135030</v>
+        <v>52608</v>
       </c>
       <c r="F8" t="n">
-        <v>347578</v>
+        <v>365340</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>376338</v>
+        <v>403027</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+28.2%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>294132</v>
+        <v>320606</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+18.2%</t>
+          <t>+14.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,41 +924,41 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1007328</v>
+        <v>1034248</v>
       </c>
       <c r="E9" t="n">
         <v>419460</v>
       </c>
       <c r="F9" t="n">
-        <v>587868</v>
+        <v>614788</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>962613</v>
+        <v>974942</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+4.6%</t>
+          <t>+6.1%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>674845</v>
+        <v>687145</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1924783</v>
+        <v>1949382</v>
       </c>
       <c r="E10" t="n">
-        <v>47508</v>
+        <v>49508</v>
       </c>
       <c r="F10" t="n">
-        <v>1877275</v>
+        <v>1899874</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1638459</v>
+        <v>1739822</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+17.5%</t>
+          <t>+12.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1638459</v>
+        <v>1739822</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+14.6%</t>
+          <t>+9.2%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>775873</v>
+        <v>799867</v>
       </c>
       <c r="P10" t="n">
-        <v>1101401</v>
+        <v>1100006</v>
       </c>
       <c r="Q10" t="n">
-        <v>1845291</v>
+        <v>1869094</v>
       </c>
     </row>
     <row r="11">
@@ -1042,13 +1042,13 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256615</v>
+        <v>273503</v>
       </c>
       <c r="E11" t="n">
-        <v>37233</v>
+        <v>54233</v>
       </c>
       <c r="F11" t="n">
-        <v>219382</v>
+        <v>219270</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1062,32 +1062,32 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>317752</v>
+        <v>336174</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>271825</v>
+        <v>290247</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>234</v>
       </c>
       <c r="O11" t="n">
-        <v>51367</v>
+        <v>63965</v>
       </c>
       <c r="P11" t="n">
-        <v>167781</v>
+        <v>155071</v>
       </c>
       <c r="Q11" t="n">
-        <v>104469</v>
+        <v>108759</v>
       </c>
     </row>
     <row r="12">
@@ -1105,50 +1105,50 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>453582</v>
+        <v>490978</v>
       </c>
       <c r="E12" t="n">
         <v>30095</v>
       </c>
       <c r="F12" t="n">
-        <v>423487</v>
+        <v>460883</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>367839</v>
+        <v>379033</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+23.3%</t>
+          <t>+29.5%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>365611</v>
+        <v>376805</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+15.8%</t>
+          <t>+22.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>66852</v>
+        <v>67250</v>
       </c>
       <c r="P12" t="n">
-        <v>356635</v>
+        <v>393633</v>
       </c>
       <c r="Q12" t="n">
-        <v>41927</v>
+        <v>48527</v>
       </c>
     </row>
     <row r="13">
@@ -1166,49 +1166,49 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>617720</v>
+        <v>669312</v>
       </c>
       <c r="E13" t="n">
         <v>68262</v>
       </c>
       <c r="F13" t="n">
-        <v>549458</v>
+        <v>601050</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>578560</v>
+        <v>663796</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+6.8%</t>
+          <t>+0.8%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>501751</v>
+        <v>586987</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+9.5%</t>
+          <t>+2.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
         <v>31727</v>
       </c>
       <c r="O13" t="n">
-        <v>37952</v>
+        <v>48748</v>
       </c>
       <c r="P13" t="n">
-        <v>479779</v>
+        <v>520575</v>
       </c>
       <c r="Q13" t="n">
         <v>106128</v>
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>323239</v>
+        <v>325009</v>
       </c>
       <c r="E14" t="n">
         <v>14866</v>
       </c>
       <c r="F14" t="n">
-        <v>308373</v>
+        <v>310143</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>427650</v>
+        <v>509092</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>350472</v>
+        <v>431914</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-28.2%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>26968</v>
+        <v>27923</v>
       </c>
       <c r="O14" t="n">
-        <v>53137</v>
+        <v>53535</v>
       </c>
       <c r="P14" t="n">
-        <v>228268</v>
+        <v>228685</v>
       </c>
       <c r="Q14" t="n">
-        <v>83033</v>
+        <v>84007</v>
       </c>
     </row>
     <row r="15">
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>148328</v>
+        <v>143367</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>132471</v>
+        <v>127510</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>194534</v>
+        <v>206932</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>179209</v>
+        <v>191607</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8555</v>
+        <v>8574</v>
       </c>
       <c r="P15" t="n">
-        <v>123916</v>
+        <v>118936</v>
       </c>
       <c r="Q15" t="n">
-        <v>39123</v>
+        <v>39142</v>
       </c>
     </row>
     <row r="16">
@@ -1353,44 +1353,44 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>354151</v>
+        <v>349171</v>
       </c>
       <c r="E16" t="n">
         <v>68917</v>
       </c>
       <c r="F16" t="n">
-        <v>285234</v>
+        <v>280254</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>322298</v>
+        <v>323492</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+7.9%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>269298</v>
+        <v>270492</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+5.9%</t>
+          <t>+3.6%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>17507</v>
+        <v>12527</v>
       </c>
       <c r="P16" t="n">
         <v>267727</v>
@@ -1414,39 +1414,39 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>619530</v>
+        <v>621730</v>
       </c>
       <c r="E17" t="n">
         <v>105631</v>
       </c>
       <c r="F17" t="n">
-        <v>513899</v>
+        <v>516099</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>439291</v>
+        <v>490291</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+41.0%</t>
+          <t>+26.8%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>342625</v>
+        <v>393625</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+50.0%</t>
+          <t>+31.1%</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -1456,10 +1456,10 @@
         <v>44534</v>
       </c>
       <c r="P17" t="n">
-        <v>399897</v>
+        <v>402097</v>
       </c>
       <c r="Q17" t="n">
-        <v>141618</v>
+        <v>143818</v>
       </c>
     </row>
     <row r="18">
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1082656</v>
+        <v>1123653</v>
       </c>
       <c r="E18" t="n">
         <v>142696</v>
       </c>
       <c r="F18" t="n">
-        <v>939959</v>
+        <v>980956</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>655530</v>
+        <v>716752</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+65.2%</t>
+          <t>+56.8%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>502724</v>
+        <v>563946</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+87.0%</t>
+          <t>+73.9%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>7250</v>
       </c>
       <c r="O18" t="n">
-        <v>229968</v>
+        <v>230267</v>
       </c>
       <c r="P18" t="n">
-        <v>702741</v>
+        <v>743439</v>
       </c>
       <c r="Q18" t="n">
-        <v>552808</v>
+        <v>553407</v>
       </c>
     </row>
     <row r="19">
@@ -1540,52 +1540,52 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>541588</v>
+        <v>549123</v>
       </c>
       <c r="E19" t="n">
         <v>86946</v>
       </c>
       <c r="F19" t="n">
-        <v>454642</v>
+        <v>462177</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>381027</v>
+        <v>383422</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+42.1%</t>
+          <t>+43.2%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>227981</v>
+        <v>230376</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+99.4%</t>
+          <t>+100.6%</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>61392</v>
+        <v>61427</v>
       </c>
       <c r="O19" t="n">
         <v>69553</v>
       </c>
       <c r="P19" t="n">
-        <v>323897</v>
+        <v>331397</v>
       </c>
       <c r="Q19" t="n">
-        <v>136988</v>
+        <v>137023</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>468752</v>
+        <v>498150</v>
       </c>
       <c r="E20" t="n">
-        <v>105502</v>
+        <v>115483</v>
       </c>
       <c r="F20" t="n">
-        <v>363250</v>
+        <v>382667</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>623446</v>
+        <v>635920</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>540327</v>
+        <v>552801</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-32.8%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>60365</v>
+        <v>50982</v>
       </c>
       <c r="P20" t="n">
-        <v>302885</v>
+        <v>331685</v>
       </c>
       <c r="Q20" t="n">
-        <v>66710</v>
+        <v>83529</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>213095</v>
+        <v>311960</v>
       </c>
       <c r="E21" t="n">
-        <v>181810</v>
+        <v>265235</v>
       </c>
       <c r="F21" t="n">
-        <v>31285</v>
+        <v>46725</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>-11171</v>
+        <v>31736</v>
       </c>
       <c r="P21" t="n">
-        <v>42456</v>
+        <v>14989</v>
       </c>
       <c r="Q21" t="n">
-        <v>31733</v>
+        <v>31173</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>11270109</v>
+        <v>11628589</v>
       </c>
       <c r="E22" t="n">
-        <v>2032029</v>
+        <v>2076953</v>
       </c>
       <c r="F22" t="n">
-        <v>9238080</v>
+        <v>9551636</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>73.5%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>9741618</v>
+        <v>10245111</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+15.7%</t>
+          <t>+13.5%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>7797605</v>
+        <v>8299950</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+18.5%</t>
+          <t>+15.1%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>197239</v>
+        <v>198229</v>
       </c>
       <c r="O22" t="n">
-        <v>4394827</v>
+        <v>4566735</v>
       </c>
       <c r="P22" t="n">
-        <v>4646415</v>
+        <v>4787072</v>
       </c>
       <c r="Q22" t="n">
-        <v>5621481</v>
+        <v>5752700</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2533503</v>
+        <v>2601445</v>
       </c>
       <c r="D2" t="n">
-        <v>17993</v>
+        <v>47793</v>
       </c>
       <c r="E2" t="n">
-        <v>2099507</v>
+        <v>2180249</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>456829</v>
+        <v>483749</v>
       </c>
       <c r="D3" t="n">
         <v>131038</v>
       </c>
       <c r="E3" t="n">
-        <v>324243</v>
+        <v>319941</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1415663</v>
+        <v>1449802</v>
       </c>
       <c r="D4" t="n">
-        <v>4454927</v>
+        <v>4593251</v>
       </c>
       <c r="E4" t="n">
-        <v>3165996</v>
+        <v>3221336</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>490662</v>
+        <v>523922</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>511220</v>
+        <v>544480</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>579472</v>
+        <v>599292</v>
       </c>
       <c r="D7" t="n">
         <v>15710</v>
       </c>
       <c r="E7" t="n">
-        <v>561599</v>
+        <v>581419</v>
       </c>
     </row>
     <row r="8">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>83165</v>
+        <v>85065</v>
       </c>
       <c r="D8" t="n">
         <v>5188</v>
       </c>
       <c r="E8" t="n">
-        <v>-35807</v>
+        <v>-33907</v>
       </c>
     </row>
     <row r="9">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>653878</v>
+        <v>668858</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>553458</v>
+        <v>558438</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>358318</v>
+        <v>368338</v>
       </c>
       <c r="D10" t="n">
         <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>221449</v>
+        <v>216469</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>366145</v>
+        <v>354107</v>
       </c>
       <c r="D11" t="n">
-        <v>-18567</v>
+        <v>11233</v>
       </c>
       <c r="E11" t="n">
-        <v>285588</v>
+        <v>311350</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>456830</v>
+        <v>483750</v>
       </c>
       <c r="D12" t="n">
         <v>131038</v>
       </c>
       <c r="E12" t="n">
-        <v>324244</v>
+        <v>319942</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>775873</v>
+        <v>799867</v>
       </c>
       <c r="D13" t="n">
-        <v>1101401</v>
+        <v>1100006</v>
       </c>
       <c r="E13" t="n">
-        <v>1845291</v>
+        <v>1869094</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51367</v>
+        <v>63965</v>
       </c>
       <c r="D14" t="n">
-        <v>167781</v>
+        <v>155071</v>
       </c>
       <c r="E14" t="n">
-        <v>104469</v>
+        <v>108759</v>
       </c>
     </row>
     <row r="15">
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>66852</v>
+        <v>67250</v>
       </c>
       <c r="D15" t="n">
-        <v>356635</v>
+        <v>393633</v>
       </c>
       <c r="E15" t="n">
-        <v>41927</v>
+        <v>48527</v>
       </c>
     </row>
     <row r="16">
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37952</v>
+        <v>48748</v>
       </c>
       <c r="D16" t="n">
-        <v>479779</v>
+        <v>520575</v>
       </c>
       <c r="E16" t="n">
         <v>106128</v>
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53137</v>
+        <v>53535</v>
       </c>
       <c r="D17" t="n">
-        <v>228268</v>
+        <v>228685</v>
       </c>
       <c r="E17" t="n">
-        <v>83033</v>
+        <v>84007</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8555</v>
+        <v>8574</v>
       </c>
       <c r="D18" t="n">
-        <v>123916</v>
+        <v>118936</v>
       </c>
       <c r="E18" t="n">
-        <v>39123</v>
+        <v>39142</v>
       </c>
     </row>
     <row r="19">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17507</v>
+        <v>12527</v>
       </c>
       <c r="D19" t="n">
         <v>267727</v>
@@ -2357,10 +2357,10 @@
         <v>44534</v>
       </c>
       <c r="D20" t="n">
-        <v>399897</v>
+        <v>402097</v>
       </c>
       <c r="E20" t="n">
-        <v>141618</v>
+        <v>143818</v>
       </c>
     </row>
     <row r="21">
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>229968</v>
+        <v>230267</v>
       </c>
       <c r="D21" t="n">
-        <v>702741</v>
+        <v>743439</v>
       </c>
       <c r="E21" t="n">
-        <v>552808</v>
+        <v>553407</v>
       </c>
     </row>
     <row r="22">
@@ -2399,10 +2399,10 @@
         <v>69553</v>
       </c>
       <c r="D22" t="n">
-        <v>323897</v>
+        <v>331397</v>
       </c>
       <c r="E22" t="n">
-        <v>136988</v>
+        <v>137023</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>60365</v>
+        <v>50982</v>
       </c>
       <c r="D23" t="n">
-        <v>302885</v>
+        <v>331685</v>
       </c>
       <c r="E23" t="n">
-        <v>66710</v>
+        <v>83529</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-11171</v>
+        <v>31736</v>
       </c>
       <c r="D24" t="n">
-        <v>42456</v>
+        <v>14989</v>
       </c>
       <c r="E24" t="n">
-        <v>31733</v>
+        <v>31173</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4394827</v>
+        <v>4566735</v>
       </c>
       <c r="D25" t="n">
-        <v>4646415</v>
+        <v>4787072</v>
       </c>
       <c r="E25" t="n">
-        <v>5621481</v>
+        <v>5752700</v>
       </c>
     </row>
   </sheetData>
@@ -2591,19 +2591,19 @@
         <v>160000</v>
       </c>
       <c r="D3" t="n">
-        <v>69479</v>
+        <v>76079</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2611,11 +2611,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>50090</v>
+        <v>56690</v>
       </c>
     </row>
     <row r="4">
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>116958</v>
+        <v>136958</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>109070.5</v>
+        <v>129070.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,19 +2717,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>95080</v>
+        <v>101740</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>79420</v>
+        <v>86080</v>
       </c>
     </row>
     <row r="7">
@@ -2801,31 +2801,31 @@
         <v>160000</v>
       </c>
       <c r="D8" t="n">
-        <v>86200</v>
+        <v>21540</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>82422</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3778</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="9">
@@ -2969,19 +2969,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>91690</v>
+        <v>101690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>104.2%</t>
+          <t>115.6%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2989,11 +2989,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>85090</v>
+        <v>95090</v>
       </c>
     </row>
     <row r="13">
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>242538</v>
+        <v>212738</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>303.2%</t>
+          <t>265.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>289.4%</t>
+          <t>252.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>231558</v>
+        <v>201758</v>
       </c>
     </row>
     <row r="14">
@@ -3137,19 +3137,19 @@
         <v>96000</v>
       </c>
       <c r="D16" t="n">
-        <v>123572</v>
+        <v>130172</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>128.7%</t>
+          <t>135.6%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -3157,11 +3157,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>55772</v>
+        <v>62372</v>
       </c>
     </row>
     <row r="17">
@@ -3221,19 +3221,19 @@
         <v>88000</v>
       </c>
       <c r="D18" t="n">
-        <v>113998</v>
+        <v>117298</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>129.5%</t>
+          <t>133.3%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>106.6%</t>
+          <t>110.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -3241,11 +3241,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>93798</v>
+        <v>97098</v>
       </c>
     </row>
     <row r="19">
@@ -3347,19 +3347,19 @@
         <v>88000</v>
       </c>
       <c r="D21" t="n">
-        <v>45200</v>
+        <v>55200</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3367,11 +3367,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7200</v>
+        <v>17200</v>
       </c>
     </row>
     <row r="22">
@@ -3389,19 +3389,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>51200</v>
+        <v>78020</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3409,11 +3409,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>43600</v>
+        <v>70420</v>
       </c>
     </row>
     <row r="23">
@@ -3515,19 +3515,19 @@
         <v>120000</v>
       </c>
       <c r="D25" t="n">
-        <v>60994</v>
+        <v>65974</v>
       </c>
       <c r="E25" t="n">
         <v>10000</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3535,11 +3535,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>42944</v>
+        <v>47924</v>
       </c>
     </row>
     <row r="26">
@@ -3569,19 +3569,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>119.6%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>30326</v>
+        <v>35306</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>191370</v>
+        <v>186390</v>
       </c>
     </row>
     <row r="27">
@@ -3599,19 +3599,19 @@
         <v>80000</v>
       </c>
       <c r="D27" t="n">
-        <v>63460</v>
+        <v>58480</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3619,11 +3619,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>54780</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="28">
@@ -3641,19 +3641,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>68798</v>
+        <v>93598</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3661,11 +3661,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>43598</v>
+        <v>68398</v>
       </c>
     </row>
     <row r="29">
@@ -3695,19 +3695,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>22103</v>
+        <v>27083</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>81135</v>
+        <v>76155</v>
       </c>
     </row>
     <row r="30">
@@ -3725,19 +3725,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>114520</v>
+        <v>119500</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>89906.60000000001</v>
+        <v>94886.60000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>91118</v>
+        <v>106118</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>66338</v>
+        <v>81338</v>
       </c>
     </row>
     <row r="34">
@@ -3893,19 +3893,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>103217</v>
+        <v>113217</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3913,11 +3913,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>93717</v>
+        <v>103717</v>
       </c>
     </row>
     <row r="35">
@@ -3935,19 +3935,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>84230</v>
+        <v>89210</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>115.9%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>84230</v>
+        <v>89210</v>
       </c>
     </row>
     <row r="36">
@@ -4061,19 +4061,19 @@
         <v>240000</v>
       </c>
       <c r="D38" t="n">
-        <v>141820</v>
+        <v>143720</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -4081,11 +4081,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>46312</v>
+        <v>48212</v>
       </c>
     </row>
     <row r="39">
@@ -4199,19 +4199,19 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9977</v>
+        <v>14957</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>74081</v>
+        <v>69101</v>
       </c>
     </row>
   </sheetData>
@@ -4285,11 +4285,11 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>298048</v>
+        <v>314242</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4297,11 +4297,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>240681.33</v>
+        <v>256875.33</v>
       </c>
     </row>
     <row r="3">
@@ -4319,11 +4319,11 @@
         <v>150000</v>
       </c>
       <c r="D3" t="n">
-        <v>71044.10000000001</v>
+        <v>88544.10000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4331,11 +4331,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65544.10000000001</v>
+        <v>83044.10000000001</v>
       </c>
     </row>
     <row r="4">
@@ -4353,11 +4353,11 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>90598.67999999999</v>
+        <v>98098.67999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90598.67999999999</v>
+        <v>98098.67999999999</v>
       </c>
     </row>
     <row r="5">
@@ -4387,11 +4387,11 @@
         <v>150000</v>
       </c>
       <c r="D5" t="n">
-        <v>59480.8</v>
+        <v>59878.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4399,11 +4399,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>56880.8</v>
+        <v>57278.8</v>
       </c>
     </row>
     <row r="6">
@@ -4455,11 +4455,11 @@
         <v>50000</v>
       </c>
       <c r="D7" t="n">
-        <v>19988</v>
+        <v>29988</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19988</v>
+        <v>29988</v>
       </c>
     </row>
     <row r="8">
@@ -4523,7 +4523,7 @@
         <v>200000</v>
       </c>
       <c r="D9" t="n">
-        <v>66601.50999999999</v>
+        <v>66636.22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>66401.50999999999</v>
+        <v>66436.22</v>
       </c>
     </row>
     <row r="10">
@@ -4625,11 +4625,11 @@
         <v>200000</v>
       </c>
       <c r="D12" t="n">
-        <v>171278.4</v>
+        <v>178778.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4637,11 +4637,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>114678.4</v>
+        <v>122178.4</v>
       </c>
     </row>
     <row r="13">
@@ -4761,11 +4761,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>98956</v>
+        <v>93976</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>80756</v>
+        <v>75776</v>
       </c>
     </row>
     <row r="17">
@@ -4829,11 +4829,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>79397</v>
+        <v>80750.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>79397</v>
+        <v>80750.8</v>
       </c>
     </row>
     <row r="19">
@@ -4931,11 +4931,11 @@
         <v>60000</v>
       </c>
       <c r="D21" t="n">
-        <v>31674.55</v>
+        <v>32072.55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31674.55</v>
+        <v>32072.55</v>
       </c>
     </row>
     <row r="22">
@@ -4999,11 +4999,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>173956</v>
+        <v>186554</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>173956</v>
+        <v>186554</v>
       </c>
     </row>
     <row r="24">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>63822</v>
+        <v>80622</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>127.6%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>63822</v>
+        <v>80622</v>
       </c>
     </row>
     <row r="28">
@@ -5203,7 +5203,7 @@
         <v>160000</v>
       </c>
       <c r="D29" t="n">
-        <v>128968</v>
+        <v>145856</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5211,15 +5211,15 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>121968</v>
+        <v>121856</v>
       </c>
     </row>
     <row r="30">
@@ -5441,11 +5441,11 @@
         <v>100000</v>
       </c>
       <c r="D36" t="n">
-        <v>142174</v>
+        <v>144374</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>135576</v>
+        <v>137776</v>
       </c>
     </row>
     <row r="37">
@@ -5543,11 +5543,11 @@
         <v>120000</v>
       </c>
       <c r="D39" t="n">
-        <v>87750</v>
+        <v>99750</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -5555,11 +5555,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>81150</v>
+        <v>93150</v>
       </c>
     </row>
     <row r="40">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>622406</v>
+        <v>650706</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>134.9%</t>
+          <t>142.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>539756</v>
+        <v>568056</v>
       </c>
     </row>
     <row r="41">
@@ -5645,11 +5645,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>135166</v>
+        <v>135564</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127566</v>
+        <v>127964</v>
       </c>
     </row>
     <row r="43">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>233590.46</v>
+        <v>237393.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>233590.46</v>
+        <v>237393.46</v>
       </c>
     </row>
     <row r="46">
@@ -5781,11 +5781,11 @@
         <v>120000</v>
       </c>
       <c r="D46" t="n">
-        <v>56723</v>
+        <v>77723</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>56723</v>
+        <v>77723</v>
       </c>
     </row>
     <row r="47">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>237335.8</v>
+        <v>236335.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>237335.8</v>
+        <v>236335.8</v>
       </c>
     </row>
     <row r="54">
@@ -6053,11 +6053,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>287418</v>
+        <v>288214</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>120.1%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>287418</v>
+        <v>288214</v>
       </c>
     </row>
     <row r="55">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>140177</v>
+        <v>157175</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>130.2%</t>
+          <t>147.2%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6099,11 +6099,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>130177</v>
+        <v>147175</v>
       </c>
     </row>
     <row r="56">
@@ -6121,11 +6121,11 @@
         <v>80000</v>
       </c>
       <c r="D56" t="n">
-        <v>42388</v>
+        <v>52786</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -6133,11 +6133,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>37388</v>
+        <v>47786</v>
       </c>
     </row>
     <row r="57">
@@ -6223,11 +6223,11 @@
         <v>60000</v>
       </c>
       <c r="D59" t="n">
-        <v>134398</v>
+        <v>144398</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>210.7%</t>
+          <t>227.3%</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>126398</v>
+        <v>136398</v>
       </c>
     </row>
     <row r="60">
@@ -6291,11 +6291,11 @@
         <v>80000</v>
       </c>
       <c r="D61" t="n">
-        <v>62944</v>
+        <v>57964</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>62944</v>
+        <v>57964</v>
       </c>
     </row>
     <row r="62">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>63570</v>
+        <v>73570</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>47770</v>
+        <v>57770</v>
       </c>
     </row>
     <row r="63">
@@ -6359,11 +6359,11 @@
         <v>6000</v>
       </c>
       <c r="D63" t="n">
-        <v>20268</v>
+        <v>10268</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>337.8%</t>
+          <t>171.1%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>20268</v>
+        <v>10268</v>
       </c>
     </row>
   </sheetData>
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1354650.52</v>
+        <v>1418370.53</v>
       </c>
       <c r="D2" t="n">
-        <v>3808</v>
+        <v>4017</v>
       </c>
       <c r="E2" t="n">
-        <v>119169</v>
+        <v>129069</v>
       </c>
       <c r="F2" t="n">
-        <v>1235481.52</v>
+        <v>1289301.53</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1238526</v>
+        <v>1295676</v>
       </c>
       <c r="D3" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E3" t="n">
-        <v>119140</v>
+        <v>129040</v>
       </c>
       <c r="F3" t="n">
-        <v>1119386</v>
+        <v>1166636</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116124.52</v>
+        <v>122694.53</v>
       </c>
       <c r="D4" t="n">
-        <v>3570</v>
+        <v>3769</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>116095.52</v>
+        <v>122665.53</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1777488</v>
+        <v>1988824</v>
       </c>
       <c r="D5" t="n">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="E5" t="n">
-        <v>86210</v>
+        <v>117432</v>
       </c>
       <c r="F5" t="n">
-        <v>1691278</v>
+        <v>1871392</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1316136</v>
+        <v>1442646</v>
       </c>
       <c r="D6" t="n">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1293538</v>
+        <v>1420048</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>441352</v>
+        <v>526178</v>
       </c>
       <c r="D7" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E7" t="n">
-        <v>63612</v>
+        <v>94834</v>
       </c>
       <c r="F7" t="n">
-        <v>377740</v>
+        <v>431344</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2023212.69</v>
+        <v>2068959.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2014428.22</v>
+        <v>2060175.07</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1198345.9</v>
+        <v>1218203.38</v>
       </c>
       <c r="D9" t="n">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1196545.9</v>
+        <v>1216403.38</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>824866.79</v>
+        <v>850756.16</v>
       </c>
       <c r="D10" t="n">
-        <v>1428</v>
+        <v>1442</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>817882.3199999999</v>
+        <v>843771.6899999999</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>529608.4</v>
+        <v>577206.4</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11" t="n">
-        <v>129202</v>
+        <v>144800</v>
       </c>
       <c r="F11" t="n">
-        <v>400406.4</v>
+        <v>432406.4</v>
       </c>
     </row>
     <row r="12">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
     </row>
     <row r="13">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>140820</v>
+        <v>113000</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>93200</v>
+        <v>63400</v>
       </c>
       <c r="F13" t="n">
-        <v>47620</v>
+        <v>49600</v>
       </c>
     </row>
     <row r="14">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
       <c r="D15" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1354650.52</v>
+        <v>1418370.53</v>
       </c>
       <c r="C2" t="n">
-        <v>552232.1800000001</v>
+        <v>568156.74</v>
       </c>
       <c r="D2" t="n">
-        <v>100988.02</v>
+        <v>111932.58</v>
       </c>
       <c r="E2" t="n">
-        <v>7.45</v>
+        <v>7.89</v>
       </c>
       <c r="F2" t="n">
-        <v>451244.16</v>
+        <v>456224.16</v>
       </c>
       <c r="G2" t="n">
-        <v>33.31</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1777488</v>
+        <v>1988824</v>
       </c>
       <c r="C3" t="n">
-        <v>783252.99</v>
+        <v>812252.99</v>
       </c>
       <c r="D3" t="n">
         <v>45598</v>
       </c>
       <c r="E3" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="F3" t="n">
-        <v>737654.99</v>
+        <v>766654.99</v>
       </c>
       <c r="G3" t="n">
-        <v>41.5</v>
+        <v>38.55</v>
       </c>
     </row>
     <row r="4">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2023212.69</v>
+        <v>2068959.54</v>
       </c>
       <c r="C4" t="n">
         <v>28999</v>
@@ -6883,7 +6883,7 @@
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="5">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>529608.4</v>
+        <v>577206.4</v>
       </c>
       <c r="C5" t="n">
         <v>190400</v>
@@ -6908,7 +6908,7 @@
         <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>35.95</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="6">
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100788</v>
+        <v>102688</v>
       </c>
       <c r="C6" t="n">
         <v>156919.9</v>
@@ -6927,13 +6927,13 @@
         <v>2017.9</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="F6" t="n">
         <v>154902</v>
       </c>
       <c r="G6" t="n">
-        <v>153.69</v>
+        <v>150.85</v>
       </c>
     </row>
     <row r="7">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>140820</v>
+        <v>113000</v>
       </c>
       <c r="C7" t="n">
         <v>299246.67</v>
@@ -6952,13 +6952,13 @@
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>37.64</v>
+        <v>46.9</v>
       </c>
       <c r="F7" t="n">
         <v>246246.67</v>
       </c>
       <c r="G7" t="n">
-        <v>174.87</v>
+        <v>217.92</v>
       </c>
     </row>
     <row r="8">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128129.24</v>
+        <v>144128.24</v>
       </c>
       <c r="C9" t="n">
         <v>18998</v>
@@ -7002,13 +7002,13 @@
         <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>13.11</v>
+        <v>11.66</v>
       </c>
     </row>
   </sheetData>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>1171572.82</v>
+        <v>1183758.82</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="C3" t="n">
-        <v>354763.32</v>
+        <v>370326.32</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" t="n">
-        <v>141622.24</v>
+        <v>158622.24</v>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C6" t="n">
-        <v>41665.66</v>
+        <v>41765.22</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>37781.7</v>
+        <v>37800.7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7166,10 +7166,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C9" t="n">
-        <v>24275</v>
+        <v>24332</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="D7" t="n">
-        <v>88046</v>
+        <v>118012</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>710</v>
+        <v>734</v>
       </c>
       <c r="D8" t="n">
-        <v>53913.82</v>
+        <v>107197.82</v>
       </c>
     </row>
     <row r="9">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D9" t="n">
-        <v>13675</v>
+        <v>13774.56</v>
       </c>
     </row>
     <row r="10">
@@ -7433,10 +7433,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>10438.7</v>
+        <v>10457.7</v>
       </c>
     </row>
     <row r="12">
@@ -7451,10 +7451,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>4042</v>
+        <v>4099</v>
       </c>
     </row>
     <row r="13">
@@ -7676,91 +7676,91 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>76331</v>
+        <v>61556.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>58699</v>
+        <v>46520</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>61829</v>
+        <v>21766</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>25029.5</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>课程3组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>21780</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="30">
@@ -7771,14 +7771,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>13200</v>
+        <v>61829</v>
       </c>
     </row>
     <row r="31">
@@ -7789,176 +7789,176 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>10256.66</v>
+        <v>25029.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>61556.4</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>36560</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>21766</v>
+        <v>10256.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D35" t="n">
-        <v>6600</v>
+        <v>97854</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>2490</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D37" t="n">
-        <v>75533.39999999999</v>
+        <v>5951</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D38" t="n">
-        <v>20500</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>9000</v>
+        <v>76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>398</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41">
@@ -7969,38 +7969,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>87854</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8027,64 +8027,64 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>5951</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>2545</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>76</v>
+        <v>62620</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>76</v>
+        <v>16637</v>
       </c>
     </row>
     <row r="48">
@@ -8095,50 +8095,50 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>62620</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D49" t="n">
-        <v>14820</v>
+        <v>74628</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>11657</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="51">
@@ -8149,50 +8149,50 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>74628</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>12000</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>318</v>
+        <v>398</v>
       </c>
     </row>
     <row r="54">
@@ -8203,38 +8203,38 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>68500</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>398</v>
+        <v>44494.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8243,10 +8243,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>16910</v>
       </c>
     </row>
     <row r="57">
@@ -8257,14 +8257,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>44494.67</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="58">
@@ -8275,122 +8275,122 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>16910</v>
+        <v>357</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>6500</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>357</v>
+        <v>31030</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>33440</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>31030</v>
+        <v>19233.35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C63" t="n">
         <v>6</v>
       </c>
       <c r="D63" t="n">
-        <v>27200</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>11299</v>
+        <v>23689</v>
       </c>
     </row>
     <row r="65">
@@ -8401,50 +8401,50 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>9009</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>19233.35</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
-        <v>18000</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="68">
@@ -8683,10 +8683,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
-        <v>630684.99</v>
+        <v>659684.99</v>
       </c>
     </row>
     <row r="3">
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
-        <v>256321.56</v>
+        <v>271261.56</v>
       </c>
     </row>
     <row r="4">
@@ -8844,10 +8844,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="C2" t="n">
-        <v>327025.35</v>
+        <v>337108.35</v>
       </c>
     </row>
     <row r="3">
@@ -8857,10 +8857,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" t="n">
-        <v>235820</v>
+        <v>247801</v>
       </c>
     </row>
     <row r="4">
@@ -8873,7 +8873,7 @@
         <v>221</v>
       </c>
       <c r="C4" t="n">
-        <v>197139.22</v>
+        <v>202100.22</v>
       </c>
     </row>
     <row r="5">
@@ -8883,10 +8883,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C5" t="n">
-        <v>196563.4</v>
+        <v>196696.4</v>
       </c>
     </row>
     <row r="6">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>127432</v>
+        <v>127461</v>
       </c>
     </row>
     <row r="8">
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>113323</v>
+        <v>113342</v>
       </c>
     </row>
     <row r="9">
@@ -8935,10 +8935,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>108229.4</v>
+        <v>108267.4</v>
       </c>
     </row>
     <row r="10">
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C10" t="n">
-        <v>73492.8</v>
+        <v>80739.8</v>
       </c>
     </row>
     <row r="11">
@@ -8961,10 +8961,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>70748.89999999999</v>
+        <v>70796.89999999999</v>
       </c>
     </row>
     <row r="12">
@@ -8987,49 +8987,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C13" t="n">
-        <v>47434</v>
+        <v>47535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="C14" t="n">
-        <v>37219</v>
+        <v>39260.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>33557</v>
+        <v>37219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古自治区</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>31824</v>
+        <v>33557</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -529,41 +529,41 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>665361</v>
+        <v>724921</v>
       </c>
       <c r="E2" t="n">
         <v>132095</v>
       </c>
       <c r="F2" t="n">
-        <v>533266</v>
+        <v>592826</v>
       </c>
       <c r="G2" t="n">
         <v>10398</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>488983</v>
+        <v>491652</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+36.1%</t>
+          <t>+47.4%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>234758</v>
+        <v>237237</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+127.2%</t>
+          <t>+149.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17018</v>
+        <v>18355</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-88.2%</t>
+          <t>-89.1%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-23766</v>
+        <v>-22429</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-108.4%</t>
+          <t>-108.9%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -639,41 +639,41 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>753934</v>
+        <v>819274</v>
       </c>
       <c r="E4" t="n">
-        <v>138932</v>
+        <v>143912</v>
       </c>
       <c r="F4" t="n">
-        <v>615001</v>
+        <v>675361</v>
       </c>
       <c r="G4" t="n">
         <v>22000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>707550</v>
+        <v>720564</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+6.6%</t>
+          <t>+13.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>530545</v>
+        <v>543379</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+15.9%</t>
+          <t>+24.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>479630</v>
+        <v>479649</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>351424</v>
+        <v>351443</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -753,41 +753,41 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>740292</v>
+        <v>779833</v>
       </c>
       <c r="E6" t="n">
         <v>64470</v>
       </c>
       <c r="F6" t="n">
-        <v>675822</v>
+        <v>715363</v>
       </c>
       <c r="G6" t="n">
         <v>49820</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>420439</v>
+        <v>445025</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+76.1%</t>
+          <t>+75.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>310042</v>
+        <v>334199</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+118.0%</t>
+          <t>+114.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -810,41 +810,41 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>461634</v>
+        <v>486534</v>
       </c>
       <c r="E7" t="n">
-        <v>94077</v>
+        <v>123857</v>
       </c>
       <c r="F7" t="n">
-        <v>367557</v>
+        <v>362677</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>368797</v>
+        <v>375548</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+25.2%</t>
+          <t>+29.6%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>260573</v>
+        <v>266641</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+41.1%</t>
+          <t>+36.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -867,41 +867,41 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>417948</v>
+        <v>437928</v>
       </c>
       <c r="E8" t="n">
         <v>52608</v>
       </c>
       <c r="F8" t="n">
-        <v>365340</v>
+        <v>385320</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>403027</v>
+        <v>403536</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>+8.5%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>320606</v>
+        <v>321039</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+14.0%</t>
+          <t>+20.0%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -924,25 +924,25 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1034248</v>
+        <v>1235648</v>
       </c>
       <c r="E9" t="n">
-        <v>419460</v>
+        <v>444276</v>
       </c>
       <c r="F9" t="n">
-        <v>614788</v>
+        <v>791372</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+6.1%</t>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>+15.2%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -981,50 +981,50 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1949382</v>
+        <v>1998285</v>
       </c>
       <c r="E10" t="n">
         <v>49508</v>
       </c>
       <c r="F10" t="n">
-        <v>1899874</v>
+        <v>1948777</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1739822</v>
+        <v>1917683</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+12.0%</t>
+          <t>+4.2%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1739822</v>
+        <v>1917683</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>799867</v>
+        <v>809724</v>
       </c>
       <c r="P10" t="n">
-        <v>1100006</v>
+        <v>1139052</v>
       </c>
       <c r="Q10" t="n">
-        <v>1869094</v>
+        <v>1917997</v>
       </c>
     </row>
     <row r="11">
@@ -1042,13 +1042,13 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>273503</v>
+        <v>273522</v>
       </c>
       <c r="E11" t="n">
         <v>54233</v>
       </c>
       <c r="F11" t="n">
-        <v>219270</v>
+        <v>219289</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
@@ -1062,32 +1062,32 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>336174</v>
+        <v>345070</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>290247</v>
+        <v>299143</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="N11" t="n">
         <v>234</v>
       </c>
       <c r="O11" t="n">
-        <v>63965</v>
+        <v>63984</v>
       </c>
       <c r="P11" t="n">
         <v>155071</v>
       </c>
       <c r="Q11" t="n">
-        <v>108759</v>
+        <v>108778</v>
       </c>
     </row>
     <row r="12">
@@ -1105,39 +1105,39 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>490978</v>
+        <v>511376</v>
       </c>
       <c r="E12" t="n">
         <v>30095</v>
       </c>
       <c r="F12" t="n">
-        <v>460883</v>
+        <v>481281</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>379033</v>
+        <v>380227</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+29.5%</t>
+          <t>+34.5%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>376805</v>
+        <v>377999</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+22.3%</t>
+          <t>+27.3%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1145,7 +1145,7 @@
         <v>67250</v>
       </c>
       <c r="P12" t="n">
-        <v>393633</v>
+        <v>414031</v>
       </c>
       <c r="Q12" t="n">
         <v>48527</v>
@@ -1166,52 +1166,52 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>669312</v>
+        <v>704877</v>
       </c>
       <c r="E13" t="n">
-        <v>68262</v>
+        <v>79281</v>
       </c>
       <c r="F13" t="n">
-        <v>601050</v>
+        <v>625596</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>663796</v>
+        <v>693613</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>586987</v>
+        <v>616804</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>31727</v>
+        <v>32292</v>
       </c>
       <c r="O13" t="n">
-        <v>48748</v>
+        <v>48729</v>
       </c>
       <c r="P13" t="n">
-        <v>520575</v>
+        <v>544575</v>
       </c>
       <c r="Q13" t="n">
-        <v>106128</v>
+        <v>106674</v>
       </c>
     </row>
     <row r="14">
@@ -1229,52 +1229,52 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>325009</v>
+        <v>336058</v>
       </c>
       <c r="E14" t="n">
-        <v>14866</v>
+        <v>22866</v>
       </c>
       <c r="F14" t="n">
-        <v>310143</v>
+        <v>313192</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>509092</v>
+        <v>583359</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>431914</v>
+        <v>506181</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-28.2%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>27923</v>
+        <v>28374</v>
       </c>
       <c r="O14" t="n">
-        <v>53535</v>
+        <v>56133</v>
       </c>
       <c r="P14" t="n">
         <v>228685</v>
       </c>
       <c r="Q14" t="n">
-        <v>84007</v>
+        <v>84458</v>
       </c>
     </row>
     <row r="15">
@@ -1292,50 +1292,50 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>143367</v>
+        <v>143785</v>
       </c>
       <c r="E15" t="n">
         <v>15857</v>
       </c>
       <c r="F15" t="n">
-        <v>127510</v>
+        <v>127928</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>206932</v>
+        <v>210892</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>191607</v>
+        <v>195567</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>8574</v>
+        <v>8992</v>
       </c>
       <c r="P15" t="n">
         <v>118936</v>
       </c>
       <c r="Q15" t="n">
-        <v>39142</v>
+        <v>39162</v>
       </c>
     </row>
     <row r="16">
@@ -1353,44 +1353,44 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>349171</v>
+        <v>349967</v>
       </c>
       <c r="E16" t="n">
         <v>68917</v>
       </c>
       <c r="F16" t="n">
-        <v>280254</v>
+        <v>281050</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>323492</v>
+        <v>323899</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+7.9%</t>
+          <t>+8.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>270492</v>
+        <v>270899</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+3.6%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12527</v>
+        <v>13323</v>
       </c>
       <c r="P16" t="n">
         <v>267727</v>
@@ -1414,49 +1414,49 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>621730</v>
+        <v>625926</v>
       </c>
       <c r="E17" t="n">
         <v>105631</v>
       </c>
       <c r="F17" t="n">
-        <v>516099</v>
+        <v>520295</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>490291</v>
+        <v>565057</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>+26.8%</t>
+          <t>+10.8%</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>393625</v>
+        <v>468391</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+31.1%</t>
+          <t>+11.1%</t>
         </is>
       </c>
       <c r="N17" t="n">
         <v>69668</v>
       </c>
       <c r="O17" t="n">
-        <v>44534</v>
+        <v>45132</v>
       </c>
       <c r="P17" t="n">
-        <v>402097</v>
+        <v>405695</v>
       </c>
       <c r="Q17" t="n">
         <v>143818</v>
@@ -1477,52 +1477,52 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1123653</v>
+        <v>1147251</v>
       </c>
       <c r="E18" t="n">
-        <v>142696</v>
+        <v>162496</v>
       </c>
       <c r="F18" t="n">
-        <v>980956</v>
+        <v>984754</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>716752</v>
+        <v>745371</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+56.8%</t>
+          <t>+53.9%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>563946</v>
+        <v>592546</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+73.9%</t>
+          <t>+66.2%</t>
         </is>
       </c>
       <c r="N18" t="n">
         <v>7250</v>
       </c>
       <c r="O18" t="n">
-        <v>230267</v>
+        <v>247265</v>
       </c>
       <c r="P18" t="n">
-        <v>743439</v>
+        <v>730239</v>
       </c>
       <c r="Q18" t="n">
-        <v>553407</v>
+        <v>566607</v>
       </c>
     </row>
     <row r="19">
@@ -1540,13 +1540,13 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>549123</v>
+        <v>549923</v>
       </c>
       <c r="E19" t="n">
-        <v>86946</v>
+        <v>86965</v>
       </c>
       <c r="F19" t="n">
-        <v>462177</v>
+        <v>462958</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
@@ -1560,32 +1560,32 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>383422</v>
+        <v>410852</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+43.2%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>230376</v>
+        <v>257806</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+100.6%</t>
+          <t>+79.6%</t>
         </is>
       </c>
       <c r="N19" t="n">
         <v>61427</v>
       </c>
       <c r="O19" t="n">
-        <v>69553</v>
+        <v>70334</v>
       </c>
       <c r="P19" t="n">
         <v>331397</v>
       </c>
       <c r="Q19" t="n">
-        <v>137023</v>
+        <v>137004</v>
       </c>
     </row>
     <row r="20">
@@ -1603,50 +1603,50 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>498150</v>
+        <v>526499</v>
       </c>
       <c r="E20" t="n">
-        <v>115483</v>
+        <v>133502</v>
       </c>
       <c r="F20" t="n">
-        <v>382667</v>
+        <v>392997</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>635920</v>
+        <v>664820</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>552801</v>
+        <v>581682</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>50982</v>
+        <v>52105</v>
       </c>
       <c r="P20" t="n">
-        <v>331685</v>
+        <v>340892</v>
       </c>
       <c r="Q20" t="n">
-        <v>83529</v>
+        <v>100665</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>311960</v>
+        <v>317608</v>
       </c>
       <c r="E21" t="n">
-        <v>265235</v>
+        <v>286208</v>
       </c>
       <c r="F21" t="n">
-        <v>46725</v>
+        <v>31400</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -1685,13 +1685,13 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>31736</v>
+        <v>19911</v>
       </c>
       <c r="P21" t="n">
-        <v>14989</v>
+        <v>11489</v>
       </c>
       <c r="Q21" t="n">
-        <v>31173</v>
+        <v>29948</v>
       </c>
     </row>
     <row r="22">
@@ -1709,54 +1709,54 @@
         <v>13000000</v>
       </c>
       <c r="D22" t="n">
-        <v>11628589</v>
+        <v>12219048</v>
       </c>
       <c r="E22" t="n">
-        <v>2076953</v>
+        <v>2214359</v>
       </c>
       <c r="F22" t="n">
-        <v>9551636</v>
+        <v>10004688</v>
       </c>
       <c r="G22" t="n">
         <v>256182</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10245111</v>
+        <v>10750114</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+13.5%</t>
+          <t>+13.7%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8299950</v>
+        <v>8803357</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+15.1%</t>
+          <t>+13.6%</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>198229</v>
+        <v>199245</v>
       </c>
       <c r="O22" t="n">
-        <v>4566735</v>
+        <v>4939224</v>
       </c>
       <c r="P22" t="n">
-        <v>4787072</v>
+        <v>4866621</v>
       </c>
       <c r="Q22" t="n">
-        <v>5752700</v>
+        <v>6158056</v>
       </c>
     </row>
   </sheetData>
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>627.8</v>
+        <v>400.8</v>
       </c>
       <c r="E2" t="n">
-        <v>12374</v>
+        <v>14946</v>
       </c>
     </row>
     <row r="3">
@@ -1826,16 +1826,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>722</v>
+        <v>768.2</v>
       </c>
       <c r="E3" t="n">
-        <v>16377</v>
+        <v>41316</v>
       </c>
     </row>
     <row r="4">
@@ -1845,16 +1845,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>585</v>
+        <v>840</v>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D4" t="n">
-        <v>1423.9</v>
+        <v>1044.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2302</v>
+        <v>2270</v>
       </c>
     </row>
   </sheetData>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2601445</v>
+        <v>2776006</v>
       </c>
       <c r="D2" t="n">
         <v>47793</v>
       </c>
       <c r="E2" t="n">
-        <v>2180249</v>
+        <v>2329990</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>483749</v>
+        <v>660333</v>
       </c>
       <c r="D3" t="n">
         <v>131038</v>
       </c>
       <c r="E3" t="n">
-        <v>319941</v>
+        <v>496525</v>
       </c>
     </row>
     <row r="4">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1449802</v>
+        <v>1482971</v>
       </c>
       <c r="D4" t="n">
-        <v>4593251</v>
+        <v>4676300</v>
       </c>
       <c r="E4" t="n">
-        <v>3221336</v>
+        <v>3301591</v>
       </c>
     </row>
     <row r="5">
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>523922</v>
+        <v>583482</v>
       </c>
       <c r="D5" t="n">
         <v>9344</v>
       </c>
       <c r="E5" t="n">
-        <v>544480</v>
+        <v>604040</v>
       </c>
     </row>
     <row r="6">
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>599292</v>
+        <v>659652</v>
       </c>
       <c r="D7" t="n">
         <v>15710</v>
       </c>
       <c r="E7" t="n">
-        <v>581419</v>
+        <v>626959</v>
       </c>
     </row>
     <row r="8">
@@ -2123,13 +2123,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>668858</v>
+        <v>708399</v>
       </c>
       <c r="D9" t="n">
         <v>6965</v>
       </c>
       <c r="E9" t="n">
-        <v>558438</v>
+        <v>597979</v>
       </c>
     </row>
     <row r="10">
@@ -2144,13 +2144,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>368338</v>
+        <v>363458</v>
       </c>
       <c r="D10" t="n">
         <v>-781</v>
       </c>
       <c r="E10" t="n">
-        <v>216469</v>
+        <v>211589</v>
       </c>
     </row>
     <row r="11">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>354107</v>
+        <v>374087</v>
       </c>
       <c r="D11" t="n">
         <v>11233</v>
       </c>
       <c r="E11" t="n">
-        <v>311350</v>
+        <v>321330</v>
       </c>
     </row>
     <row r="12">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>483750</v>
+        <v>660334</v>
       </c>
       <c r="D12" t="n">
         <v>131038</v>
       </c>
       <c r="E12" t="n">
-        <v>319942</v>
+        <v>496526</v>
       </c>
     </row>
     <row r="13">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>799867</v>
+        <v>809724</v>
       </c>
       <c r="D13" t="n">
-        <v>1100006</v>
+        <v>1139052</v>
       </c>
       <c r="E13" t="n">
-        <v>1869094</v>
+        <v>1917997</v>
       </c>
     </row>
     <row r="14">
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63965</v>
+        <v>63984</v>
       </c>
       <c r="D14" t="n">
         <v>155071</v>
       </c>
       <c r="E14" t="n">
-        <v>108759</v>
+        <v>108778</v>
       </c>
     </row>
     <row r="15">
@@ -2252,7 +2252,7 @@
         <v>67250</v>
       </c>
       <c r="D15" t="n">
-        <v>393633</v>
+        <v>414031</v>
       </c>
       <c r="E15" t="n">
         <v>48527</v>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48748</v>
+        <v>48729</v>
       </c>
       <c r="D16" t="n">
-        <v>520575</v>
+        <v>544575</v>
       </c>
       <c r="E16" t="n">
-        <v>106128</v>
+        <v>106674</v>
       </c>
     </row>
     <row r="17">
@@ -2291,13 +2291,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53535</v>
+        <v>56133</v>
       </c>
       <c r="D17" t="n">
         <v>228685</v>
       </c>
       <c r="E17" t="n">
-        <v>84007</v>
+        <v>84458</v>
       </c>
     </row>
     <row r="18">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8574</v>
+        <v>8992</v>
       </c>
       <c r="D18" t="n">
         <v>118936</v>
       </c>
       <c r="E18" t="n">
-        <v>39142</v>
+        <v>39162</v>
       </c>
     </row>
     <row r="19">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12527</v>
+        <v>13323</v>
       </c>
       <c r="D19" t="n">
         <v>267727</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>44534</v>
+        <v>45132</v>
       </c>
       <c r="D20" t="n">
-        <v>402097</v>
+        <v>405695</v>
       </c>
       <c r="E20" t="n">
         <v>143818</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>230267</v>
+        <v>247265</v>
       </c>
       <c r="D21" t="n">
-        <v>743439</v>
+        <v>730239</v>
       </c>
       <c r="E21" t="n">
-        <v>553407</v>
+        <v>566607</v>
       </c>
     </row>
     <row r="22">
@@ -2396,13 +2396,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>69553</v>
+        <v>70334</v>
       </c>
       <c r="D22" t="n">
         <v>331397</v>
       </c>
       <c r="E22" t="n">
-        <v>137023</v>
+        <v>137004</v>
       </c>
     </row>
     <row r="23">
@@ -2417,13 +2417,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50982</v>
+        <v>52105</v>
       </c>
       <c r="D23" t="n">
-        <v>331685</v>
+        <v>340892</v>
       </c>
       <c r="E23" t="n">
-        <v>83529</v>
+        <v>100665</v>
       </c>
     </row>
     <row r="24">
@@ -2438,13 +2438,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>31736</v>
+        <v>19911</v>
       </c>
       <c r="D24" t="n">
-        <v>14989</v>
+        <v>11489</v>
       </c>
       <c r="E24" t="n">
-        <v>31173</v>
+        <v>29948</v>
       </c>
     </row>
     <row r="25">
@@ -2459,13 +2459,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4566735</v>
+        <v>4939224</v>
       </c>
       <c r="D25" t="n">
-        <v>4787072</v>
+        <v>4866621</v>
       </c>
       <c r="E25" t="n">
-        <v>5752700</v>
+        <v>6158056</v>
       </c>
     </row>
   </sheetData>
@@ -2633,19 +2633,19 @@
         <v>120000</v>
       </c>
       <c r="D4" t="n">
-        <v>61996</v>
+        <v>86796</v>
       </c>
       <c r="E4" t="n">
         <v>10398</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17436</v>
+        <v>42236</v>
       </c>
     </row>
     <row r="5">
@@ -2675,19 +2675,19 @@
         <v>120000</v>
       </c>
       <c r="D5" t="n">
-        <v>136958</v>
+        <v>166738</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>138.9%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>107.6%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2695,11 +2695,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>129070.5</v>
+        <v>158850.5</v>
       </c>
     </row>
     <row r="6">
@@ -2717,19 +2717,19 @@
         <v>120000</v>
       </c>
       <c r="D6" t="n">
-        <v>101740</v>
+        <v>106720</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -2737,11 +2737,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>86080</v>
+        <v>91060</v>
       </c>
     </row>
     <row r="7">
@@ -2843,19 +2843,19 @@
         <v>80000</v>
       </c>
       <c r="D9" t="n">
-        <v>43080</v>
+        <v>48060</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>31501</v>
+        <v>36481</v>
       </c>
     </row>
     <row r="10">
@@ -2885,19 +2885,19 @@
         <v>160000</v>
       </c>
       <c r="D10" t="n">
-        <v>119352</v>
+        <v>129352</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>111393</v>
+        <v>121393</v>
       </c>
     </row>
     <row r="11">
@@ -2927,19 +2927,19 @@
         <v>120000</v>
       </c>
       <c r="D11" t="n">
-        <v>85418</v>
+        <v>90418</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2947,11 +2947,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>71478</v>
+        <v>76478</v>
       </c>
     </row>
     <row r="12">
@@ -2969,19 +2969,19 @@
         <v>88000</v>
       </c>
       <c r="D12" t="n">
-        <v>101690</v>
+        <v>111690</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>115.6%</t>
+          <t>126.9%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2989,11 +2989,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>95090</v>
+        <v>105090</v>
       </c>
     </row>
     <row r="13">
@@ -3011,19 +3011,19 @@
         <v>80000</v>
       </c>
       <c r="D13" t="n">
-        <v>212738</v>
+        <v>357538</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>265.9%</t>
+          <t>446.9%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>252.2%</t>
+          <t>433.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>201758</v>
+        <v>346558</v>
       </c>
     </row>
     <row r="14">
@@ -3095,19 +3095,19 @@
         <v>80000</v>
       </c>
       <c r="D15" t="n">
-        <v>10398</v>
+        <v>11398</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -3115,11 +3115,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-2802</v>
+        <v>-1802</v>
       </c>
     </row>
     <row r="16">
@@ -3233,19 +3233,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>110.3%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>20200</v>
+        <v>38416</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>97098</v>
+        <v>78882</v>
       </c>
     </row>
     <row r="19">
@@ -3317,19 +3317,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6600</v>
+        <v>13200</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>87820</v>
+        <v>81220</v>
       </c>
     </row>
     <row r="21">
@@ -3389,19 +3389,19 @@
         <v>80000</v>
       </c>
       <c r="D22" t="n">
-        <v>78020</v>
+        <v>123620</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>154.5%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>145.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3409,11 +3409,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>70420</v>
+        <v>116020</v>
       </c>
     </row>
     <row r="23">
@@ -3557,19 +3557,19 @@
         <v>160000</v>
       </c>
       <c r="D26" t="n">
-        <v>221696</v>
+        <v>253096</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>138.6%</t>
+          <t>158.2%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3577,11 +3577,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>186390</v>
+        <v>217790</v>
       </c>
     </row>
     <row r="27">
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8680</v>
+        <v>13660</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>49800</v>
+        <v>44820</v>
       </c>
     </row>
     <row r="28">
@@ -3641,19 +3641,19 @@
         <v>144000</v>
       </c>
       <c r="D28" t="n">
-        <v>93598</v>
+        <v>108418</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3661,11 +3661,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>68398</v>
+        <v>83218</v>
       </c>
     </row>
     <row r="29">
@@ -3683,19 +3683,19 @@
         <v>128000</v>
       </c>
       <c r="D29" t="n">
-        <v>103238</v>
+        <v>114818</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>76155</v>
+        <v>87735</v>
       </c>
     </row>
     <row r="30">
@@ -3725,19 +3725,19 @@
         <v>128000</v>
       </c>
       <c r="D30" t="n">
-        <v>119500</v>
+        <v>127040</v>
       </c>
       <c r="E30" t="n">
         <v>12000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>102.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3745,11 +3745,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>94886.60000000001</v>
+        <v>102426.6</v>
       </c>
     </row>
     <row r="31">
@@ -3767,31 +3767,31 @@
         <v>160000</v>
       </c>
       <c r="D31" t="n">
-        <v>250094</v>
+        <v>265034</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>156.3%</t>
+          <t>165.6%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>113.1%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>54340</v>
+        <v>84120</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>195754</v>
+        <v>180914</v>
       </c>
     </row>
     <row r="32">
@@ -3851,19 +3851,19 @@
         <v>120000</v>
       </c>
       <c r="D33" t="n">
-        <v>106118</v>
+        <v>111098</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>88.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3871,11 +3871,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>81338</v>
+        <v>86318</v>
       </c>
     </row>
     <row r="34">
@@ -3893,19 +3893,19 @@
         <v>120000</v>
       </c>
       <c r="D34" t="n">
-        <v>113217</v>
+        <v>127858</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3913,11 +3913,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>103717</v>
+        <v>118358</v>
       </c>
     </row>
     <row r="35">
@@ -3935,19 +3935,19 @@
         <v>120000</v>
       </c>
       <c r="D35" t="n">
-        <v>89210</v>
+        <v>104150</v>
       </c>
       <c r="E35" t="n">
         <v>49820</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>115.9%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>89210</v>
+        <v>104150</v>
       </c>
     </row>
     <row r="36">
@@ -3977,19 +3977,19 @@
         <v>96000</v>
       </c>
       <c r="D36" t="n">
-        <v>126874</v>
+        <v>131854</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>137.3%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>129.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3997,11 +3997,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>118914</v>
+        <v>123894</v>
       </c>
     </row>
     <row r="37">
@@ -4019,19 +4019,19 @@
         <v>104000</v>
       </c>
       <c r="D37" t="n">
-        <v>150816</v>
+        <v>155796</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>145.0%</t>
+          <t>149.8%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>137.4%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4039,11 +4039,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>137876</v>
+        <v>142856</v>
       </c>
     </row>
     <row r="38">
@@ -4187,19 +4187,19 @@
         <v>80000</v>
       </c>
       <c r="D41" t="n">
-        <v>84058</v>
+        <v>89038</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4207,11 +4207,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>69101</v>
+        <v>74081</v>
       </c>
     </row>
   </sheetData>
@@ -4285,23 +4285,23 @@
         <v>230000</v>
       </c>
       <c r="D2" t="n">
-        <v>314242</v>
+        <v>349259</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>57366.67</v>
+        <v>68366.67</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>256875.33</v>
+        <v>280892.33</v>
       </c>
     </row>
     <row r="3">
@@ -4591,11 +4591,11 @@
         <v>100000</v>
       </c>
       <c r="D11" t="n">
-        <v>27500</v>
+        <v>28300</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27500</v>
+        <v>28300</v>
       </c>
     </row>
     <row r="12">
@@ -4761,11 +4761,11 @@
         <v>120000</v>
       </c>
       <c r="D16" t="n">
-        <v>93976</v>
+        <v>94374</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>75776</v>
+        <v>76174</v>
       </c>
     </row>
     <row r="17">
@@ -4795,11 +4795,11 @@
         <v>50000</v>
       </c>
       <c r="D17" t="n">
-        <v>29576</v>
+        <v>29974</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4811,7 +4811,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29576</v>
+        <v>29974</v>
       </c>
     </row>
     <row r="18">
@@ -4829,11 +4829,11 @@
         <v>280000</v>
       </c>
       <c r="D18" t="n">
-        <v>80750.8</v>
+        <v>81348.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80750.8</v>
+        <v>81348.8</v>
       </c>
     </row>
     <row r="19">
@@ -4863,23 +4863,23 @@
         <v>180000</v>
       </c>
       <c r="D19" t="n">
-        <v>129937.4</v>
+        <v>130387.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>124937.4</v>
+        <v>117387.7</v>
       </c>
     </row>
     <row r="20">
@@ -4897,11 +4897,11 @@
         <v>220000</v>
       </c>
       <c r="D20" t="n">
-        <v>81188.7</v>
+        <v>91188.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4909,11 +4909,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77188.7</v>
+        <v>87188.7</v>
       </c>
     </row>
     <row r="21">
@@ -4999,11 +4999,11 @@
         <v>200000</v>
       </c>
       <c r="D23" t="n">
-        <v>186554</v>
+        <v>204150</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>186554</v>
+        <v>204150</v>
       </c>
     </row>
     <row r="24">
@@ -5067,11 +5067,11 @@
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>124440</v>
+        <v>134440</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5079,11 +5079,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>114640</v>
+        <v>124640</v>
       </c>
     </row>
     <row r="26">
@@ -5105,19 +5105,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>51552</v>
+        <v>41552</v>
       </c>
     </row>
     <row r="27">
@@ -5135,11 +5135,11 @@
         <v>50000</v>
       </c>
       <c r="D27" t="n">
-        <v>80622</v>
+        <v>81020</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>162.0%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>80622</v>
+        <v>81020</v>
       </c>
     </row>
     <row r="28">
@@ -5339,11 +5339,11 @@
         <v>180000</v>
       </c>
       <c r="D33" t="n">
-        <v>160667.64</v>
+        <v>162765.64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -5351,11 +5351,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126867.64</v>
+        <v>128965.64</v>
       </c>
     </row>
     <row r="34">
@@ -5407,11 +5407,11 @@
         <v>130000</v>
       </c>
       <c r="D35" t="n">
-        <v>104240.92</v>
+        <v>104838.92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>97640.92</v>
+        <v>98238.92</v>
       </c>
     </row>
     <row r="36">
@@ -5475,11 +5475,11 @@
         <v>40000</v>
       </c>
       <c r="D37" t="n">
-        <v>14288</v>
+        <v>15788</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14288</v>
+        <v>15788</v>
       </c>
     </row>
     <row r="38">
@@ -5547,19 +5547,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6600</v>
+        <v>26400</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>93150</v>
+        <v>73350</v>
       </c>
     </row>
     <row r="40">
@@ -5577,11 +5577,11 @@
         <v>400000</v>
       </c>
       <c r="D40" t="n">
-        <v>650706</v>
+        <v>660706.01</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>142.0%</t>
+          <t>144.5%</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -5589,11 +5589,11 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>568056</v>
+        <v>578056.01</v>
       </c>
     </row>
     <row r="41">
@@ -5611,11 +5611,11 @@
         <v>120000</v>
       </c>
       <c r="D41" t="n">
-        <v>104869</v>
+        <v>111469</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>104869</v>
+        <v>111469</v>
       </c>
     </row>
     <row r="42">
@@ -5645,11 +5645,11 @@
         <v>105000</v>
       </c>
       <c r="D42" t="n">
-        <v>135564</v>
+        <v>142164</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>121.9%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -5657,11 +5657,11 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>127964</v>
+        <v>134564</v>
       </c>
     </row>
     <row r="43">
@@ -5679,11 +5679,11 @@
         <v>105000</v>
       </c>
       <c r="D43" t="n">
-        <v>126947</v>
+        <v>127345</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -5691,11 +5691,11 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>94724.76000000001</v>
+        <v>95122.76000000001</v>
       </c>
     </row>
     <row r="44">
@@ -5747,11 +5747,11 @@
         <v>270000</v>
       </c>
       <c r="D45" t="n">
-        <v>237393.46</v>
+        <v>241686.46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>237393.46</v>
+        <v>241686.46</v>
       </c>
     </row>
     <row r="46">
@@ -5815,11 +5815,11 @@
         <v>250000</v>
       </c>
       <c r="D47" t="n">
-        <v>228917</v>
+        <v>233563</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>228917</v>
+        <v>233563</v>
       </c>
     </row>
     <row r="48">
@@ -5849,11 +5849,11 @@
         <v>210000</v>
       </c>
       <c r="D48" t="n">
-        <v>162490.4</v>
+        <v>155121.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>162490.4</v>
+        <v>155121.4</v>
       </c>
     </row>
     <row r="49">
@@ -5883,11 +5883,11 @@
         <v>230000</v>
       </c>
       <c r="D49" t="n">
-        <v>286122.04</v>
+        <v>297151.04</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>129.2%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>286122.04</v>
+        <v>297151.04</v>
       </c>
     </row>
     <row r="50">
@@ -5985,11 +5985,11 @@
         <v>300000</v>
       </c>
       <c r="D52" t="n">
-        <v>386638.97</v>
+        <v>426689.97</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>142.2%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6001,7 +6001,7 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>386638.97</v>
+        <v>426689.97</v>
       </c>
     </row>
     <row r="53">
@@ -6019,11 +6019,11 @@
         <v>220000</v>
       </c>
       <c r="D53" t="n">
-        <v>236335.8</v>
+        <v>238293.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>236335.8</v>
+        <v>238293.8</v>
       </c>
     </row>
     <row r="54">
@@ -6053,11 +6053,11 @@
         <v>240000</v>
       </c>
       <c r="D54" t="n">
-        <v>288214</v>
+        <v>288490</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>120.1%</t>
+          <t>120.2%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>288214</v>
+        <v>288490</v>
       </c>
     </row>
     <row r="55">
@@ -6087,11 +6087,11 @@
         <v>100000</v>
       </c>
       <c r="D55" t="n">
-        <v>157175</v>
+        <v>177573</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>147.2%</t>
+          <t>167.6%</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -6099,11 +6099,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>147175</v>
+        <v>167573</v>
       </c>
     </row>
     <row r="56">
@@ -6325,11 +6325,11 @@
         <v>120000</v>
       </c>
       <c r="D62" t="n">
-        <v>73570</v>
+        <v>73968</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -6337,11 +6337,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>57770</v>
+        <v>58168</v>
       </c>
     </row>
     <row r="63">
@@ -6436,16 +6436,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1418370.53</v>
+        <v>1540712.53</v>
       </c>
       <c r="D2" t="n">
-        <v>4017</v>
+        <v>4165</v>
       </c>
       <c r="E2" t="n">
         <v>129069</v>
       </c>
       <c r="F2" t="n">
-        <v>1289301.53</v>
+        <v>1411643.53</v>
       </c>
     </row>
     <row r="3">
@@ -6460,16 +6460,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1295676</v>
+        <v>1413097</v>
       </c>
       <c r="D3" t="n">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="E3" t="n">
         <v>129040</v>
       </c>
       <c r="F3" t="n">
-        <v>1166636</v>
+        <v>1284057</v>
       </c>
     </row>
     <row r="4">
@@ -6484,16 +6484,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>122694.53</v>
+        <v>127615.53</v>
       </c>
       <c r="D4" t="n">
-        <v>3769</v>
+        <v>3893</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>122665.53</v>
+        <v>127586.53</v>
       </c>
     </row>
     <row r="5">
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1988824</v>
+        <v>2107422</v>
       </c>
       <c r="D5" t="n">
-        <v>450</v>
+        <v>501</v>
       </c>
       <c r="E5" t="n">
         <v>117432</v>
       </c>
       <c r="F5" t="n">
-        <v>1871392</v>
+        <v>1989990</v>
       </c>
     </row>
     <row r="6">
@@ -6532,16 +6532,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1442646</v>
+        <v>1512040</v>
       </c>
       <c r="D6" t="n">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E6" t="n">
         <v>22598</v>
       </c>
       <c r="F6" t="n">
-        <v>1420048</v>
+        <v>1489442</v>
       </c>
     </row>
     <row r="7">
@@ -6556,16 +6556,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>526178</v>
+        <v>575382</v>
       </c>
       <c r="D7" t="n">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="E7" t="n">
         <v>94834</v>
       </c>
       <c r="F7" t="n">
-        <v>431344</v>
+        <v>480548</v>
       </c>
     </row>
     <row r="8">
@@ -6580,16 +6580,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2068959.54</v>
+        <v>2136679.13</v>
       </c>
       <c r="D8" t="n">
-        <v>2587</v>
+        <v>2726</v>
       </c>
       <c r="E8" t="n">
         <v>8784.469999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2060175.07</v>
+        <v>2127894.66</v>
       </c>
     </row>
     <row r="9">
@@ -6604,16 +6604,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1218203.38</v>
+        <v>1276047.08</v>
       </c>
       <c r="D9" t="n">
-        <v>1145</v>
+        <v>1202</v>
       </c>
       <c r="E9" t="n">
         <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1216403.38</v>
+        <v>1274247.08</v>
       </c>
     </row>
     <row r="10">
@@ -6628,16 +6628,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>850756.16</v>
+        <v>860632.05</v>
       </c>
       <c r="D10" t="n">
-        <v>1442</v>
+        <v>1524</v>
       </c>
       <c r="E10" t="n">
         <v>6984.47</v>
       </c>
       <c r="F10" t="n">
-        <v>843771.6899999999</v>
+        <v>853647.58</v>
       </c>
     </row>
     <row r="11">
@@ -6652,16 +6652,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>577206.4</v>
+        <v>843006.4</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>144800</v>
+        <v>336200</v>
       </c>
       <c r="F11" t="n">
-        <v>432406.4</v>
+        <v>506806.4</v>
       </c>
     </row>
     <row r="12">
@@ -6700,16 +6700,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>113000</v>
+        <v>128000</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>63400</v>
+        <v>73400</v>
       </c>
       <c r="F13" t="n">
-        <v>49600</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="14">
@@ -6748,16 +6748,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
       <c r="D15" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
     </row>
   </sheetData>
@@ -6818,22 +6818,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1418370.53</v>
+        <v>1540712.53</v>
       </c>
       <c r="C2" t="n">
-        <v>568156.74</v>
+        <v>604082.74</v>
       </c>
       <c r="D2" t="n">
-        <v>111932.58</v>
+        <v>118096.58</v>
       </c>
       <c r="E2" t="n">
-        <v>7.89</v>
+        <v>7.67</v>
       </c>
       <c r="F2" t="n">
-        <v>456224.16</v>
+        <v>485986.16</v>
       </c>
       <c r="G2" t="n">
-        <v>32.17</v>
+        <v>31.54</v>
       </c>
     </row>
     <row r="3">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1988824</v>
+        <v>2107422</v>
       </c>
       <c r="C3" t="n">
-        <v>812252.99</v>
+        <v>883152.99</v>
       </c>
       <c r="D3" t="n">
-        <v>45598</v>
+        <v>54598</v>
       </c>
       <c r="E3" t="n">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="F3" t="n">
-        <v>766654.99</v>
+        <v>828554.99</v>
       </c>
       <c r="G3" t="n">
-        <v>38.55</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="4">
@@ -6868,22 +6868,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2068959.54</v>
+        <v>2136679.13</v>
       </c>
       <c r="C4" t="n">
-        <v>28999</v>
+        <v>29799</v>
       </c>
       <c r="D4" t="n">
-        <v>249</v>
+        <v>1049</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
         <v>28750</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="5">
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>577206.4</v>
+        <v>843006.4</v>
       </c>
       <c r="C5" t="n">
         <v>190400</v>
@@ -6908,7 +6908,7 @@
         <v>190400</v>
       </c>
       <c r="G5" t="n">
-        <v>32.99</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="6">
@@ -6943,22 +6943,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113000</v>
+        <v>128000</v>
       </c>
       <c r="C7" t="n">
-        <v>299246.67</v>
+        <v>327046.67</v>
       </c>
       <c r="D7" t="n">
         <v>53000</v>
       </c>
       <c r="E7" t="n">
-        <v>46.9</v>
+        <v>41.41</v>
       </c>
       <c r="F7" t="n">
-        <v>246246.67</v>
+        <v>274046.67</v>
       </c>
       <c r="G7" t="n">
-        <v>217.92</v>
+        <v>214.1</v>
       </c>
     </row>
     <row r="8">
@@ -6971,7 +6971,7 @@
         <v>13860</v>
       </c>
       <c r="C8" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6980,10 +6980,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1980</v>
+        <v>3960</v>
       </c>
       <c r="G8" t="n">
-        <v>14.29</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="9">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144128.24</v>
+        <v>145127.25</v>
       </c>
       <c r="C9" t="n">
         <v>18998</v>
@@ -7002,13 +7002,13 @@
         <v>2198</v>
       </c>
       <c r="E9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="F9" t="n">
         <v>16800</v>
       </c>
       <c r="G9" t="n">
-        <v>11.66</v>
+        <v>11.58</v>
       </c>
     </row>
   </sheetData>
@@ -7054,13 +7054,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C2" t="n">
-        <v>1183758.82</v>
+        <v>1229026.82</v>
       </c>
       <c r="D2" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3">
@@ -7070,13 +7070,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>826</v>
+        <v>842</v>
       </c>
       <c r="C3" t="n">
-        <v>370326.32</v>
+        <v>396737.32</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -7086,13 +7086,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>230401</v>
+        <v>253980</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -7102,13 +7102,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>158622.24</v>
+        <v>198422.24</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -7118,13 +7118,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C6" t="n">
-        <v>41765.22</v>
+        <v>43835.22</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>37800.7</v>
+        <v>38059.7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -7198,10 +7198,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7234,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>14900</v>
+        <v>39716</v>
       </c>
     </row>
     <row r="5">
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D7" t="n">
-        <v>118012</v>
+        <v>122500</v>
       </c>
     </row>
     <row r="8">
@@ -7379,10 +7379,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="D8" t="n">
-        <v>107197.82</v>
+        <v>108773.82</v>
       </c>
     </row>
     <row r="9">
@@ -7393,14 +7393,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>178</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>13774.56</v>
+        <v>14636</v>
       </c>
     </row>
     <row r="10">
@@ -7411,14 +7411,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>10754</v>
+        <v>13845.56</v>
       </c>
     </row>
     <row r="11">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>10457.7</v>
+        <v>10754</v>
       </c>
     </row>
     <row r="12">
@@ -7447,14 +7447,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>4099</v>
+        <v>10716.7</v>
       </c>
     </row>
     <row r="13">
@@ -7465,14 +7465,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>617</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="14">
@@ -7483,14 +7483,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>209</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>教材问题</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
@@ -7532,37 +7532,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>85388</v>
+        <v>85250</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>72193</v>
+        <v>61522.24</v>
       </c>
     </row>
     <row r="19">
@@ -7573,14 +7573,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>85250</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="20">
@@ -7591,14 +7591,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>50722.24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -7609,14 +7609,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>6600</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
@@ -7627,50 +7627,50 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>85388</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>课程4组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>72193</v>
       </c>
     </row>
     <row r="25">
@@ -7685,10 +7685,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>61556.4</v>
+        <v>66536.39999999999</v>
       </c>
     </row>
     <row r="26">
@@ -7766,7 +7766,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7775,34 +7775,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>61829</v>
+        <v>97854</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>25029.5</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7811,46 +7811,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>21780</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D33" t="n">
-        <v>13200</v>
+        <v>5970</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D34" t="n">
-        <v>10256.66</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="35">
@@ -7861,14 +7861,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>97854</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -7879,38 +7879,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>9000</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>5951</v>
+        <v>61829</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7919,142 +7919,142 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>2526</v>
+        <v>25029.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>76</v>
+        <v>21780</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程1组</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>75533.39999999999</v>
+        <v>10256.66</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>20500</v>
+        <v>90420</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>9000</v>
+        <v>16637</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>398</v>
+        <v>14820</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>课程6组</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>200</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8063,70 +8063,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D46" t="n">
-        <v>62620</v>
+        <v>75533.39999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>16637</v>
+        <v>20500</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>14820</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>74628</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>12000</v>
+        <v>200</v>
       </c>
     </row>
     <row r="51">
@@ -8149,61 +8149,61 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>318</v>
+        <v>74628</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D52" t="n">
-        <v>68500</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>398</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -8239,14 +8239,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>16910</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="57">
@@ -8257,14 +8257,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D57" t="n">
-        <v>6500</v>
+        <v>16929</v>
       </c>
     </row>
     <row r="58">
@@ -8288,7 +8288,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -8300,49 +8300,49 @@
         <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>33440</v>
+        <v>68500</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>31030</v>
+        <v>398</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>35000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8351,154 +8351,154 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D62" t="n">
-        <v>19233.35</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>课程5组</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
-        <v>28919</v>
+        <v>31030</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D64" t="n">
-        <v>23689</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" t="n">
-        <v>27200</v>
+        <v>19233.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
-        <v>11299</v>
+        <v>28919</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>课程7组</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>11009</v>
+        <v>23689</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>咨询结案/好转</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>15019</v>
+        <v>27200</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" t="n">
-        <v>15009</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>48</v>
+        <v>11009</v>
       </c>
     </row>
     <row r="71">
@@ -8509,20 +8509,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>15019</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8531,46 +8531,46 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72" t="n">
-        <v>9000</v>
+        <v>15009</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>6800</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
@@ -8585,10 +8585,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>9318</v>
+        <v>17318</v>
       </c>
     </row>
     <row r="76">
@@ -8643,6 +8643,60 @@
       </c>
       <c r="D78" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>其他/未说明</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>家人不支持</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>珠海</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>主动放弃/拍错</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -8683,62 +8737,62 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C2" t="n">
-        <v>659684.99</v>
+        <v>720584.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>户外营地（户外组专用）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>271261.56</v>
+        <v>283466.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>青少年家庭同行者计划</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>255666.67</v>
+        <v>281220.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>少年说倾听计划</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
-        <v>190400</v>
+        <v>194760</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>188160</v>
+        <v>190400</v>
       </c>
     </row>
     <row r="7">
@@ -8761,49 +8815,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>129498</v>
+        <v>140298</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>夏令营</t>
+          <t>少年说陪伴计划</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>39380</v>
+        <v>44616</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>家庭守护计划</t>
+          <t>夏令营</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>32041</v>
+        <v>39380</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>少年说陪伴计划</t>
+          <t>家庭守护计划</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>26400</v>
+        <v>32041</v>
       </c>
     </row>
   </sheetData>
@@ -8844,10 +8898,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C2" t="n">
-        <v>337108.35</v>
+        <v>388742.35</v>
       </c>
     </row>
     <row r="3">
@@ -8857,10 +8911,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C3" t="n">
-        <v>247801</v>
+        <v>270818</v>
       </c>
     </row>
     <row r="4">
@@ -8870,10 +8924,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>202100.22</v>
+        <v>218612.22</v>
       </c>
     </row>
     <row r="5">
@@ -8883,10 +8937,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C5" t="n">
-        <v>196696.4</v>
+        <v>198581.4</v>
       </c>
     </row>
     <row r="6">
@@ -8896,10 +8950,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>138217.5</v>
+        <v>148217.5</v>
       </c>
     </row>
     <row r="7">
@@ -8909,10 +8963,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>127461</v>
+        <v>137374</v>
       </c>
     </row>
     <row r="8">
@@ -8922,10 +8976,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>113342</v>
+        <v>113661</v>
       </c>
     </row>
     <row r="9">
@@ -8935,10 +8989,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" t="n">
-        <v>108267.4</v>
+        <v>108305.4</v>
       </c>
     </row>
     <row r="10">
@@ -8948,10 +9002,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C10" t="n">
-        <v>80739.8</v>
+        <v>98993.8</v>
       </c>
     </row>
     <row r="11">
@@ -8987,10 +9041,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>47535</v>
+        <v>47573</v>
       </c>
     </row>
     <row r="14">
@@ -9000,10 +9054,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="n">
-        <v>39260.37</v>
+        <v>44200.37</v>
       </c>
     </row>
     <row r="15">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>491652</v>
+        <v>657054</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>+47.4%</t>
+          <t>+10.3%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>237237</v>
+        <v>402444</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+149.9%</t>
+          <t>+47.3%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18355</v>
+        <v>18393</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-22429</v>
+        <v>-22420</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>720564</v>
+        <v>792934</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>+13.7%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>543379</v>
+        <v>611387</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+24.3%</t>
+          <t>+10.5%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>479649</v>
+        <v>483707</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>351443</v>
+        <v>355472</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>445025</v>
+        <v>464746</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+75.2%</t>
+          <t>+67.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>334199</v>
+        <v>346212</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+114.1%</t>
+          <t>+106.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -832,19 +832,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>375548</v>
+        <v>436684</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+29.6%</t>
+          <t>+11.4%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>266641</v>
+        <v>327394</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+36.0%</t>
+          <t>+10.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>403536</v>
+        <v>443341</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>+8.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>321039</v>
+        <v>358776</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+20.0%</t>
+          <t>+7.4%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -946,19 +946,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>974942</v>
+        <v>1319532</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>687145</v>
+        <v>965347</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+15.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1001,19 +1001,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1917683</v>
+        <v>2025422</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+4.2%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1917683</v>
+        <v>2025422</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1062,19 +1062,19 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>345070</v>
+        <v>447986</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>299143</v>
+        <v>371659</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -1125,19 +1125,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>380227</v>
+        <v>382023</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>+34.5%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>377999</v>
+        <v>379795</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+27.3%</t>
+          <t>+26.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>693613</v>
+        <v>701632</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>616804</v>
+        <v>624804</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -1249,19 +1249,19 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>583359</v>
+        <v>779679</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-56.9%</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>506181</v>
+        <v>679401</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-53.9%</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -1312,19 +1312,19 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>210892</v>
+        <v>253829</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-43.4%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>195567</v>
+        <v>238504</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-46.4%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>323899</v>
+        <v>364724</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>+8.0%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>270899</v>
+        <v>311724</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>565057</v>
+        <v>565084</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>468391</v>
+        <v>468418</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1497,19 +1497,19 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>745371</v>
+        <v>867685</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+53.9%</t>
+          <t>+32.2%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>592546</v>
+        <v>711381</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+66.2%</t>
+          <t>+38.4%</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>410852</v>
+        <v>420390</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+30.8%</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>257806</v>
+        <v>234394</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+79.6%</t>
+          <t>+97.5%</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -1623,19 +1623,19 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>664820</v>
+        <v>674896</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>581682</v>
+        <v>591739</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -1676,13 +1676,21 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>11980</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>+2551.2%</t>
+        </is>
+      </c>
       <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
+        <v>-124600</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-125.2%</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>19911</v>
@@ -1731,19 +1739,19 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10750114</v>
+        <v>12111722</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>+13.7%</t>
+          <t>+0.9%</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>8803357</v>
+        <v>9857255</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+13.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="N22" t="n">

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -17,8 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款服务类型" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="退款省份" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电话" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协同" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新老客" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新老客" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,48 +521,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>760000</v>
+        <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>724921</v>
+        <v>32223</v>
       </c>
       <c r="E2" t="n">
-        <v>132095</v>
+        <v>845</v>
       </c>
       <c r="F2" t="n">
-        <v>592826</v>
+        <v>31378</v>
       </c>
       <c r="G2" t="n">
-        <v>10398</v>
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>657054</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>+10.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>402444</v>
+        <v>-68335</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+47.3%</t>
+          <t>-145.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -579,44 +574,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>7863</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>46334</v>
       </c>
       <c r="F3" t="n">
-        <v>2000</v>
+        <v>-38471</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>18393</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>-89.1%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-22420</v>
+        <v>-54963</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-108.9%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -632,48 +627,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>760000</v>
+        <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>819274</v>
+        <v>48586</v>
       </c>
       <c r="E4" t="n">
-        <v>143912</v>
+        <v>1714</v>
       </c>
       <c r="F4" t="n">
-        <v>675361</v>
+        <v>46872</v>
       </c>
       <c r="G4" t="n">
-        <v>22000</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>792934</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>+3.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>611387</v>
+        <v>-65634</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+10.5%</t>
+          <t>-171.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -689,48 +680,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>520000</v>
+        <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>247834</v>
+        <v>156757</v>
       </c>
       <c r="E5" t="n">
-        <v>157581</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>90253</v>
+        <v>156690</v>
       </c>
       <c r="G5" t="n">
-        <v>173964</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>483707</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-48.8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>355472</v>
+        <v>-230448</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-168.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -741,230 +728,244 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>600000</v>
+        <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>779833</v>
+        <v>195696</v>
       </c>
       <c r="E6" t="n">
-        <v>64470</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>715363</v>
-      </c>
-      <c r="G6" t="n">
-        <v>49820</v>
-      </c>
+        <v>195696</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>127.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>464746</v>
+        <v>422080</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>+67.8%</t>
+          <t>-53.6%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>346212</v>
+        <v>422080</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+106.6%</t>
+          <t>-53.6%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>75335</v>
+      </c>
+      <c r="P6" t="n">
+        <v>120361</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>185298</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360000</v>
+        <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>486534</v>
+        <v>24628</v>
       </c>
       <c r="E7" t="n">
-        <v>123857</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>362677</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
+        <v>24609</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>436684</v>
+        <v>210</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+11.4%</t>
+          <t>+11627.6%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>327394</v>
+        <v>-8790</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+10.8%</t>
+          <t>-380.0%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>14590</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10019</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>640000</v>
+        <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>437928</v>
+        <v>101194</v>
       </c>
       <c r="E8" t="n">
-        <v>52608</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>385320</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
+        <v>101194</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>443341</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-1.2%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>358776</v>
+        <v>-28</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+7.4%</t>
+          <t>-361507.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>21194</v>
+      </c>
+      <c r="P8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1120000</v>
+        <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>1235648</v>
+        <v>70893</v>
       </c>
       <c r="E9" t="n">
-        <v>444276</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>791372</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
+        <v>70893</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1319532</v>
+        <v>7234</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>+880.0%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>965347</v>
+        <v>-17193</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-18.0%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+          <t>-512.3%</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5383</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8694</v>
+      </c>
+      <c r="P9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12699</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -974,57 +975,59 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>1998285</v>
+        <v>34101</v>
       </c>
       <c r="E10" t="n">
-        <v>49508</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1948777</v>
+        <v>34101</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2025422</v>
+        <v>5431</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+527.9%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2025422</v>
+        <v>65</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-3.8%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>+52363.1%</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1494</v>
+      </c>
       <c r="O10" t="n">
-        <v>809724</v>
+        <v>9</v>
       </c>
       <c r="P10" t="n">
-        <v>1139052</v>
+        <v>32598</v>
       </c>
       <c r="Q10" t="n">
-        <v>1917997</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="11">
@@ -1035,59 +1038,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>380000</v>
+        <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>273522</v>
+        <v>6053</v>
       </c>
       <c r="E11" t="n">
-        <v>54233</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>219289</v>
+        <v>6053</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>447986</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>-38.9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>371659</v>
+        <v>-38</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-41.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>234</v>
-      </c>
+          <t>-16028.9%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>63984</v>
+        <v>57</v>
       </c>
       <c r="P11" t="n">
-        <v>155071</v>
+        <v>5996</v>
       </c>
       <c r="Q11" t="n">
-        <v>108778</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1098,57 +1095,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>511376</v>
+        <v>46811</v>
       </c>
       <c r="E12" t="n">
-        <v>30095</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>481281</v>
+        <v>46811</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>382023</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>+33.9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>379795</v>
+        <v>-417</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>+26.7%</t>
+          <t>-11325.7%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>67250</v>
+        <v>6015</v>
       </c>
       <c r="P12" t="n">
-        <v>414031</v>
+        <v>40796</v>
       </c>
       <c r="Q12" t="n">
-        <v>48527</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -1159,59 +1152,59 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>800000</v>
+        <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>704877</v>
+        <v>19335</v>
       </c>
       <c r="E13" t="n">
-        <v>79281</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>625596</v>
+        <v>19335</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>701632</v>
+        <v>1473</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1212.6%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>624804</v>
+        <v>-38527</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+0.1%</t>
+          <t>-150.2%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>32292</v>
+        <v>2226</v>
       </c>
       <c r="O13" t="n">
-        <v>48729</v>
+        <v>417</v>
       </c>
       <c r="P13" t="n">
-        <v>544575</v>
+        <v>16692</v>
       </c>
       <c r="Q13" t="n">
-        <v>106674</v>
+        <v>8845</v>
       </c>
     </row>
     <row r="14">
@@ -1222,59 +1215,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>800000</v>
+        <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>336058</v>
+        <v>101937</v>
       </c>
       <c r="E14" t="n">
-        <v>22866</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>313192</v>
+        <v>101890</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>779679</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-56.9%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>679401</v>
+        <v>-19</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-53.9%</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>28374</v>
-      </c>
+          <t>-536363.2%</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>56133</v>
+        <v>14293</v>
       </c>
       <c r="P14" t="n">
-        <v>228685</v>
+        <v>87597</v>
       </c>
       <c r="Q14" t="n">
-        <v>84458</v>
+        <v>50284</v>
       </c>
     </row>
     <row r="15">
@@ -1285,57 +1272,59 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>260000</v>
+        <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>143785</v>
+        <v>65825</v>
       </c>
       <c r="E15" t="n">
-        <v>15857</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>127928</v>
+        <v>65825</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>253829</v>
+        <v>3303</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-43.4%</t>
+          <t>+1892.9%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>238504</v>
+        <v>3094</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-46.4%</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>+2027.5%</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5835</v>
+      </c>
       <c r="O15" t="n">
-        <v>8992</v>
+        <v>27594</v>
       </c>
       <c r="P15" t="n">
-        <v>118936</v>
+        <v>32396</v>
       </c>
       <c r="Q15" t="n">
-        <v>39162</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="16">
@@ -1346,425 +1335,167 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400000</v>
+        <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>349967</v>
+        <v>38194</v>
       </c>
       <c r="E16" t="n">
-        <v>68917</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>281050</v>
+        <v>38194</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>364724</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-4.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>311724</v>
+        <v>-38556</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-199.1%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>13323</v>
+        <v>10898</v>
       </c>
       <c r="P16" t="n">
-        <v>267727</v>
+        <v>27296</v>
       </c>
       <c r="Q16" t="n">
-        <v>47902</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>门店</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>625926</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>105631</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>520295</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>74.3%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>74.3%</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>565084</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>+10.8%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>468418</v>
+        <v>-2773</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+11.1%</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>69668</v>
-      </c>
+          <t>-100.0%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>45132</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>405695</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>143818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>门店</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>南区合计</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>900000</v>
+        <v>14090000</v>
       </c>
       <c r="D18" t="n">
-        <v>1147251</v>
+        <v>950096</v>
       </c>
       <c r="E18" t="n">
-        <v>162496</v>
+        <v>49026</v>
       </c>
       <c r="F18" t="n">
-        <v>984754</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>901070</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>867685</v>
+        <v>439731</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>+32.2%</t>
+          <t>+116.1%</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>711381</v>
+        <v>-100482</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+38.4%</t>
+          <t>-996.7%</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>7250</v>
+        <v>14938</v>
       </c>
       <c r="O18" t="n">
-        <v>247265</v>
+        <v>374420</v>
       </c>
       <c r="P18" t="n">
-        <v>730239</v>
+        <v>511712</v>
       </c>
       <c r="Q18" t="n">
-        <v>566607</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D19" t="n">
-        <v>549923</v>
-      </c>
-      <c r="E19" t="n">
-        <v>86965</v>
-      </c>
-      <c r="F19" t="n">
-        <v>462958</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>51.4%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>51.4%</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>420390</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>+30.8%</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>234394</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>+97.5%</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>61427</v>
-      </c>
-      <c r="O19" t="n">
-        <v>70334</v>
-      </c>
-      <c r="P19" t="n">
-        <v>331397</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>137004</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D20" t="n">
-        <v>526499</v>
-      </c>
-      <c r="E20" t="n">
-        <v>133502</v>
-      </c>
-      <c r="F20" t="n">
-        <v>392997</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>56.1%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>56.1%</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>674896</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-22.0%</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>591739</v>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-33.6%</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>52105</v>
-      </c>
-      <c r="P20" t="n">
-        <v>340892</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>100665</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>317608</v>
-      </c>
-      <c r="E21" t="n">
-        <v>286208</v>
-      </c>
-      <c r="F21" t="n">
-        <v>31400</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
-        <v>11980</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>+2551.2%</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>-124600</v>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>-125.2%</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="n">
-        <v>19911</v>
-      </c>
-      <c r="P21" t="n">
-        <v>11489</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>29948</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>南区合计</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="D22" t="n">
-        <v>12219048</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2214359</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10004688</v>
-      </c>
-      <c r="G22" t="n">
-        <v>256182</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>78.9%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>77.0%</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>12111722</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>+0.9%</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>9857255</v>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>+1.5%</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>199245</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4939224</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4866621</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6158056</v>
+        <v>353720</v>
       </c>
     </row>
   </sheetData>
@@ -1778,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1815,54 +1546,35 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>400.8</v>
+        <v>182.6</v>
       </c>
       <c r="E2" t="n">
-        <v>14946</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43</v>
+        <v>324</v>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>768.2</v>
+        <v>459.3</v>
       </c>
       <c r="E3" t="n">
-        <v>41316</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>840</v>
-      </c>
-      <c r="C4" t="n">
-        <v>89</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1044.9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2270</v>
+        <v>5929</v>
       </c>
     </row>
   </sheetData>
@@ -1876,184 +1588,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>分组</t>
+          <t>维度</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>协同金额(元)</t>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>新客净流水(元)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>老客净流水(元)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>非1V1及菌群净(元)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>22000</v>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>销售</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>195324</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1144</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89059</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>49820</v>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>179096</v>
+      </c>
+      <c r="D3" t="n">
+        <v>510567</v>
+      </c>
+      <c r="E3" t="n">
+        <v>264661</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>173964</v>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>观行组</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>30551</v>
+      </c>
+      <c r="D4" t="n">
+        <v>827</v>
+      </c>
+      <c r="E4" t="n">
+        <v>29584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>10398</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>新客净流水(元)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>老客净流水(元)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>非1V1及菌群净(元)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>销售</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2776006</v>
-      </c>
-      <c r="D2" t="n">
-        <v>47793</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2329990</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>班主任</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>660333</v>
-      </c>
-      <c r="D3" t="n">
-        <v>131038</v>
-      </c>
-      <c r="E3" t="n">
-        <v>496525</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1482971</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4676300</v>
-      </c>
-      <c r="E4" t="n">
-        <v>3301591</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
           <t>分组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>583482</v>
+        <v>-38789</v>
       </c>
       <c r="D5" t="n">
-        <v>9344</v>
+        <v>318</v>
       </c>
       <c r="E5" t="n">
-        <v>604040</v>
+        <v>-38471</v>
       </c>
     </row>
     <row r="6">
@@ -2064,17 +1710,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1865</v>
+        <v>46872</v>
       </c>
       <c r="D6" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2000</v>
+        <v>26674</v>
       </c>
     </row>
     <row r="7">
@@ -2085,17 +1731,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>659652</v>
+        <v>156690</v>
       </c>
       <c r="D7" t="n">
-        <v>15710</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>626959</v>
+        <v>71272</v>
       </c>
     </row>
     <row r="8">
@@ -2106,17 +1752,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>85065</v>
+        <v>75335</v>
       </c>
       <c r="D8" t="n">
-        <v>5188</v>
+        <v>120361</v>
       </c>
       <c r="E8" t="n">
-        <v>-33907</v>
+        <v>185298</v>
       </c>
     </row>
     <row r="9">
@@ -2127,17 +1773,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>708399</v>
+        <v>14590</v>
       </c>
       <c r="D9" t="n">
-        <v>6965</v>
+        <v>10019</v>
       </c>
       <c r="E9" t="n">
-        <v>597979</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2148,17 +1794,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>363458</v>
+        <v>21194</v>
       </c>
       <c r="D10" t="n">
-        <v>-781</v>
+        <v>80000</v>
       </c>
       <c r="E10" t="n">
-        <v>211589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2169,17 +1815,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>374087</v>
+        <v>8694</v>
       </c>
       <c r="D11" t="n">
-        <v>11233</v>
+        <v>56816</v>
       </c>
       <c r="E11" t="n">
-        <v>321330</v>
+        <v>12699</v>
       </c>
     </row>
     <row r="12">
@@ -2190,17 +1836,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>660334</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>131038</v>
+        <v>32598</v>
       </c>
       <c r="E12" t="n">
-        <v>496526</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="13">
@@ -2211,17 +1857,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>809724</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>1139052</v>
+        <v>5996</v>
       </c>
       <c r="E13" t="n">
-        <v>1917997</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -2232,17 +1878,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63984</v>
+        <v>6015</v>
       </c>
       <c r="D14" t="n">
-        <v>155071</v>
+        <v>40796</v>
       </c>
       <c r="E14" t="n">
-        <v>108778</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2253,17 +1899,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>67250</v>
+        <v>417</v>
       </c>
       <c r="D15" t="n">
-        <v>414031</v>
+        <v>16692</v>
       </c>
       <c r="E15" t="n">
-        <v>48527</v>
+        <v>8845</v>
       </c>
     </row>
     <row r="16">
@@ -2274,17 +1920,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>48729</v>
+        <v>14293</v>
       </c>
       <c r="D16" t="n">
-        <v>544575</v>
+        <v>87597</v>
       </c>
       <c r="E16" t="n">
-        <v>106674</v>
+        <v>50284</v>
       </c>
     </row>
     <row r="17">
@@ -2295,17 +1941,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56133</v>
+        <v>27594</v>
       </c>
       <c r="D17" t="n">
-        <v>228685</v>
+        <v>32396</v>
       </c>
       <c r="E17" t="n">
-        <v>84458</v>
+        <v>5835</v>
       </c>
     </row>
     <row r="18">
@@ -2316,17 +1962,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8992</v>
+        <v>10898</v>
       </c>
       <c r="D18" t="n">
-        <v>118936</v>
+        <v>27296</v>
       </c>
       <c r="E18" t="n">
-        <v>39162</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19">
@@ -2337,143 +1983,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13323</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>267727</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>47902</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>分组</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>南区合计</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>45132</v>
+        <v>374420</v>
       </c>
       <c r="D20" t="n">
-        <v>405695</v>
+        <v>511712</v>
       </c>
       <c r="E20" t="n">
-        <v>143818</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>247265</v>
-      </c>
-      <c r="D21" t="n">
-        <v>730239</v>
-      </c>
-      <c r="E21" t="n">
-        <v>566607</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>70334</v>
-      </c>
-      <c r="D22" t="n">
-        <v>331397</v>
-      </c>
-      <c r="E22" t="n">
-        <v>137004</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>52105</v>
-      </c>
-      <c r="D23" t="n">
-        <v>340892</v>
-      </c>
-      <c r="E23" t="n">
-        <v>100665</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>分组</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>19911</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11489</v>
-      </c>
-      <c r="E24" t="n">
-        <v>29948</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>南区合计</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4939224</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4866621</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6158056</v>
+        <v>353720</v>
       </c>
     </row>
   </sheetData>
@@ -2487,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,283 +2086,283 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>李钰坤</t>
+          <t>高曌</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>240000</v>
+        <v>191500</v>
       </c>
       <c r="D2" t="n">
-        <v>250832</v>
+        <v>6774</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44598.66</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>206233.34</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>于鹏飞</t>
+          <t>司法</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>160000</v>
+        <v>185200</v>
       </c>
       <c r="D3" t="n">
-        <v>76079</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>19389</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>56690</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>闫丽东</t>
+          <t>刘孟杰</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120000</v>
+        <v>165200</v>
       </c>
       <c r="D4" t="n">
-        <v>86796</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>10398</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>44560</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>42236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>唐歌</t>
+          <t>高铭瑞</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120000</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="n">
-        <v>166738</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>132.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7887.5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>158850.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>何媛媛</t>
+          <t>王渊亮</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>120000</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="n">
-        <v>106720</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15660</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>91060</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>陈志强</t>
+          <t>郑美琦</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>120000</v>
+        <v>148350</v>
       </c>
       <c r="D7" t="n">
-        <v>116260</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19130</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>97130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>关万辉</t>
+          <t>郑理</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>160000</v>
+        <v>115750</v>
       </c>
       <c r="D8" t="n">
-        <v>21540</v>
+        <v>4980</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -2833,667 +2374,667 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>21540</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>郑理</t>
+          <t>李钰坤</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80000</v>
+        <v>207250</v>
       </c>
       <c r="D9" t="n">
-        <v>48060</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11579</v>
+        <v>45600</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>36481</v>
+        <v>-45600</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>肖伟</t>
+          <t>唐歌</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>160000</v>
+        <v>168625</v>
       </c>
       <c r="D10" t="n">
-        <v>129352</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7959</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>121393</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>刘士明</t>
+          <t>陈志强</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120000</v>
+        <v>168625</v>
       </c>
       <c r="D11" t="n">
-        <v>90418</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>13940</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>76478</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>张孟蝶</t>
+          <t>何媛媛</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>88000</v>
+        <v>148625</v>
       </c>
       <c r="D12" t="n">
-        <v>111690</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>105090</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>江敏</t>
+          <t>关万辉</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>80000</v>
+        <v>141500</v>
       </c>
       <c r="D13" t="n">
-        <v>357538</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>446.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>433.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10980</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>346558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>武存英</t>
+          <t>闫丽东</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96000</v>
+        <v>128625</v>
       </c>
       <c r="D14" t="n">
-        <v>84200</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>132380</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>157.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>-48180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>李天阳</t>
+          <t>于鹏飞</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>80000</v>
+        <v>91500</v>
       </c>
       <c r="D15" t="n">
-        <v>11398</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>-1802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>王航</t>
+          <t>车宏祥</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>96000</v>
+        <v>171500</v>
       </c>
       <c r="D16" t="n">
-        <v>130172</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>135.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>67800</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>62372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>安百柠</t>
+          <t>陈斌斌</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80000</v>
+        <v>175475</v>
       </c>
       <c r="D17" t="n">
-        <v>28020</v>
+        <v>30458</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>52100</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>185.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>-24080</v>
+        <v>30458</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>姜人荷</t>
+          <t>严闽龙</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>88000</v>
+        <v>178625</v>
       </c>
       <c r="D18" t="n">
-        <v>117298</v>
+        <v>4980</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>38416</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>78882</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>冯岚</t>
+          <t>卢忠慧</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>88000</v>
+        <v>178900</v>
       </c>
       <c r="D19" t="n">
-        <v>74320</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>50800</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23520</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>郑鲁</t>
+          <t>刘俊彤</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>88000</v>
+        <v>108625</v>
       </c>
       <c r="D20" t="n">
-        <v>94420</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>81220</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周玉枝</t>
+          <t>李洋洋</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>88000</v>
+        <v>95750</v>
       </c>
       <c r="D21" t="n">
-        <v>55200</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>龙少海</t>
+          <t>刘士明</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>80000</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="n">
-        <v>123620</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>154.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>145.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>116020</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>宋晨曦</t>
+          <t>岳跃峰</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>80000</v>
+        <v>207895</v>
       </c>
       <c r="D23" t="n">
-        <v>31760</v>
+        <v>24598</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>25160</v>
+        <v>24598</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>张天昂</t>
+          <t>姜人荷</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>88000</v>
+        <v>104842</v>
       </c>
       <c r="D24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3505,457 +3046,457 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>王渊亮</t>
+          <t>王航</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>120000</v>
+        <v>100737</v>
       </c>
       <c r="D25" t="n">
-        <v>65974</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>18050</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>47924</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>高曌</t>
+          <t>张孟蝶</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160000</v>
+        <v>154842</v>
       </c>
       <c r="D26" t="n">
-        <v>253096</v>
+        <v>12000</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>158.2%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>35306</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>217790</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>黄梦妹</t>
+          <t>武存英</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>80000</v>
+        <v>150737</v>
       </c>
       <c r="D27" t="n">
-        <v>58480</v>
+        <v>66400</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13660</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>44820</v>
+        <v>66400</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>郑美琦</t>
+          <t>郑鲁</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>144000</v>
+        <v>80000</v>
       </c>
       <c r="D28" t="n">
-        <v>108418</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>25200</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>83218</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刘孟杰</t>
+          <t>冯岚</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>128000</v>
+        <v>80000</v>
       </c>
       <c r="D29" t="n">
-        <v>114818</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>27083</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>87735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>司法</t>
+          <t>龙少海</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>128000</v>
+        <v>108947</v>
       </c>
       <c r="D30" t="n">
-        <v>127040</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>24613.4</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>102426.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>岳跃峰</t>
+          <t>周玉枝</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="D31" t="n">
-        <v>265034</v>
+        <v>10000</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>165.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>113.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>84120</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>180914</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>车宏祥</t>
+          <t>张天昂</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160000</v>
+        <v>80000</v>
       </c>
       <c r="D32" t="n">
-        <v>196958</v>
+        <v>38820</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>106.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>25940</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>171018</v>
+        <v>38820</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>高铭瑞</t>
+          <t>宋晨曦</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D33" t="n">
-        <v>111098</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>24780</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>86318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>刘俊彤</t>
+          <t>安百柠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D34" t="n">
-        <v>127858</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>106.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>118358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>严闽龙</t>
+          <t>李天阳</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="D35" t="n">
-        <v>104150</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>49820</v>
+        <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3967,259 +3508,49 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>104150</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>卢忠慧</t>
+          <t>侯晓光</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>96000</v>
+        <v>80000</v>
       </c>
       <c r="D36" t="n">
-        <v>131854</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>137.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>129.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>7960</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>123894</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>陈斌斌</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>104000</v>
-      </c>
-      <c r="D37" t="n">
-        <v>155796</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>149.8%</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>137.4%</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>12940</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>8.3%</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>142856</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>丁蕾</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D38" t="n">
-        <v>143720</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>59.9%</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20.1%</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>95508</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>66.5%</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>48212</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>梁志超</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D39" t="n">
-        <v>91928</v>
-      </c>
-      <c r="E39" t="n">
-        <v>173964</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>110.8%</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>54073</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>37855</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>周紫姻</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8780</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>21.9%</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>91.1%</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>李洋洋</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D41" t="n">
-        <v>89038</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>111.3%</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>92.6%</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>14957</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16.8%</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>74081</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4233,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4281,91 +3612,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>钟燕红</t>
+          <t>赵越</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>230000</v>
+        <v>140000</v>
       </c>
       <c r="D2" t="n">
-        <v>349259</v>
+        <v>2678</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>68366.67</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>280892.33</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>田奇</t>
+          <t>岳伟伟</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="D3" t="n">
-        <v>88544.10000000001</v>
+        <v>77176</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>83044.10000000001</v>
+        <v>77176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>李明</t>
+          <t>陶雯</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="D4" t="n">
-        <v>98098.67999999999</v>
+        <v>1996</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4377,63 +3708,63 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>98098.67999999999</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>苏怡意</t>
+          <t>陈翔宇</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="D5" t="n">
-        <v>59878.8</v>
+        <v>698</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>57278.8</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>姜玮</t>
+          <t>王秋</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D6" t="n">
-        <v>74548.06</v>
+        <v>17198</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4445,29 +3776,29 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>74548.06</v>
+        <v>17198</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>李家慧</t>
+          <t>余婉丽</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50000</v>
+        <v>140000</v>
       </c>
       <c r="D7" t="n">
-        <v>29988</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4479,29 +3810,29 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>29988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>孙君兰</t>
+          <t>褚月月</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="D8" t="n">
-        <v>62137.21</v>
+        <v>31500</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4513,63 +3844,63 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>62137.21</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>陈紫灵</t>
+          <t>白蕾</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200000</v>
+        <v>140000</v>
       </c>
       <c r="D9" t="n">
-        <v>66636.22</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>66436.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>林非凡</t>
+          <t>刘沁</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D10" t="n">
-        <v>161239.7</v>
+        <v>398</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4581,29 +3912,29 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>161239.7</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>米兰兰</t>
+          <t>芊雅</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>140000</v>
       </c>
       <c r="D11" t="n">
-        <v>28300</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4615,63 +3946,63 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>28300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>李雅玲</t>
+          <t>刘馨</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>200000</v>
+        <v>50000</v>
       </c>
       <c r="D12" t="n">
-        <v>178778.4</v>
+        <v>6194</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56600</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>122178.4</v>
+        <v>6194</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>朱锋剑</t>
+          <t>陈洁</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100000</v>
+        <v>290000</v>
       </c>
       <c r="D13" t="n">
-        <v>38899.23</v>
+        <v>13274</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4683,131 +4014,131 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>38899.23</v>
+        <v>13274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>曾妍妍</t>
+          <t>韩雪</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>120000</v>
+        <v>140000</v>
       </c>
       <c r="D14" t="n">
-        <v>118770</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>21500</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>97270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>张虹</t>
+          <t>李菲菲</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>120000</v>
+        <v>290000</v>
       </c>
       <c r="D15" t="n">
-        <v>106630</v>
+        <v>47668</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29198</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77432</v>
+        <v>47668</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朱碧丹</t>
+          <t>李浩然</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>120000</v>
+        <v>220000</v>
       </c>
       <c r="D16" t="n">
-        <v>94374</v>
+        <v>28196</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18200</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>76174</v>
+        <v>28196</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>王钰尧</t>
+          <t>李怡慧</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50000</v>
+        <v>230000</v>
       </c>
       <c r="D17" t="n">
-        <v>29974</v>
+        <v>26469</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4819,29 +4150,29 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>29974</v>
+        <v>26469</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>邓璐</t>
+          <t>唐晟</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>280000</v>
+        <v>90000</v>
       </c>
       <c r="D18" t="n">
-        <v>81348.8</v>
+        <v>2090</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4853,97 +4184,97 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>81348.8</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>马雅丽</t>
+          <t>王凯</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>180000</v>
+        <v>90000</v>
       </c>
       <c r="D19" t="n">
-        <v>130387.7</v>
+        <v>0</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>117387.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周思若</t>
+          <t>王倩雅</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>220000</v>
+        <v>340000</v>
       </c>
       <c r="D20" t="n">
-        <v>91188.7</v>
+        <v>30887</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>87188.7</v>
+        <v>30887</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>袁登玉</t>
+          <t>韦微</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>60000</v>
+        <v>260000</v>
       </c>
       <c r="D21" t="n">
-        <v>32072.55</v>
+        <v>36695</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4955,29 +4286,29 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>32072.55</v>
+        <v>36695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>邝玉萍</t>
+          <t>余佼</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>60000</v>
+        <v>280000</v>
       </c>
       <c r="D22" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4989,29 +4320,29 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>398</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>褚月月</t>
+          <t>黄雅晴</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>200000</v>
+        <v>190000</v>
       </c>
       <c r="D23" t="n">
-        <v>204150</v>
+        <v>11894</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -5023,29 +4354,29 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>204150</v>
+        <v>11894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>白蕾</t>
+          <t>郑巨光</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>150000</v>
+        <v>190000</v>
       </c>
       <c r="D24" t="n">
-        <v>8590</v>
+        <v>2225.88</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5057,97 +4388,97 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>8590</v>
+        <v>2225.88</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刘沁</t>
+          <t>陈舒羽</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>150000</v>
       </c>
       <c r="D25" t="n">
-        <v>134440</v>
+        <v>1798</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>124640</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>王芊雅</t>
+          <t>沈悦</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>150000</v>
       </c>
       <c r="D26" t="n">
-        <v>51552</v>
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>41552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刘馨</t>
+          <t>张回</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="D27" t="n">
-        <v>81020</v>
+        <v>3398</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>162.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5159,131 +4490,131 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>81020</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>陈月娇</t>
+          <t>冯兰兰</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>70000</v>
       </c>
       <c r="D28" t="n">
-        <v>15186</v>
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>19399.98</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>127.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>-4213.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>刘玉静</t>
+          <t>钟燕红</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>160000</v>
+        <v>250000</v>
       </c>
       <c r="D29" t="n">
-        <v>145856</v>
+        <v>26777.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>121856</v>
+        <v>26777.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>杨红瑞</t>
+          <t>田奇</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>60000</v>
+        <v>130000</v>
       </c>
       <c r="D30" t="n">
-        <v>48376</v>
+        <v>7500</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>38376</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>普元媛</t>
+          <t>李明</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>60000</v>
+        <v>115000</v>
       </c>
       <c r="D31" t="n">
-        <v>22894</v>
+        <v>8098</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5295,29 +4626,29 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>22894</v>
+        <v>8098</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>马奇君</t>
+          <t>苏怡意</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30000</v>
+        <v>115000</v>
       </c>
       <c r="D32" t="n">
-        <v>28392</v>
+        <v>398</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -5329,165 +4660,165 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>28392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>黄雅晴</t>
+          <t>姜玮</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>180000</v>
+        <v>125000</v>
       </c>
       <c r="D33" t="n">
-        <v>162765.64</v>
+        <v>16998</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>128965.64</v>
+        <v>16998</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>郑巨光</t>
+          <t>李家慧</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>180000</v>
+        <v>65000</v>
       </c>
       <c r="D34" t="n">
-        <v>165530.37</v>
+        <v>10000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>39833.4</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>125696.97</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>陈舒羽</t>
+          <t>邓璐</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>130000</v>
+        <v>150000</v>
       </c>
       <c r="D35" t="n">
-        <v>104838.92</v>
+        <v>13596.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>98238.92</v>
+        <v>13596.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>沈悦</t>
+          <t>马雅丽</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D36" t="n">
-        <v>144374</v>
+        <v>495.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6598</v>
+        <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>137776</v>
+        <v>495.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>张回</t>
+          <t>袁登玉</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>40000</v>
+        <v>100000</v>
       </c>
       <c r="D37" t="n">
-        <v>15788</v>
+        <v>20000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5499,29 +4830,29 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>15788</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>冯兰兰</t>
+          <t>黄惠作</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>30000</v>
+        <v>200000</v>
       </c>
       <c r="D38" t="n">
-        <v>31295</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>104.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5533,97 +4864,97 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>31295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>陶雯</t>
+          <t>韦新妮</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="D39" t="n">
-        <v>99750</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>26400</v>
+        <v>0</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>73350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>岳伟伟</t>
+          <t>郭海明</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>400000</v>
+        <v>200000</v>
       </c>
       <c r="D40" t="n">
-        <v>660706.01</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>144.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>82650</v>
+        <v>0</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>578056.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>赵越</t>
+          <t>杨琴</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="D41" t="n">
-        <v>111469</v>
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -5635,131 +4966,131 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>111469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>王秋</t>
+          <t>陈新星</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>105000</v>
+        <v>70000</v>
       </c>
       <c r="D42" t="n">
-        <v>142164</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>7600</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>134564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>陈翔宇</t>
+          <t>田婉丽</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>105000</v>
+        <v>110000</v>
       </c>
       <c r="D43" t="n">
-        <v>127345</v>
+        <v>5000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>32222.24</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>95122.76000000001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>余婉丽</t>
+          <t>罗晗</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>50000</v>
       </c>
       <c r="D44" t="n">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>996</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>陈洁</t>
+          <t>陈思羽</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>270000</v>
+        <v>30000</v>
       </c>
       <c r="D45" t="n">
-        <v>241686.46</v>
+        <v>0</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5771,29 +5102,29 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>241686.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>韩雪</t>
+          <t>曾妍妍</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>120000</v>
+        <v>110000</v>
       </c>
       <c r="D46" t="n">
-        <v>77723</v>
+        <v>32796</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -5805,29 +5136,29 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>77723</v>
+        <v>32796</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>李菲菲</t>
+          <t>张虹</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>250000</v>
+        <v>110000</v>
       </c>
       <c r="D47" t="n">
-        <v>233563</v>
+        <v>5996</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -5839,29 +5170,29 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>233563</v>
+        <v>5996</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>李浩然</t>
+          <t>朱碧丹</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>210000</v>
+        <v>110000</v>
       </c>
       <c r="D48" t="n">
-        <v>155121.4</v>
+        <v>8000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5873,29 +5204,29 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>155121.4</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>李怡慧</t>
+          <t>王钰尧</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>230000</v>
+        <v>70000</v>
       </c>
       <c r="D49" t="n">
-        <v>297151.04</v>
+        <v>0</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>129.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5907,29 +5238,29 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>297151.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>唐晟</t>
+          <t>孙君兰</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D50" t="n">
-        <v>8399</v>
+        <v>5668.15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5941,29 +5272,29 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>8399</v>
+        <v>5668.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>王凯</t>
+          <t>陈紫灵</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>80000</v>
+        <v>160000</v>
       </c>
       <c r="D51" t="n">
-        <v>16338</v>
+        <v>11368.38</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5975,29 +5306,29 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>16338</v>
+        <v>11368.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>王倩雅</t>
+          <t>林非凡</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="D52" t="n">
-        <v>426689.97</v>
+        <v>67.16</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>142.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -6009,29 +5340,29 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>426689.97</v>
+        <v>67.16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>韦微</t>
+          <t>米兰兰</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>220000</v>
+        <v>110000</v>
       </c>
       <c r="D53" t="n">
-        <v>238293.8</v>
+        <v>28800</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6043,29 +5374,29 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>238293.8</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>余佼</t>
+          <t>李雅玲</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>240000</v>
+        <v>110000</v>
       </c>
       <c r="D54" t="n">
-        <v>288490</v>
+        <v>7500</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>120.2%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -6077,41 +5408,41 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>288490</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>陈静</t>
+          <t>朱锋剑</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="D55" t="n">
-        <v>177573</v>
+        <v>10700</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>167.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>167573</v>
+        <v>10700</v>
       </c>
     </row>
     <row r="56">
@@ -6122,30 +5453,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>谌黎平</t>
+          <t>陈静</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80000</v>
+        <v>90000</v>
       </c>
       <c r="D56" t="n">
-        <v>52786</v>
+        <v>50398</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>47786</v>
+        <v>50398</v>
       </c>
     </row>
     <row r="57">
@@ -6156,18 +5487,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>马春兰</t>
+          <t>谌黎平</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>80000</v>
       </c>
       <c r="D57" t="n">
-        <v>55252</v>
+        <v>796</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -6179,7 +5510,7 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>55252</v>
+        <v>796</v>
       </c>
     </row>
     <row r="58">
@@ -6190,30 +5521,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>李颜君</t>
+          <t>马春兰</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="D58" t="n">
-        <v>33272</v>
+        <v>10000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>26272</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="59">
@@ -6224,30 +5555,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>蔡清霞</t>
+          <t>李颜君</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>60000</v>
+        <v>70000</v>
       </c>
       <c r="D59" t="n">
-        <v>144398</v>
+        <v>20000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>227.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>136398</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="60">
@@ -6258,18 +5589,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>吴静文</t>
+          <t>蔡清霞</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="D60" t="n">
-        <v>46592</v>
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>233.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -6281,29 +5612,29 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>46592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>陈新星</t>
+          <t>吴静文</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="D61" t="n">
-        <v>57964</v>
+        <v>20000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -6315,63 +5646,63 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>57964</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>田婉丽</t>
+          <t>陈月娇</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>120000</v>
+        <v>70000</v>
       </c>
       <c r="D62" t="n">
-        <v>73968</v>
+        <v>0</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>15800</v>
+        <v>0</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>58168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>罗晗</t>
+          <t>刘玉静</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6000</v>
+        <v>170000</v>
       </c>
       <c r="D63" t="n">
-        <v>10268</v>
+        <v>12996</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>171.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -6383,7 +5714,109 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10268</v>
+        <v>12996</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>杨红瑞</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>普元媛</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>马奇君</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1594</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1594</v>
       </c>
     </row>
   </sheetData>
@@ -6444,16 +5877,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1540712.53</v>
+        <v>87221</v>
       </c>
       <c r="D2" t="n">
-        <v>4165</v>
+        <v>997</v>
       </c>
       <c r="E2" t="n">
-        <v>129069</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1411643.53</v>
+        <v>87221</v>
       </c>
     </row>
     <row r="3">
@@ -6468,16 +5901,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1413097</v>
+        <v>53040</v>
       </c>
       <c r="D3" t="n">
-        <v>272</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>129040</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1284057</v>
+        <v>53040</v>
       </c>
     </row>
     <row r="4">
@@ -6492,16 +5925,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>127615.53</v>
+        <v>34181</v>
       </c>
       <c r="D4" t="n">
-        <v>3893</v>
+        <v>986</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>127586.53</v>
+        <v>34181</v>
       </c>
     </row>
     <row r="5">
@@ -6516,16 +5949,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2107422</v>
+        <v>547748</v>
       </c>
       <c r="D5" t="n">
-        <v>501</v>
+        <v>106</v>
       </c>
       <c r="E5" t="n">
-        <v>117432</v>
+        <v>60820</v>
       </c>
       <c r="F5" t="n">
-        <v>1989990</v>
+        <v>486928</v>
       </c>
     </row>
     <row r="6">
@@ -6540,16 +5973,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1512040</v>
+        <v>349086</v>
       </c>
       <c r="D6" t="n">
-        <v>275</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>22598</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1489442</v>
+        <v>349086</v>
       </c>
     </row>
     <row r="7">
@@ -6564,16 +5997,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>575382</v>
+        <v>198264</v>
       </c>
       <c r="D7" t="n">
-        <v>223</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>94834</v>
+        <v>60820</v>
       </c>
       <c r="F7" t="n">
-        <v>480548</v>
+        <v>137444</v>
       </c>
     </row>
     <row r="8">
@@ -6588,16 +6021,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2136679.13</v>
+        <v>258666.54</v>
       </c>
       <c r="D8" t="n">
-        <v>2726</v>
+        <v>248</v>
       </c>
       <c r="E8" t="n">
-        <v>8784.469999999999</v>
+        <v>17440</v>
       </c>
       <c r="F8" t="n">
-        <v>2127894.66</v>
+        <v>241226.54</v>
       </c>
     </row>
     <row r="9">
@@ -6612,16 +6045,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1276047.08</v>
+        <v>157865.89</v>
       </c>
       <c r="D9" t="n">
-        <v>1202</v>
+        <v>150</v>
       </c>
       <c r="E9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1274247.08</v>
+        <v>157865.89</v>
       </c>
     </row>
     <row r="10">
@@ -6636,16 +6069,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>860632.05</v>
+        <v>100800.65</v>
       </c>
       <c r="D10" t="n">
-        <v>1524</v>
+        <v>98</v>
       </c>
       <c r="E10" t="n">
-        <v>6984.47</v>
+        <v>17440</v>
       </c>
       <c r="F10" t="n">
-        <v>853647.58</v>
+        <v>83360.64999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6660,16 +6093,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>843006.4</v>
+        <v>49600</v>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>336200</v>
+        <v>49600</v>
       </c>
       <c r="F11" t="n">
-        <v>506806.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6684,16 +6117,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6708,16 +6141,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>73400</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>54600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6732,16 +6165,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="15">
@@ -6756,16 +6189,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>145127.25</v>
+        <v>4275.36</v>
       </c>
       <c r="D15" t="n">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>2277.36</v>
       </c>
       <c r="F15" t="n">
-        <v>145127.25</v>
+        <v>1998</v>
       </c>
     </row>
   </sheetData>
@@ -6826,22 +6259,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1540712.53</v>
+        <v>87221</v>
       </c>
       <c r="C2" t="n">
-        <v>604082.74</v>
+        <v>3426</v>
       </c>
       <c r="D2" t="n">
-        <v>118096.58</v>
+        <v>2056</v>
       </c>
       <c r="E2" t="n">
-        <v>7.67</v>
+        <v>2.36</v>
       </c>
       <c r="F2" t="n">
-        <v>485986.16</v>
+        <v>1370</v>
       </c>
       <c r="G2" t="n">
-        <v>31.54</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="3">
@@ -6851,22 +6284,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2107422</v>
+        <v>547748</v>
       </c>
       <c r="C3" t="n">
-        <v>883152.99</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>54598</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>828554.99</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>39.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6876,22 +6309,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2136679.13</v>
+        <v>258666.54</v>
       </c>
       <c r="C4" t="n">
-        <v>29799</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1049</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>28750</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6901,10 +6334,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>843006.4</v>
+        <v>49600</v>
       </c>
       <c r="C5" t="n">
-        <v>190400</v>
+        <v>45600</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6913,10 +6346,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>190400</v>
+        <v>45600</v>
       </c>
       <c r="G5" t="n">
-        <v>22.59</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="6">
@@ -6926,22 +6359,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102688</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>156919.9</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2017.9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>154902</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>150.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6951,22 +6384,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>128000</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>327046.67</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>41.41</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>274046.67</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>214.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6976,10 +6409,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13860</v>
+        <v>1980</v>
       </c>
       <c r="C8" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6988,10 +6421,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7001,22 +6434,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145127.25</v>
+        <v>4275.36</v>
       </c>
       <c r="C9" t="n">
-        <v>18998</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2198</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>16800</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.58</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7030,7 +6463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,17 +6491,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>612</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1229026.82</v>
+        <v>45600</v>
       </c>
       <c r="D2" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -7078,61 +6511,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>842</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>396737.32</v>
+        <v>1458</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>253980</v>
+        <v>924</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>198422.24</v>
+        <v>826</v>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43835.22</v>
+        <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7142,92 +6575,60 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>38059.7</v>
+        <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>29064</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>24332</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>617</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>教材问题</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C11" t="n">
-        <v>228</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>商家操作失误</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>57</v>
-      </c>
-      <c r="D12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7242,7 +6643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7270,61 +6671,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>家人不支持</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>235360</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>155000</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>39716</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -7336,259 +6737,259 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>13200</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>价格问题</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>456</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>122500</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>747</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>108773.82</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>14636</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>时间/适配冲突</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13845.56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>效果不满意</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>10754</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>10716.7</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>服务未交付/联系不上</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>4080</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>价格问题</t>
+          <t>时间/适配冲突</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>617</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>教材问题</t>
+          <t>服务未交付/联系不上</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>228</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>未映射</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>商家操作失误</t>
+          <t>效果不满意</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>其他/未说明</t>
+          <t>商家操作失误</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>85250</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>咨询结案/好转</t>
+          <t>协商一致</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>61522.24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>家人不支持</t>
+          <t>主动放弃/拍错</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>15600</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -7603,10 +7004,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -7621,10 +7022,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -7635,1076 +7036,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>协商一致</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>主动放弃/拍错</t>
+          <t>其他/未说明</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>85388</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>课程4组</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>72193</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>66536.39999999999</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D26" t="n">
-        <v>46520</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D27" t="n">
-        <v>21766</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>课程3组</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>24</v>
-      </c>
-      <c r="D30" t="n">
-        <v>97854</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" t="n">
-        <v>5970</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>25</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2526</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4</v>
-      </c>
-      <c r="D35" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D36" t="n">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>61829</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>6</v>
-      </c>
-      <c r="D38" t="n">
-        <v>25029.5</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>21780</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="n">
-        <v>13200</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>课程1组</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>10256.66</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>10</v>
-      </c>
-      <c r="D42" t="n">
-        <v>90420</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" t="n">
-        <v>16637</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>效果不满意</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="n">
-        <v>14820</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>课程6组</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" t="n">
-        <v>75533.39999999999</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>20500</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>杭州</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>16</v>
-      </c>
-      <c r="D51" t="n">
-        <v>74628</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2</v>
-      </c>
-      <c r="D52" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" t="n">
         <v>19</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>44494.67</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>4</v>
-      </c>
-      <c r="D56" t="n">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>14</v>
-      </c>
-      <c r="D57" t="n">
-        <v>16929</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>广州</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>服务未交付/联系不上</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>7</v>
-      </c>
-      <c r="D59" t="n">
-        <v>68500</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="n">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>福州</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>7</v>
-      </c>
-      <c r="D62" t="n">
-        <v>33440</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>课程5组</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" t="n">
-        <v>31030</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>9</v>
-      </c>
-      <c r="D64" t="n">
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>昆明</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>5</v>
-      </c>
-      <c r="D65" t="n">
-        <v>19233.35</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>6</v>
-      </c>
-      <c r="D66" t="n">
-        <v>28919</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>课程7组</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>6</v>
-      </c>
-      <c r="D67" t="n">
-        <v>23689</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>6</v>
-      </c>
-      <c r="D68" t="n">
-        <v>27200</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>2</v>
-      </c>
-      <c r="D69" t="n">
-        <v>11299</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>普陀</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" t="n">
-        <v>11009</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" t="n">
-        <v>15019</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" t="n">
-        <v>15009</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>2</v>
-      </c>
-      <c r="D73" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>成都</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
-      <c r="D74" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>5</v>
-      </c>
-      <c r="D75" t="n">
-        <v>17318</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>咨询结案/好转</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="n">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>时间/适配冲突</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
-      <c r="D77" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>深圳</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>协商一致</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>其他/未说明</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>家人不支持</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
-        <v>6800</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>珠海</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>主动放弃/拍错</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>3</v>
-      </c>
-      <c r="D81" t="n">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -8718,7 +7075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8741,131 +7098,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>分享咨询</t>
+          <t>肠道菌群移植</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>720584.99</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>户外营地（户外组专用）</t>
+          <t>19元青少年（体验课）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>283466.67</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>青少年家庭同行者计划</t>
+          <t>299元青春期家庭21天陪跑</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>281220.56</v>
+        <v>897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>少年说倾听计划</t>
+          <t>29睡眠基础营</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>194760</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>肠道菌群移植</t>
+          <t>29认知基础营</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>190400</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>心灯—长程课</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="n">
-        <v>148273</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C8" t="n">
-        <v>140298</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>少年说陪伴计划</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>44616</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>夏令营</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>39380</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>家庭守护计划</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>32041</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -8902,196 +7194,196 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>397</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>388742.35</v>
+        <v>45676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>141</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>270818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>230</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n">
-        <v>218612.22</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>198581.4</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>148217.5</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>137374</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>113661</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>108305.4</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>98993.8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>70796.89999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>49427</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>47573</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>65</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>44200.37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>37219</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>内蒙古自治区</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>33557</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/导出_总表.xlsx
+++ b/导出_总表.xlsx
@@ -528,25 +528,25 @@
         <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>32223</v>
+        <v>70915</v>
       </c>
       <c r="E2" t="n">
-        <v>845</v>
+        <v>11584</v>
       </c>
       <c r="F2" t="n">
-        <v>31378</v>
+        <v>59331</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -554,11 +554,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-68335</v>
+        <v>-75535</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-145.9%</t>
+          <t>-178.5%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -581,25 +581,25 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>7863</v>
+        <v>52937</v>
       </c>
       <c r="E3" t="n">
-        <v>46334</v>
+        <v>98928</v>
       </c>
       <c r="F3" t="n">
-        <v>-38471</v>
+        <v>-45991</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -607,11 +607,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-54963</v>
+        <v>-55181</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -634,25 +634,25 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>48586</v>
+        <v>139027</v>
       </c>
       <c r="E4" t="n">
-        <v>1714</v>
+        <v>28253</v>
       </c>
       <c r="F4" t="n">
-        <v>46872</v>
+        <v>110774</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -660,11 +660,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>-65634</v>
+        <v>-73305</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-171.4%</t>
+          <t>-251.1%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -687,25 +687,25 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>156757</v>
+        <v>184107</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>13038</v>
       </c>
       <c r="F5" t="n">
-        <v>156690</v>
+        <v>171069</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -713,11 +713,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-230448</v>
+        <v>-237404</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-168.0%</t>
+          <t>-172.1%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -740,50 +740,50 @@
         <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>195696</v>
+        <v>215005</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>195696</v>
+        <v>215005</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>422080</v>
+        <v>428587</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-53.6%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>422080</v>
+        <v>428587</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-53.6%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>75335</v>
+        <v>85731</v>
       </c>
       <c r="P6" t="n">
-        <v>120361</v>
+        <v>129274</v>
       </c>
       <c r="Q6" t="n">
-        <v>185298</v>
+        <v>204607</v>
       </c>
     </row>
     <row r="7">
@@ -801,23 +801,23 @@
         <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>24628</v>
+        <v>26225</v>
       </c>
       <c r="E7" t="n">
         <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>24609</v>
+        <v>26206</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -825,26 +825,26 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>+11627.6%</t>
+          <t>+12388.1%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-8790</v>
+        <v>-19190</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-380.0%</t>
+          <t>-236.6%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>14590</v>
+        <v>16187</v>
       </c>
       <c r="P7" t="n">
         <v>10019</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="8">
@@ -862,23 +862,23 @@
         <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>101194</v>
+        <v>167988</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>101194</v>
+        <v>167988</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -890,18 +890,18 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-361507.1%</t>
+          <t>-600057.1%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>21194</v>
+        <v>21592</v>
       </c>
       <c r="P8" t="n">
-        <v>80000</v>
+        <v>146396</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="9">
@@ -919,52 +919,52 @@
         <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>70893</v>
+        <v>100769</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>70893</v>
+        <v>100769</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7234</v>
+        <v>7946</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>+880.0%</t>
+          <t>+1168.2%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-17193</v>
+        <v>-17982</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-512.3%</t>
+          <t>-660.4%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>5383</v>
+        <v>6023</v>
       </c>
       <c r="O9" t="n">
-        <v>8694</v>
+        <v>10129</v>
       </c>
       <c r="P9" t="n">
-        <v>56816</v>
+        <v>84616</v>
       </c>
       <c r="Q9" t="n">
-        <v>12699</v>
+        <v>14577</v>
       </c>
     </row>
     <row r="10">
@@ -982,52 +982,52 @@
         <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>34101</v>
+        <v>34130</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>42780</v>
       </c>
       <c r="F10" t="n">
-        <v>34101</v>
+        <v>-8650</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5431</v>
+        <v>7276</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>+527.9%</t>
+          <t>+369.1%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>65</v>
+        <v>-7590</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+52363.1%</t>
+          <t>+14.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
         <v>1494</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>-35542</v>
       </c>
       <c r="P10" t="n">
-        <v>32598</v>
+        <v>25398</v>
       </c>
       <c r="Q10" t="n">
-        <v>1503</v>
+        <v>-34048</v>
       </c>
     </row>
     <row r="11">
@@ -1045,23 +1045,23 @@
         <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>6053</v>
+        <v>14053</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6053</v>
+        <v>14053</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-16028.9%</t>
+          <t>-37081.6%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1081,7 +1081,7 @@
         <v>57</v>
       </c>
       <c r="P11" t="n">
-        <v>5996</v>
+        <v>13996</v>
       </c>
       <c r="Q11" t="n">
         <v>57</v>
@@ -1102,23 +1102,23 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>46811</v>
+        <v>54407</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>46811</v>
+        <v>45207</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1130,18 +1130,18 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-11325.7%</t>
+          <t>-10941.0%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>6015</v>
+        <v>6613</v>
       </c>
       <c r="P12" t="n">
-        <v>40796</v>
+        <v>38594</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="13">
@@ -1159,52 +1159,52 @@
         <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>19335</v>
+        <v>33617</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>19335</v>
+        <v>33617</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1473</v>
+        <v>5210</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>+1212.6%</t>
+          <t>+545.2%</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-38527</v>
+        <v>-34790</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>-150.2%</t>
+          <t>-196.6%</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2226</v>
+        <v>2318</v>
       </c>
       <c r="O13" t="n">
-        <v>417</v>
+        <v>2209</v>
       </c>
       <c r="P13" t="n">
-        <v>16692</v>
+        <v>29090</v>
       </c>
       <c r="Q13" t="n">
-        <v>8845</v>
+        <v>8937</v>
       </c>
     </row>
     <row r="14">
@@ -1222,23 +1222,23 @@
         <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>101937</v>
+        <v>113750</v>
       </c>
       <c r="E14" t="n">
-        <v>47</v>
+        <v>58847</v>
       </c>
       <c r="F14" t="n">
-        <v>101890</v>
+        <v>54903</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1246,22 +1246,22 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>-19</v>
+        <v>-19657</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-536363.2%</t>
+          <t>-379.3%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>14293</v>
+        <v>-30909</v>
       </c>
       <c r="P14" t="n">
-        <v>87597</v>
+        <v>85812</v>
       </c>
       <c r="Q14" t="n">
-        <v>50284</v>
+        <v>5303</v>
       </c>
     </row>
     <row r="15">
@@ -1279,39 +1279,39 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>65825</v>
+        <v>85825</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F15" t="n">
-        <v>65825</v>
+        <v>77825</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3303</v>
+        <v>3608</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>+1892.9%</t>
+          <t>+2278.7%</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3094</v>
+        <v>3399</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2027.5%</t>
+          <t>+2189.6%</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1321,7 +1321,7 @@
         <v>27594</v>
       </c>
       <c r="P15" t="n">
-        <v>32396</v>
+        <v>44396</v>
       </c>
       <c r="Q15" t="n">
         <v>5835</v>
@@ -1342,23 +1342,23 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>38194</v>
+        <v>38990</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>38194</v>
+        <v>38990</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1366,19 +1366,19 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>-38556</v>
+        <v>-38651</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-199.1%</t>
+          <t>-200.9%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>10898</v>
+        <v>11296</v>
       </c>
       <c r="P16" t="n">
-        <v>27296</v>
+        <v>27694</v>
       </c>
       <c r="Q16" t="n">
         <v>102</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>-2773</v>
+        <v>-6781</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>